--- a/all-test-reports/vulnerability/vulnerability_test_report.xlsx
+++ b/all-test-reports/vulnerability/vulnerability_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 8:51:52 am</t>
+    <t>28/7/2026, 10:34:34 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1694,7 +1694,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="10">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>28</v>
@@ -1717,7 +1717,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="10">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>31</v>
@@ -1740,7 +1740,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>28</v>
@@ -1763,7 +1763,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="10">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>34</v>
@@ -1786,7 +1786,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="10">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>28</v>
@@ -1809,7 +1809,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="10">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>31</v>
@@ -1832,7 +1832,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="10">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>28</v>
@@ -1855,7 +1855,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="10">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>34</v>
@@ -1878,7 +1878,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="10">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>28</v>
@@ -1901,7 +1901,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="10">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>31</v>
@@ -1924,7 +1924,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="10">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>28</v>
@@ -1947,7 +1947,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="10">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>34</v>
@@ -1970,7 +1970,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="10">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>28</v>
@@ -1993,7 +1993,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="10">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>31</v>
@@ -2016,7 +2016,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="10">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>28</v>
@@ -2039,7 +2039,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="10">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>34</v>
@@ -2062,7 +2062,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="10">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>28</v>
@@ -2085,7 +2085,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="10">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>31</v>
@@ -2131,7 +2131,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="10">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>34</v>
@@ -2154,7 +2154,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="10">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>28</v>
@@ -2177,7 +2177,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="10">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>31</v>
@@ -2200,7 +2200,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="10">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>28</v>
@@ -2223,7 +2223,7 @@
         <v>27</v>
       </c>
       <c r="E25" s="10">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>34</v>
@@ -2269,7 +2269,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="10">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>31</v>
@@ -2292,7 +2292,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="10">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>28</v>
@@ -2338,7 +2338,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="10">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>28</v>
@@ -2361,7 +2361,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="10">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>31</v>
@@ -2384,7 +2384,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="10">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>28</v>
@@ -2407,7 +2407,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="10">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>31</v>
@@ -2430,7 +2430,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="10">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>28</v>
@@ -2453,7 +2453,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="10">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>34</v>
@@ -2476,7 +2476,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="10">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>28</v>
@@ -2499,7 +2499,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>31</v>
@@ -2522,7 +2522,7 @@
         <v>27</v>
       </c>
       <c r="E38" s="10">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>28</v>
@@ -2545,7 +2545,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="10">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>34</v>
@@ -2591,7 +2591,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="10">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>31</v>
@@ -2614,7 +2614,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="10">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>28</v>
@@ -2637,7 +2637,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="10">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>34</v>
@@ -2660,7 +2660,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="10">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>28</v>
@@ -2683,7 +2683,7 @@
         <v>27</v>
       </c>
       <c r="E45" s="10">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>31</v>
@@ -2706,7 +2706,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="10">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>28</v>
@@ -2729,7 +2729,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="10">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>34</v>
@@ -2752,7 +2752,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="10">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>28</v>
@@ -2775,7 +2775,7 @@
         <v>27</v>
       </c>
       <c r="E49" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>31</v>
@@ -2798,7 +2798,7 @@
         <v>27</v>
       </c>
       <c r="E50" s="10">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>28</v>
@@ -2821,7 +2821,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="10">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>34</v>
@@ -2844,7 +2844,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="10">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>28</v>
@@ -2867,7 +2867,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="10">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>31</v>
@@ -2890,7 +2890,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="10">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>28</v>
@@ -2913,7 +2913,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="10">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>34</v>
@@ -2936,7 +2936,7 @@
         <v>27</v>
       </c>
       <c r="E56" s="10">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>28</v>
@@ -2959,7 +2959,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="10">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>31</v>
@@ -2982,7 +2982,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="10">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>28</v>
@@ -3028,7 +3028,7 @@
         <v>27</v>
       </c>
       <c r="E60" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>28</v>
@@ -3051,7 +3051,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="10">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>31</v>
@@ -3074,7 +3074,7 @@
         <v>27</v>
       </c>
       <c r="E62" s="10">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>28</v>
@@ -3097,7 +3097,7 @@
         <v>27</v>
       </c>
       <c r="E63" s="10">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>31</v>
@@ -3120,7 +3120,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="10">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>28</v>
@@ -3143,7 +3143,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="10">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>34</v>
@@ -3166,7 +3166,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="10">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>28</v>
@@ -3189,7 +3189,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>31</v>
@@ -3212,7 +3212,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="10">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>28</v>
@@ -3235,7 +3235,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="10">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>34</v>
@@ -3258,7 +3258,7 @@
         <v>27</v>
       </c>
       <c r="E70" s="10">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>28</v>
@@ -3281,7 +3281,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="10">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>31</v>
@@ -3304,7 +3304,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="10">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>28</v>
@@ -3327,7 +3327,7 @@
         <v>27</v>
       </c>
       <c r="E73" s="10">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>34</v>
@@ -3350,7 +3350,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="10">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>28</v>
@@ -3373,7 +3373,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="10">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>31</v>
@@ -3396,7 +3396,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="10">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>28</v>
@@ -3419,7 +3419,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>34</v>
@@ -3442,7 +3442,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="10">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>28</v>
@@ -3465,7 +3465,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="10">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>31</v>
@@ -3488,7 +3488,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="10">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>28</v>
@@ -3511,7 +3511,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="10">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>34</v>
@@ -3534,7 +3534,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="10">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>28</v>
@@ -3557,7 +3557,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="10">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>31</v>
@@ -3580,7 +3580,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="10">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>28</v>
@@ -3603,7 +3603,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="10">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>34</v>
@@ -3626,7 +3626,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="10">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>28</v>
@@ -3649,7 +3649,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="10">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>31</v>
@@ -3672,7 +3672,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="10">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>28</v>
@@ -3695,7 +3695,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="10">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>34</v>
@@ -3718,7 +3718,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="10">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>28</v>
@@ -3741,7 +3741,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="10">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>31</v>
@@ -3764,7 +3764,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>28</v>
@@ -3787,7 +3787,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="10">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>31</v>
@@ -3810,7 +3810,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="10">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>28</v>
@@ -3833,7 +3833,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="10">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>34</v>
@@ -3856,7 +3856,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="10">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F96" s="8" t="s">
         <v>28</v>
@@ -3879,7 +3879,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="10">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>31</v>
@@ -3902,7 +3902,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="10">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>28</v>
@@ -3925,7 +3925,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="10">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>34</v>
@@ -3971,7 +3971,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="10">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>31</v>
@@ -3994,7 +3994,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="10">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>28</v>
@@ -4017,7 +4017,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="10">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>34</v>
@@ -4040,7 +4040,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="10">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>28</v>
@@ -4063,7 +4063,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="10">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>31</v>
@@ -4086,7 +4086,7 @@
         <v>27</v>
       </c>
       <c r="E106" s="10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>28</v>
@@ -4109,7 +4109,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>34</v>
@@ -4132,7 +4132,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="10">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>28</v>
@@ -4178,7 +4178,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="10">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>28</v>
@@ -4201,7 +4201,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="10">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>34</v>
@@ -4224,7 +4224,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="10">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>28</v>
@@ -4247,7 +4247,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="10">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F113" s="8" t="s">
         <v>31</v>
@@ -4270,7 +4270,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="10">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>28</v>
@@ -4293,7 +4293,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="10">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>34</v>
@@ -4316,7 +4316,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="10">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>28</v>
@@ -4339,7 +4339,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="10">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F117" s="8" t="s">
         <v>31</v>
@@ -4362,7 +4362,7 @@
         <v>27</v>
       </c>
       <c r="E118" s="10">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F118" s="8" t="s">
         <v>28</v>
@@ -4385,7 +4385,7 @@
         <v>27</v>
       </c>
       <c r="E119" s="10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F119" s="8" t="s">
         <v>34</v>
@@ -4408,7 +4408,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="10">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F120" s="8" t="s">
         <v>28</v>
@@ -4431,7 +4431,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="10">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F121" s="8" t="s">
         <v>31</v>
@@ -4454,7 +4454,7 @@
         <v>27</v>
       </c>
       <c r="E122" s="10">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F122" s="8" t="s">
         <v>28</v>
@@ -4477,7 +4477,7 @@
         <v>27</v>
       </c>
       <c r="E123" s="10">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>31</v>
@@ -4500,7 +4500,7 @@
         <v>27</v>
       </c>
       <c r="E124" s="10">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F124" s="8" t="s">
         <v>28</v>
@@ -4523,7 +4523,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="10">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>34</v>
@@ -4569,7 +4569,7 @@
         <v>27</v>
       </c>
       <c r="E127" s="10">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F127" s="8" t="s">
         <v>31</v>
@@ -4592,7 +4592,7 @@
         <v>27</v>
       </c>
       <c r="E128" s="10">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F128" s="8" t="s">
         <v>28</v>
@@ -4615,7 +4615,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="10">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F129" s="8" t="s">
         <v>34</v>
@@ -4638,7 +4638,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="10">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F130" s="8" t="s">
         <v>28</v>
@@ -4661,7 +4661,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="10">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F131" s="8" t="s">
         <v>31</v>
@@ -4684,7 +4684,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="10">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F132" s="8" t="s">
         <v>28</v>
@@ -4707,7 +4707,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="10">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F133" s="8" t="s">
         <v>34</v>
@@ -4730,7 +4730,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="10">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F134" s="8" t="s">
         <v>28</v>
@@ -4753,7 +4753,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="10">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F135" s="8" t="s">
         <v>31</v>
@@ -4776,7 +4776,7 @@
         <v>27</v>
       </c>
       <c r="E136" s="10">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F136" s="8" t="s">
         <v>28</v>
@@ -4799,7 +4799,7 @@
         <v>27</v>
       </c>
       <c r="E137" s="10">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F137" s="8" t="s">
         <v>34</v>
@@ -4822,7 +4822,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="10">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F138" s="8" t="s">
         <v>28</v>
@@ -4845,7 +4845,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="10">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F139" s="8" t="s">
         <v>31</v>
@@ -4868,7 +4868,7 @@
         <v>27</v>
       </c>
       <c r="E140" s="10">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F140" s="8" t="s">
         <v>28</v>
@@ -4891,7 +4891,7 @@
         <v>27</v>
       </c>
       <c r="E141" s="10">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F141" s="8" t="s">
         <v>34</v>
@@ -4914,7 +4914,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F142" s="8" t="s">
         <v>28</v>
@@ -4960,7 +4960,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="10">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F144" s="8" t="s">
         <v>28</v>
@@ -4983,7 +4983,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="10">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F145" s="8" t="s">
         <v>34</v>
@@ -5006,7 +5006,7 @@
         <v>27</v>
       </c>
       <c r="E146" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>28</v>
@@ -5029,7 +5029,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F147" s="8" t="s">
         <v>31</v>
@@ -5052,7 +5052,7 @@
         <v>27</v>
       </c>
       <c r="E148" s="10">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F148" s="8" t="s">
         <v>28</v>
@@ -5075,7 +5075,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="10">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F149" s="8" t="s">
         <v>34</v>
@@ -5098,7 +5098,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="10">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>28</v>
@@ -5121,7 +5121,7 @@
         <v>27</v>
       </c>
       <c r="E151" s="10">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>31</v>
@@ -5144,7 +5144,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="10">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>28</v>
@@ -5167,7 +5167,7 @@
         <v>27</v>
       </c>
       <c r="E153" s="10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F153" s="8" t="s">
         <v>31</v>
@@ -5190,7 +5190,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="10">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>28</v>
@@ -5213,7 +5213,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="10">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F155" s="8" t="s">
         <v>34</v>
@@ -5236,7 +5236,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="10">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F156" s="8" t="s">
         <v>28</v>
@@ -5259,7 +5259,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="10">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F157" s="8" t="s">
         <v>31</v>
@@ -5282,7 +5282,7 @@
         <v>27</v>
       </c>
       <c r="E158" s="10">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F158" s="8" t="s">
         <v>28</v>
@@ -5328,7 +5328,7 @@
         <v>27</v>
       </c>
       <c r="E160" s="10">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F160" s="8" t="s">
         <v>28</v>
@@ -5351,7 +5351,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="10">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F161" s="8" t="s">
         <v>31</v>
@@ -5374,7 +5374,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="10">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F162" s="8" t="s">
         <v>28</v>
@@ -5397,7 +5397,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="10">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F163" s="8" t="s">
         <v>34</v>
@@ -5420,7 +5420,7 @@
         <v>27</v>
       </c>
       <c r="E164" s="10">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F164" s="8" t="s">
         <v>28</v>
@@ -5443,7 +5443,7 @@
         <v>27</v>
       </c>
       <c r="E165" s="10">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F165" s="8" t="s">
         <v>31</v>
@@ -5466,7 +5466,7 @@
         <v>27</v>
       </c>
       <c r="E166" s="10">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F166" s="8" t="s">
         <v>28</v>
@@ -5489,7 +5489,7 @@
         <v>27</v>
       </c>
       <c r="E167" s="10">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F167" s="8" t="s">
         <v>34</v>
@@ -5512,7 +5512,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F168" s="8" t="s">
         <v>28</v>
@@ -5535,7 +5535,7 @@
         <v>27</v>
       </c>
       <c r="E169" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F169" s="8" t="s">
         <v>31</v>
@@ -5558,7 +5558,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="10">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F170" s="8" t="s">
         <v>28</v>
@@ -5581,7 +5581,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="10">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F171" s="8" t="s">
         <v>34</v>
@@ -5604,7 +5604,7 @@
         <v>27</v>
       </c>
       <c r="E172" s="10">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F172" s="8" t="s">
         <v>28</v>
@@ -5627,7 +5627,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="10">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F173" s="8" t="s">
         <v>31</v>
@@ -5650,7 +5650,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="10">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F174" s="8" t="s">
         <v>28</v>
@@ -5673,7 +5673,7 @@
         <v>27</v>
       </c>
       <c r="E175" s="10">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F175" s="8" t="s">
         <v>34</v>
@@ -5696,7 +5696,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="10">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F176" s="8" t="s">
         <v>28</v>
@@ -5719,7 +5719,7 @@
         <v>27</v>
       </c>
       <c r="E177" s="10">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F177" s="8" t="s">
         <v>28</v>
@@ -5742,7 +5742,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="10">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F178" s="8" t="s">
         <v>31</v>
@@ -5765,7 +5765,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="10">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F179" s="8" t="s">
         <v>28</v>
@@ -5788,7 +5788,7 @@
         <v>27</v>
       </c>
       <c r="E180" s="10">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F180" s="8" t="s">
         <v>34</v>
@@ -5811,7 +5811,7 @@
         <v>27</v>
       </c>
       <c r="E181" s="10">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F181" s="8" t="s">
         <v>28</v>
@@ -5834,7 +5834,7 @@
         <v>27</v>
       </c>
       <c r="E182" s="10">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F182" s="8" t="s">
         <v>31</v>
@@ -5857,7 +5857,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="10">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F183" s="8" t="s">
         <v>28</v>
@@ -5880,7 +5880,7 @@
         <v>27</v>
       </c>
       <c r="E184" s="10">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F184" s="8" t="s">
         <v>34</v>
@@ -5903,7 +5903,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="10">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F185" s="8" t="s">
         <v>28</v>
@@ -5926,7 +5926,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="10">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F186" s="8" t="s">
         <v>31</v>
@@ -5949,7 +5949,7 @@
         <v>27</v>
       </c>
       <c r="E187" s="10">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F187" s="8" t="s">
         <v>28</v>
@@ -5972,7 +5972,7 @@
         <v>27</v>
       </c>
       <c r="E188" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F188" s="8" t="s">
         <v>34</v>
@@ -6018,7 +6018,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="10">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F190" s="8" t="s">
         <v>31</v>
@@ -6041,7 +6041,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="10">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F191" s="8" t="s">
         <v>28</v>
@@ -6064,7 +6064,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="10">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F192" s="8" t="s">
         <v>34</v>
@@ -6087,7 +6087,7 @@
         <v>27</v>
       </c>
       <c r="E193" s="10">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F193" s="8" t="s">
         <v>28</v>
@@ -6110,7 +6110,7 @@
         <v>27</v>
       </c>
       <c r="E194" s="10">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F194" s="8" t="s">
         <v>31</v>
@@ -6133,7 +6133,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="10">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F195" s="8" t="s">
         <v>28</v>
@@ -6156,7 +6156,7 @@
         <v>27</v>
       </c>
       <c r="E196" s="10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F196" s="8" t="s">
         <v>34</v>
@@ -6179,7 +6179,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="10">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F197" s="8" t="s">
         <v>28</v>
@@ -6202,7 +6202,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="10">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F198" s="8" t="s">
         <v>31</v>
@@ -6225,7 +6225,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="10">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F199" s="8" t="s">
         <v>28</v>
@@ -6248,7 +6248,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="10">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F200" s="8" t="s">
         <v>34</v>
@@ -6271,7 +6271,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="10">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F201" s="8" t="s">
         <v>28</v>
@@ -6294,7 +6294,7 @@
         <v>27</v>
       </c>
       <c r="E202" s="10">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F202" s="8" t="s">
         <v>28</v>
@@ -6317,7 +6317,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="10">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F203" s="8" t="s">
         <v>31</v>
@@ -6340,7 +6340,7 @@
         <v>27</v>
       </c>
       <c r="E204" s="10">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F204" s="8" t="s">
         <v>28</v>
@@ -6363,7 +6363,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="10">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F205" s="8" t="s">
         <v>34</v>
@@ -6386,7 +6386,7 @@
         <v>27</v>
       </c>
       <c r="E206" s="10">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F206" s="8" t="s">
         <v>28</v>
@@ -6409,7 +6409,7 @@
         <v>27</v>
       </c>
       <c r="E207" s="10">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F207" s="8" t="s">
         <v>31</v>
@@ -6432,7 +6432,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="10">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F208" s="8" t="s">
         <v>28</v>
@@ -6455,7 +6455,7 @@
         <v>27</v>
       </c>
       <c r="E209" s="10">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F209" s="8" t="s">
         <v>34</v>
@@ -6478,7 +6478,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="10">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F210" s="8" t="s">
         <v>28</v>
@@ -6501,7 +6501,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="10">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F211" s="8" t="s">
         <v>31</v>
@@ -6524,7 +6524,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="10">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F212" s="8" t="s">
         <v>28</v>
@@ -6547,7 +6547,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="10">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F213" s="8" t="s">
         <v>34</v>
@@ -6570,7 +6570,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="10">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F214" s="8" t="s">
         <v>28</v>
@@ -6593,7 +6593,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="10">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F215" s="8" t="s">
         <v>31</v>
@@ -6616,7 +6616,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="10">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F216" s="8" t="s">
         <v>28</v>
@@ -6639,7 +6639,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F217" s="8" t="s">
         <v>34</v>
@@ -6662,7 +6662,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="10">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F218" s="8" t="s">
         <v>28</v>
@@ -6685,7 +6685,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="10">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F219" s="8" t="s">
         <v>31</v>
@@ -6708,7 +6708,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="10">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F220" s="8" t="s">
         <v>28</v>
@@ -6731,7 +6731,7 @@
         <v>27</v>
       </c>
       <c r="E221" s="10">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F221" s="8" t="s">
         <v>34</v>
@@ -6754,7 +6754,7 @@
         <v>27</v>
       </c>
       <c r="E222" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F222" s="8" t="s">
         <v>28</v>
@@ -6777,7 +6777,7 @@
         <v>27</v>
       </c>
       <c r="E223" s="10">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F223" s="8" t="s">
         <v>31</v>
@@ -6800,7 +6800,7 @@
         <v>27</v>
       </c>
       <c r="E224" s="10">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F224" s="8" t="s">
         <v>28</v>
@@ -6823,7 +6823,7 @@
         <v>27</v>
       </c>
       <c r="E225" s="10">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F225" s="8" t="s">
         <v>34</v>
@@ -6846,7 +6846,7 @@
         <v>27</v>
       </c>
       <c r="E226" s="10">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F226" s="8" t="s">
         <v>28</v>
@@ -6869,7 +6869,7 @@
         <v>27</v>
       </c>
       <c r="E227" s="10">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F227" s="8" t="s">
         <v>28</v>
@@ -6892,7 +6892,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="10">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F228" s="8" t="s">
         <v>31</v>
@@ -6915,7 +6915,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="10">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F229" s="8" t="s">
         <v>28</v>
@@ -6938,7 +6938,7 @@
         <v>27</v>
       </c>
       <c r="E230" s="10">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F230" s="8" t="s">
         <v>34</v>
@@ -6961,7 +6961,7 @@
         <v>27</v>
       </c>
       <c r="E231" s="10">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F231" s="8" t="s">
         <v>28</v>
@@ -6984,7 +6984,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="10">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F232" s="8" t="s">
         <v>31</v>
@@ -7007,7 +7007,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="10">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F233" s="8" t="s">
         <v>28</v>
@@ -7030,7 +7030,7 @@
         <v>27</v>
       </c>
       <c r="E234" s="10">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F234" s="8" t="s">
         <v>34</v>
@@ -7053,7 +7053,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="10">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F235" s="8" t="s">
         <v>28</v>
@@ -7076,7 +7076,7 @@
         <v>27</v>
       </c>
       <c r="E236" s="10">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F236" s="8" t="s">
         <v>31</v>
@@ -7099,7 +7099,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="10">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F237" s="8" t="s">
         <v>28</v>
@@ -7122,7 +7122,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="10">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F238" s="8" t="s">
         <v>34</v>
@@ -7145,7 +7145,7 @@
         <v>27</v>
       </c>
       <c r="E239" s="10">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F239" s="8" t="s">
         <v>28</v>
@@ -7168,7 +7168,7 @@
         <v>27</v>
       </c>
       <c r="E240" s="10">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F240" s="8" t="s">
         <v>31</v>
@@ -7191,7 +7191,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="10">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F241" s="8" t="s">
         <v>28</v>
@@ -7214,7 +7214,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="10">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F242" s="8" t="s">
         <v>34</v>
@@ -7237,7 +7237,7 @@
         <v>27</v>
       </c>
       <c r="E243" s="10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F243" s="8" t="s">
         <v>28</v>
@@ -7283,7 +7283,7 @@
         <v>27</v>
       </c>
       <c r="E245" s="10">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F245" s="8" t="s">
         <v>28</v>
@@ -7306,7 +7306,7 @@
         <v>27</v>
       </c>
       <c r="E246" s="10">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F246" s="8" t="s">
         <v>34</v>
@@ -7329,7 +7329,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="10">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F247" s="8" t="s">
         <v>28</v>
@@ -7352,7 +7352,7 @@
         <v>27</v>
       </c>
       <c r="E248" s="10">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F248" s="8" t="s">
         <v>31</v>
@@ -7375,7 +7375,7 @@
         <v>27</v>
       </c>
       <c r="E249" s="10">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F249" s="8" t="s">
         <v>28</v>
@@ -7398,7 +7398,7 @@
         <v>27</v>
       </c>
       <c r="E250" s="10">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F250" s="8" t="s">
         <v>34</v>
@@ -7421,7 +7421,7 @@
         <v>27</v>
       </c>
       <c r="E251" s="10">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F251" s="8" t="s">
         <v>28</v>
@@ -7444,7 +7444,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="10">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F252" s="8" t="s">
         <v>28</v>
@@ -7467,7 +7467,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="10">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F253" s="8" t="s">
         <v>31</v>
@@ -7490,7 +7490,7 @@
         <v>27</v>
       </c>
       <c r="E254" s="10">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F254" s="8" t="s">
         <v>28</v>
@@ -7513,7 +7513,7 @@
         <v>27</v>
       </c>
       <c r="E255" s="10">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F255" s="8" t="s">
         <v>34</v>
@@ -7536,7 +7536,7 @@
         <v>27</v>
       </c>
       <c r="E256" s="10">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F256" s="8" t="s">
         <v>28</v>
@@ -7559,7 +7559,7 @@
         <v>27</v>
       </c>
       <c r="E257" s="10">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F257" s="8" t="s">
         <v>31</v>
@@ -7582,7 +7582,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="10">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F258" s="8" t="s">
         <v>28</v>
@@ -7605,7 +7605,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="10">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F259" s="8" t="s">
         <v>34</v>
@@ -7628,7 +7628,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="10">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F260" s="8" t="s">
         <v>28</v>
@@ -7651,7 +7651,7 @@
         <v>27</v>
       </c>
       <c r="E261" s="10">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F261" s="8" t="s">
         <v>31</v>
@@ -7674,7 +7674,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="10">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F262" s="8" t="s">
         <v>28</v>
@@ -7697,7 +7697,7 @@
         <v>27</v>
       </c>
       <c r="E263" s="10">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F263" s="8" t="s">
         <v>34</v>
@@ -7720,7 +7720,7 @@
         <v>27</v>
       </c>
       <c r="E264" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F264" s="8" t="s">
         <v>28</v>
@@ -7743,7 +7743,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="10">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F265" s="8" t="s">
         <v>31</v>
@@ -7766,7 +7766,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="10">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F266" s="8" t="s">
         <v>28</v>
@@ -7789,7 +7789,7 @@
         <v>27</v>
       </c>
       <c r="E267" s="10">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F267" s="8" t="s">
         <v>34</v>
@@ -7812,7 +7812,7 @@
         <v>27</v>
       </c>
       <c r="E268" s="10">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F268" s="8" t="s">
         <v>28</v>
@@ -7835,7 +7835,7 @@
         <v>27</v>
       </c>
       <c r="E269" s="10">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F269" s="8" t="s">
         <v>31</v>
@@ -7858,7 +7858,7 @@
         <v>27</v>
       </c>
       <c r="E270" s="10">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F270" s="8" t="s">
         <v>28</v>
@@ -7904,7 +7904,7 @@
         <v>27</v>
       </c>
       <c r="E272" s="10">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F272" s="8" t="s">
         <v>28</v>
@@ -7927,7 +7927,7 @@
         <v>27</v>
       </c>
       <c r="E273" s="10">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F273" s="8" t="s">
         <v>31</v>
@@ -7950,7 +7950,7 @@
         <v>27</v>
       </c>
       <c r="E274" s="10">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F274" s="8" t="s">
         <v>28</v>
@@ -7973,7 +7973,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="10">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F275" s="8" t="s">
         <v>34</v>
@@ -7996,7 +7996,7 @@
         <v>27</v>
       </c>
       <c r="E276" s="10">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F276" s="8" t="s">
         <v>28</v>
@@ -8019,7 +8019,7 @@
         <v>27</v>
       </c>
       <c r="E277" s="10">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F277" s="8" t="s">
         <v>28</v>
@@ -8042,7 +8042,7 @@
         <v>27</v>
       </c>
       <c r="E278" s="10">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F278" s="8" t="s">
         <v>31</v>
@@ -8065,7 +8065,7 @@
         <v>27</v>
       </c>
       <c r="E279" s="10">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F279" s="8" t="s">
         <v>28</v>
@@ -8088,7 +8088,7 @@
         <v>27</v>
       </c>
       <c r="E280" s="10">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F280" s="8" t="s">
         <v>34</v>
@@ -8111,7 +8111,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="10">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F281" s="8" t="s">
         <v>28</v>
@@ -8134,7 +8134,7 @@
         <v>27</v>
       </c>
       <c r="E282" s="10">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F282" s="8" t="s">
         <v>31</v>
@@ -8157,7 +8157,7 @@
         <v>27</v>
       </c>
       <c r="E283" s="10">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F283" s="8" t="s">
         <v>28</v>
@@ -8180,7 +8180,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="10">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F284" s="8" t="s">
         <v>34</v>
@@ -8203,7 +8203,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="10">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F285" s="8" t="s">
         <v>28</v>
@@ -8226,7 +8226,7 @@
         <v>27</v>
       </c>
       <c r="E286" s="10">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F286" s="8" t="s">
         <v>31</v>
@@ -8249,7 +8249,7 @@
         <v>27</v>
       </c>
       <c r="E287" s="10">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F287" s="8" t="s">
         <v>28</v>
@@ -8272,7 +8272,7 @@
         <v>27</v>
       </c>
       <c r="E288" s="10">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F288" s="8" t="s">
         <v>34</v>
@@ -8295,7 +8295,7 @@
         <v>27</v>
       </c>
       <c r="E289" s="10">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F289" s="8" t="s">
         <v>28</v>
@@ -8318,7 +8318,7 @@
         <v>27</v>
       </c>
       <c r="E290" s="10">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F290" s="8" t="s">
         <v>31</v>
@@ -8341,7 +8341,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="10">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F291" s="8" t="s">
         <v>28</v>
@@ -8364,7 +8364,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="10">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F292" s="8" t="s">
         <v>34</v>
@@ -8387,7 +8387,7 @@
         <v>27</v>
       </c>
       <c r="E293" s="10">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F293" s="8" t="s">
         <v>28</v>
@@ -8410,7 +8410,7 @@
         <v>27</v>
       </c>
       <c r="E294" s="10">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F294" s="8" t="s">
         <v>31</v>
@@ -8433,7 +8433,7 @@
         <v>27</v>
       </c>
       <c r="E295" s="10">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F295" s="8" t="s">
         <v>28</v>
@@ -8456,7 +8456,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="10">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F296" s="8" t="s">
         <v>34</v>
@@ -8479,7 +8479,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="10">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F297" s="8" t="s">
         <v>28</v>
@@ -8502,7 +8502,7 @@
         <v>27</v>
       </c>
       <c r="E298" s="10">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F298" s="8" t="s">
         <v>31</v>
@@ -8525,7 +8525,7 @@
         <v>27</v>
       </c>
       <c r="E299" s="10">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F299" s="8" t="s">
         <v>28</v>
@@ -8548,7 +8548,7 @@
         <v>27</v>
       </c>
       <c r="E300" s="10">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F300" s="8" t="s">
         <v>34</v>
@@ -8571,7 +8571,7 @@
         <v>27</v>
       </c>
       <c r="E301" s="10">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F301" s="8" t="s">
         <v>28</v>
@@ -8636,7 +8636,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -8659,7 +8659,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="F3" t="s">
         <v>31</v>
@@ -8682,7 +8682,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -8705,7 +8705,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
         <v>34</v>
@@ -8728,7 +8728,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -8751,7 +8751,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
         <v>31</v>
@@ -8774,7 +8774,7 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -8797,7 +8797,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
@@ -8820,7 +8820,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -8843,7 +8843,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
         <v>31</v>
@@ -8866,7 +8866,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -8889,7 +8889,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F13" t="s">
         <v>34</v>
@@ -8912,7 +8912,7 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -8935,7 +8935,7 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s">
         <v>31</v>
@@ -8958,7 +8958,7 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -8981,7 +8981,7 @@
         <v>27</v>
       </c>
       <c r="E17">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F17" t="s">
         <v>34</v>
@@ -9004,7 +9004,7 @@
         <v>27</v>
       </c>
       <c r="E18">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -9027,7 +9027,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F19" t="s">
         <v>31</v>
@@ -9073,7 +9073,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F21" t="s">
         <v>34</v>
@@ -9096,7 +9096,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -9119,7 +9119,7 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F23" t="s">
         <v>31</v>
@@ -9142,7 +9142,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -9165,7 +9165,7 @@
         <v>27</v>
       </c>
       <c r="E25">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
         <v>34</v>
@@ -9211,7 +9211,7 @@
         <v>27</v>
       </c>
       <c r="E27">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F27" t="s">
         <v>31</v>
@@ -9234,7 +9234,7 @@
         <v>27</v>
       </c>
       <c r="E28">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -9280,7 +9280,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -9303,7 +9303,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F31" t="s">
         <v>31</v>
@@ -9326,7 +9326,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -9349,7 +9349,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F33" t="s">
         <v>31</v>
@@ -9372,7 +9372,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -9395,7 +9395,7 @@
         <v>27</v>
       </c>
       <c r="E35">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
@@ -9418,7 +9418,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -9441,7 +9441,7 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F37" t="s">
         <v>31</v>
@@ -9464,7 +9464,7 @@
         <v>27</v>
       </c>
       <c r="E38">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -9487,7 +9487,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F39" t="s">
         <v>34</v>
@@ -9533,7 +9533,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F41" t="s">
         <v>31</v>
@@ -9556,7 +9556,7 @@
         <v>27</v>
       </c>
       <c r="E42">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -9579,7 +9579,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F43" t="s">
         <v>34</v>
@@ -9602,7 +9602,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -9625,7 +9625,7 @@
         <v>27</v>
       </c>
       <c r="E45">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F45" t="s">
         <v>31</v>
@@ -9648,7 +9648,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -9671,7 +9671,7 @@
         <v>27</v>
       </c>
       <c r="E47">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F47" t="s">
         <v>34</v>
@@ -9694,7 +9694,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -9717,7 +9717,7 @@
         <v>27</v>
       </c>
       <c r="E49">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F49" t="s">
         <v>31</v>
@@ -9740,7 +9740,7 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F50" t="s">
         <v>28</v>
@@ -9763,7 +9763,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F51" t="s">
         <v>34</v>
@@ -9786,7 +9786,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -9809,7 +9809,7 @@
         <v>27</v>
       </c>
       <c r="E53">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F53" t="s">
         <v>31</v>
@@ -9832,7 +9832,7 @@
         <v>27</v>
       </c>
       <c r="E54">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -9855,7 +9855,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F55" t="s">
         <v>34</v>
@@ -9878,7 +9878,7 @@
         <v>27</v>
       </c>
       <c r="E56">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -9901,7 +9901,7 @@
         <v>27</v>
       </c>
       <c r="E57">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F57" t="s">
         <v>31</v>
@@ -9924,7 +9924,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -9970,7 +9970,7 @@
         <v>27</v>
       </c>
       <c r="E60">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -9993,7 +9993,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F61" t="s">
         <v>31</v>
@@ -10016,7 +10016,7 @@
         <v>27</v>
       </c>
       <c r="E62">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F62" t="s">
         <v>28</v>
@@ -10039,7 +10039,7 @@
         <v>27</v>
       </c>
       <c r="E63">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F63" t="s">
         <v>31</v>
@@ -10062,7 +10062,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -10085,7 +10085,7 @@
         <v>27</v>
       </c>
       <c r="E65">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F65" t="s">
         <v>34</v>
@@ -10108,7 +10108,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -10131,7 +10131,7 @@
         <v>27</v>
       </c>
       <c r="E67">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F67" t="s">
         <v>31</v>
@@ -10154,7 +10154,7 @@
         <v>27</v>
       </c>
       <c r="E68">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
@@ -10177,7 +10177,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F69" t="s">
         <v>34</v>
@@ -10200,7 +10200,7 @@
         <v>27</v>
       </c>
       <c r="E70">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -10223,7 +10223,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F71" t="s">
         <v>31</v>
@@ -10246,7 +10246,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -10269,7 +10269,7 @@
         <v>27</v>
       </c>
       <c r="E73">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F73" t="s">
         <v>34</v>
@@ -10292,7 +10292,7 @@
         <v>27</v>
       </c>
       <c r="E74">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -10315,7 +10315,7 @@
         <v>27</v>
       </c>
       <c r="E75">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F75" t="s">
         <v>31</v>
@@ -10338,7 +10338,7 @@
         <v>27</v>
       </c>
       <c r="E76">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
@@ -10361,7 +10361,7 @@
         <v>27</v>
       </c>
       <c r="E77">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F77" t="s">
         <v>34</v>
@@ -10384,7 +10384,7 @@
         <v>27</v>
       </c>
       <c r="E78">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
@@ -10407,7 +10407,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F79" t="s">
         <v>31</v>
@@ -10430,7 +10430,7 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
@@ -10453,7 +10453,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F81" t="s">
         <v>34</v>
@@ -10476,7 +10476,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -10499,7 +10499,7 @@
         <v>27</v>
       </c>
       <c r="E83">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F83" t="s">
         <v>31</v>
@@ -10522,7 +10522,7 @@
         <v>27</v>
       </c>
       <c r="E84">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
@@ -10545,7 +10545,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F85" t="s">
         <v>34</v>
@@ -10568,7 +10568,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -10591,7 +10591,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F87" t="s">
         <v>31</v>
@@ -10614,7 +10614,7 @@
         <v>27</v>
       </c>
       <c r="E88">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -10637,7 +10637,7 @@
         <v>27</v>
       </c>
       <c r="E89">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F89" t="s">
         <v>34</v>
@@ -10660,7 +10660,7 @@
         <v>27</v>
       </c>
       <c r="E90">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F90" t="s">
         <v>28</v>
@@ -10683,7 +10683,7 @@
         <v>27</v>
       </c>
       <c r="E91">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F91" t="s">
         <v>31</v>
@@ -10706,7 +10706,7 @@
         <v>27</v>
       </c>
       <c r="E92">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
@@ -10729,7 +10729,7 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F93" t="s">
         <v>31</v>
@@ -10752,7 +10752,7 @@
         <v>27</v>
       </c>
       <c r="E94">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -10775,7 +10775,7 @@
         <v>27</v>
       </c>
       <c r="E95">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F95" t="s">
         <v>34</v>
@@ -10798,7 +10798,7 @@
         <v>27</v>
       </c>
       <c r="E96">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -10821,7 +10821,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F97" t="s">
         <v>31</v>
@@ -10844,7 +10844,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -10867,7 +10867,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F99" t="s">
         <v>34</v>
@@ -10913,7 +10913,7 @@
         <v>27</v>
       </c>
       <c r="E101">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F101" t="s">
         <v>31</v>
@@ -10936,7 +10936,7 @@
         <v>27</v>
       </c>
       <c r="E102">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
@@ -10959,7 +10959,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F103" t="s">
         <v>34</v>
@@ -10982,7 +10982,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -11005,7 +11005,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F105" t="s">
         <v>31</v>
@@ -11028,7 +11028,7 @@
         <v>27</v>
       </c>
       <c r="E106">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
@@ -11051,7 +11051,7 @@
         <v>27</v>
       </c>
       <c r="E107">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F107" t="s">
         <v>34</v>
@@ -11074,7 +11074,7 @@
         <v>27</v>
       </c>
       <c r="E108">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
@@ -11120,7 +11120,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -11143,7 +11143,7 @@
         <v>27</v>
       </c>
       <c r="E111">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F111" t="s">
         <v>34</v>
@@ -11166,7 +11166,7 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F112" t="s">
         <v>28</v>
@@ -11189,7 +11189,7 @@
         <v>27</v>
       </c>
       <c r="E113">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F113" t="s">
         <v>31</v>
@@ -11212,7 +11212,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -11235,7 +11235,7 @@
         <v>27</v>
       </c>
       <c r="E115">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F115" t="s">
         <v>34</v>
@@ -11258,7 +11258,7 @@
         <v>27</v>
       </c>
       <c r="E116">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F116" t="s">
         <v>28</v>
@@ -11281,7 +11281,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F117" t="s">
         <v>31</v>
@@ -11304,7 +11304,7 @@
         <v>27</v>
       </c>
       <c r="E118">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F118" t="s">
         <v>28</v>
@@ -11327,7 +11327,7 @@
         <v>27</v>
       </c>
       <c r="E119">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F119" t="s">
         <v>34</v>
@@ -11350,7 +11350,7 @@
         <v>27</v>
       </c>
       <c r="E120">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
@@ -11373,7 +11373,7 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F121" t="s">
         <v>31</v>
@@ -11396,7 +11396,7 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -11419,7 +11419,7 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F123" t="s">
         <v>31</v>
@@ -11442,7 +11442,7 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F124" t="s">
         <v>28</v>
@@ -11465,7 +11465,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F125" t="s">
         <v>34</v>
@@ -11511,7 +11511,7 @@
         <v>27</v>
       </c>
       <c r="E127">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F127" t="s">
         <v>31</v>
@@ -11534,7 +11534,7 @@
         <v>27</v>
       </c>
       <c r="E128">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -11557,7 +11557,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F129" t="s">
         <v>34</v>
@@ -11580,7 +11580,7 @@
         <v>27</v>
       </c>
       <c r="E130">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
@@ -11603,7 +11603,7 @@
         <v>27</v>
       </c>
       <c r="E131">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F131" t="s">
         <v>31</v>
@@ -11626,7 +11626,7 @@
         <v>27</v>
       </c>
       <c r="E132">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F132" t="s">
         <v>28</v>
@@ -11649,7 +11649,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F133" t="s">
         <v>34</v>
@@ -11672,7 +11672,7 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -11695,7 +11695,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F135" t="s">
         <v>31</v>
@@ -11718,7 +11718,7 @@
         <v>27</v>
       </c>
       <c r="E136">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
@@ -11741,7 +11741,7 @@
         <v>27</v>
       </c>
       <c r="E137">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F137" t="s">
         <v>34</v>
@@ -11764,7 +11764,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -11787,7 +11787,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F139" t="s">
         <v>31</v>
@@ -11810,7 +11810,7 @@
         <v>27</v>
       </c>
       <c r="E140">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
@@ -11833,7 +11833,7 @@
         <v>27</v>
       </c>
       <c r="E141">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F141" t="s">
         <v>34</v>
@@ -11856,7 +11856,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -11902,7 +11902,7 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F144" t="s">
         <v>28</v>
@@ -11925,7 +11925,7 @@
         <v>27</v>
       </c>
       <c r="E145">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F145" t="s">
         <v>34</v>
@@ -11948,7 +11948,7 @@
         <v>27</v>
       </c>
       <c r="E146">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F146" t="s">
         <v>28</v>
@@ -11971,7 +11971,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F147" t="s">
         <v>31</v>
@@ -11994,7 +11994,7 @@
         <v>27</v>
       </c>
       <c r="E148">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
@@ -12017,7 +12017,7 @@
         <v>27</v>
       </c>
       <c r="E149">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F149" t="s">
         <v>34</v>
@@ -12040,7 +12040,7 @@
         <v>27</v>
       </c>
       <c r="E150">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
@@ -12063,7 +12063,7 @@
         <v>27</v>
       </c>
       <c r="E151">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F151" t="s">
         <v>31</v>
@@ -12086,7 +12086,7 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F152" t="s">
         <v>28</v>
@@ -12109,7 +12109,7 @@
         <v>27</v>
       </c>
       <c r="E153">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F153" t="s">
         <v>31</v>
@@ -12132,7 +12132,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -12155,7 +12155,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F155" t="s">
         <v>34</v>
@@ -12178,7 +12178,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -12201,7 +12201,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F157" t="s">
         <v>31</v>
@@ -12224,7 +12224,7 @@
         <v>27</v>
       </c>
       <c r="E158">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F158" t="s">
         <v>28</v>
@@ -12270,7 +12270,7 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F160" t="s">
         <v>28</v>
@@ -12293,7 +12293,7 @@
         <v>27</v>
       </c>
       <c r="E161">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F161" t="s">
         <v>31</v>
@@ -12316,7 +12316,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -12339,7 +12339,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F163" t="s">
         <v>34</v>
@@ -12362,7 +12362,7 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
@@ -12385,7 +12385,7 @@
         <v>27</v>
       </c>
       <c r="E165">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F165" t="s">
         <v>31</v>
@@ -12408,7 +12408,7 @@
         <v>27</v>
       </c>
       <c r="E166">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -12431,7 +12431,7 @@
         <v>27</v>
       </c>
       <c r="E167">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F167" t="s">
         <v>34</v>
@@ -12454,7 +12454,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -12477,7 +12477,7 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F169" t="s">
         <v>31</v>
@@ -12500,7 +12500,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -12523,7 +12523,7 @@
         <v>27</v>
       </c>
       <c r="E171">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F171" t="s">
         <v>34</v>
@@ -12546,7 +12546,7 @@
         <v>27</v>
       </c>
       <c r="E172">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
@@ -12569,7 +12569,7 @@
         <v>27</v>
       </c>
       <c r="E173">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F173" t="s">
         <v>31</v>
@@ -12592,7 +12592,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -12615,7 +12615,7 @@
         <v>27</v>
       </c>
       <c r="E175">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F175" t="s">
         <v>34</v>
@@ -12638,7 +12638,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -12661,7 +12661,7 @@
         <v>27</v>
       </c>
       <c r="E177">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
@@ -12684,7 +12684,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F178" t="s">
         <v>31</v>
@@ -12707,7 +12707,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -12730,7 +12730,7 @@
         <v>27</v>
       </c>
       <c r="E180">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F180" t="s">
         <v>34</v>
@@ -12753,7 +12753,7 @@
         <v>27</v>
       </c>
       <c r="E181">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F181" t="s">
         <v>28</v>
@@ -12776,7 +12776,7 @@
         <v>27</v>
       </c>
       <c r="E182">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F182" t="s">
         <v>31</v>
@@ -12799,7 +12799,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -12822,7 +12822,7 @@
         <v>27</v>
       </c>
       <c r="E184">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F184" t="s">
         <v>34</v>
@@ -12845,7 +12845,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -12868,7 +12868,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F186" t="s">
         <v>31</v>
@@ -12891,7 +12891,7 @@
         <v>27</v>
       </c>
       <c r="E187">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F187" t="s">
         <v>28</v>
@@ -12914,7 +12914,7 @@
         <v>27</v>
       </c>
       <c r="E188">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F188" t="s">
         <v>34</v>
@@ -12960,7 +12960,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F190" t="s">
         <v>31</v>
@@ -12983,7 +12983,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -13006,7 +13006,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F192" t="s">
         <v>34</v>
@@ -13029,7 +13029,7 @@
         <v>27</v>
       </c>
       <c r="E193">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -13052,7 +13052,7 @@
         <v>27</v>
       </c>
       <c r="E194">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F194" t="s">
         <v>31</v>
@@ -13075,7 +13075,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -13098,7 +13098,7 @@
         <v>27</v>
       </c>
       <c r="E196">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F196" t="s">
         <v>34</v>
@@ -13121,7 +13121,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -13144,7 +13144,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F198" t="s">
         <v>31</v>
@@ -13167,7 +13167,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -13190,7 +13190,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F200" t="s">
         <v>34</v>
@@ -13213,7 +13213,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -13236,7 +13236,7 @@
         <v>27</v>
       </c>
       <c r="E202">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -13259,7 +13259,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F203" t="s">
         <v>31</v>
@@ -13282,7 +13282,7 @@
         <v>27</v>
       </c>
       <c r="E204">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -13305,7 +13305,7 @@
         <v>27</v>
       </c>
       <c r="E205">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F205" t="s">
         <v>34</v>
@@ -13328,7 +13328,7 @@
         <v>27</v>
       </c>
       <c r="E206">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -13351,7 +13351,7 @@
         <v>27</v>
       </c>
       <c r="E207">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F207" t="s">
         <v>31</v>
@@ -13374,7 +13374,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -13397,7 +13397,7 @@
         <v>27</v>
       </c>
       <c r="E209">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F209" t="s">
         <v>34</v>
@@ -13420,7 +13420,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -13443,7 +13443,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F211" t="s">
         <v>31</v>
@@ -13466,7 +13466,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -13489,7 +13489,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F213" t="s">
         <v>34</v>
@@ -13512,7 +13512,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -13535,7 +13535,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F215" t="s">
         <v>31</v>
@@ -13558,7 +13558,7 @@
         <v>27</v>
       </c>
       <c r="E216">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F216" t="s">
         <v>28</v>
@@ -13581,7 +13581,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F217" t="s">
         <v>34</v>
@@ -13604,7 +13604,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -13627,7 +13627,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F219" t="s">
         <v>31</v>
@@ -13650,7 +13650,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -13673,7 +13673,7 @@
         <v>27</v>
       </c>
       <c r="E221">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F221" t="s">
         <v>34</v>
@@ -13696,7 +13696,7 @@
         <v>27</v>
       </c>
       <c r="E222">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F222" t="s">
         <v>28</v>
@@ -13719,7 +13719,7 @@
         <v>27</v>
       </c>
       <c r="E223">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F223" t="s">
         <v>31</v>
@@ -13742,7 +13742,7 @@
         <v>27</v>
       </c>
       <c r="E224">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F224" t="s">
         <v>28</v>
@@ -13765,7 +13765,7 @@
         <v>27</v>
       </c>
       <c r="E225">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F225" t="s">
         <v>34</v>
@@ -13788,7 +13788,7 @@
         <v>27</v>
       </c>
       <c r="E226">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F226" t="s">
         <v>28</v>
@@ -13811,7 +13811,7 @@
         <v>27</v>
       </c>
       <c r="E227">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F227" t="s">
         <v>28</v>
@@ -13834,7 +13834,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F228" t="s">
         <v>31</v>
@@ -13857,7 +13857,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -13880,7 +13880,7 @@
         <v>27</v>
       </c>
       <c r="E230">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F230" t="s">
         <v>34</v>
@@ -13903,7 +13903,7 @@
         <v>27</v>
       </c>
       <c r="E231">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F231" t="s">
         <v>28</v>
@@ -13926,7 +13926,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F232" t="s">
         <v>31</v>
@@ -13949,7 +13949,7 @@
         <v>27</v>
       </c>
       <c r="E233">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F233" t="s">
         <v>28</v>
@@ -13972,7 +13972,7 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F234" t="s">
         <v>34</v>
@@ -13995,7 +13995,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -14018,7 +14018,7 @@
         <v>27</v>
       </c>
       <c r="E236">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F236" t="s">
         <v>31</v>
@@ -14041,7 +14041,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -14064,7 +14064,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F238" t="s">
         <v>34</v>
@@ -14087,7 +14087,7 @@
         <v>27</v>
       </c>
       <c r="E239">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F239" t="s">
         <v>28</v>
@@ -14110,7 +14110,7 @@
         <v>27</v>
       </c>
       <c r="E240">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F240" t="s">
         <v>31</v>
@@ -14133,7 +14133,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -14156,7 +14156,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F242" t="s">
         <v>34</v>
@@ -14179,7 +14179,7 @@
         <v>27</v>
       </c>
       <c r="E243">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -14225,7 +14225,7 @@
         <v>27</v>
       </c>
       <c r="E245">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F245" t="s">
         <v>28</v>
@@ -14248,7 +14248,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F246" t="s">
         <v>34</v>
@@ -14271,7 +14271,7 @@
         <v>27</v>
       </c>
       <c r="E247">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F247" t="s">
         <v>28</v>
@@ -14294,7 +14294,7 @@
         <v>27</v>
       </c>
       <c r="E248">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F248" t="s">
         <v>31</v>
@@ -14317,7 +14317,7 @@
         <v>27</v>
       </c>
       <c r="E249">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F249" t="s">
         <v>28</v>
@@ -14340,7 +14340,7 @@
         <v>27</v>
       </c>
       <c r="E250">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F250" t="s">
         <v>34</v>
@@ -14363,7 +14363,7 @@
         <v>27</v>
       </c>
       <c r="E251">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F251" t="s">
         <v>28</v>
@@ -14386,7 +14386,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -14409,7 +14409,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F253" t="s">
         <v>31</v>
@@ -14432,7 +14432,7 @@
         <v>27</v>
       </c>
       <c r="E254">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F254" t="s">
         <v>28</v>
@@ -14455,7 +14455,7 @@
         <v>27</v>
       </c>
       <c r="E255">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F255" t="s">
         <v>34</v>
@@ -14478,7 +14478,7 @@
         <v>27</v>
       </c>
       <c r="E256">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F256" t="s">
         <v>28</v>
@@ -14501,7 +14501,7 @@
         <v>27</v>
       </c>
       <c r="E257">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F257" t="s">
         <v>31</v>
@@ -14524,7 +14524,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -14547,7 +14547,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F259" t="s">
         <v>34</v>
@@ -14570,7 +14570,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -14593,7 +14593,7 @@
         <v>27</v>
       </c>
       <c r="E261">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F261" t="s">
         <v>31</v>
@@ -14616,7 +14616,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -14639,7 +14639,7 @@
         <v>27</v>
       </c>
       <c r="E263">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F263" t="s">
         <v>34</v>
@@ -14662,7 +14662,7 @@
         <v>27</v>
       </c>
       <c r="E264">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -14685,7 +14685,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F265" t="s">
         <v>31</v>
@@ -14708,7 +14708,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -14731,7 +14731,7 @@
         <v>27</v>
       </c>
       <c r="E267">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F267" t="s">
         <v>34</v>
@@ -14754,7 +14754,7 @@
         <v>27</v>
       </c>
       <c r="E268">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F268" t="s">
         <v>28</v>
@@ -14777,7 +14777,7 @@
         <v>27</v>
       </c>
       <c r="E269">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F269" t="s">
         <v>31</v>
@@ -14800,7 +14800,7 @@
         <v>27</v>
       </c>
       <c r="E270">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F270" t="s">
         <v>28</v>
@@ -14846,7 +14846,7 @@
         <v>27</v>
       </c>
       <c r="E272">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F272" t="s">
         <v>28</v>
@@ -14869,7 +14869,7 @@
         <v>27</v>
       </c>
       <c r="E273">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F273" t="s">
         <v>31</v>
@@ -14892,7 +14892,7 @@
         <v>27</v>
       </c>
       <c r="E274">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F274" t="s">
         <v>28</v>
@@ -14915,7 +14915,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F275" t="s">
         <v>34</v>
@@ -14938,7 +14938,7 @@
         <v>27</v>
       </c>
       <c r="E276">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F276" t="s">
         <v>28</v>
@@ -14961,7 +14961,7 @@
         <v>27</v>
       </c>
       <c r="E277">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F277" t="s">
         <v>28</v>
@@ -14984,7 +14984,7 @@
         <v>27</v>
       </c>
       <c r="E278">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F278" t="s">
         <v>31</v>
@@ -15007,7 +15007,7 @@
         <v>27</v>
       </c>
       <c r="E279">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -15030,7 +15030,7 @@
         <v>27</v>
       </c>
       <c r="E280">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F280" t="s">
         <v>34</v>
@@ -15053,7 +15053,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -15076,7 +15076,7 @@
         <v>27</v>
       </c>
       <c r="E282">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F282" t="s">
         <v>31</v>
@@ -15099,7 +15099,7 @@
         <v>27</v>
       </c>
       <c r="E283">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F283" t="s">
         <v>28</v>
@@ -15122,7 +15122,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F284" t="s">
         <v>34</v>
@@ -15145,7 +15145,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -15168,7 +15168,7 @@
         <v>27</v>
       </c>
       <c r="E286">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F286" t="s">
         <v>31</v>
@@ -15191,7 +15191,7 @@
         <v>27</v>
       </c>
       <c r="E287">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F287" t="s">
         <v>28</v>
@@ -15214,7 +15214,7 @@
         <v>27</v>
       </c>
       <c r="E288">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F288" t="s">
         <v>34</v>
@@ -15237,7 +15237,7 @@
         <v>27</v>
       </c>
       <c r="E289">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F289" t="s">
         <v>28</v>
@@ -15260,7 +15260,7 @@
         <v>27</v>
       </c>
       <c r="E290">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F290" t="s">
         <v>31</v>
@@ -15283,7 +15283,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -15306,7 +15306,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F292" t="s">
         <v>34</v>
@@ -15329,7 +15329,7 @@
         <v>27</v>
       </c>
       <c r="E293">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -15352,7 +15352,7 @@
         <v>27</v>
       </c>
       <c r="E294">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F294" t="s">
         <v>31</v>
@@ -15375,7 +15375,7 @@
         <v>27</v>
       </c>
       <c r="E295">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F295" t="s">
         <v>28</v>
@@ -15398,7 +15398,7 @@
         <v>27</v>
       </c>
       <c r="E296">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F296" t="s">
         <v>34</v>
@@ -15421,7 +15421,7 @@
         <v>27</v>
       </c>
       <c r="E297">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F297" t="s">
         <v>28</v>
@@ -15444,7 +15444,7 @@
         <v>27</v>
       </c>
       <c r="E298">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F298" t="s">
         <v>31</v>
@@ -15467,7 +15467,7 @@
         <v>27</v>
       </c>
       <c r="E299">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F299" t="s">
         <v>28</v>
@@ -15490,7 +15490,7 @@
         <v>27</v>
       </c>
       <c r="E300">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F300" t="s">
         <v>34</v>
@@ -15513,7 +15513,7 @@
         <v>27</v>
       </c>
       <c r="E301">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F301" t="s">
         <v>28</v>

--- a/all-test-reports/vulnerability/vulnerability_test_report.xlsx
+++ b/all-test-reports/vulnerability/vulnerability_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 10:34:34 am</t>
+    <t>28/7/2026, 10:42:39 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1694,7 +1694,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="10">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>28</v>
@@ -1717,7 +1717,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="10">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>31</v>
@@ -1740,7 +1740,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="10">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>28</v>
@@ -1763,7 +1763,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="10">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>34</v>
@@ -1786,7 +1786,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="10">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>28</v>
@@ -1809,7 +1809,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="10">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>31</v>
@@ -1832,7 +1832,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="10">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>28</v>
@@ -1855,7 +1855,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>34</v>
@@ -1878,7 +1878,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="10">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>28</v>
@@ -1901,7 +1901,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="10">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>31</v>
@@ -1924,7 +1924,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>28</v>
@@ -1947,7 +1947,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="10">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>34</v>
@@ -1970,7 +1970,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="10">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>28</v>
@@ -1993,7 +1993,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="10">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>31</v>
@@ -2016,7 +2016,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="10">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>28</v>
@@ -2039,7 +2039,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="10">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>34</v>
@@ -2062,7 +2062,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="10">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>28</v>
@@ -2085,7 +2085,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="10">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>31</v>
@@ -2108,7 +2108,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="10">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>28</v>
@@ -2131,7 +2131,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="10">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>34</v>
@@ -2154,7 +2154,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="10">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>28</v>
@@ -2177,7 +2177,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="10">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>31</v>
@@ -2200,7 +2200,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="10">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>28</v>
@@ -2223,7 +2223,7 @@
         <v>27</v>
       </c>
       <c r="E25" s="10">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>34</v>
@@ -2246,7 +2246,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="10">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>28</v>
@@ -2315,7 +2315,7 @@
         <v>27</v>
       </c>
       <c r="E29" s="10">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>34</v>
@@ -2338,7 +2338,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="10">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>28</v>
@@ -2361,7 +2361,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="10">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>31</v>
@@ -2384,7 +2384,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="10">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>28</v>
@@ -2407,7 +2407,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="10">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>31</v>
@@ -2430,7 +2430,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="10">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>28</v>
@@ -2453,7 +2453,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="10">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>34</v>
@@ -2476,7 +2476,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="10">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>28</v>
@@ -2499,7 +2499,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="10">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>31</v>
@@ -2522,7 +2522,7 @@
         <v>27</v>
       </c>
       <c r="E38" s="10">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>28</v>
@@ -2545,7 +2545,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="10">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>34</v>
@@ -2568,7 +2568,7 @@
         <v>27</v>
       </c>
       <c r="E40" s="10">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>28</v>
@@ -2591,7 +2591,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="10">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>31</v>
@@ -2614,7 +2614,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="10">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>28</v>
@@ -2637,7 +2637,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="10">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>34</v>
@@ -2660,7 +2660,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="10">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>28</v>
@@ -2683,7 +2683,7 @@
         <v>27</v>
       </c>
       <c r="E45" s="10">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>31</v>
@@ -2706,7 +2706,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="10">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>28</v>
@@ -2729,7 +2729,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="10">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>34</v>
@@ -2752,7 +2752,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="10">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>28</v>
@@ -2775,7 +2775,7 @@
         <v>27</v>
       </c>
       <c r="E49" s="10">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>31</v>
@@ -2798,7 +2798,7 @@
         <v>27</v>
       </c>
       <c r="E50" s="10">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>28</v>
@@ -2821,7 +2821,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="10">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>34</v>
@@ -2844,7 +2844,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="10">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>28</v>
@@ -2867,7 +2867,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="10">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>31</v>
@@ -2890,7 +2890,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="10">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>28</v>
@@ -2913,7 +2913,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="10">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>34</v>
@@ -2936,7 +2936,7 @@
         <v>27</v>
       </c>
       <c r="E56" s="10">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>28</v>
@@ -2959,7 +2959,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="10">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>31</v>
@@ -2982,7 +2982,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="10">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>28</v>
@@ -3005,7 +3005,7 @@
         <v>27</v>
       </c>
       <c r="E59" s="10">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>34</v>
@@ -3028,7 +3028,7 @@
         <v>27</v>
       </c>
       <c r="E60" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>28</v>
@@ -3051,7 +3051,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="10">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>31</v>
@@ -3074,7 +3074,7 @@
         <v>27</v>
       </c>
       <c r="E62" s="10">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>28</v>
@@ -3097,7 +3097,7 @@
         <v>27</v>
       </c>
       <c r="E63" s="10">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>31</v>
@@ -3120,7 +3120,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="10">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>28</v>
@@ -3143,7 +3143,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="10">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>34</v>
@@ -3166,7 +3166,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="10">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>28</v>
@@ -3189,7 +3189,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="10">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>31</v>
@@ -3212,7 +3212,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="10">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>28</v>
@@ -3235,7 +3235,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="10">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>34</v>
@@ -3258,7 +3258,7 @@
         <v>27</v>
       </c>
       <c r="E70" s="10">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>28</v>
@@ -3281,7 +3281,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="10">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>31</v>
@@ -3304,7 +3304,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="10">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>28</v>
@@ -3327,7 +3327,7 @@
         <v>27</v>
       </c>
       <c r="E73" s="10">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>34</v>
@@ -3350,7 +3350,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="10">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>28</v>
@@ -3373,7 +3373,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="10">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>31</v>
@@ -3396,7 +3396,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="10">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>28</v>
@@ -3419,7 +3419,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="10">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>34</v>
@@ -3442,7 +3442,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="10">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>28</v>
@@ -3465,7 +3465,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="10">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>31</v>
@@ -3488,7 +3488,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="10">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>28</v>
@@ -3511,7 +3511,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="10">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>34</v>
@@ -3534,7 +3534,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="10">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>28</v>
@@ -3557,7 +3557,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>31</v>
@@ -3580,7 +3580,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="10">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>28</v>
@@ -3603,7 +3603,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="10">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>34</v>
@@ -3626,7 +3626,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="10">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>28</v>
@@ -3649,7 +3649,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="10">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>31</v>
@@ -3672,7 +3672,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="10">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>28</v>
@@ -3695,7 +3695,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="10">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>34</v>
@@ -3718,7 +3718,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>28</v>
@@ -3764,7 +3764,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="10">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>28</v>
@@ -3787,7 +3787,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="10">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>31</v>
@@ -3810,7 +3810,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="10">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>28</v>
@@ -3833,7 +3833,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="10">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>34</v>
@@ -3856,7 +3856,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="10">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F96" s="8" t="s">
         <v>28</v>
@@ -3879,7 +3879,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="10">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>31</v>
@@ -3902,7 +3902,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="10">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>28</v>
@@ -3925,7 +3925,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="10">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>34</v>
@@ -3948,7 +3948,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="10">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>28</v>
@@ -3971,7 +3971,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="10">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>31</v>
@@ -3994,7 +3994,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="10">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>28</v>
@@ -4017,7 +4017,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="10">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>34</v>
@@ -4040,7 +4040,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="10">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>28</v>
@@ -4063,7 +4063,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>31</v>
@@ -4086,7 +4086,7 @@
         <v>27</v>
       </c>
       <c r="E106" s="10">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>28</v>
@@ -4109,7 +4109,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="10">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>34</v>
@@ -4132,7 +4132,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="10">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>28</v>
@@ -4155,7 +4155,7 @@
         <v>27</v>
       </c>
       <c r="E109" s="10">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>31</v>
@@ -4178,7 +4178,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="10">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>28</v>
@@ -4201,7 +4201,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="10">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>34</v>
@@ -4224,7 +4224,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="10">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>28</v>
@@ -4247,7 +4247,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="10">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F113" s="8" t="s">
         <v>31</v>
@@ -4270,7 +4270,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="10">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>28</v>
@@ -4293,7 +4293,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="10">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>34</v>
@@ -4316,7 +4316,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="10">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>28</v>
@@ -4339,7 +4339,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F117" s="8" t="s">
         <v>31</v>
@@ -4385,7 +4385,7 @@
         <v>27</v>
       </c>
       <c r="E119" s="10">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F119" s="8" t="s">
         <v>34</v>
@@ -4408,7 +4408,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="10">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F120" s="8" t="s">
         <v>28</v>
@@ -4431,7 +4431,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="10">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F121" s="8" t="s">
         <v>31</v>
@@ -4454,7 +4454,7 @@
         <v>27</v>
       </c>
       <c r="E122" s="10">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F122" s="8" t="s">
         <v>28</v>
@@ -4477,7 +4477,7 @@
         <v>27</v>
       </c>
       <c r="E123" s="10">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>31</v>
@@ -4500,7 +4500,7 @@
         <v>27</v>
       </c>
       <c r="E124" s="10">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F124" s="8" t="s">
         <v>28</v>
@@ -4523,7 +4523,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="10">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>34</v>
@@ -4546,7 +4546,7 @@
         <v>27</v>
       </c>
       <c r="E126" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F126" s="8" t="s">
         <v>28</v>
@@ -4569,7 +4569,7 @@
         <v>27</v>
       </c>
       <c r="E127" s="10">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F127" s="8" t="s">
         <v>31</v>
@@ -4592,7 +4592,7 @@
         <v>27</v>
       </c>
       <c r="E128" s="10">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F128" s="8" t="s">
         <v>28</v>
@@ -4615,7 +4615,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="10">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F129" s="8" t="s">
         <v>34</v>
@@ -4638,7 +4638,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="10">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F130" s="8" t="s">
         <v>28</v>
@@ -4661,7 +4661,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="10">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F131" s="8" t="s">
         <v>31</v>
@@ -4684,7 +4684,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="10">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F132" s="8" t="s">
         <v>28</v>
@@ -4707,7 +4707,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="10">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F133" s="8" t="s">
         <v>34</v>
@@ -4730,7 +4730,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="10">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F134" s="8" t="s">
         <v>28</v>
@@ -4753,7 +4753,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="10">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F135" s="8" t="s">
         <v>31</v>
@@ -4776,7 +4776,7 @@
         <v>27</v>
       </c>
       <c r="E136" s="10">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F136" s="8" t="s">
         <v>28</v>
@@ -4822,7 +4822,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="10">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F138" s="8" t="s">
         <v>28</v>
@@ -4845,7 +4845,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="10">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F139" s="8" t="s">
         <v>31</v>
@@ -4868,7 +4868,7 @@
         <v>27</v>
       </c>
       <c r="E140" s="10">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F140" s="8" t="s">
         <v>28</v>
@@ -4891,7 +4891,7 @@
         <v>27</v>
       </c>
       <c r="E141" s="10">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F141" s="8" t="s">
         <v>34</v>
@@ -4914,7 +4914,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="10">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F142" s="8" t="s">
         <v>28</v>
@@ -4937,7 +4937,7 @@
         <v>27</v>
       </c>
       <c r="E143" s="10">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F143" s="8" t="s">
         <v>31</v>
@@ -4960,7 +4960,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F144" s="8" t="s">
         <v>28</v>
@@ -4983,7 +4983,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="10">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F145" s="8" t="s">
         <v>34</v>
@@ -5006,7 +5006,7 @@
         <v>27</v>
       </c>
       <c r="E146" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>28</v>
@@ -5029,7 +5029,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="10">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F147" s="8" t="s">
         <v>31</v>
@@ -5052,7 +5052,7 @@
         <v>27</v>
       </c>
       <c r="E148" s="10">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F148" s="8" t="s">
         <v>28</v>
@@ -5075,7 +5075,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="10">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F149" s="8" t="s">
         <v>34</v>
@@ -5098,7 +5098,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="10">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>28</v>
@@ -5121,7 +5121,7 @@
         <v>27</v>
       </c>
       <c r="E151" s="10">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>31</v>
@@ -5144,7 +5144,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="10">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>28</v>
@@ -5167,7 +5167,7 @@
         <v>27</v>
       </c>
       <c r="E153" s="10">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F153" s="8" t="s">
         <v>31</v>
@@ -5190,7 +5190,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>28</v>
@@ -5213,7 +5213,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="10">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F155" s="8" t="s">
         <v>34</v>
@@ -5236,7 +5236,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F156" s="8" t="s">
         <v>28</v>
@@ -5259,7 +5259,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="10">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F157" s="8" t="s">
         <v>31</v>
@@ -5282,7 +5282,7 @@
         <v>27</v>
       </c>
       <c r="E158" s="10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F158" s="8" t="s">
         <v>28</v>
@@ -5305,7 +5305,7 @@
         <v>27</v>
       </c>
       <c r="E159" s="10">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F159" s="8" t="s">
         <v>34</v>
@@ -5328,7 +5328,7 @@
         <v>27</v>
       </c>
       <c r="E160" s="10">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F160" s="8" t="s">
         <v>28</v>
@@ -5351,7 +5351,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="10">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F161" s="8" t="s">
         <v>31</v>
@@ -5374,7 +5374,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F162" s="8" t="s">
         <v>28</v>
@@ -5397,7 +5397,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F163" s="8" t="s">
         <v>34</v>
@@ -5420,7 +5420,7 @@
         <v>27</v>
       </c>
       <c r="E164" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F164" s="8" t="s">
         <v>28</v>
@@ -5466,7 +5466,7 @@
         <v>27</v>
       </c>
       <c r="E166" s="10">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F166" s="8" t="s">
         <v>28</v>
@@ -5489,7 +5489,7 @@
         <v>27</v>
       </c>
       <c r="E167" s="10">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F167" s="8" t="s">
         <v>34</v>
@@ -5512,7 +5512,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="10">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F168" s="8" t="s">
         <v>28</v>
@@ -5535,7 +5535,7 @@
         <v>27</v>
       </c>
       <c r="E169" s="10">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F169" s="8" t="s">
         <v>31</v>
@@ -5558,7 +5558,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="10">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F170" s="8" t="s">
         <v>28</v>
@@ -5581,7 +5581,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F171" s="8" t="s">
         <v>34</v>
@@ -5604,7 +5604,7 @@
         <v>27</v>
       </c>
       <c r="E172" s="10">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F172" s="8" t="s">
         <v>28</v>
@@ -5627,7 +5627,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="10">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F173" s="8" t="s">
         <v>31</v>
@@ -5650,7 +5650,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="10">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F174" s="8" t="s">
         <v>28</v>
@@ -5673,7 +5673,7 @@
         <v>27</v>
       </c>
       <c r="E175" s="10">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F175" s="8" t="s">
         <v>34</v>
@@ -5696,7 +5696,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="10">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F176" s="8" t="s">
         <v>28</v>
@@ -5719,7 +5719,7 @@
         <v>27</v>
       </c>
       <c r="E177" s="10">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F177" s="8" t="s">
         <v>28</v>
@@ -5742,7 +5742,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="10">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F178" s="8" t="s">
         <v>31</v>
@@ -5765,7 +5765,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="10">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F179" s="8" t="s">
         <v>28</v>
@@ -5788,7 +5788,7 @@
         <v>27</v>
       </c>
       <c r="E180" s="10">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F180" s="8" t="s">
         <v>34</v>
@@ -5811,7 +5811,7 @@
         <v>27</v>
       </c>
       <c r="E181" s="10">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F181" s="8" t="s">
         <v>28</v>
@@ -5834,7 +5834,7 @@
         <v>27</v>
       </c>
       <c r="E182" s="10">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F182" s="8" t="s">
         <v>31</v>
@@ -5857,7 +5857,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F183" s="8" t="s">
         <v>28</v>
@@ -5880,7 +5880,7 @@
         <v>27</v>
       </c>
       <c r="E184" s="10">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F184" s="8" t="s">
         <v>34</v>
@@ -5903,7 +5903,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="10">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F185" s="8" t="s">
         <v>28</v>
@@ -5926,7 +5926,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="10">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F186" s="8" t="s">
         <v>31</v>
@@ -5949,7 +5949,7 @@
         <v>27</v>
       </c>
       <c r="E187" s="10">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F187" s="8" t="s">
         <v>28</v>
@@ -5972,7 +5972,7 @@
         <v>27</v>
       </c>
       <c r="E188" s="10">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F188" s="8" t="s">
         <v>34</v>
@@ -5995,7 +5995,7 @@
         <v>27</v>
       </c>
       <c r="E189" s="10">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F189" s="8" t="s">
         <v>28</v>
@@ -6018,7 +6018,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="10">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F190" s="8" t="s">
         <v>31</v>
@@ -6041,7 +6041,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="10">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F191" s="8" t="s">
         <v>28</v>
@@ -6064,7 +6064,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="10">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F192" s="8" t="s">
         <v>34</v>
@@ -6087,7 +6087,7 @@
         <v>27</v>
       </c>
       <c r="E193" s="10">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F193" s="8" t="s">
         <v>28</v>
@@ -6110,7 +6110,7 @@
         <v>27</v>
       </c>
       <c r="E194" s="10">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F194" s="8" t="s">
         <v>31</v>
@@ -6133,7 +6133,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="10">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F195" s="8" t="s">
         <v>28</v>
@@ -6156,7 +6156,7 @@
         <v>27</v>
       </c>
       <c r="E196" s="10">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F196" s="8" t="s">
         <v>34</v>
@@ -6179,7 +6179,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="10">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F197" s="8" t="s">
         <v>28</v>
@@ -6202,7 +6202,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="10">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F198" s="8" t="s">
         <v>31</v>
@@ -6225,7 +6225,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="10">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F199" s="8" t="s">
         <v>28</v>
@@ -6248,7 +6248,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="10">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F200" s="8" t="s">
         <v>34</v>
@@ -6271,7 +6271,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="10">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F201" s="8" t="s">
         <v>28</v>
@@ -6294,7 +6294,7 @@
         <v>27</v>
       </c>
       <c r="E202" s="10">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F202" s="8" t="s">
         <v>28</v>
@@ -6317,7 +6317,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="10">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F203" s="8" t="s">
         <v>31</v>
@@ -6340,7 +6340,7 @@
         <v>27</v>
       </c>
       <c r="E204" s="10">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F204" s="8" t="s">
         <v>28</v>
@@ -6363,7 +6363,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="10">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F205" s="8" t="s">
         <v>34</v>
@@ -6386,7 +6386,7 @@
         <v>27</v>
       </c>
       <c r="E206" s="10">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F206" s="8" t="s">
         <v>28</v>
@@ -6432,7 +6432,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="10">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F208" s="8" t="s">
         <v>28</v>
@@ -6455,7 +6455,7 @@
         <v>27</v>
       </c>
       <c r="E209" s="10">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F209" s="8" t="s">
         <v>34</v>
@@ -6478,7 +6478,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="10">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F210" s="8" t="s">
         <v>28</v>
@@ -6501,7 +6501,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="10">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F211" s="8" t="s">
         <v>31</v>
@@ -6524,7 +6524,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="10">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F212" s="8" t="s">
         <v>28</v>
@@ -6547,7 +6547,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F213" s="8" t="s">
         <v>34</v>
@@ -6570,7 +6570,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F214" s="8" t="s">
         <v>28</v>
@@ -6593,7 +6593,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="10">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F215" s="8" t="s">
         <v>31</v>
@@ -6616,7 +6616,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="10">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F216" s="8" t="s">
         <v>28</v>
@@ -6639,7 +6639,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="10">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F217" s="8" t="s">
         <v>34</v>
@@ -6662,7 +6662,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="10">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F218" s="8" t="s">
         <v>28</v>
@@ -6685,7 +6685,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="10">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F219" s="8" t="s">
         <v>31</v>
@@ -6708,7 +6708,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F220" s="8" t="s">
         <v>28</v>
@@ -6731,7 +6731,7 @@
         <v>27</v>
       </c>
       <c r="E221" s="10">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F221" s="8" t="s">
         <v>34</v>
@@ -6754,7 +6754,7 @@
         <v>27</v>
       </c>
       <c r="E222" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F222" s="8" t="s">
         <v>28</v>
@@ -6777,7 +6777,7 @@
         <v>27</v>
       </c>
       <c r="E223" s="10">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F223" s="8" t="s">
         <v>31</v>
@@ -6800,7 +6800,7 @@
         <v>27</v>
       </c>
       <c r="E224" s="10">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F224" s="8" t="s">
         <v>28</v>
@@ -6823,7 +6823,7 @@
         <v>27</v>
       </c>
       <c r="E225" s="10">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F225" s="8" t="s">
         <v>34</v>
@@ -6846,7 +6846,7 @@
         <v>27</v>
       </c>
       <c r="E226" s="10">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F226" s="8" t="s">
         <v>28</v>
@@ -6869,7 +6869,7 @@
         <v>27</v>
       </c>
       <c r="E227" s="10">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F227" s="8" t="s">
         <v>28</v>
@@ -6892,7 +6892,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="10">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F228" s="8" t="s">
         <v>31</v>
@@ -6915,7 +6915,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="10">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F229" s="8" t="s">
         <v>28</v>
@@ -6938,7 +6938,7 @@
         <v>27</v>
       </c>
       <c r="E230" s="10">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F230" s="8" t="s">
         <v>34</v>
@@ -6961,7 +6961,7 @@
         <v>27</v>
       </c>
       <c r="E231" s="10">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F231" s="8" t="s">
         <v>28</v>
@@ -6984,7 +6984,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="10">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F232" s="8" t="s">
         <v>31</v>
@@ -7007,7 +7007,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="10">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F233" s="8" t="s">
         <v>28</v>
@@ -7030,7 +7030,7 @@
         <v>27</v>
       </c>
       <c r="E234" s="10">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F234" s="8" t="s">
         <v>34</v>
@@ -7053,7 +7053,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="10">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F235" s="8" t="s">
         <v>28</v>
@@ -7076,7 +7076,7 @@
         <v>27</v>
       </c>
       <c r="E236" s="10">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F236" s="8" t="s">
         <v>31</v>
@@ -7099,7 +7099,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="10">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F237" s="8" t="s">
         <v>28</v>
@@ -7122,7 +7122,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="10">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F238" s="8" t="s">
         <v>34</v>
@@ -7145,7 +7145,7 @@
         <v>27</v>
       </c>
       <c r="E239" s="10">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F239" s="8" t="s">
         <v>28</v>
@@ -7168,7 +7168,7 @@
         <v>27</v>
       </c>
       <c r="E240" s="10">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F240" s="8" t="s">
         <v>31</v>
@@ -7191,7 +7191,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="10">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F241" s="8" t="s">
         <v>28</v>
@@ -7214,7 +7214,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="10">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F242" s="8" t="s">
         <v>34</v>
@@ -7237,7 +7237,7 @@
         <v>27</v>
       </c>
       <c r="E243" s="10">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F243" s="8" t="s">
         <v>28</v>
@@ -7260,7 +7260,7 @@
         <v>27</v>
       </c>
       <c r="E244" s="10">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F244" s="8" t="s">
         <v>31</v>
@@ -7283,7 +7283,7 @@
         <v>27</v>
       </c>
       <c r="E245" s="10">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F245" s="8" t="s">
         <v>28</v>
@@ -7306,7 +7306,7 @@
         <v>27</v>
       </c>
       <c r="E246" s="10">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F246" s="8" t="s">
         <v>34</v>
@@ -7329,7 +7329,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="10">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F247" s="8" t="s">
         <v>28</v>
@@ -7352,7 +7352,7 @@
         <v>27</v>
       </c>
       <c r="E248" s="10">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F248" s="8" t="s">
         <v>31</v>
@@ -7375,7 +7375,7 @@
         <v>27</v>
       </c>
       <c r="E249" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F249" s="8" t="s">
         <v>28</v>
@@ -7398,7 +7398,7 @@
         <v>27</v>
       </c>
       <c r="E250" s="10">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F250" s="8" t="s">
         <v>34</v>
@@ -7421,7 +7421,7 @@
         <v>27</v>
       </c>
       <c r="E251" s="10">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F251" s="8" t="s">
         <v>28</v>
@@ -7444,7 +7444,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="10">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F252" s="8" t="s">
         <v>28</v>
@@ -7467,7 +7467,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="10">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F253" s="8" t="s">
         <v>31</v>
@@ -7490,7 +7490,7 @@
         <v>27</v>
       </c>
       <c r="E254" s="10">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F254" s="8" t="s">
         <v>28</v>
@@ -7513,7 +7513,7 @@
         <v>27</v>
       </c>
       <c r="E255" s="10">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F255" s="8" t="s">
         <v>34</v>
@@ -7536,7 +7536,7 @@
         <v>27</v>
       </c>
       <c r="E256" s="10">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F256" s="8" t="s">
         <v>28</v>
@@ -7559,7 +7559,7 @@
         <v>27</v>
       </c>
       <c r="E257" s="10">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F257" s="8" t="s">
         <v>31</v>
@@ -7582,7 +7582,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="10">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F258" s="8" t="s">
         <v>28</v>
@@ -7605,7 +7605,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="10">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F259" s="8" t="s">
         <v>34</v>
@@ -7628,7 +7628,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="10">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F260" s="8" t="s">
         <v>28</v>
@@ -7651,7 +7651,7 @@
         <v>27</v>
       </c>
       <c r="E261" s="10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F261" s="8" t="s">
         <v>31</v>
@@ -7674,7 +7674,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F262" s="8" t="s">
         <v>28</v>
@@ -7697,7 +7697,7 @@
         <v>27</v>
       </c>
       <c r="E263" s="10">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F263" s="8" t="s">
         <v>34</v>
@@ -7720,7 +7720,7 @@
         <v>27</v>
       </c>
       <c r="E264" s="10">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F264" s="8" t="s">
         <v>28</v>
@@ -7743,7 +7743,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="10">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F265" s="8" t="s">
         <v>31</v>
@@ -7766,7 +7766,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="10">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F266" s="8" t="s">
         <v>28</v>
@@ -7789,7 +7789,7 @@
         <v>27</v>
       </c>
       <c r="E267" s="10">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F267" s="8" t="s">
         <v>34</v>
@@ -7812,7 +7812,7 @@
         <v>27</v>
       </c>
       <c r="E268" s="10">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F268" s="8" t="s">
         <v>28</v>
@@ -7835,7 +7835,7 @@
         <v>27</v>
       </c>
       <c r="E269" s="10">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F269" s="8" t="s">
         <v>31</v>
@@ -7858,7 +7858,7 @@
         <v>27</v>
       </c>
       <c r="E270" s="10">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F270" s="8" t="s">
         <v>28</v>
@@ -7881,7 +7881,7 @@
         <v>27</v>
       </c>
       <c r="E271" s="10">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F271" s="8" t="s">
         <v>34</v>
@@ -7904,7 +7904,7 @@
         <v>27</v>
       </c>
       <c r="E272" s="10">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F272" s="8" t="s">
         <v>28</v>
@@ -7927,7 +7927,7 @@
         <v>27</v>
       </c>
       <c r="E273" s="10">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F273" s="8" t="s">
         <v>31</v>
@@ -7950,7 +7950,7 @@
         <v>27</v>
       </c>
       <c r="E274" s="10">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F274" s="8" t="s">
         <v>28</v>
@@ -7973,7 +7973,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="10">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F275" s="8" t="s">
         <v>34</v>
@@ -7996,7 +7996,7 @@
         <v>27</v>
       </c>
       <c r="E276" s="10">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F276" s="8" t="s">
         <v>28</v>
@@ -8042,7 +8042,7 @@
         <v>27</v>
       </c>
       <c r="E278" s="10">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F278" s="8" t="s">
         <v>31</v>
@@ -8065,7 +8065,7 @@
         <v>27</v>
       </c>
       <c r="E279" s="10">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F279" s="8" t="s">
         <v>28</v>
@@ -8088,7 +8088,7 @@
         <v>27</v>
       </c>
       <c r="E280" s="10">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F280" s="8" t="s">
         <v>34</v>
@@ -8111,7 +8111,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="10">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F281" s="8" t="s">
         <v>28</v>
@@ -8134,7 +8134,7 @@
         <v>27</v>
       </c>
       <c r="E282" s="10">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F282" s="8" t="s">
         <v>31</v>
@@ -8157,7 +8157,7 @@
         <v>27</v>
       </c>
       <c r="E283" s="10">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F283" s="8" t="s">
         <v>28</v>
@@ -8180,7 +8180,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="10">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F284" s="8" t="s">
         <v>34</v>
@@ -8203,7 +8203,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="10">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F285" s="8" t="s">
         <v>28</v>
@@ -8226,7 +8226,7 @@
         <v>27</v>
       </c>
       <c r="E286" s="10">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F286" s="8" t="s">
         <v>31</v>
@@ -8249,7 +8249,7 @@
         <v>27</v>
       </c>
       <c r="E287" s="10">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F287" s="8" t="s">
         <v>28</v>
@@ -8272,7 +8272,7 @@
         <v>27</v>
       </c>
       <c r="E288" s="10">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F288" s="8" t="s">
         <v>34</v>
@@ -8295,7 +8295,7 @@
         <v>27</v>
       </c>
       <c r="E289" s="10">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F289" s="8" t="s">
         <v>28</v>
@@ -8318,7 +8318,7 @@
         <v>27</v>
       </c>
       <c r="E290" s="10">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F290" s="8" t="s">
         <v>31</v>
@@ -8341,7 +8341,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="10">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F291" s="8" t="s">
         <v>28</v>
@@ -8364,7 +8364,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="10">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F292" s="8" t="s">
         <v>34</v>
@@ -8387,7 +8387,7 @@
         <v>27</v>
       </c>
       <c r="E293" s="10">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F293" s="8" t="s">
         <v>28</v>
@@ -8410,7 +8410,7 @@
         <v>27</v>
       </c>
       <c r="E294" s="10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F294" s="8" t="s">
         <v>31</v>
@@ -8433,7 +8433,7 @@
         <v>27</v>
       </c>
       <c r="E295" s="10">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F295" s="8" t="s">
         <v>28</v>
@@ -8456,7 +8456,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="10">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F296" s="8" t="s">
         <v>34</v>
@@ -8479,7 +8479,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="10">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F297" s="8" t="s">
         <v>28</v>
@@ -8502,7 +8502,7 @@
         <v>27</v>
       </c>
       <c r="E298" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F298" s="8" t="s">
         <v>31</v>
@@ -8525,7 +8525,7 @@
         <v>27</v>
       </c>
       <c r="E299" s="10">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F299" s="8" t="s">
         <v>28</v>
@@ -8548,7 +8548,7 @@
         <v>27</v>
       </c>
       <c r="E300" s="10">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F300" s="8" t="s">
         <v>34</v>
@@ -8571,7 +8571,7 @@
         <v>27</v>
       </c>
       <c r="E301" s="10">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F301" s="8" t="s">
         <v>28</v>
@@ -8636,7 +8636,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -8659,7 +8659,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
         <v>31</v>
@@ -8682,7 +8682,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -8705,7 +8705,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
         <v>34</v>
@@ -8728,7 +8728,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -8751,7 +8751,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
         <v>31</v>
@@ -8774,7 +8774,7 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -8797,7 +8797,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
@@ -8820,7 +8820,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -8843,7 +8843,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
         <v>31</v>
@@ -8866,7 +8866,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -8889,7 +8889,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
         <v>34</v>
@@ -8912,7 +8912,7 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -8935,7 +8935,7 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F15" t="s">
         <v>31</v>
@@ -8958,7 +8958,7 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -8981,7 +8981,7 @@
         <v>27</v>
       </c>
       <c r="E17">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F17" t="s">
         <v>34</v>
@@ -9004,7 +9004,7 @@
         <v>27</v>
       </c>
       <c r="E18">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -9027,7 +9027,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F19" t="s">
         <v>31</v>
@@ -9050,7 +9050,7 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -9073,7 +9073,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F21" t="s">
         <v>34</v>
@@ -9096,7 +9096,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -9119,7 +9119,7 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F23" t="s">
         <v>31</v>
@@ -9142,7 +9142,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -9165,7 +9165,7 @@
         <v>27</v>
       </c>
       <c r="E25">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F25" t="s">
         <v>34</v>
@@ -9188,7 +9188,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -9257,7 +9257,7 @@
         <v>27</v>
       </c>
       <c r="E29">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F29" t="s">
         <v>34</v>
@@ -9280,7 +9280,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -9303,7 +9303,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F31" t="s">
         <v>31</v>
@@ -9326,7 +9326,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -9349,7 +9349,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F33" t="s">
         <v>31</v>
@@ -9372,7 +9372,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -9395,7 +9395,7 @@
         <v>27</v>
       </c>
       <c r="E35">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
@@ -9418,7 +9418,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -9441,7 +9441,7 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F37" t="s">
         <v>31</v>
@@ -9464,7 +9464,7 @@
         <v>27</v>
       </c>
       <c r="E38">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -9487,7 +9487,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F39" t="s">
         <v>34</v>
@@ -9510,7 +9510,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -9533,7 +9533,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F41" t="s">
         <v>31</v>
@@ -9556,7 +9556,7 @@
         <v>27</v>
       </c>
       <c r="E42">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -9579,7 +9579,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F43" t="s">
         <v>34</v>
@@ -9602,7 +9602,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -9625,7 +9625,7 @@
         <v>27</v>
       </c>
       <c r="E45">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F45" t="s">
         <v>31</v>
@@ -9648,7 +9648,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -9671,7 +9671,7 @@
         <v>27</v>
       </c>
       <c r="E47">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F47" t="s">
         <v>34</v>
@@ -9694,7 +9694,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -9717,7 +9717,7 @@
         <v>27</v>
       </c>
       <c r="E49">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F49" t="s">
         <v>31</v>
@@ -9740,7 +9740,7 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F50" t="s">
         <v>28</v>
@@ -9763,7 +9763,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F51" t="s">
         <v>34</v>
@@ -9786,7 +9786,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -9809,7 +9809,7 @@
         <v>27</v>
       </c>
       <c r="E53">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F53" t="s">
         <v>31</v>
@@ -9832,7 +9832,7 @@
         <v>27</v>
       </c>
       <c r="E54">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -9855,7 +9855,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F55" t="s">
         <v>34</v>
@@ -9878,7 +9878,7 @@
         <v>27</v>
       </c>
       <c r="E56">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -9901,7 +9901,7 @@
         <v>27</v>
       </c>
       <c r="E57">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F57" t="s">
         <v>31</v>
@@ -9924,7 +9924,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -9947,7 +9947,7 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F59" t="s">
         <v>34</v>
@@ -9970,7 +9970,7 @@
         <v>27</v>
       </c>
       <c r="E60">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -9993,7 +9993,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F61" t="s">
         <v>31</v>
@@ -10016,7 +10016,7 @@
         <v>27</v>
       </c>
       <c r="E62">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F62" t="s">
         <v>28</v>
@@ -10039,7 +10039,7 @@
         <v>27</v>
       </c>
       <c r="E63">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F63" t="s">
         <v>31</v>
@@ -10062,7 +10062,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -10085,7 +10085,7 @@
         <v>27</v>
       </c>
       <c r="E65">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F65" t="s">
         <v>34</v>
@@ -10108,7 +10108,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -10131,7 +10131,7 @@
         <v>27</v>
       </c>
       <c r="E67">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F67" t="s">
         <v>31</v>
@@ -10154,7 +10154,7 @@
         <v>27</v>
       </c>
       <c r="E68">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
@@ -10177,7 +10177,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F69" t="s">
         <v>34</v>
@@ -10200,7 +10200,7 @@
         <v>27</v>
       </c>
       <c r="E70">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -10223,7 +10223,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F71" t="s">
         <v>31</v>
@@ -10246,7 +10246,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -10269,7 +10269,7 @@
         <v>27</v>
       </c>
       <c r="E73">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F73" t="s">
         <v>34</v>
@@ -10292,7 +10292,7 @@
         <v>27</v>
       </c>
       <c r="E74">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -10315,7 +10315,7 @@
         <v>27</v>
       </c>
       <c r="E75">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F75" t="s">
         <v>31</v>
@@ -10338,7 +10338,7 @@
         <v>27</v>
       </c>
       <c r="E76">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
@@ -10361,7 +10361,7 @@
         <v>27</v>
       </c>
       <c r="E77">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F77" t="s">
         <v>34</v>
@@ -10384,7 +10384,7 @@
         <v>27</v>
       </c>
       <c r="E78">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
@@ -10407,7 +10407,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F79" t="s">
         <v>31</v>
@@ -10430,7 +10430,7 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
@@ -10453,7 +10453,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F81" t="s">
         <v>34</v>
@@ -10476,7 +10476,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -10499,7 +10499,7 @@
         <v>27</v>
       </c>
       <c r="E83">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F83" t="s">
         <v>31</v>
@@ -10522,7 +10522,7 @@
         <v>27</v>
       </c>
       <c r="E84">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
@@ -10545,7 +10545,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F85" t="s">
         <v>34</v>
@@ -10568,7 +10568,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -10591,7 +10591,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F87" t="s">
         <v>31</v>
@@ -10614,7 +10614,7 @@
         <v>27</v>
       </c>
       <c r="E88">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -10637,7 +10637,7 @@
         <v>27</v>
       </c>
       <c r="E89">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F89" t="s">
         <v>34</v>
@@ -10660,7 +10660,7 @@
         <v>27</v>
       </c>
       <c r="E90">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F90" t="s">
         <v>28</v>
@@ -10706,7 +10706,7 @@
         <v>27</v>
       </c>
       <c r="E92">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
@@ -10729,7 +10729,7 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F93" t="s">
         <v>31</v>
@@ -10752,7 +10752,7 @@
         <v>27</v>
       </c>
       <c r="E94">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -10775,7 +10775,7 @@
         <v>27</v>
       </c>
       <c r="E95">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F95" t="s">
         <v>34</v>
@@ -10798,7 +10798,7 @@
         <v>27</v>
       </c>
       <c r="E96">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -10821,7 +10821,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F97" t="s">
         <v>31</v>
@@ -10844,7 +10844,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -10867,7 +10867,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F99" t="s">
         <v>34</v>
@@ -10890,7 +10890,7 @@
         <v>27</v>
       </c>
       <c r="E100">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
@@ -10913,7 +10913,7 @@
         <v>27</v>
       </c>
       <c r="E101">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F101" t="s">
         <v>31</v>
@@ -10936,7 +10936,7 @@
         <v>27</v>
       </c>
       <c r="E102">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
@@ -10959,7 +10959,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F103" t="s">
         <v>34</v>
@@ -10982,7 +10982,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -11005,7 +11005,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F105" t="s">
         <v>31</v>
@@ -11028,7 +11028,7 @@
         <v>27</v>
       </c>
       <c r="E106">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
@@ -11051,7 +11051,7 @@
         <v>27</v>
       </c>
       <c r="E107">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F107" t="s">
         <v>34</v>
@@ -11074,7 +11074,7 @@
         <v>27</v>
       </c>
       <c r="E108">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
@@ -11097,7 +11097,7 @@
         <v>27</v>
       </c>
       <c r="E109">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F109" t="s">
         <v>31</v>
@@ -11120,7 +11120,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -11143,7 +11143,7 @@
         <v>27</v>
       </c>
       <c r="E111">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F111" t="s">
         <v>34</v>
@@ -11166,7 +11166,7 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F112" t="s">
         <v>28</v>
@@ -11189,7 +11189,7 @@
         <v>27</v>
       </c>
       <c r="E113">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F113" t="s">
         <v>31</v>
@@ -11212,7 +11212,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -11235,7 +11235,7 @@
         <v>27</v>
       </c>
       <c r="E115">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F115" t="s">
         <v>34</v>
@@ -11258,7 +11258,7 @@
         <v>27</v>
       </c>
       <c r="E116">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F116" t="s">
         <v>28</v>
@@ -11281,7 +11281,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F117" t="s">
         <v>31</v>
@@ -11327,7 +11327,7 @@
         <v>27</v>
       </c>
       <c r="E119">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F119" t="s">
         <v>34</v>
@@ -11350,7 +11350,7 @@
         <v>27</v>
       </c>
       <c r="E120">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
@@ -11373,7 +11373,7 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F121" t="s">
         <v>31</v>
@@ -11396,7 +11396,7 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -11419,7 +11419,7 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F123" t="s">
         <v>31</v>
@@ -11442,7 +11442,7 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F124" t="s">
         <v>28</v>
@@ -11465,7 +11465,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F125" t="s">
         <v>34</v>
@@ -11488,7 +11488,7 @@
         <v>27</v>
       </c>
       <c r="E126">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
@@ -11511,7 +11511,7 @@
         <v>27</v>
       </c>
       <c r="E127">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F127" t="s">
         <v>31</v>
@@ -11534,7 +11534,7 @@
         <v>27</v>
       </c>
       <c r="E128">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -11557,7 +11557,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F129" t="s">
         <v>34</v>
@@ -11580,7 +11580,7 @@
         <v>27</v>
       </c>
       <c r="E130">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
@@ -11603,7 +11603,7 @@
         <v>27</v>
       </c>
       <c r="E131">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F131" t="s">
         <v>31</v>
@@ -11626,7 +11626,7 @@
         <v>27</v>
       </c>
       <c r="E132">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F132" t="s">
         <v>28</v>
@@ -11649,7 +11649,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F133" t="s">
         <v>34</v>
@@ -11672,7 +11672,7 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -11695,7 +11695,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F135" t="s">
         <v>31</v>
@@ -11718,7 +11718,7 @@
         <v>27</v>
       </c>
       <c r="E136">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
@@ -11764,7 +11764,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -11787,7 +11787,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F139" t="s">
         <v>31</v>
@@ -11810,7 +11810,7 @@
         <v>27</v>
       </c>
       <c r="E140">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
@@ -11833,7 +11833,7 @@
         <v>27</v>
       </c>
       <c r="E141">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F141" t="s">
         <v>34</v>
@@ -11856,7 +11856,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -11879,7 +11879,7 @@
         <v>27</v>
       </c>
       <c r="E143">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F143" t="s">
         <v>31</v>
@@ -11902,7 +11902,7 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F144" t="s">
         <v>28</v>
@@ -11925,7 +11925,7 @@
         <v>27</v>
       </c>
       <c r="E145">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F145" t="s">
         <v>34</v>
@@ -11948,7 +11948,7 @@
         <v>27</v>
       </c>
       <c r="E146">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F146" t="s">
         <v>28</v>
@@ -11971,7 +11971,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F147" t="s">
         <v>31</v>
@@ -11994,7 +11994,7 @@
         <v>27</v>
       </c>
       <c r="E148">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
@@ -12017,7 +12017,7 @@
         <v>27</v>
       </c>
       <c r="E149">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F149" t="s">
         <v>34</v>
@@ -12040,7 +12040,7 @@
         <v>27</v>
       </c>
       <c r="E150">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
@@ -12063,7 +12063,7 @@
         <v>27</v>
       </c>
       <c r="E151">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F151" t="s">
         <v>31</v>
@@ -12086,7 +12086,7 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F152" t="s">
         <v>28</v>
@@ -12109,7 +12109,7 @@
         <v>27</v>
       </c>
       <c r="E153">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F153" t="s">
         <v>31</v>
@@ -12132,7 +12132,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -12155,7 +12155,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F155" t="s">
         <v>34</v>
@@ -12178,7 +12178,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -12201,7 +12201,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F157" t="s">
         <v>31</v>
@@ -12224,7 +12224,7 @@
         <v>27</v>
       </c>
       <c r="E158">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F158" t="s">
         <v>28</v>
@@ -12247,7 +12247,7 @@
         <v>27</v>
       </c>
       <c r="E159">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F159" t="s">
         <v>34</v>
@@ -12270,7 +12270,7 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F160" t="s">
         <v>28</v>
@@ -12293,7 +12293,7 @@
         <v>27</v>
       </c>
       <c r="E161">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F161" t="s">
         <v>31</v>
@@ -12316,7 +12316,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -12339,7 +12339,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F163" t="s">
         <v>34</v>
@@ -12362,7 +12362,7 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
@@ -12408,7 +12408,7 @@
         <v>27</v>
       </c>
       <c r="E166">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -12431,7 +12431,7 @@
         <v>27</v>
       </c>
       <c r="E167">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F167" t="s">
         <v>34</v>
@@ -12454,7 +12454,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -12477,7 +12477,7 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F169" t="s">
         <v>31</v>
@@ -12500,7 +12500,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -12523,7 +12523,7 @@
         <v>27</v>
       </c>
       <c r="E171">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F171" t="s">
         <v>34</v>
@@ -12546,7 +12546,7 @@
         <v>27</v>
       </c>
       <c r="E172">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
@@ -12569,7 +12569,7 @@
         <v>27</v>
       </c>
       <c r="E173">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F173" t="s">
         <v>31</v>
@@ -12592,7 +12592,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -12615,7 +12615,7 @@
         <v>27</v>
       </c>
       <c r="E175">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F175" t="s">
         <v>34</v>
@@ -12638,7 +12638,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -12661,7 +12661,7 @@
         <v>27</v>
       </c>
       <c r="E177">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
@@ -12684,7 +12684,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F178" t="s">
         <v>31</v>
@@ -12707,7 +12707,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -12730,7 +12730,7 @@
         <v>27</v>
       </c>
       <c r="E180">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F180" t="s">
         <v>34</v>
@@ -12753,7 +12753,7 @@
         <v>27</v>
       </c>
       <c r="E181">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F181" t="s">
         <v>28</v>
@@ -12776,7 +12776,7 @@
         <v>27</v>
       </c>
       <c r="E182">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F182" t="s">
         <v>31</v>
@@ -12799,7 +12799,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -12822,7 +12822,7 @@
         <v>27</v>
       </c>
       <c r="E184">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F184" t="s">
         <v>34</v>
@@ -12845,7 +12845,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -12868,7 +12868,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F186" t="s">
         <v>31</v>
@@ -12891,7 +12891,7 @@
         <v>27</v>
       </c>
       <c r="E187">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F187" t="s">
         <v>28</v>
@@ -12914,7 +12914,7 @@
         <v>27</v>
       </c>
       <c r="E188">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F188" t="s">
         <v>34</v>
@@ -12937,7 +12937,7 @@
         <v>27</v>
       </c>
       <c r="E189">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F189" t="s">
         <v>28</v>
@@ -12960,7 +12960,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F190" t="s">
         <v>31</v>
@@ -12983,7 +12983,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -13006,7 +13006,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F192" t="s">
         <v>34</v>
@@ -13029,7 +13029,7 @@
         <v>27</v>
       </c>
       <c r="E193">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -13052,7 +13052,7 @@
         <v>27</v>
       </c>
       <c r="E194">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F194" t="s">
         <v>31</v>
@@ -13075,7 +13075,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -13098,7 +13098,7 @@
         <v>27</v>
       </c>
       <c r="E196">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F196" t="s">
         <v>34</v>
@@ -13121,7 +13121,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -13144,7 +13144,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F198" t="s">
         <v>31</v>
@@ -13167,7 +13167,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -13190,7 +13190,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F200" t="s">
         <v>34</v>
@@ -13213,7 +13213,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -13236,7 +13236,7 @@
         <v>27</v>
       </c>
       <c r="E202">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -13259,7 +13259,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F203" t="s">
         <v>31</v>
@@ -13282,7 +13282,7 @@
         <v>27</v>
       </c>
       <c r="E204">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -13305,7 +13305,7 @@
         <v>27</v>
       </c>
       <c r="E205">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F205" t="s">
         <v>34</v>
@@ -13328,7 +13328,7 @@
         <v>27</v>
       </c>
       <c r="E206">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -13374,7 +13374,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -13397,7 +13397,7 @@
         <v>27</v>
       </c>
       <c r="E209">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F209" t="s">
         <v>34</v>
@@ -13420,7 +13420,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -13443,7 +13443,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F211" t="s">
         <v>31</v>
@@ -13466,7 +13466,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -13489,7 +13489,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F213" t="s">
         <v>34</v>
@@ -13512,7 +13512,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -13535,7 +13535,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F215" t="s">
         <v>31</v>
@@ -13558,7 +13558,7 @@
         <v>27</v>
       </c>
       <c r="E216">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F216" t="s">
         <v>28</v>
@@ -13581,7 +13581,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F217" t="s">
         <v>34</v>
@@ -13604,7 +13604,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -13627,7 +13627,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F219" t="s">
         <v>31</v>
@@ -13650,7 +13650,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -13673,7 +13673,7 @@
         <v>27</v>
       </c>
       <c r="E221">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F221" t="s">
         <v>34</v>
@@ -13696,7 +13696,7 @@
         <v>27</v>
       </c>
       <c r="E222">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F222" t="s">
         <v>28</v>
@@ -13719,7 +13719,7 @@
         <v>27</v>
       </c>
       <c r="E223">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F223" t="s">
         <v>31</v>
@@ -13742,7 +13742,7 @@
         <v>27</v>
       </c>
       <c r="E224">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F224" t="s">
         <v>28</v>
@@ -13765,7 +13765,7 @@
         <v>27</v>
       </c>
       <c r="E225">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F225" t="s">
         <v>34</v>
@@ -13788,7 +13788,7 @@
         <v>27</v>
       </c>
       <c r="E226">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F226" t="s">
         <v>28</v>
@@ -13811,7 +13811,7 @@
         <v>27</v>
       </c>
       <c r="E227">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F227" t="s">
         <v>28</v>
@@ -13834,7 +13834,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F228" t="s">
         <v>31</v>
@@ -13857,7 +13857,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -13880,7 +13880,7 @@
         <v>27</v>
       </c>
       <c r="E230">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F230" t="s">
         <v>34</v>
@@ -13903,7 +13903,7 @@
         <v>27</v>
       </c>
       <c r="E231">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F231" t="s">
         <v>28</v>
@@ -13926,7 +13926,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F232" t="s">
         <v>31</v>
@@ -13949,7 +13949,7 @@
         <v>27</v>
       </c>
       <c r="E233">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F233" t="s">
         <v>28</v>
@@ -13972,7 +13972,7 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F234" t="s">
         <v>34</v>
@@ -13995,7 +13995,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -14018,7 +14018,7 @@
         <v>27</v>
       </c>
       <c r="E236">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F236" t="s">
         <v>31</v>
@@ -14041,7 +14041,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -14064,7 +14064,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F238" t="s">
         <v>34</v>
@@ -14087,7 +14087,7 @@
         <v>27</v>
       </c>
       <c r="E239">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F239" t="s">
         <v>28</v>
@@ -14110,7 +14110,7 @@
         <v>27</v>
       </c>
       <c r="E240">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F240" t="s">
         <v>31</v>
@@ -14133,7 +14133,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -14156,7 +14156,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F242" t="s">
         <v>34</v>
@@ -14179,7 +14179,7 @@
         <v>27</v>
       </c>
       <c r="E243">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -14202,7 +14202,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F244" t="s">
         <v>31</v>
@@ -14225,7 +14225,7 @@
         <v>27</v>
       </c>
       <c r="E245">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F245" t="s">
         <v>28</v>
@@ -14248,7 +14248,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F246" t="s">
         <v>34</v>
@@ -14271,7 +14271,7 @@
         <v>27</v>
       </c>
       <c r="E247">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F247" t="s">
         <v>28</v>
@@ -14294,7 +14294,7 @@
         <v>27</v>
       </c>
       <c r="E248">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F248" t="s">
         <v>31</v>
@@ -14317,7 +14317,7 @@
         <v>27</v>
       </c>
       <c r="E249">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F249" t="s">
         <v>28</v>
@@ -14340,7 +14340,7 @@
         <v>27</v>
       </c>
       <c r="E250">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F250" t="s">
         <v>34</v>
@@ -14363,7 +14363,7 @@
         <v>27</v>
       </c>
       <c r="E251">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F251" t="s">
         <v>28</v>
@@ -14386,7 +14386,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -14409,7 +14409,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F253" t="s">
         <v>31</v>
@@ -14432,7 +14432,7 @@
         <v>27</v>
       </c>
       <c r="E254">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F254" t="s">
         <v>28</v>
@@ -14455,7 +14455,7 @@
         <v>27</v>
       </c>
       <c r="E255">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F255" t="s">
         <v>34</v>
@@ -14478,7 +14478,7 @@
         <v>27</v>
       </c>
       <c r="E256">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F256" t="s">
         <v>28</v>
@@ -14501,7 +14501,7 @@
         <v>27</v>
       </c>
       <c r="E257">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F257" t="s">
         <v>31</v>
@@ -14524,7 +14524,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -14547,7 +14547,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F259" t="s">
         <v>34</v>
@@ -14570,7 +14570,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -14593,7 +14593,7 @@
         <v>27</v>
       </c>
       <c r="E261">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F261" t="s">
         <v>31</v>
@@ -14616,7 +14616,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -14639,7 +14639,7 @@
         <v>27</v>
       </c>
       <c r="E263">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F263" t="s">
         <v>34</v>
@@ -14662,7 +14662,7 @@
         <v>27</v>
       </c>
       <c r="E264">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -14685,7 +14685,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F265" t="s">
         <v>31</v>
@@ -14708,7 +14708,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -14731,7 +14731,7 @@
         <v>27</v>
       </c>
       <c r="E267">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F267" t="s">
         <v>34</v>
@@ -14754,7 +14754,7 @@
         <v>27</v>
       </c>
       <c r="E268">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F268" t="s">
         <v>28</v>
@@ -14777,7 +14777,7 @@
         <v>27</v>
       </c>
       <c r="E269">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F269" t="s">
         <v>31</v>
@@ -14800,7 +14800,7 @@
         <v>27</v>
       </c>
       <c r="E270">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F270" t="s">
         <v>28</v>
@@ -14823,7 +14823,7 @@
         <v>27</v>
       </c>
       <c r="E271">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F271" t="s">
         <v>34</v>
@@ -14846,7 +14846,7 @@
         <v>27</v>
       </c>
       <c r="E272">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F272" t="s">
         <v>28</v>
@@ -14869,7 +14869,7 @@
         <v>27</v>
       </c>
       <c r="E273">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F273" t="s">
         <v>31</v>
@@ -14892,7 +14892,7 @@
         <v>27</v>
       </c>
       <c r="E274">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F274" t="s">
         <v>28</v>
@@ -14915,7 +14915,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F275" t="s">
         <v>34</v>
@@ -14938,7 +14938,7 @@
         <v>27</v>
       </c>
       <c r="E276">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F276" t="s">
         <v>28</v>
@@ -14984,7 +14984,7 @@
         <v>27</v>
       </c>
       <c r="E278">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F278" t="s">
         <v>31</v>
@@ -15007,7 +15007,7 @@
         <v>27</v>
       </c>
       <c r="E279">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -15030,7 +15030,7 @@
         <v>27</v>
       </c>
       <c r="E280">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F280" t="s">
         <v>34</v>
@@ -15053,7 +15053,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -15076,7 +15076,7 @@
         <v>27</v>
       </c>
       <c r="E282">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F282" t="s">
         <v>31</v>
@@ -15099,7 +15099,7 @@
         <v>27</v>
       </c>
       <c r="E283">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F283" t="s">
         <v>28</v>
@@ -15122,7 +15122,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F284" t="s">
         <v>34</v>
@@ -15145,7 +15145,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -15168,7 +15168,7 @@
         <v>27</v>
       </c>
       <c r="E286">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F286" t="s">
         <v>31</v>
@@ -15191,7 +15191,7 @@
         <v>27</v>
       </c>
       <c r="E287">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F287" t="s">
         <v>28</v>
@@ -15214,7 +15214,7 @@
         <v>27</v>
       </c>
       <c r="E288">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F288" t="s">
         <v>34</v>
@@ -15237,7 +15237,7 @@
         <v>27</v>
       </c>
       <c r="E289">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F289" t="s">
         <v>28</v>
@@ -15260,7 +15260,7 @@
         <v>27</v>
       </c>
       <c r="E290">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F290" t="s">
         <v>31</v>
@@ -15283,7 +15283,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -15306,7 +15306,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F292" t="s">
         <v>34</v>
@@ -15329,7 +15329,7 @@
         <v>27</v>
       </c>
       <c r="E293">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -15352,7 +15352,7 @@
         <v>27</v>
       </c>
       <c r="E294">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F294" t="s">
         <v>31</v>
@@ -15375,7 +15375,7 @@
         <v>27</v>
       </c>
       <c r="E295">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F295" t="s">
         <v>28</v>
@@ -15398,7 +15398,7 @@
         <v>27</v>
       </c>
       <c r="E296">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F296" t="s">
         <v>34</v>
@@ -15421,7 +15421,7 @@
         <v>27</v>
       </c>
       <c r="E297">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F297" t="s">
         <v>28</v>
@@ -15444,7 +15444,7 @@
         <v>27</v>
       </c>
       <c r="E298">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F298" t="s">
         <v>31</v>
@@ -15467,7 +15467,7 @@
         <v>27</v>
       </c>
       <c r="E299">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F299" t="s">
         <v>28</v>
@@ -15490,7 +15490,7 @@
         <v>27</v>
       </c>
       <c r="E300">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F300" t="s">
         <v>34</v>
@@ -15513,7 +15513,7 @@
         <v>27</v>
       </c>
       <c r="E301">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F301" t="s">
         <v>28</v>

--- a/all-test-reports/vulnerability/vulnerability_test_report.xlsx
+++ b/all-test-reports/vulnerability/vulnerability_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 10:42:39 am</t>
+    <t>28/7/2026, 10:47:42 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1694,7 +1694,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="10">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>28</v>
@@ -1717,7 +1717,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="10">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>31</v>
@@ -1740,7 +1740,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="10">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>28</v>
@@ -1763,7 +1763,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="10">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>34</v>
@@ -1809,7 +1809,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="10">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>31</v>
@@ -1832,7 +1832,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="10">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>28</v>
@@ -1855,7 +1855,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="10">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>34</v>
@@ -1901,7 +1901,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="10">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>31</v>
@@ -1924,7 +1924,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="10">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>28</v>
@@ -1947,7 +1947,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="10">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>34</v>
@@ -1970,7 +1970,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="10">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>28</v>
@@ -1993,7 +1993,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="10">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>31</v>
@@ -2016,7 +2016,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="10">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>28</v>
@@ -2039,7 +2039,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="10">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>34</v>
@@ -2085,7 +2085,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="10">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>31</v>
@@ -2108,7 +2108,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>28</v>
@@ -2131,7 +2131,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="10">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>34</v>
@@ -2154,7 +2154,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="10">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>28</v>
@@ -2177,7 +2177,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="10">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>31</v>
@@ -2200,7 +2200,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="10">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>28</v>
@@ -2223,7 +2223,7 @@
         <v>27</v>
       </c>
       <c r="E25" s="10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>34</v>
@@ -2246,7 +2246,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="10">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>28</v>
@@ -2269,7 +2269,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="10">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>31</v>
@@ -2292,7 +2292,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="10">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>28</v>
@@ -2315,7 +2315,7 @@
         <v>27</v>
       </c>
       <c r="E29" s="10">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>34</v>
@@ -2338,7 +2338,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="10">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>28</v>
@@ -2361,7 +2361,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="10">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>31</v>
@@ -2384,7 +2384,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="10">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>28</v>
@@ -2407,7 +2407,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="10">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>31</v>
@@ -2430,7 +2430,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="10">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>28</v>
@@ -2453,7 +2453,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="10">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>34</v>
@@ -2476,7 +2476,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="10">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>28</v>
@@ -2499,7 +2499,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="10">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>31</v>
@@ -2522,7 +2522,7 @@
         <v>27</v>
       </c>
       <c r="E38" s="10">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>28</v>
@@ -2545,7 +2545,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="10">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>34</v>
@@ -2568,7 +2568,7 @@
         <v>27</v>
       </c>
       <c r="E40" s="10">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>28</v>
@@ -2591,7 +2591,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="10">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>31</v>
@@ -2614,7 +2614,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="10">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>28</v>
@@ -2637,7 +2637,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="10">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>34</v>
@@ -2660,7 +2660,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="10">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>28</v>
@@ -2683,7 +2683,7 @@
         <v>27</v>
       </c>
       <c r="E45" s="10">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>31</v>
@@ -2706,7 +2706,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="10">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>28</v>
@@ -2729,7 +2729,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="10">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>34</v>
@@ -2752,7 +2752,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="10">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>28</v>
@@ -2775,7 +2775,7 @@
         <v>27</v>
       </c>
       <c r="E49" s="10">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>31</v>
@@ -2798,7 +2798,7 @@
         <v>27</v>
       </c>
       <c r="E50" s="10">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>28</v>
@@ -2821,7 +2821,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="10">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>34</v>
@@ -2844,7 +2844,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="10">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>28</v>
@@ -2867,7 +2867,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="10">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>31</v>
@@ -2890,7 +2890,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="10">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>28</v>
@@ -2913,7 +2913,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="10">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>34</v>
@@ -2936,7 +2936,7 @@
         <v>27</v>
       </c>
       <c r="E56" s="10">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>28</v>
@@ -2959,7 +2959,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="10">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>31</v>
@@ -2982,7 +2982,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="10">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>28</v>
@@ -3005,7 +3005,7 @@
         <v>27</v>
       </c>
       <c r="E59" s="10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>34</v>
@@ -3028,7 +3028,7 @@
         <v>27</v>
       </c>
       <c r="E60" s="10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>28</v>
@@ -3051,7 +3051,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>31</v>
@@ -3074,7 +3074,7 @@
         <v>27</v>
       </c>
       <c r="E62" s="10">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>28</v>
@@ -3097,7 +3097,7 @@
         <v>27</v>
       </c>
       <c r="E63" s="10">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>31</v>
@@ -3120,7 +3120,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="10">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>28</v>
@@ -3143,7 +3143,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="10">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>34</v>
@@ -3166,7 +3166,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="10">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>28</v>
@@ -3189,7 +3189,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="10">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>31</v>
@@ -3212,7 +3212,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="10">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>28</v>
@@ -3235,7 +3235,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="10">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>34</v>
@@ -3258,7 +3258,7 @@
         <v>27</v>
       </c>
       <c r="E70" s="10">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>28</v>
@@ -3281,7 +3281,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="10">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>31</v>
@@ -3304,7 +3304,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="10">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>28</v>
@@ -3327,7 +3327,7 @@
         <v>27</v>
       </c>
       <c r="E73" s="10">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>34</v>
@@ -3350,7 +3350,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="10">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>28</v>
@@ -3373,7 +3373,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="10">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>31</v>
@@ -3396,7 +3396,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="10">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>28</v>
@@ -3419,7 +3419,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="10">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>34</v>
@@ -3442,7 +3442,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="10">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>28</v>
@@ -3465,7 +3465,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="10">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>31</v>
@@ -3488,7 +3488,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="10">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>28</v>
@@ -3511,7 +3511,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="10">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>34</v>
@@ -3534,7 +3534,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="10">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>28</v>
@@ -3557,7 +3557,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="10">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>31</v>
@@ -3580,7 +3580,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="10">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>28</v>
@@ -3603,7 +3603,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="10">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>34</v>
@@ -3626,7 +3626,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>28</v>
@@ -3649,7 +3649,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="10">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>31</v>
@@ -3672,7 +3672,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="10">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>28</v>
@@ -3695,7 +3695,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="10">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>34</v>
@@ -3718,7 +3718,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="10">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>28</v>
@@ -3741,7 +3741,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="10">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>31</v>
@@ -3764,7 +3764,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="10">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>28</v>
@@ -3787,7 +3787,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="10">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>31</v>
@@ -3810,7 +3810,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="10">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>28</v>
@@ -3833,7 +3833,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="10">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>34</v>
@@ -3856,7 +3856,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="10">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F96" s="8" t="s">
         <v>28</v>
@@ -3879,7 +3879,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="10">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>31</v>
@@ -3902,7 +3902,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="10">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>28</v>
@@ -3925,7 +3925,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="10">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>34</v>
@@ -3948,7 +3948,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="10">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>28</v>
@@ -3971,7 +3971,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="10">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>31</v>
@@ -3994,7 +3994,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="10">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>28</v>
@@ -4017,7 +4017,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="10">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>34</v>
@@ -4040,7 +4040,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>28</v>
@@ -4063,7 +4063,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="10">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>31</v>
@@ -4086,7 +4086,7 @@
         <v>27</v>
       </c>
       <c r="E106" s="10">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>28</v>
@@ -4109,7 +4109,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="10">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>34</v>
@@ -4132,7 +4132,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="10">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>28</v>
@@ -4155,7 +4155,7 @@
         <v>27</v>
       </c>
       <c r="E109" s="10">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>31</v>
@@ -4178,7 +4178,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="10">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>28</v>
@@ -4201,7 +4201,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="10">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>34</v>
@@ -4224,7 +4224,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="10">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>28</v>
@@ -4270,7 +4270,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="10">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>28</v>
@@ -4293,7 +4293,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="10">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>34</v>
@@ -4316,7 +4316,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="10">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>28</v>
@@ -4339,7 +4339,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="10">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F117" s="8" t="s">
         <v>31</v>
@@ -4362,7 +4362,7 @@
         <v>27</v>
       </c>
       <c r="E118" s="10">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F118" s="8" t="s">
         <v>28</v>
@@ -4408,7 +4408,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="10">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F120" s="8" t="s">
         <v>28</v>
@@ -4431,7 +4431,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="10">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F121" s="8" t="s">
         <v>31</v>
@@ -4454,7 +4454,7 @@
         <v>27</v>
       </c>
       <c r="E122" s="10">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F122" s="8" t="s">
         <v>28</v>
@@ -4477,7 +4477,7 @@
         <v>27</v>
       </c>
       <c r="E123" s="10">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>31</v>
@@ -4523,7 +4523,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="10">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>34</v>
@@ -4546,7 +4546,7 @@
         <v>27</v>
       </c>
       <c r="E126" s="10">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F126" s="8" t="s">
         <v>28</v>
@@ -4569,7 +4569,7 @@
         <v>27</v>
       </c>
       <c r="E127" s="10">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F127" s="8" t="s">
         <v>31</v>
@@ -4592,7 +4592,7 @@
         <v>27</v>
       </c>
       <c r="E128" s="10">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F128" s="8" t="s">
         <v>28</v>
@@ -4615,7 +4615,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="10">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F129" s="8" t="s">
         <v>34</v>
@@ -4638,7 +4638,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="10">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F130" s="8" t="s">
         <v>28</v>
@@ -4661,7 +4661,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="10">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F131" s="8" t="s">
         <v>31</v>
@@ -4684,7 +4684,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="10">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F132" s="8" t="s">
         <v>28</v>
@@ -4707,7 +4707,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F133" s="8" t="s">
         <v>34</v>
@@ -4730,7 +4730,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="10">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F134" s="8" t="s">
         <v>28</v>
@@ -4753,7 +4753,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="10">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F135" s="8" t="s">
         <v>31</v>
@@ -4776,7 +4776,7 @@
         <v>27</v>
       </c>
       <c r="E136" s="10">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F136" s="8" t="s">
         <v>28</v>
@@ -4799,7 +4799,7 @@
         <v>27</v>
       </c>
       <c r="E137" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F137" s="8" t="s">
         <v>34</v>
@@ -4822,7 +4822,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="10">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F138" s="8" t="s">
         <v>28</v>
@@ -4845,7 +4845,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F139" s="8" t="s">
         <v>31</v>
@@ -4891,7 +4891,7 @@
         <v>27</v>
       </c>
       <c r="E141" s="10">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F141" s="8" t="s">
         <v>34</v>
@@ -4914,7 +4914,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="10">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F142" s="8" t="s">
         <v>28</v>
@@ -4937,7 +4937,7 @@
         <v>27</v>
       </c>
       <c r="E143" s="10">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F143" s="8" t="s">
         <v>31</v>
@@ -4960,7 +4960,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="10">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F144" s="8" t="s">
         <v>28</v>
@@ -4983,7 +4983,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="10">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F145" s="8" t="s">
         <v>34</v>
@@ -5006,7 +5006,7 @@
         <v>27</v>
       </c>
       <c r="E146" s="10">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>28</v>
@@ -5029,7 +5029,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="10">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F147" s="8" t="s">
         <v>31</v>
@@ -5052,7 +5052,7 @@
         <v>27</v>
       </c>
       <c r="E148" s="10">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F148" s="8" t="s">
         <v>28</v>
@@ -5075,7 +5075,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="10">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F149" s="8" t="s">
         <v>34</v>
@@ -5098,7 +5098,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="10">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>28</v>
@@ -5121,7 +5121,7 @@
         <v>27</v>
       </c>
       <c r="E151" s="10">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>31</v>
@@ -5144,7 +5144,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>28</v>
@@ -5167,7 +5167,7 @@
         <v>27</v>
       </c>
       <c r="E153" s="10">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F153" s="8" t="s">
         <v>31</v>
@@ -5190,7 +5190,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="10">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>28</v>
@@ -5213,7 +5213,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="10">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F155" s="8" t="s">
         <v>34</v>
@@ -5236,7 +5236,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="10">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F156" s="8" t="s">
         <v>28</v>
@@ -5259,7 +5259,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="10">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F157" s="8" t="s">
         <v>31</v>
@@ -5282,7 +5282,7 @@
         <v>27</v>
       </c>
       <c r="E158" s="10">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F158" s="8" t="s">
         <v>28</v>
@@ -5305,7 +5305,7 @@
         <v>27</v>
       </c>
       <c r="E159" s="10">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F159" s="8" t="s">
         <v>34</v>
@@ -5351,7 +5351,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="10">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F161" s="8" t="s">
         <v>31</v>
@@ -5374,7 +5374,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="10">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F162" s="8" t="s">
         <v>28</v>
@@ -5397,7 +5397,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="10">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F163" s="8" t="s">
         <v>34</v>
@@ -5420,7 +5420,7 @@
         <v>27</v>
       </c>
       <c r="E164" s="10">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F164" s="8" t="s">
         <v>28</v>
@@ -5443,7 +5443,7 @@
         <v>27</v>
       </c>
       <c r="E165" s="10">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F165" s="8" t="s">
         <v>31</v>
@@ -5466,7 +5466,7 @@
         <v>27</v>
       </c>
       <c r="E166" s="10">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F166" s="8" t="s">
         <v>28</v>
@@ -5489,7 +5489,7 @@
         <v>27</v>
       </c>
       <c r="E167" s="10">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F167" s="8" t="s">
         <v>34</v>
@@ -5512,7 +5512,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="10">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F168" s="8" t="s">
         <v>28</v>
@@ -5535,7 +5535,7 @@
         <v>27</v>
       </c>
       <c r="E169" s="10">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F169" s="8" t="s">
         <v>31</v>
@@ -5558,7 +5558,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="10">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F170" s="8" t="s">
         <v>28</v>
@@ -5581,7 +5581,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="10">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F171" s="8" t="s">
         <v>34</v>
@@ -5604,7 +5604,7 @@
         <v>27</v>
       </c>
       <c r="E172" s="10">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F172" s="8" t="s">
         <v>28</v>
@@ -5627,7 +5627,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="10">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F173" s="8" t="s">
         <v>31</v>
@@ -5650,7 +5650,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F174" s="8" t="s">
         <v>28</v>
@@ -5673,7 +5673,7 @@
         <v>27</v>
       </c>
       <c r="E175" s="10">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F175" s="8" t="s">
         <v>34</v>
@@ -5696,7 +5696,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F176" s="8" t="s">
         <v>28</v>
@@ -5719,7 +5719,7 @@
         <v>27</v>
       </c>
       <c r="E177" s="10">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F177" s="8" t="s">
         <v>28</v>
@@ -5742,7 +5742,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="10">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F178" s="8" t="s">
         <v>31</v>
@@ -5765,7 +5765,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="10">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F179" s="8" t="s">
         <v>28</v>
@@ -5788,7 +5788,7 @@
         <v>27</v>
       </c>
       <c r="E180" s="10">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F180" s="8" t="s">
         <v>34</v>
@@ -5811,7 +5811,7 @@
         <v>27</v>
       </c>
       <c r="E181" s="10">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F181" s="8" t="s">
         <v>28</v>
@@ -5834,7 +5834,7 @@
         <v>27</v>
       </c>
       <c r="E182" s="10">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F182" s="8" t="s">
         <v>31</v>
@@ -5857,7 +5857,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="10">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F183" s="8" t="s">
         <v>28</v>
@@ -5880,7 +5880,7 @@
         <v>27</v>
       </c>
       <c r="E184" s="10">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F184" s="8" t="s">
         <v>34</v>
@@ -5903,7 +5903,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F185" s="8" t="s">
         <v>28</v>
@@ -5926,7 +5926,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="10">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F186" s="8" t="s">
         <v>31</v>
@@ -5949,7 +5949,7 @@
         <v>27</v>
       </c>
       <c r="E187" s="10">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F187" s="8" t="s">
         <v>28</v>
@@ -5972,7 +5972,7 @@
         <v>27</v>
       </c>
       <c r="E188" s="10">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F188" s="8" t="s">
         <v>34</v>
@@ -5995,7 +5995,7 @@
         <v>27</v>
       </c>
       <c r="E189" s="10">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F189" s="8" t="s">
         <v>28</v>
@@ -6018,7 +6018,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="10">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F190" s="8" t="s">
         <v>31</v>
@@ -6041,7 +6041,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="10">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F191" s="8" t="s">
         <v>28</v>
@@ -6064,7 +6064,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="10">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F192" s="8" t="s">
         <v>34</v>
@@ -6087,7 +6087,7 @@
         <v>27</v>
       </c>
       <c r="E193" s="10">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F193" s="8" t="s">
         <v>28</v>
@@ -6110,7 +6110,7 @@
         <v>27</v>
       </c>
       <c r="E194" s="10">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F194" s="8" t="s">
         <v>31</v>
@@ -6133,7 +6133,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F195" s="8" t="s">
         <v>28</v>
@@ -6156,7 +6156,7 @@
         <v>27</v>
       </c>
       <c r="E196" s="10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F196" s="8" t="s">
         <v>34</v>
@@ -6179,7 +6179,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F197" s="8" t="s">
         <v>28</v>
@@ -6202,7 +6202,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="10">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F198" s="8" t="s">
         <v>31</v>
@@ -6225,7 +6225,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="10">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F199" s="8" t="s">
         <v>28</v>
@@ -6248,7 +6248,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="10">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F200" s="8" t="s">
         <v>34</v>
@@ -6271,7 +6271,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="10">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F201" s="8" t="s">
         <v>28</v>
@@ -6294,7 +6294,7 @@
         <v>27</v>
       </c>
       <c r="E202" s="10">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F202" s="8" t="s">
         <v>28</v>
@@ -6317,7 +6317,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="10">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F203" s="8" t="s">
         <v>31</v>
@@ -6340,7 +6340,7 @@
         <v>27</v>
       </c>
       <c r="E204" s="10">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F204" s="8" t="s">
         <v>28</v>
@@ -6363,7 +6363,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="10">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F205" s="8" t="s">
         <v>34</v>
@@ -6386,7 +6386,7 @@
         <v>27</v>
       </c>
       <c r="E206" s="10">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F206" s="8" t="s">
         <v>28</v>
@@ -6409,7 +6409,7 @@
         <v>27</v>
       </c>
       <c r="E207" s="10">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F207" s="8" t="s">
         <v>31</v>
@@ -6432,7 +6432,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="10">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F208" s="8" t="s">
         <v>28</v>
@@ -6455,7 +6455,7 @@
         <v>27</v>
       </c>
       <c r="E209" s="10">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F209" s="8" t="s">
         <v>34</v>
@@ -6478,7 +6478,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="10">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F210" s="8" t="s">
         <v>28</v>
@@ -6501,7 +6501,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F211" s="8" t="s">
         <v>31</v>
@@ -6524,7 +6524,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="10">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F212" s="8" t="s">
         <v>28</v>
@@ -6547,7 +6547,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="10">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F213" s="8" t="s">
         <v>34</v>
@@ -6570,7 +6570,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="10">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F214" s="8" t="s">
         <v>28</v>
@@ -6593,7 +6593,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="10">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F215" s="8" t="s">
         <v>31</v>
@@ -6616,7 +6616,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="10">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F216" s="8" t="s">
         <v>28</v>
@@ -6639,7 +6639,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="10">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F217" s="8" t="s">
         <v>34</v>
@@ -6662,7 +6662,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="10">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F218" s="8" t="s">
         <v>28</v>
@@ -6685,7 +6685,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="10">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F219" s="8" t="s">
         <v>31</v>
@@ -6708,7 +6708,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="10">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F220" s="8" t="s">
         <v>28</v>
@@ -6731,7 +6731,7 @@
         <v>27</v>
       </c>
       <c r="E221" s="10">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F221" s="8" t="s">
         <v>34</v>
@@ -6800,7 +6800,7 @@
         <v>27</v>
       </c>
       <c r="E224" s="10">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F224" s="8" t="s">
         <v>28</v>
@@ -6823,7 +6823,7 @@
         <v>27</v>
       </c>
       <c r="E225" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F225" s="8" t="s">
         <v>34</v>
@@ -6846,7 +6846,7 @@
         <v>27</v>
       </c>
       <c r="E226" s="10">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F226" s="8" t="s">
         <v>28</v>
@@ -6869,7 +6869,7 @@
         <v>27</v>
       </c>
       <c r="E227" s="10">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F227" s="8" t="s">
         <v>28</v>
@@ -6892,7 +6892,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="10">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F228" s="8" t="s">
         <v>31</v>
@@ -6915,7 +6915,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="10">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F229" s="8" t="s">
         <v>28</v>
@@ -6938,7 +6938,7 @@
         <v>27</v>
       </c>
       <c r="E230" s="10">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F230" s="8" t="s">
         <v>34</v>
@@ -6961,7 +6961,7 @@
         <v>27</v>
       </c>
       <c r="E231" s="10">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F231" s="8" t="s">
         <v>28</v>
@@ -6984,7 +6984,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F232" s="8" t="s">
         <v>31</v>
@@ -7007,7 +7007,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F233" s="8" t="s">
         <v>28</v>
@@ -7030,7 +7030,7 @@
         <v>27</v>
       </c>
       <c r="E234" s="10">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F234" s="8" t="s">
         <v>34</v>
@@ -7053,7 +7053,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="10">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F235" s="8" t="s">
         <v>28</v>
@@ -7076,7 +7076,7 @@
         <v>27</v>
       </c>
       <c r="E236" s="10">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F236" s="8" t="s">
         <v>31</v>
@@ -7099,7 +7099,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="10">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F237" s="8" t="s">
         <v>28</v>
@@ -7122,7 +7122,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="10">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F238" s="8" t="s">
         <v>34</v>
@@ -7145,7 +7145,7 @@
         <v>27</v>
       </c>
       <c r="E239" s="10">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F239" s="8" t="s">
         <v>28</v>
@@ -7168,7 +7168,7 @@
         <v>27</v>
       </c>
       <c r="E240" s="10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F240" s="8" t="s">
         <v>31</v>
@@ -7191,7 +7191,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="10">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F241" s="8" t="s">
         <v>28</v>
@@ -7214,7 +7214,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="10">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F242" s="8" t="s">
         <v>34</v>
@@ -7237,7 +7237,7 @@
         <v>27</v>
       </c>
       <c r="E243" s="10">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F243" s="8" t="s">
         <v>28</v>
@@ -7260,7 +7260,7 @@
         <v>27</v>
       </c>
       <c r="E244" s="10">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F244" s="8" t="s">
         <v>31</v>
@@ -7283,7 +7283,7 @@
         <v>27</v>
       </c>
       <c r="E245" s="10">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F245" s="8" t="s">
         <v>28</v>
@@ -7306,7 +7306,7 @@
         <v>27</v>
       </c>
       <c r="E246" s="10">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F246" s="8" t="s">
         <v>34</v>
@@ -7329,7 +7329,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="10">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F247" s="8" t="s">
         <v>28</v>
@@ -7352,7 +7352,7 @@
         <v>27</v>
       </c>
       <c r="E248" s="10">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F248" s="8" t="s">
         <v>31</v>
@@ -7375,7 +7375,7 @@
         <v>27</v>
       </c>
       <c r="E249" s="10">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F249" s="8" t="s">
         <v>28</v>
@@ -7398,7 +7398,7 @@
         <v>27</v>
       </c>
       <c r="E250" s="10">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F250" s="8" t="s">
         <v>34</v>
@@ -7421,7 +7421,7 @@
         <v>27</v>
       </c>
       <c r="E251" s="10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F251" s="8" t="s">
         <v>28</v>
@@ -7444,7 +7444,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="10">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F252" s="8" t="s">
         <v>28</v>
@@ -7467,7 +7467,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="10">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F253" s="8" t="s">
         <v>31</v>
@@ -7490,7 +7490,7 @@
         <v>27</v>
       </c>
       <c r="E254" s="10">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F254" s="8" t="s">
         <v>28</v>
@@ -7513,7 +7513,7 @@
         <v>27</v>
       </c>
       <c r="E255" s="10">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F255" s="8" t="s">
         <v>34</v>
@@ -7536,7 +7536,7 @@
         <v>27</v>
       </c>
       <c r="E256" s="10">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F256" s="8" t="s">
         <v>28</v>
@@ -7559,7 +7559,7 @@
         <v>27</v>
       </c>
       <c r="E257" s="10">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F257" s="8" t="s">
         <v>31</v>
@@ -7582,7 +7582,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="10">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F258" s="8" t="s">
         <v>28</v>
@@ -7605,7 +7605,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="10">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F259" s="8" t="s">
         <v>34</v>
@@ -7628,7 +7628,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="10">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F260" s="8" t="s">
         <v>28</v>
@@ -7651,7 +7651,7 @@
         <v>27</v>
       </c>
       <c r="E261" s="10">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F261" s="8" t="s">
         <v>31</v>
@@ -7674,7 +7674,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="10">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F262" s="8" t="s">
         <v>28</v>
@@ -7697,7 +7697,7 @@
         <v>27</v>
       </c>
       <c r="E263" s="10">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F263" s="8" t="s">
         <v>34</v>
@@ -7720,7 +7720,7 @@
         <v>27</v>
       </c>
       <c r="E264" s="10">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F264" s="8" t="s">
         <v>28</v>
@@ -7743,7 +7743,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="10">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F265" s="8" t="s">
         <v>31</v>
@@ -7766,7 +7766,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="10">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F266" s="8" t="s">
         <v>28</v>
@@ -7789,7 +7789,7 @@
         <v>27</v>
       </c>
       <c r="E267" s="10">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F267" s="8" t="s">
         <v>34</v>
@@ -7812,7 +7812,7 @@
         <v>27</v>
       </c>
       <c r="E268" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F268" s="8" t="s">
         <v>28</v>
@@ -7858,7 +7858,7 @@
         <v>27</v>
       </c>
       <c r="E270" s="10">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F270" s="8" t="s">
         <v>28</v>
@@ -7881,7 +7881,7 @@
         <v>27</v>
       </c>
       <c r="E271" s="10">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F271" s="8" t="s">
         <v>34</v>
@@ -7904,7 +7904,7 @@
         <v>27</v>
       </c>
       <c r="E272" s="10">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F272" s="8" t="s">
         <v>28</v>
@@ -7927,7 +7927,7 @@
         <v>27</v>
       </c>
       <c r="E273" s="10">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F273" s="8" t="s">
         <v>31</v>
@@ -7950,7 +7950,7 @@
         <v>27</v>
       </c>
       <c r="E274" s="10">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F274" s="8" t="s">
         <v>28</v>
@@ -7973,7 +7973,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="10">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F275" s="8" t="s">
         <v>34</v>
@@ -7996,7 +7996,7 @@
         <v>27</v>
       </c>
       <c r="E276" s="10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F276" s="8" t="s">
         <v>28</v>
@@ -8019,7 +8019,7 @@
         <v>27</v>
       </c>
       <c r="E277" s="10">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F277" s="8" t="s">
         <v>28</v>
@@ -8042,7 +8042,7 @@
         <v>27</v>
       </c>
       <c r="E278" s="10">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F278" s="8" t="s">
         <v>31</v>
@@ -8065,7 +8065,7 @@
         <v>27</v>
       </c>
       <c r="E279" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F279" s="8" t="s">
         <v>28</v>
@@ -8111,7 +8111,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="10">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F281" s="8" t="s">
         <v>28</v>
@@ -8134,7 +8134,7 @@
         <v>27</v>
       </c>
       <c r="E282" s="10">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F282" s="8" t="s">
         <v>31</v>
@@ -8157,7 +8157,7 @@
         <v>27</v>
       </c>
       <c r="E283" s="10">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F283" s="8" t="s">
         <v>28</v>
@@ -8180,7 +8180,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="10">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F284" s="8" t="s">
         <v>34</v>
@@ -8203,7 +8203,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="10">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F285" s="8" t="s">
         <v>28</v>
@@ -8249,7 +8249,7 @@
         <v>27</v>
       </c>
       <c r="E287" s="10">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F287" s="8" t="s">
         <v>28</v>
@@ -8272,7 +8272,7 @@
         <v>27</v>
       </c>
       <c r="E288" s="10">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F288" s="8" t="s">
         <v>34</v>
@@ -8295,7 +8295,7 @@
         <v>27</v>
       </c>
       <c r="E289" s="10">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F289" s="8" t="s">
         <v>28</v>
@@ -8318,7 +8318,7 @@
         <v>27</v>
       </c>
       <c r="E290" s="10">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F290" s="8" t="s">
         <v>31</v>
@@ -8341,7 +8341,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="10">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F291" s="8" t="s">
         <v>28</v>
@@ -8364,7 +8364,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="10">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F292" s="8" t="s">
         <v>34</v>
@@ -8387,7 +8387,7 @@
         <v>27</v>
       </c>
       <c r="E293" s="10">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F293" s="8" t="s">
         <v>28</v>
@@ -8410,7 +8410,7 @@
         <v>27</v>
       </c>
       <c r="E294" s="10">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F294" s="8" t="s">
         <v>31</v>
@@ -8433,7 +8433,7 @@
         <v>27</v>
       </c>
       <c r="E295" s="10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F295" s="8" t="s">
         <v>28</v>
@@ -8456,7 +8456,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="10">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F296" s="8" t="s">
         <v>34</v>
@@ -8479,7 +8479,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="10">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F297" s="8" t="s">
         <v>28</v>
@@ -8502,7 +8502,7 @@
         <v>27</v>
       </c>
       <c r="E298" s="10">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F298" s="8" t="s">
         <v>31</v>
@@ -8525,7 +8525,7 @@
         <v>27</v>
       </c>
       <c r="E299" s="10">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F299" s="8" t="s">
         <v>28</v>
@@ -8548,7 +8548,7 @@
         <v>27</v>
       </c>
       <c r="E300" s="10">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F300" s="8" t="s">
         <v>34</v>
@@ -8571,7 +8571,7 @@
         <v>27</v>
       </c>
       <c r="E301" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F301" s="8" t="s">
         <v>28</v>
@@ -8636,7 +8636,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -8659,7 +8659,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F3" t="s">
         <v>31</v>
@@ -8682,7 +8682,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -8705,7 +8705,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>34</v>
@@ -8751,7 +8751,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
         <v>31</v>
@@ -8774,7 +8774,7 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -8797,7 +8797,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
@@ -8843,7 +8843,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
         <v>31</v>
@@ -8866,7 +8866,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -8889,7 +8889,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s">
         <v>34</v>
@@ -8912,7 +8912,7 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -8935,7 +8935,7 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F15" t="s">
         <v>31</v>
@@ -8958,7 +8958,7 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -8981,7 +8981,7 @@
         <v>27</v>
       </c>
       <c r="E17">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F17" t="s">
         <v>34</v>
@@ -9027,7 +9027,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F19" t="s">
         <v>31</v>
@@ -9050,7 +9050,7 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -9073,7 +9073,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F21" t="s">
         <v>34</v>
@@ -9096,7 +9096,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -9119,7 +9119,7 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F23" t="s">
         <v>31</v>
@@ -9142,7 +9142,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -9165,7 +9165,7 @@
         <v>27</v>
       </c>
       <c r="E25">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F25" t="s">
         <v>34</v>
@@ -9188,7 +9188,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -9211,7 +9211,7 @@
         <v>27</v>
       </c>
       <c r="E27">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F27" t="s">
         <v>31</v>
@@ -9234,7 +9234,7 @@
         <v>27</v>
       </c>
       <c r="E28">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -9257,7 +9257,7 @@
         <v>27</v>
       </c>
       <c r="E29">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F29" t="s">
         <v>34</v>
@@ -9280,7 +9280,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -9303,7 +9303,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F31" t="s">
         <v>31</v>
@@ -9326,7 +9326,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -9349,7 +9349,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F33" t="s">
         <v>31</v>
@@ -9372,7 +9372,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -9395,7 +9395,7 @@
         <v>27</v>
       </c>
       <c r="E35">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
@@ -9418,7 +9418,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -9441,7 +9441,7 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F37" t="s">
         <v>31</v>
@@ -9464,7 +9464,7 @@
         <v>27</v>
       </c>
       <c r="E38">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -9487,7 +9487,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F39" t="s">
         <v>34</v>
@@ -9510,7 +9510,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -9533,7 +9533,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F41" t="s">
         <v>31</v>
@@ -9556,7 +9556,7 @@
         <v>27</v>
       </c>
       <c r="E42">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -9579,7 +9579,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F43" t="s">
         <v>34</v>
@@ -9602,7 +9602,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -9625,7 +9625,7 @@
         <v>27</v>
       </c>
       <c r="E45">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F45" t="s">
         <v>31</v>
@@ -9648,7 +9648,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -9671,7 +9671,7 @@
         <v>27</v>
       </c>
       <c r="E47">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F47" t="s">
         <v>34</v>
@@ -9694,7 +9694,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -9717,7 +9717,7 @@
         <v>27</v>
       </c>
       <c r="E49">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F49" t="s">
         <v>31</v>
@@ -9740,7 +9740,7 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F50" t="s">
         <v>28</v>
@@ -9763,7 +9763,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F51" t="s">
         <v>34</v>
@@ -9786,7 +9786,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -9809,7 +9809,7 @@
         <v>27</v>
       </c>
       <c r="E53">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F53" t="s">
         <v>31</v>
@@ -9832,7 +9832,7 @@
         <v>27</v>
       </c>
       <c r="E54">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -9855,7 +9855,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F55" t="s">
         <v>34</v>
@@ -9878,7 +9878,7 @@
         <v>27</v>
       </c>
       <c r="E56">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -9901,7 +9901,7 @@
         <v>27</v>
       </c>
       <c r="E57">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F57" t="s">
         <v>31</v>
@@ -9924,7 +9924,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -9947,7 +9947,7 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F59" t="s">
         <v>34</v>
@@ -9970,7 +9970,7 @@
         <v>27</v>
       </c>
       <c r="E60">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -9993,7 +9993,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F61" t="s">
         <v>31</v>
@@ -10016,7 +10016,7 @@
         <v>27</v>
       </c>
       <c r="E62">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F62" t="s">
         <v>28</v>
@@ -10039,7 +10039,7 @@
         <v>27</v>
       </c>
       <c r="E63">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F63" t="s">
         <v>31</v>
@@ -10062,7 +10062,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -10085,7 +10085,7 @@
         <v>27</v>
       </c>
       <c r="E65">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F65" t="s">
         <v>34</v>
@@ -10108,7 +10108,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -10131,7 +10131,7 @@
         <v>27</v>
       </c>
       <c r="E67">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F67" t="s">
         <v>31</v>
@@ -10154,7 +10154,7 @@
         <v>27</v>
       </c>
       <c r="E68">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
@@ -10177,7 +10177,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F69" t="s">
         <v>34</v>
@@ -10200,7 +10200,7 @@
         <v>27</v>
       </c>
       <c r="E70">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -10223,7 +10223,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F71" t="s">
         <v>31</v>
@@ -10246,7 +10246,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -10269,7 +10269,7 @@
         <v>27</v>
       </c>
       <c r="E73">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F73" t="s">
         <v>34</v>
@@ -10292,7 +10292,7 @@
         <v>27</v>
       </c>
       <c r="E74">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -10315,7 +10315,7 @@
         <v>27</v>
       </c>
       <c r="E75">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F75" t="s">
         <v>31</v>
@@ -10338,7 +10338,7 @@
         <v>27</v>
       </c>
       <c r="E76">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
@@ -10361,7 +10361,7 @@
         <v>27</v>
       </c>
       <c r="E77">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F77" t="s">
         <v>34</v>
@@ -10384,7 +10384,7 @@
         <v>27</v>
       </c>
       <c r="E78">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
@@ -10407,7 +10407,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F79" t="s">
         <v>31</v>
@@ -10430,7 +10430,7 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
@@ -10453,7 +10453,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F81" t="s">
         <v>34</v>
@@ -10476,7 +10476,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -10499,7 +10499,7 @@
         <v>27</v>
       </c>
       <c r="E83">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F83" t="s">
         <v>31</v>
@@ -10522,7 +10522,7 @@
         <v>27</v>
       </c>
       <c r="E84">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
@@ -10545,7 +10545,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F85" t="s">
         <v>34</v>
@@ -10568,7 +10568,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -10591,7 +10591,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F87" t="s">
         <v>31</v>
@@ -10614,7 +10614,7 @@
         <v>27</v>
       </c>
       <c r="E88">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -10637,7 +10637,7 @@
         <v>27</v>
       </c>
       <c r="E89">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F89" t="s">
         <v>34</v>
@@ -10660,7 +10660,7 @@
         <v>27</v>
       </c>
       <c r="E90">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F90" t="s">
         <v>28</v>
@@ -10683,7 +10683,7 @@
         <v>27</v>
       </c>
       <c r="E91">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F91" t="s">
         <v>31</v>
@@ -10706,7 +10706,7 @@
         <v>27</v>
       </c>
       <c r="E92">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
@@ -10729,7 +10729,7 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F93" t="s">
         <v>31</v>
@@ -10752,7 +10752,7 @@
         <v>27</v>
       </c>
       <c r="E94">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -10775,7 +10775,7 @@
         <v>27</v>
       </c>
       <c r="E95">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F95" t="s">
         <v>34</v>
@@ -10798,7 +10798,7 @@
         <v>27</v>
       </c>
       <c r="E96">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -10821,7 +10821,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F97" t="s">
         <v>31</v>
@@ -10844,7 +10844,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -10867,7 +10867,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F99" t="s">
         <v>34</v>
@@ -10890,7 +10890,7 @@
         <v>27</v>
       </c>
       <c r="E100">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
@@ -10913,7 +10913,7 @@
         <v>27</v>
       </c>
       <c r="E101">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F101" t="s">
         <v>31</v>
@@ -10936,7 +10936,7 @@
         <v>27</v>
       </c>
       <c r="E102">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
@@ -10959,7 +10959,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F103" t="s">
         <v>34</v>
@@ -10982,7 +10982,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -11005,7 +11005,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F105" t="s">
         <v>31</v>
@@ -11028,7 +11028,7 @@
         <v>27</v>
       </c>
       <c r="E106">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
@@ -11051,7 +11051,7 @@
         <v>27</v>
       </c>
       <c r="E107">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F107" t="s">
         <v>34</v>
@@ -11074,7 +11074,7 @@
         <v>27</v>
       </c>
       <c r="E108">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
@@ -11097,7 +11097,7 @@
         <v>27</v>
       </c>
       <c r="E109">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F109" t="s">
         <v>31</v>
@@ -11120,7 +11120,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -11143,7 +11143,7 @@
         <v>27</v>
       </c>
       <c r="E111">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F111" t="s">
         <v>34</v>
@@ -11166,7 +11166,7 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F112" t="s">
         <v>28</v>
@@ -11212,7 +11212,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -11235,7 +11235,7 @@
         <v>27</v>
       </c>
       <c r="E115">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F115" t="s">
         <v>34</v>
@@ -11258,7 +11258,7 @@
         <v>27</v>
       </c>
       <c r="E116">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F116" t="s">
         <v>28</v>
@@ -11281,7 +11281,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F117" t="s">
         <v>31</v>
@@ -11304,7 +11304,7 @@
         <v>27</v>
       </c>
       <c r="E118">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F118" t="s">
         <v>28</v>
@@ -11350,7 +11350,7 @@
         <v>27</v>
       </c>
       <c r="E120">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
@@ -11373,7 +11373,7 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F121" t="s">
         <v>31</v>
@@ -11396,7 +11396,7 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -11419,7 +11419,7 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F123" t="s">
         <v>31</v>
@@ -11465,7 +11465,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F125" t="s">
         <v>34</v>
@@ -11488,7 +11488,7 @@
         <v>27</v>
       </c>
       <c r="E126">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
@@ -11511,7 +11511,7 @@
         <v>27</v>
       </c>
       <c r="E127">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F127" t="s">
         <v>31</v>
@@ -11534,7 +11534,7 @@
         <v>27</v>
       </c>
       <c r="E128">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -11557,7 +11557,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F129" t="s">
         <v>34</v>
@@ -11580,7 +11580,7 @@
         <v>27</v>
       </c>
       <c r="E130">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
@@ -11603,7 +11603,7 @@
         <v>27</v>
       </c>
       <c r="E131">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F131" t="s">
         <v>31</v>
@@ -11626,7 +11626,7 @@
         <v>27</v>
       </c>
       <c r="E132">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F132" t="s">
         <v>28</v>
@@ -11649,7 +11649,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F133" t="s">
         <v>34</v>
@@ -11672,7 +11672,7 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -11695,7 +11695,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F135" t="s">
         <v>31</v>
@@ -11718,7 +11718,7 @@
         <v>27</v>
       </c>
       <c r="E136">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
@@ -11741,7 +11741,7 @@
         <v>27</v>
       </c>
       <c r="E137">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F137" t="s">
         <v>34</v>
@@ -11764,7 +11764,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -11787,7 +11787,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F139" t="s">
         <v>31</v>
@@ -11833,7 +11833,7 @@
         <v>27</v>
       </c>
       <c r="E141">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F141" t="s">
         <v>34</v>
@@ -11856,7 +11856,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -11879,7 +11879,7 @@
         <v>27</v>
       </c>
       <c r="E143">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F143" t="s">
         <v>31</v>
@@ -11902,7 +11902,7 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F144" t="s">
         <v>28</v>
@@ -11925,7 +11925,7 @@
         <v>27</v>
       </c>
       <c r="E145">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F145" t="s">
         <v>34</v>
@@ -11948,7 +11948,7 @@
         <v>27</v>
       </c>
       <c r="E146">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F146" t="s">
         <v>28</v>
@@ -11971,7 +11971,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F147" t="s">
         <v>31</v>
@@ -11994,7 +11994,7 @@
         <v>27</v>
       </c>
       <c r="E148">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
@@ -12017,7 +12017,7 @@
         <v>27</v>
       </c>
       <c r="E149">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F149" t="s">
         <v>34</v>
@@ -12040,7 +12040,7 @@
         <v>27</v>
       </c>
       <c r="E150">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
@@ -12063,7 +12063,7 @@
         <v>27</v>
       </c>
       <c r="E151">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F151" t="s">
         <v>31</v>
@@ -12086,7 +12086,7 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F152" t="s">
         <v>28</v>
@@ -12109,7 +12109,7 @@
         <v>27</v>
       </c>
       <c r="E153">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F153" t="s">
         <v>31</v>
@@ -12132,7 +12132,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -12155,7 +12155,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F155" t="s">
         <v>34</v>
@@ -12178,7 +12178,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -12201,7 +12201,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F157" t="s">
         <v>31</v>
@@ -12224,7 +12224,7 @@
         <v>27</v>
       </c>
       <c r="E158">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F158" t="s">
         <v>28</v>
@@ -12247,7 +12247,7 @@
         <v>27</v>
       </c>
       <c r="E159">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F159" t="s">
         <v>34</v>
@@ -12293,7 +12293,7 @@
         <v>27</v>
       </c>
       <c r="E161">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F161" t="s">
         <v>31</v>
@@ -12316,7 +12316,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -12339,7 +12339,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F163" t="s">
         <v>34</v>
@@ -12362,7 +12362,7 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
@@ -12385,7 +12385,7 @@
         <v>27</v>
       </c>
       <c r="E165">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F165" t="s">
         <v>31</v>
@@ -12408,7 +12408,7 @@
         <v>27</v>
       </c>
       <c r="E166">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -12431,7 +12431,7 @@
         <v>27</v>
       </c>
       <c r="E167">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F167" t="s">
         <v>34</v>
@@ -12454,7 +12454,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -12477,7 +12477,7 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F169" t="s">
         <v>31</v>
@@ -12500,7 +12500,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -12523,7 +12523,7 @@
         <v>27</v>
       </c>
       <c r="E171">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F171" t="s">
         <v>34</v>
@@ -12546,7 +12546,7 @@
         <v>27</v>
       </c>
       <c r="E172">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
@@ -12569,7 +12569,7 @@
         <v>27</v>
       </c>
       <c r="E173">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F173" t="s">
         <v>31</v>
@@ -12592,7 +12592,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -12615,7 +12615,7 @@
         <v>27</v>
       </c>
       <c r="E175">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F175" t="s">
         <v>34</v>
@@ -12638,7 +12638,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -12661,7 +12661,7 @@
         <v>27</v>
       </c>
       <c r="E177">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
@@ -12684,7 +12684,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F178" t="s">
         <v>31</v>
@@ -12707,7 +12707,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -12730,7 +12730,7 @@
         <v>27</v>
       </c>
       <c r="E180">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F180" t="s">
         <v>34</v>
@@ -12753,7 +12753,7 @@
         <v>27</v>
       </c>
       <c r="E181">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F181" t="s">
         <v>28</v>
@@ -12776,7 +12776,7 @@
         <v>27</v>
       </c>
       <c r="E182">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F182" t="s">
         <v>31</v>
@@ -12799,7 +12799,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -12822,7 +12822,7 @@
         <v>27</v>
       </c>
       <c r="E184">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F184" t="s">
         <v>34</v>
@@ -12845,7 +12845,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -12868,7 +12868,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F186" t="s">
         <v>31</v>
@@ -12891,7 +12891,7 @@
         <v>27</v>
       </c>
       <c r="E187">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F187" t="s">
         <v>28</v>
@@ -12914,7 +12914,7 @@
         <v>27</v>
       </c>
       <c r="E188">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F188" t="s">
         <v>34</v>
@@ -12937,7 +12937,7 @@
         <v>27</v>
       </c>
       <c r="E189">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F189" t="s">
         <v>28</v>
@@ -12960,7 +12960,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F190" t="s">
         <v>31</v>
@@ -12983,7 +12983,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -13006,7 +13006,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F192" t="s">
         <v>34</v>
@@ -13029,7 +13029,7 @@
         <v>27</v>
       </c>
       <c r="E193">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -13052,7 +13052,7 @@
         <v>27</v>
       </c>
       <c r="E194">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F194" t="s">
         <v>31</v>
@@ -13075,7 +13075,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -13098,7 +13098,7 @@
         <v>27</v>
       </c>
       <c r="E196">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F196" t="s">
         <v>34</v>
@@ -13121,7 +13121,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -13144,7 +13144,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F198" t="s">
         <v>31</v>
@@ -13167,7 +13167,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -13190,7 +13190,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F200" t="s">
         <v>34</v>
@@ -13213,7 +13213,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -13236,7 +13236,7 @@
         <v>27</v>
       </c>
       <c r="E202">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -13259,7 +13259,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F203" t="s">
         <v>31</v>
@@ -13282,7 +13282,7 @@
         <v>27</v>
       </c>
       <c r="E204">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -13305,7 +13305,7 @@
         <v>27</v>
       </c>
       <c r="E205">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F205" t="s">
         <v>34</v>
@@ -13328,7 +13328,7 @@
         <v>27</v>
       </c>
       <c r="E206">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -13351,7 +13351,7 @@
         <v>27</v>
       </c>
       <c r="E207">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F207" t="s">
         <v>31</v>
@@ -13374,7 +13374,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -13397,7 +13397,7 @@
         <v>27</v>
       </c>
       <c r="E209">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F209" t="s">
         <v>34</v>
@@ -13420,7 +13420,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -13443,7 +13443,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F211" t="s">
         <v>31</v>
@@ -13466,7 +13466,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -13489,7 +13489,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F213" t="s">
         <v>34</v>
@@ -13512,7 +13512,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -13535,7 +13535,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F215" t="s">
         <v>31</v>
@@ -13558,7 +13558,7 @@
         <v>27</v>
       </c>
       <c r="E216">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F216" t="s">
         <v>28</v>
@@ -13581,7 +13581,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F217" t="s">
         <v>34</v>
@@ -13604,7 +13604,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -13627,7 +13627,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F219" t="s">
         <v>31</v>
@@ -13650,7 +13650,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -13673,7 +13673,7 @@
         <v>27</v>
       </c>
       <c r="E221">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F221" t="s">
         <v>34</v>
@@ -13742,7 +13742,7 @@
         <v>27</v>
       </c>
       <c r="E224">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F224" t="s">
         <v>28</v>
@@ -13765,7 +13765,7 @@
         <v>27</v>
       </c>
       <c r="E225">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F225" t="s">
         <v>34</v>
@@ -13788,7 +13788,7 @@
         <v>27</v>
       </c>
       <c r="E226">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F226" t="s">
         <v>28</v>
@@ -13811,7 +13811,7 @@
         <v>27</v>
       </c>
       <c r="E227">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F227" t="s">
         <v>28</v>
@@ -13834,7 +13834,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F228" t="s">
         <v>31</v>
@@ -13857,7 +13857,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -13880,7 +13880,7 @@
         <v>27</v>
       </c>
       <c r="E230">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F230" t="s">
         <v>34</v>
@@ -13903,7 +13903,7 @@
         <v>27</v>
       </c>
       <c r="E231">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F231" t="s">
         <v>28</v>
@@ -13926,7 +13926,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F232" t="s">
         <v>31</v>
@@ -13949,7 +13949,7 @@
         <v>27</v>
       </c>
       <c r="E233">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F233" t="s">
         <v>28</v>
@@ -13972,7 +13972,7 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F234" t="s">
         <v>34</v>
@@ -13995,7 +13995,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -14018,7 +14018,7 @@
         <v>27</v>
       </c>
       <c r="E236">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F236" t="s">
         <v>31</v>
@@ -14041,7 +14041,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -14064,7 +14064,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F238" t="s">
         <v>34</v>
@@ -14087,7 +14087,7 @@
         <v>27</v>
       </c>
       <c r="E239">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F239" t="s">
         <v>28</v>
@@ -14110,7 +14110,7 @@
         <v>27</v>
       </c>
       <c r="E240">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F240" t="s">
         <v>31</v>
@@ -14133,7 +14133,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -14156,7 +14156,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F242" t="s">
         <v>34</v>
@@ -14179,7 +14179,7 @@
         <v>27</v>
       </c>
       <c r="E243">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -14202,7 +14202,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F244" t="s">
         <v>31</v>
@@ -14225,7 +14225,7 @@
         <v>27</v>
       </c>
       <c r="E245">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F245" t="s">
         <v>28</v>
@@ -14248,7 +14248,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F246" t="s">
         <v>34</v>
@@ -14271,7 +14271,7 @@
         <v>27</v>
       </c>
       <c r="E247">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F247" t="s">
         <v>28</v>
@@ -14294,7 +14294,7 @@
         <v>27</v>
       </c>
       <c r="E248">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F248" t="s">
         <v>31</v>
@@ -14317,7 +14317,7 @@
         <v>27</v>
       </c>
       <c r="E249">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F249" t="s">
         <v>28</v>
@@ -14340,7 +14340,7 @@
         <v>27</v>
       </c>
       <c r="E250">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F250" t="s">
         <v>34</v>
@@ -14363,7 +14363,7 @@
         <v>27</v>
       </c>
       <c r="E251">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F251" t="s">
         <v>28</v>
@@ -14386,7 +14386,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -14409,7 +14409,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F253" t="s">
         <v>31</v>
@@ -14432,7 +14432,7 @@
         <v>27</v>
       </c>
       <c r="E254">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F254" t="s">
         <v>28</v>
@@ -14455,7 +14455,7 @@
         <v>27</v>
       </c>
       <c r="E255">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F255" t="s">
         <v>34</v>
@@ -14478,7 +14478,7 @@
         <v>27</v>
       </c>
       <c r="E256">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F256" t="s">
         <v>28</v>
@@ -14501,7 +14501,7 @@
         <v>27</v>
       </c>
       <c r="E257">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F257" t="s">
         <v>31</v>
@@ -14524,7 +14524,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -14547,7 +14547,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F259" t="s">
         <v>34</v>
@@ -14570,7 +14570,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -14593,7 +14593,7 @@
         <v>27</v>
       </c>
       <c r="E261">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F261" t="s">
         <v>31</v>
@@ -14616,7 +14616,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -14639,7 +14639,7 @@
         <v>27</v>
       </c>
       <c r="E263">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F263" t="s">
         <v>34</v>
@@ -14662,7 +14662,7 @@
         <v>27</v>
       </c>
       <c r="E264">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -14685,7 +14685,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F265" t="s">
         <v>31</v>
@@ -14708,7 +14708,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -14731,7 +14731,7 @@
         <v>27</v>
       </c>
       <c r="E267">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F267" t="s">
         <v>34</v>
@@ -14754,7 +14754,7 @@
         <v>27</v>
       </c>
       <c r="E268">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F268" t="s">
         <v>28</v>
@@ -14800,7 +14800,7 @@
         <v>27</v>
       </c>
       <c r="E270">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F270" t="s">
         <v>28</v>
@@ -14823,7 +14823,7 @@
         <v>27</v>
       </c>
       <c r="E271">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F271" t="s">
         <v>34</v>
@@ -14846,7 +14846,7 @@
         <v>27</v>
       </c>
       <c r="E272">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F272" t="s">
         <v>28</v>
@@ -14869,7 +14869,7 @@
         <v>27</v>
       </c>
       <c r="E273">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F273" t="s">
         <v>31</v>
@@ -14892,7 +14892,7 @@
         <v>27</v>
       </c>
       <c r="E274">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F274" t="s">
         <v>28</v>
@@ -14915,7 +14915,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F275" t="s">
         <v>34</v>
@@ -14938,7 +14938,7 @@
         <v>27</v>
       </c>
       <c r="E276">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F276" t="s">
         <v>28</v>
@@ -14961,7 +14961,7 @@
         <v>27</v>
       </c>
       <c r="E277">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F277" t="s">
         <v>28</v>
@@ -14984,7 +14984,7 @@
         <v>27</v>
       </c>
       <c r="E278">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F278" t="s">
         <v>31</v>
@@ -15007,7 +15007,7 @@
         <v>27</v>
       </c>
       <c r="E279">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -15053,7 +15053,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -15076,7 +15076,7 @@
         <v>27</v>
       </c>
       <c r="E282">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F282" t="s">
         <v>31</v>
@@ -15099,7 +15099,7 @@
         <v>27</v>
       </c>
       <c r="E283">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F283" t="s">
         <v>28</v>
@@ -15122,7 +15122,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F284" t="s">
         <v>34</v>
@@ -15145,7 +15145,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -15191,7 +15191,7 @@
         <v>27</v>
       </c>
       <c r="E287">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F287" t="s">
         <v>28</v>
@@ -15214,7 +15214,7 @@
         <v>27</v>
       </c>
       <c r="E288">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F288" t="s">
         <v>34</v>
@@ -15237,7 +15237,7 @@
         <v>27</v>
       </c>
       <c r="E289">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F289" t="s">
         <v>28</v>
@@ -15260,7 +15260,7 @@
         <v>27</v>
       </c>
       <c r="E290">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F290" t="s">
         <v>31</v>
@@ -15283,7 +15283,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -15306,7 +15306,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F292" t="s">
         <v>34</v>
@@ -15329,7 +15329,7 @@
         <v>27</v>
       </c>
       <c r="E293">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -15352,7 +15352,7 @@
         <v>27</v>
       </c>
       <c r="E294">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F294" t="s">
         <v>31</v>
@@ -15375,7 +15375,7 @@
         <v>27</v>
       </c>
       <c r="E295">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F295" t="s">
         <v>28</v>
@@ -15398,7 +15398,7 @@
         <v>27</v>
       </c>
       <c r="E296">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F296" t="s">
         <v>34</v>
@@ -15421,7 +15421,7 @@
         <v>27</v>
       </c>
       <c r="E297">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F297" t="s">
         <v>28</v>
@@ -15444,7 +15444,7 @@
         <v>27</v>
       </c>
       <c r="E298">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F298" t="s">
         <v>31</v>
@@ -15467,7 +15467,7 @@
         <v>27</v>
       </c>
       <c r="E299">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F299" t="s">
         <v>28</v>
@@ -15490,7 +15490,7 @@
         <v>27</v>
       </c>
       <c r="E300">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F300" t="s">
         <v>34</v>
@@ -15513,7 +15513,7 @@
         <v>27</v>
       </c>
       <c r="E301">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F301" t="s">
         <v>28</v>

--- a/all-test-reports/vulnerability/vulnerability_test_report.xlsx
+++ b/all-test-reports/vulnerability/vulnerability_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 10:47:42 am</t>
+    <t>28/7/2026, 10:59:39 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1694,7 +1694,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="10">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>28</v>
@@ -1717,7 +1717,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="10">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>31</v>
@@ -1740,7 +1740,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="10">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>28</v>
@@ -1763,7 +1763,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="10">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>34</v>
@@ -1786,7 +1786,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="10">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>28</v>
@@ -1809,7 +1809,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="10">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>31</v>
@@ -1832,7 +1832,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="10">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>28</v>
@@ -1855,7 +1855,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="10">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>34</v>
@@ -1878,7 +1878,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="10">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>28</v>
@@ -1901,7 +1901,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>31</v>
@@ -1924,7 +1924,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="10">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>28</v>
@@ -1947,7 +1947,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="10">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>34</v>
@@ -1970,7 +1970,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="10">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>28</v>
@@ -1993,7 +1993,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="10">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>31</v>
@@ -2016,7 +2016,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="10">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>28</v>
@@ -2039,7 +2039,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="10">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>34</v>
@@ -2062,7 +2062,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="10">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>28</v>
@@ -2085,7 +2085,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="10">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>31</v>
@@ -2108,7 +2108,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="10">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>28</v>
@@ -2131,7 +2131,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="10">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>34</v>
@@ -2154,7 +2154,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="10">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>28</v>
@@ -2177,7 +2177,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="10">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>31</v>
@@ -2200,7 +2200,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="10">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>28</v>
@@ -2223,7 +2223,7 @@
         <v>27</v>
       </c>
       <c r="E25" s="10">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>34</v>
@@ -2246,7 +2246,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="10">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>28</v>
@@ -2269,7 +2269,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="10">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>31</v>
@@ -2292,7 +2292,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="10">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>28</v>
@@ -2315,7 +2315,7 @@
         <v>27</v>
       </c>
       <c r="E29" s="10">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>34</v>
@@ -2338,7 +2338,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="10">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>28</v>
@@ -2361,7 +2361,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="10">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>31</v>
@@ -2384,7 +2384,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="10">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>28</v>
@@ -2407,7 +2407,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>31</v>
@@ -2430,7 +2430,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="10">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>28</v>
@@ -2453,7 +2453,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="10">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>34</v>
@@ -2476,7 +2476,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="10">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>28</v>
@@ -2499,7 +2499,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="10">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>31</v>
@@ -2522,7 +2522,7 @@
         <v>27</v>
       </c>
       <c r="E38" s="10">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>28</v>
@@ -2545,7 +2545,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="10">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>34</v>
@@ -2568,7 +2568,7 @@
         <v>27</v>
       </c>
       <c r="E40" s="10">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>28</v>
@@ -2591,7 +2591,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="10">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>31</v>
@@ -2614,7 +2614,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="10">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>28</v>
@@ -2637,7 +2637,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="10">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>34</v>
@@ -2660,7 +2660,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="10">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>28</v>
@@ -2683,7 +2683,7 @@
         <v>27</v>
       </c>
       <c r="E45" s="10">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>31</v>
@@ -2706,7 +2706,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="10">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>28</v>
@@ -2729,7 +2729,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="10">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>34</v>
@@ -2752,7 +2752,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="10">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>28</v>
@@ -2775,7 +2775,7 @@
         <v>27</v>
       </c>
       <c r="E49" s="10">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>31</v>
@@ -2798,7 +2798,7 @@
         <v>27</v>
       </c>
       <c r="E50" s="10">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>28</v>
@@ -2821,7 +2821,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="10">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>34</v>
@@ -2844,7 +2844,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="10">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>28</v>
@@ -2867,7 +2867,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="10">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>31</v>
@@ -2890,7 +2890,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="10">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>28</v>
@@ -2913,7 +2913,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="10">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>34</v>
@@ -2936,7 +2936,7 @@
         <v>27</v>
       </c>
       <c r="E56" s="10">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>28</v>
@@ -2959,7 +2959,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="10">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>31</v>
@@ -2982,7 +2982,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="10">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>28</v>
@@ -3005,7 +3005,7 @@
         <v>27</v>
       </c>
       <c r="E59" s="10">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>34</v>
@@ -3028,7 +3028,7 @@
         <v>27</v>
       </c>
       <c r="E60" s="10">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>28</v>
@@ -3051,7 +3051,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="10">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>31</v>
@@ -3074,7 +3074,7 @@
         <v>27</v>
       </c>
       <c r="E62" s="10">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>28</v>
@@ -3097,7 +3097,7 @@
         <v>27</v>
       </c>
       <c r="E63" s="10">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>31</v>
@@ -3120,7 +3120,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="10">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>28</v>
@@ -3143,7 +3143,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="10">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>34</v>
@@ -3166,7 +3166,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="10">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>28</v>
@@ -3189,7 +3189,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="10">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>31</v>
@@ -3212,7 +3212,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="10">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>28</v>
@@ -3235,7 +3235,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="10">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>34</v>
@@ -3258,7 +3258,7 @@
         <v>27</v>
       </c>
       <c r="E70" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>28</v>
@@ -3281,7 +3281,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="10">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>31</v>
@@ -3304,7 +3304,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="10">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>28</v>
@@ -3350,7 +3350,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="10">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>28</v>
@@ -3373,7 +3373,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="10">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>31</v>
@@ -3419,7 +3419,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="10">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>34</v>
@@ -3442,7 +3442,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="10">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>28</v>
@@ -3465,7 +3465,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="10">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>31</v>
@@ -3488,7 +3488,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="10">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>28</v>
@@ -3511,7 +3511,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="10">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>34</v>
@@ -3534,7 +3534,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>28</v>
@@ -3557,7 +3557,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="10">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>31</v>
@@ -3603,7 +3603,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="10">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>34</v>
@@ -3626,7 +3626,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="10">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>28</v>
@@ -3649,7 +3649,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>31</v>
@@ -3672,7 +3672,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="10">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>28</v>
@@ -3695,7 +3695,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="10">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>34</v>
@@ -3741,7 +3741,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="10">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>31</v>
@@ -3764,7 +3764,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="10">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>28</v>
@@ -3787,7 +3787,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="10">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>31</v>
@@ -3810,7 +3810,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="10">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>28</v>
@@ -3833,7 +3833,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="10">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>34</v>
@@ -3879,7 +3879,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>31</v>
@@ -3902,7 +3902,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="10">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>28</v>
@@ -3925,7 +3925,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>34</v>
@@ -3948,7 +3948,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="10">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>28</v>
@@ -3971,7 +3971,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="10">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>31</v>
@@ -3994,7 +3994,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="10">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>28</v>
@@ -4017,7 +4017,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>34</v>
@@ -4040,7 +4040,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="10">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>28</v>
@@ -4063,7 +4063,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="10">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>31</v>
@@ -4109,7 +4109,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="10">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>34</v>
@@ -4132,7 +4132,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="10">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>28</v>
@@ -4155,7 +4155,7 @@
         <v>27</v>
       </c>
       <c r="E109" s="10">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>31</v>
@@ -4178,7 +4178,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="10">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>28</v>
@@ -4201,7 +4201,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="10">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>34</v>
@@ -4224,7 +4224,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="10">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>28</v>
@@ -4247,7 +4247,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="10">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F113" s="8" t="s">
         <v>31</v>
@@ -4270,7 +4270,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="10">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>28</v>
@@ -4293,7 +4293,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="10">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>34</v>
@@ -4316,7 +4316,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="10">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>28</v>
@@ -4339,7 +4339,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="10">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F117" s="8" t="s">
         <v>31</v>
@@ -4362,7 +4362,7 @@
         <v>27</v>
       </c>
       <c r="E118" s="10">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F118" s="8" t="s">
         <v>28</v>
@@ -4385,7 +4385,7 @@
         <v>27</v>
       </c>
       <c r="E119" s="10">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F119" s="8" t="s">
         <v>34</v>
@@ -4408,7 +4408,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="10">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F120" s="8" t="s">
         <v>28</v>
@@ -4431,7 +4431,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="10">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F121" s="8" t="s">
         <v>31</v>
@@ -4454,7 +4454,7 @@
         <v>27</v>
       </c>
       <c r="E122" s="10">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F122" s="8" t="s">
         <v>28</v>
@@ -4477,7 +4477,7 @@
         <v>27</v>
       </c>
       <c r="E123" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>31</v>
@@ -4500,7 +4500,7 @@
         <v>27</v>
       </c>
       <c r="E124" s="10">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F124" s="8" t="s">
         <v>28</v>
@@ -4523,7 +4523,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="10">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>34</v>
@@ -4546,7 +4546,7 @@
         <v>27</v>
       </c>
       <c r="E126" s="10">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F126" s="8" t="s">
         <v>28</v>
@@ -4569,7 +4569,7 @@
         <v>27</v>
       </c>
       <c r="E127" s="10">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F127" s="8" t="s">
         <v>31</v>
@@ -4592,7 +4592,7 @@
         <v>27</v>
       </c>
       <c r="E128" s="10">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F128" s="8" t="s">
         <v>28</v>
@@ -4615,7 +4615,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="10">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F129" s="8" t="s">
         <v>34</v>
@@ -4638,7 +4638,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="10">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F130" s="8" t="s">
         <v>28</v>
@@ -4661,7 +4661,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F131" s="8" t="s">
         <v>31</v>
@@ -4684,7 +4684,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="10">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F132" s="8" t="s">
         <v>28</v>
@@ -4707,7 +4707,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="10">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F133" s="8" t="s">
         <v>34</v>
@@ -4730,7 +4730,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="10">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F134" s="8" t="s">
         <v>28</v>
@@ -4753,7 +4753,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="10">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F135" s="8" t="s">
         <v>31</v>
@@ -4776,7 +4776,7 @@
         <v>27</v>
       </c>
       <c r="E136" s="10">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F136" s="8" t="s">
         <v>28</v>
@@ -4799,7 +4799,7 @@
         <v>27</v>
       </c>
       <c r="E137" s="10">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F137" s="8" t="s">
         <v>34</v>
@@ -4822,7 +4822,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="10">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F138" s="8" t="s">
         <v>28</v>
@@ -4845,7 +4845,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="10">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F139" s="8" t="s">
         <v>31</v>
@@ -4868,7 +4868,7 @@
         <v>27</v>
       </c>
       <c r="E140" s="10">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F140" s="8" t="s">
         <v>28</v>
@@ -4891,7 +4891,7 @@
         <v>27</v>
       </c>
       <c r="E141" s="10">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F141" s="8" t="s">
         <v>34</v>
@@ -4914,7 +4914,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="10">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F142" s="8" t="s">
         <v>28</v>
@@ -4937,7 +4937,7 @@
         <v>27</v>
       </c>
       <c r="E143" s="10">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F143" s="8" t="s">
         <v>31</v>
@@ -4960,7 +4960,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="10">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F144" s="8" t="s">
         <v>28</v>
@@ -4983,7 +4983,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="10">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F145" s="8" t="s">
         <v>34</v>
@@ -5006,7 +5006,7 @@
         <v>27</v>
       </c>
       <c r="E146" s="10">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>28</v>
@@ -5029,7 +5029,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="10">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F147" s="8" t="s">
         <v>31</v>
@@ -5052,7 +5052,7 @@
         <v>27</v>
       </c>
       <c r="E148" s="10">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F148" s="8" t="s">
         <v>28</v>
@@ -5075,7 +5075,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="10">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F149" s="8" t="s">
         <v>34</v>
@@ -5098,7 +5098,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="10">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>28</v>
@@ -5121,7 +5121,7 @@
         <v>27</v>
       </c>
       <c r="E151" s="10">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>31</v>
@@ -5144,7 +5144,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="10">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>28</v>
@@ -5167,7 +5167,7 @@
         <v>27</v>
       </c>
       <c r="E153" s="10">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F153" s="8" t="s">
         <v>31</v>
@@ -5190,7 +5190,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="10">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>28</v>
@@ -5213,7 +5213,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F155" s="8" t="s">
         <v>34</v>
@@ -5236,7 +5236,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="10">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F156" s="8" t="s">
         <v>28</v>
@@ -5259,7 +5259,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="10">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F157" s="8" t="s">
         <v>31</v>
@@ -5282,7 +5282,7 @@
         <v>27</v>
       </c>
       <c r="E158" s="10">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F158" s="8" t="s">
         <v>28</v>
@@ -5328,7 +5328,7 @@
         <v>27</v>
       </c>
       <c r="E160" s="10">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F160" s="8" t="s">
         <v>28</v>
@@ -5374,7 +5374,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="10">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F162" s="8" t="s">
         <v>28</v>
@@ -5397,7 +5397,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="10">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F163" s="8" t="s">
         <v>34</v>
@@ -5420,7 +5420,7 @@
         <v>27</v>
       </c>
       <c r="E164" s="10">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F164" s="8" t="s">
         <v>28</v>
@@ -5443,7 +5443,7 @@
         <v>27</v>
       </c>
       <c r="E165" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F165" s="8" t="s">
         <v>31</v>
@@ -5466,7 +5466,7 @@
         <v>27</v>
       </c>
       <c r="E166" s="10">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F166" s="8" t="s">
         <v>28</v>
@@ -5489,7 +5489,7 @@
         <v>27</v>
       </c>
       <c r="E167" s="10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F167" s="8" t="s">
         <v>34</v>
@@ -5512,7 +5512,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="10">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F168" s="8" t="s">
         <v>28</v>
@@ -5535,7 +5535,7 @@
         <v>27</v>
       </c>
       <c r="E169" s="10">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F169" s="8" t="s">
         <v>31</v>
@@ -5558,7 +5558,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="10">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F170" s="8" t="s">
         <v>28</v>
@@ -5581,7 +5581,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="10">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F171" s="8" t="s">
         <v>34</v>
@@ -5604,7 +5604,7 @@
         <v>27</v>
       </c>
       <c r="E172" s="10">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F172" s="8" t="s">
         <v>28</v>
@@ -5627,7 +5627,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="10">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F173" s="8" t="s">
         <v>31</v>
@@ -5650,7 +5650,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="10">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F174" s="8" t="s">
         <v>28</v>
@@ -5673,7 +5673,7 @@
         <v>27</v>
       </c>
       <c r="E175" s="10">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F175" s="8" t="s">
         <v>34</v>
@@ -5696,7 +5696,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="10">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F176" s="8" t="s">
         <v>28</v>
@@ -5719,7 +5719,7 @@
         <v>27</v>
       </c>
       <c r="E177" s="10">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F177" s="8" t="s">
         <v>28</v>
@@ -5742,7 +5742,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="10">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F178" s="8" t="s">
         <v>31</v>
@@ -5765,7 +5765,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="10">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F179" s="8" t="s">
         <v>28</v>
@@ -5788,7 +5788,7 @@
         <v>27</v>
       </c>
       <c r="E180" s="10">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F180" s="8" t="s">
         <v>34</v>
@@ -5811,7 +5811,7 @@
         <v>27</v>
       </c>
       <c r="E181" s="10">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F181" s="8" t="s">
         <v>28</v>
@@ -5834,7 +5834,7 @@
         <v>27</v>
       </c>
       <c r="E182" s="10">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F182" s="8" t="s">
         <v>31</v>
@@ -5857,7 +5857,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="10">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F183" s="8" t="s">
         <v>28</v>
@@ -5880,7 +5880,7 @@
         <v>27</v>
       </c>
       <c r="E184" s="10">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F184" s="8" t="s">
         <v>34</v>
@@ -5903,7 +5903,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="10">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F185" s="8" t="s">
         <v>28</v>
@@ -5926,7 +5926,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="10">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F186" s="8" t="s">
         <v>31</v>
@@ -5949,7 +5949,7 @@
         <v>27</v>
       </c>
       <c r="E187" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F187" s="8" t="s">
         <v>28</v>
@@ -5972,7 +5972,7 @@
         <v>27</v>
       </c>
       <c r="E188" s="10">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F188" s="8" t="s">
         <v>34</v>
@@ -5995,7 +5995,7 @@
         <v>27</v>
       </c>
       <c r="E189" s="10">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F189" s="8" t="s">
         <v>28</v>
@@ -6018,7 +6018,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="10">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F190" s="8" t="s">
         <v>31</v>
@@ -6041,7 +6041,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="10">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F191" s="8" t="s">
         <v>28</v>
@@ -6064,7 +6064,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="10">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F192" s="8" t="s">
         <v>34</v>
@@ -6110,7 +6110,7 @@
         <v>27</v>
       </c>
       <c r="E194" s="10">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F194" s="8" t="s">
         <v>31</v>
@@ -6133,7 +6133,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F195" s="8" t="s">
         <v>28</v>
@@ -6156,7 +6156,7 @@
         <v>27</v>
       </c>
       <c r="E196" s="10">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F196" s="8" t="s">
         <v>34</v>
@@ -6179,7 +6179,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F197" s="8" t="s">
         <v>28</v>
@@ -6202,7 +6202,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="10">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F198" s="8" t="s">
         <v>31</v>
@@ -6225,7 +6225,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="10">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F199" s="8" t="s">
         <v>28</v>
@@ -6248,7 +6248,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="10">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F200" s="8" t="s">
         <v>34</v>
@@ -6271,7 +6271,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F201" s="8" t="s">
         <v>28</v>
@@ -6294,7 +6294,7 @@
         <v>27</v>
       </c>
       <c r="E202" s="10">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F202" s="8" t="s">
         <v>28</v>
@@ -6317,7 +6317,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="10">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F203" s="8" t="s">
         <v>31</v>
@@ -6340,7 +6340,7 @@
         <v>27</v>
       </c>
       <c r="E204" s="10">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F204" s="8" t="s">
         <v>28</v>
@@ -6363,7 +6363,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="10">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F205" s="8" t="s">
         <v>34</v>
@@ -6386,7 +6386,7 @@
         <v>27</v>
       </c>
       <c r="E206" s="10">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F206" s="8" t="s">
         <v>28</v>
@@ -6409,7 +6409,7 @@
         <v>27</v>
       </c>
       <c r="E207" s="10">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F207" s="8" t="s">
         <v>31</v>
@@ -6432,7 +6432,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="10">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F208" s="8" t="s">
         <v>28</v>
@@ -6455,7 +6455,7 @@
         <v>27</v>
       </c>
       <c r="E209" s="10">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F209" s="8" t="s">
         <v>34</v>
@@ -6478,7 +6478,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="10">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F210" s="8" t="s">
         <v>28</v>
@@ -6501,7 +6501,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="10">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F211" s="8" t="s">
         <v>31</v>
@@ -6524,7 +6524,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="10">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F212" s="8" t="s">
         <v>28</v>
@@ -6547,7 +6547,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F213" s="8" t="s">
         <v>34</v>
@@ -6570,7 +6570,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="10">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F214" s="8" t="s">
         <v>28</v>
@@ -6593,7 +6593,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="10">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F215" s="8" t="s">
         <v>31</v>
@@ -6616,7 +6616,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="10">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F216" s="8" t="s">
         <v>28</v>
@@ -6639,7 +6639,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="10">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F217" s="8" t="s">
         <v>34</v>
@@ -6662,7 +6662,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="10">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F218" s="8" t="s">
         <v>28</v>
@@ -6685,7 +6685,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="10">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F219" s="8" t="s">
         <v>31</v>
@@ -6708,7 +6708,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="10">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F220" s="8" t="s">
         <v>28</v>
@@ -6731,7 +6731,7 @@
         <v>27</v>
       </c>
       <c r="E221" s="10">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F221" s="8" t="s">
         <v>34</v>
@@ -6754,7 +6754,7 @@
         <v>27</v>
       </c>
       <c r="E222" s="10">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F222" s="8" t="s">
         <v>28</v>
@@ -6777,7 +6777,7 @@
         <v>27</v>
       </c>
       <c r="E223" s="10">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F223" s="8" t="s">
         <v>31</v>
@@ -6800,7 +6800,7 @@
         <v>27</v>
       </c>
       <c r="E224" s="10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F224" s="8" t="s">
         <v>28</v>
@@ -6823,7 +6823,7 @@
         <v>27</v>
       </c>
       <c r="E225" s="10">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F225" s="8" t="s">
         <v>34</v>
@@ -6846,7 +6846,7 @@
         <v>27</v>
       </c>
       <c r="E226" s="10">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F226" s="8" t="s">
         <v>28</v>
@@ -6869,7 +6869,7 @@
         <v>27</v>
       </c>
       <c r="E227" s="10">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F227" s="8" t="s">
         <v>28</v>
@@ -6892,7 +6892,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="10">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F228" s="8" t="s">
         <v>31</v>
@@ -6915,7 +6915,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="10">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F229" s="8" t="s">
         <v>28</v>
@@ -6938,7 +6938,7 @@
         <v>27</v>
       </c>
       <c r="E230" s="10">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F230" s="8" t="s">
         <v>34</v>
@@ -6961,7 +6961,7 @@
         <v>27</v>
       </c>
       <c r="E231" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F231" s="8" t="s">
         <v>28</v>
@@ -6984,7 +6984,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="10">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F232" s="8" t="s">
         <v>31</v>
@@ -7007,7 +7007,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="10">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F233" s="8" t="s">
         <v>28</v>
@@ -7030,7 +7030,7 @@
         <v>27</v>
       </c>
       <c r="E234" s="10">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F234" s="8" t="s">
         <v>34</v>
@@ -7053,7 +7053,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="10">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F235" s="8" t="s">
         <v>28</v>
@@ -7076,7 +7076,7 @@
         <v>27</v>
       </c>
       <c r="E236" s="10">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F236" s="8" t="s">
         <v>31</v>
@@ -7099,7 +7099,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="10">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F237" s="8" t="s">
         <v>28</v>
@@ -7122,7 +7122,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F238" s="8" t="s">
         <v>34</v>
@@ -7145,7 +7145,7 @@
         <v>27</v>
       </c>
       <c r="E239" s="10">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F239" s="8" t="s">
         <v>28</v>
@@ -7191,7 +7191,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="10">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F241" s="8" t="s">
         <v>28</v>
@@ -7214,7 +7214,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="10">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F242" s="8" t="s">
         <v>34</v>
@@ -7237,7 +7237,7 @@
         <v>27</v>
       </c>
       <c r="E243" s="10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F243" s="8" t="s">
         <v>28</v>
@@ -7260,7 +7260,7 @@
         <v>27</v>
       </c>
       <c r="E244" s="10">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F244" s="8" t="s">
         <v>31</v>
@@ -7283,7 +7283,7 @@
         <v>27</v>
       </c>
       <c r="E245" s="10">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F245" s="8" t="s">
         <v>28</v>
@@ -7306,7 +7306,7 @@
         <v>27</v>
       </c>
       <c r="E246" s="10">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F246" s="8" t="s">
         <v>34</v>
@@ -7329,7 +7329,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="10">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F247" s="8" t="s">
         <v>28</v>
@@ -7352,7 +7352,7 @@
         <v>27</v>
       </c>
       <c r="E248" s="10">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F248" s="8" t="s">
         <v>31</v>
@@ -7375,7 +7375,7 @@
         <v>27</v>
       </c>
       <c r="E249" s="10">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F249" s="8" t="s">
         <v>28</v>
@@ -7398,7 +7398,7 @@
         <v>27</v>
       </c>
       <c r="E250" s="10">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F250" s="8" t="s">
         <v>34</v>
@@ -7421,7 +7421,7 @@
         <v>27</v>
       </c>
       <c r="E251" s="10">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F251" s="8" t="s">
         <v>28</v>
@@ -7444,7 +7444,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="10">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F252" s="8" t="s">
         <v>28</v>
@@ -7467,7 +7467,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="10">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F253" s="8" t="s">
         <v>31</v>
@@ -7490,7 +7490,7 @@
         <v>27</v>
       </c>
       <c r="E254" s="10">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F254" s="8" t="s">
         <v>28</v>
@@ -7536,7 +7536,7 @@
         <v>27</v>
       </c>
       <c r="E256" s="10">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F256" s="8" t="s">
         <v>28</v>
@@ -7559,7 +7559,7 @@
         <v>27</v>
       </c>
       <c r="E257" s="10">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F257" s="8" t="s">
         <v>31</v>
@@ -7582,7 +7582,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="10">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F258" s="8" t="s">
         <v>28</v>
@@ -7605,7 +7605,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="10">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F259" s="8" t="s">
         <v>34</v>
@@ -7628,7 +7628,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="10">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F260" s="8" t="s">
         <v>28</v>
@@ -7674,7 +7674,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="10">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F262" s="8" t="s">
         <v>28</v>
@@ -7697,7 +7697,7 @@
         <v>27</v>
       </c>
       <c r="E263" s="10">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F263" s="8" t="s">
         <v>34</v>
@@ -7720,7 +7720,7 @@
         <v>27</v>
       </c>
       <c r="E264" s="10">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F264" s="8" t="s">
         <v>28</v>
@@ -7743,7 +7743,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="10">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F265" s="8" t="s">
         <v>31</v>
@@ -7766,7 +7766,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="10">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F266" s="8" t="s">
         <v>28</v>
@@ -7789,7 +7789,7 @@
         <v>27</v>
       </c>
       <c r="E267" s="10">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F267" s="8" t="s">
         <v>34</v>
@@ -7812,7 +7812,7 @@
         <v>27</v>
       </c>
       <c r="E268" s="10">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F268" s="8" t="s">
         <v>28</v>
@@ -7858,7 +7858,7 @@
         <v>27</v>
       </c>
       <c r="E270" s="10">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F270" s="8" t="s">
         <v>28</v>
@@ -7881,7 +7881,7 @@
         <v>27</v>
       </c>
       <c r="E271" s="10">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F271" s="8" t="s">
         <v>34</v>
@@ -7904,7 +7904,7 @@
         <v>27</v>
       </c>
       <c r="E272" s="10">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F272" s="8" t="s">
         <v>28</v>
@@ -7927,7 +7927,7 @@
         <v>27</v>
       </c>
       <c r="E273" s="10">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F273" s="8" t="s">
         <v>31</v>
@@ -7950,7 +7950,7 @@
         <v>27</v>
       </c>
       <c r="E274" s="10">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F274" s="8" t="s">
         <v>28</v>
@@ -7973,7 +7973,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="10">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F275" s="8" t="s">
         <v>34</v>
@@ -7996,7 +7996,7 @@
         <v>27</v>
       </c>
       <c r="E276" s="10">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F276" s="8" t="s">
         <v>28</v>
@@ -8019,7 +8019,7 @@
         <v>27</v>
       </c>
       <c r="E277" s="10">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F277" s="8" t="s">
         <v>28</v>
@@ -8042,7 +8042,7 @@
         <v>27</v>
       </c>
       <c r="E278" s="10">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F278" s="8" t="s">
         <v>31</v>
@@ -8065,7 +8065,7 @@
         <v>27</v>
       </c>
       <c r="E279" s="10">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F279" s="8" t="s">
         <v>28</v>
@@ -8088,7 +8088,7 @@
         <v>27</v>
       </c>
       <c r="E280" s="10">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F280" s="8" t="s">
         <v>34</v>
@@ -8111,7 +8111,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="10">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F281" s="8" t="s">
         <v>28</v>
@@ -8134,7 +8134,7 @@
         <v>27</v>
       </c>
       <c r="E282" s="10">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F282" s="8" t="s">
         <v>31</v>
@@ -8157,7 +8157,7 @@
         <v>27</v>
       </c>
       <c r="E283" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F283" s="8" t="s">
         <v>28</v>
@@ -8180,7 +8180,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="10">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F284" s="8" t="s">
         <v>34</v>
@@ -8203,7 +8203,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="10">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F285" s="8" t="s">
         <v>28</v>
@@ -8226,7 +8226,7 @@
         <v>27</v>
       </c>
       <c r="E286" s="10">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F286" s="8" t="s">
         <v>31</v>
@@ -8249,7 +8249,7 @@
         <v>27</v>
       </c>
       <c r="E287" s="10">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F287" s="8" t="s">
         <v>28</v>
@@ -8272,7 +8272,7 @@
         <v>27</v>
       </c>
       <c r="E288" s="10">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F288" s="8" t="s">
         <v>34</v>
@@ -8318,7 +8318,7 @@
         <v>27</v>
       </c>
       <c r="E290" s="10">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F290" s="8" t="s">
         <v>31</v>
@@ -8341,7 +8341,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="10">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F291" s="8" t="s">
         <v>28</v>
@@ -8364,7 +8364,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="10">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F292" s="8" t="s">
         <v>34</v>
@@ -8387,7 +8387,7 @@
         <v>27</v>
       </c>
       <c r="E293" s="10">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F293" s="8" t="s">
         <v>28</v>
@@ -8410,7 +8410,7 @@
         <v>27</v>
       </c>
       <c r="E294" s="10">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F294" s="8" t="s">
         <v>31</v>
@@ -8433,7 +8433,7 @@
         <v>27</v>
       </c>
       <c r="E295" s="10">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F295" s="8" t="s">
         <v>28</v>
@@ -8479,7 +8479,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="10">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F297" s="8" t="s">
         <v>28</v>
@@ -8502,7 +8502,7 @@
         <v>27</v>
       </c>
       <c r="E298" s="10">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F298" s="8" t="s">
         <v>31</v>
@@ -8525,7 +8525,7 @@
         <v>27</v>
       </c>
       <c r="E299" s="10">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F299" s="8" t="s">
         <v>28</v>
@@ -8548,7 +8548,7 @@
         <v>27</v>
       </c>
       <c r="E300" s="10">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F300" s="8" t="s">
         <v>34</v>
@@ -8571,7 +8571,7 @@
         <v>27</v>
       </c>
       <c r="E301" s="10">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F301" s="8" t="s">
         <v>28</v>
@@ -8636,7 +8636,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -8659,7 +8659,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>31</v>
@@ -8682,7 +8682,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -8705,7 +8705,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s">
         <v>34</v>
@@ -8728,7 +8728,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -8751,7 +8751,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
         <v>31</v>
@@ -8774,7 +8774,7 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -8797,7 +8797,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
@@ -8820,7 +8820,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -8843,7 +8843,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F11" t="s">
         <v>31</v>
@@ -8866,7 +8866,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -8889,7 +8889,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
         <v>34</v>
@@ -8912,7 +8912,7 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -8935,7 +8935,7 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F15" t="s">
         <v>31</v>
@@ -8958,7 +8958,7 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -8981,7 +8981,7 @@
         <v>27</v>
       </c>
       <c r="E17">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F17" t="s">
         <v>34</v>
@@ -9004,7 +9004,7 @@
         <v>27</v>
       </c>
       <c r="E18">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -9027,7 +9027,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F19" t="s">
         <v>31</v>
@@ -9050,7 +9050,7 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -9073,7 +9073,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F21" t="s">
         <v>34</v>
@@ -9096,7 +9096,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -9119,7 +9119,7 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F23" t="s">
         <v>31</v>
@@ -9142,7 +9142,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -9165,7 +9165,7 @@
         <v>27</v>
       </c>
       <c r="E25">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F25" t="s">
         <v>34</v>
@@ -9188,7 +9188,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -9211,7 +9211,7 @@
         <v>27</v>
       </c>
       <c r="E27">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F27" t="s">
         <v>31</v>
@@ -9234,7 +9234,7 @@
         <v>27</v>
       </c>
       <c r="E28">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -9257,7 +9257,7 @@
         <v>27</v>
       </c>
       <c r="E29">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F29" t="s">
         <v>34</v>
@@ -9280,7 +9280,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -9303,7 +9303,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F31" t="s">
         <v>31</v>
@@ -9326,7 +9326,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -9349,7 +9349,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F33" t="s">
         <v>31</v>
@@ -9372,7 +9372,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -9395,7 +9395,7 @@
         <v>27</v>
       </c>
       <c r="E35">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
@@ -9418,7 +9418,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -9441,7 +9441,7 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F37" t="s">
         <v>31</v>
@@ -9464,7 +9464,7 @@
         <v>27</v>
       </c>
       <c r="E38">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -9487,7 +9487,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F39" t="s">
         <v>34</v>
@@ -9510,7 +9510,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -9533,7 +9533,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F41" t="s">
         <v>31</v>
@@ -9556,7 +9556,7 @@
         <v>27</v>
       </c>
       <c r="E42">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -9579,7 +9579,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F43" t="s">
         <v>34</v>
@@ -9602,7 +9602,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -9625,7 +9625,7 @@
         <v>27</v>
       </c>
       <c r="E45">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F45" t="s">
         <v>31</v>
@@ -9648,7 +9648,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -9671,7 +9671,7 @@
         <v>27</v>
       </c>
       <c r="E47">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F47" t="s">
         <v>34</v>
@@ -9694,7 +9694,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -9717,7 +9717,7 @@
         <v>27</v>
       </c>
       <c r="E49">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F49" t="s">
         <v>31</v>
@@ -9740,7 +9740,7 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F50" t="s">
         <v>28</v>
@@ -9763,7 +9763,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F51" t="s">
         <v>34</v>
@@ -9786,7 +9786,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -9809,7 +9809,7 @@
         <v>27</v>
       </c>
       <c r="E53">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F53" t="s">
         <v>31</v>
@@ -9832,7 +9832,7 @@
         <v>27</v>
       </c>
       <c r="E54">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -9855,7 +9855,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F55" t="s">
         <v>34</v>
@@ -9878,7 +9878,7 @@
         <v>27</v>
       </c>
       <c r="E56">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -9901,7 +9901,7 @@
         <v>27</v>
       </c>
       <c r="E57">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F57" t="s">
         <v>31</v>
@@ -9924,7 +9924,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -9947,7 +9947,7 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F59" t="s">
         <v>34</v>
@@ -9970,7 +9970,7 @@
         <v>27</v>
       </c>
       <c r="E60">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -9993,7 +9993,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F61" t="s">
         <v>31</v>
@@ -10016,7 +10016,7 @@
         <v>27</v>
       </c>
       <c r="E62">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F62" t="s">
         <v>28</v>
@@ -10039,7 +10039,7 @@
         <v>27</v>
       </c>
       <c r="E63">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F63" t="s">
         <v>31</v>
@@ -10062,7 +10062,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -10085,7 +10085,7 @@
         <v>27</v>
       </c>
       <c r="E65">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F65" t="s">
         <v>34</v>
@@ -10108,7 +10108,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -10131,7 +10131,7 @@
         <v>27</v>
       </c>
       <c r="E67">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F67" t="s">
         <v>31</v>
@@ -10154,7 +10154,7 @@
         <v>27</v>
       </c>
       <c r="E68">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
@@ -10177,7 +10177,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F69" t="s">
         <v>34</v>
@@ -10200,7 +10200,7 @@
         <v>27</v>
       </c>
       <c r="E70">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -10223,7 +10223,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F71" t="s">
         <v>31</v>
@@ -10246,7 +10246,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -10292,7 +10292,7 @@
         <v>27</v>
       </c>
       <c r="E74">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -10315,7 +10315,7 @@
         <v>27</v>
       </c>
       <c r="E75">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F75" t="s">
         <v>31</v>
@@ -10361,7 +10361,7 @@
         <v>27</v>
       </c>
       <c r="E77">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F77" t="s">
         <v>34</v>
@@ -10384,7 +10384,7 @@
         <v>27</v>
       </c>
       <c r="E78">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
@@ -10407,7 +10407,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F79" t="s">
         <v>31</v>
@@ -10430,7 +10430,7 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
@@ -10453,7 +10453,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F81" t="s">
         <v>34</v>
@@ -10476,7 +10476,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -10499,7 +10499,7 @@
         <v>27</v>
       </c>
       <c r="E83">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F83" t="s">
         <v>31</v>
@@ -10545,7 +10545,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F85" t="s">
         <v>34</v>
@@ -10568,7 +10568,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -10591,7 +10591,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F87" t="s">
         <v>31</v>
@@ -10614,7 +10614,7 @@
         <v>27</v>
       </c>
       <c r="E88">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -10637,7 +10637,7 @@
         <v>27</v>
       </c>
       <c r="E89">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F89" t="s">
         <v>34</v>
@@ -10683,7 +10683,7 @@
         <v>27</v>
       </c>
       <c r="E91">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F91" t="s">
         <v>31</v>
@@ -10706,7 +10706,7 @@
         <v>27</v>
       </c>
       <c r="E92">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
@@ -10729,7 +10729,7 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F93" t="s">
         <v>31</v>
@@ -10752,7 +10752,7 @@
         <v>27</v>
       </c>
       <c r="E94">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -10775,7 +10775,7 @@
         <v>27</v>
       </c>
       <c r="E95">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F95" t="s">
         <v>34</v>
@@ -10821,7 +10821,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F97" t="s">
         <v>31</v>
@@ -10844,7 +10844,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -10867,7 +10867,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F99" t="s">
         <v>34</v>
@@ -10890,7 +10890,7 @@
         <v>27</v>
       </c>
       <c r="E100">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
@@ -10913,7 +10913,7 @@
         <v>27</v>
       </c>
       <c r="E101">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F101" t="s">
         <v>31</v>
@@ -10936,7 +10936,7 @@
         <v>27</v>
       </c>
       <c r="E102">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
@@ -10959,7 +10959,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F103" t="s">
         <v>34</v>
@@ -10982,7 +10982,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -11005,7 +11005,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F105" t="s">
         <v>31</v>
@@ -11051,7 +11051,7 @@
         <v>27</v>
       </c>
       <c r="E107">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F107" t="s">
         <v>34</v>
@@ -11074,7 +11074,7 @@
         <v>27</v>
       </c>
       <c r="E108">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
@@ -11097,7 +11097,7 @@
         <v>27</v>
       </c>
       <c r="E109">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F109" t="s">
         <v>31</v>
@@ -11120,7 +11120,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -11143,7 +11143,7 @@
         <v>27</v>
       </c>
       <c r="E111">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F111" t="s">
         <v>34</v>
@@ -11166,7 +11166,7 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F112" t="s">
         <v>28</v>
@@ -11189,7 +11189,7 @@
         <v>27</v>
       </c>
       <c r="E113">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F113" t="s">
         <v>31</v>
@@ -11212,7 +11212,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -11235,7 +11235,7 @@
         <v>27</v>
       </c>
       <c r="E115">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F115" t="s">
         <v>34</v>
@@ -11258,7 +11258,7 @@
         <v>27</v>
       </c>
       <c r="E116">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F116" t="s">
         <v>28</v>
@@ -11281,7 +11281,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F117" t="s">
         <v>31</v>
@@ -11304,7 +11304,7 @@
         <v>27</v>
       </c>
       <c r="E118">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F118" t="s">
         <v>28</v>
@@ -11327,7 +11327,7 @@
         <v>27</v>
       </c>
       <c r="E119">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F119" t="s">
         <v>34</v>
@@ -11350,7 +11350,7 @@
         <v>27</v>
       </c>
       <c r="E120">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
@@ -11373,7 +11373,7 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F121" t="s">
         <v>31</v>
@@ -11396,7 +11396,7 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -11419,7 +11419,7 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F123" t="s">
         <v>31</v>
@@ -11442,7 +11442,7 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F124" t="s">
         <v>28</v>
@@ -11465,7 +11465,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F125" t="s">
         <v>34</v>
@@ -11488,7 +11488,7 @@
         <v>27</v>
       </c>
       <c r="E126">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
@@ -11511,7 +11511,7 @@
         <v>27</v>
       </c>
       <c r="E127">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F127" t="s">
         <v>31</v>
@@ -11534,7 +11534,7 @@
         <v>27</v>
       </c>
       <c r="E128">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -11557,7 +11557,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F129" t="s">
         <v>34</v>
@@ -11580,7 +11580,7 @@
         <v>27</v>
       </c>
       <c r="E130">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
@@ -11603,7 +11603,7 @@
         <v>27</v>
       </c>
       <c r="E131">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F131" t="s">
         <v>31</v>
@@ -11626,7 +11626,7 @@
         <v>27</v>
       </c>
       <c r="E132">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F132" t="s">
         <v>28</v>
@@ -11649,7 +11649,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F133" t="s">
         <v>34</v>
@@ -11672,7 +11672,7 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -11695,7 +11695,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F135" t="s">
         <v>31</v>
@@ -11718,7 +11718,7 @@
         <v>27</v>
       </c>
       <c r="E136">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
@@ -11741,7 +11741,7 @@
         <v>27</v>
       </c>
       <c r="E137">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F137" t="s">
         <v>34</v>
@@ -11764,7 +11764,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -11787,7 +11787,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F139" t="s">
         <v>31</v>
@@ -11810,7 +11810,7 @@
         <v>27</v>
       </c>
       <c r="E140">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
@@ -11833,7 +11833,7 @@
         <v>27</v>
       </c>
       <c r="E141">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F141" t="s">
         <v>34</v>
@@ -11856,7 +11856,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -11879,7 +11879,7 @@
         <v>27</v>
       </c>
       <c r="E143">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F143" t="s">
         <v>31</v>
@@ -11902,7 +11902,7 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F144" t="s">
         <v>28</v>
@@ -11925,7 +11925,7 @@
         <v>27</v>
       </c>
       <c r="E145">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F145" t="s">
         <v>34</v>
@@ -11948,7 +11948,7 @@
         <v>27</v>
       </c>
       <c r="E146">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F146" t="s">
         <v>28</v>
@@ -11971,7 +11971,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F147" t="s">
         <v>31</v>
@@ -11994,7 +11994,7 @@
         <v>27</v>
       </c>
       <c r="E148">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
@@ -12017,7 +12017,7 @@
         <v>27</v>
       </c>
       <c r="E149">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F149" t="s">
         <v>34</v>
@@ -12040,7 +12040,7 @@
         <v>27</v>
       </c>
       <c r="E150">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
@@ -12063,7 +12063,7 @@
         <v>27</v>
       </c>
       <c r="E151">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F151" t="s">
         <v>31</v>
@@ -12086,7 +12086,7 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F152" t="s">
         <v>28</v>
@@ -12109,7 +12109,7 @@
         <v>27</v>
       </c>
       <c r="E153">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F153" t="s">
         <v>31</v>
@@ -12132,7 +12132,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -12155,7 +12155,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F155" t="s">
         <v>34</v>
@@ -12178,7 +12178,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -12201,7 +12201,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F157" t="s">
         <v>31</v>
@@ -12224,7 +12224,7 @@
         <v>27</v>
       </c>
       <c r="E158">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F158" t="s">
         <v>28</v>
@@ -12270,7 +12270,7 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F160" t="s">
         <v>28</v>
@@ -12316,7 +12316,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -12339,7 +12339,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F163" t="s">
         <v>34</v>
@@ -12362,7 +12362,7 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
@@ -12385,7 +12385,7 @@
         <v>27</v>
       </c>
       <c r="E165">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F165" t="s">
         <v>31</v>
@@ -12408,7 +12408,7 @@
         <v>27</v>
       </c>
       <c r="E166">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -12431,7 +12431,7 @@
         <v>27</v>
       </c>
       <c r="E167">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F167" t="s">
         <v>34</v>
@@ -12454,7 +12454,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -12477,7 +12477,7 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F169" t="s">
         <v>31</v>
@@ -12500,7 +12500,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -12523,7 +12523,7 @@
         <v>27</v>
       </c>
       <c r="E171">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F171" t="s">
         <v>34</v>
@@ -12546,7 +12546,7 @@
         <v>27</v>
       </c>
       <c r="E172">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
@@ -12569,7 +12569,7 @@
         <v>27</v>
       </c>
       <c r="E173">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F173" t="s">
         <v>31</v>
@@ -12592,7 +12592,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -12615,7 +12615,7 @@
         <v>27</v>
       </c>
       <c r="E175">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F175" t="s">
         <v>34</v>
@@ -12638,7 +12638,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -12661,7 +12661,7 @@
         <v>27</v>
       </c>
       <c r="E177">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
@@ -12684,7 +12684,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F178" t="s">
         <v>31</v>
@@ -12707,7 +12707,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -12730,7 +12730,7 @@
         <v>27</v>
       </c>
       <c r="E180">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F180" t="s">
         <v>34</v>
@@ -12753,7 +12753,7 @@
         <v>27</v>
       </c>
       <c r="E181">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F181" t="s">
         <v>28</v>
@@ -12776,7 +12776,7 @@
         <v>27</v>
       </c>
       <c r="E182">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F182" t="s">
         <v>31</v>
@@ -12799,7 +12799,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -12822,7 +12822,7 @@
         <v>27</v>
       </c>
       <c r="E184">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F184" t="s">
         <v>34</v>
@@ -12845,7 +12845,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -12868,7 +12868,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F186" t="s">
         <v>31</v>
@@ -12891,7 +12891,7 @@
         <v>27</v>
       </c>
       <c r="E187">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F187" t="s">
         <v>28</v>
@@ -12914,7 +12914,7 @@
         <v>27</v>
       </c>
       <c r="E188">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F188" t="s">
         <v>34</v>
@@ -12937,7 +12937,7 @@
         <v>27</v>
       </c>
       <c r="E189">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F189" t="s">
         <v>28</v>
@@ -12960,7 +12960,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F190" t="s">
         <v>31</v>
@@ -12983,7 +12983,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -13006,7 +13006,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F192" t="s">
         <v>34</v>
@@ -13052,7 +13052,7 @@
         <v>27</v>
       </c>
       <c r="E194">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F194" t="s">
         <v>31</v>
@@ -13075,7 +13075,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -13098,7 +13098,7 @@
         <v>27</v>
       </c>
       <c r="E196">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F196" t="s">
         <v>34</v>
@@ -13121,7 +13121,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -13144,7 +13144,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F198" t="s">
         <v>31</v>
@@ -13167,7 +13167,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -13190,7 +13190,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F200" t="s">
         <v>34</v>
@@ -13213,7 +13213,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -13236,7 +13236,7 @@
         <v>27</v>
       </c>
       <c r="E202">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -13259,7 +13259,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F203" t="s">
         <v>31</v>
@@ -13282,7 +13282,7 @@
         <v>27</v>
       </c>
       <c r="E204">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -13305,7 +13305,7 @@
         <v>27</v>
       </c>
       <c r="E205">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F205" t="s">
         <v>34</v>
@@ -13328,7 +13328,7 @@
         <v>27</v>
       </c>
       <c r="E206">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -13351,7 +13351,7 @@
         <v>27</v>
       </c>
       <c r="E207">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F207" t="s">
         <v>31</v>
@@ -13374,7 +13374,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -13397,7 +13397,7 @@
         <v>27</v>
       </c>
       <c r="E209">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F209" t="s">
         <v>34</v>
@@ -13420,7 +13420,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -13443,7 +13443,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F211" t="s">
         <v>31</v>
@@ -13466,7 +13466,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -13489,7 +13489,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F213" t="s">
         <v>34</v>
@@ -13512,7 +13512,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -13535,7 +13535,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F215" t="s">
         <v>31</v>
@@ -13558,7 +13558,7 @@
         <v>27</v>
       </c>
       <c r="E216">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F216" t="s">
         <v>28</v>
@@ -13581,7 +13581,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F217" t="s">
         <v>34</v>
@@ -13604,7 +13604,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -13627,7 +13627,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F219" t="s">
         <v>31</v>
@@ -13650,7 +13650,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -13673,7 +13673,7 @@
         <v>27</v>
       </c>
       <c r="E221">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F221" t="s">
         <v>34</v>
@@ -13696,7 +13696,7 @@
         <v>27</v>
       </c>
       <c r="E222">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F222" t="s">
         <v>28</v>
@@ -13719,7 +13719,7 @@
         <v>27</v>
       </c>
       <c r="E223">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F223" t="s">
         <v>31</v>
@@ -13742,7 +13742,7 @@
         <v>27</v>
       </c>
       <c r="E224">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F224" t="s">
         <v>28</v>
@@ -13765,7 +13765,7 @@
         <v>27</v>
       </c>
       <c r="E225">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F225" t="s">
         <v>34</v>
@@ -13788,7 +13788,7 @@
         <v>27</v>
       </c>
       <c r="E226">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F226" t="s">
         <v>28</v>
@@ -13811,7 +13811,7 @@
         <v>27</v>
       </c>
       <c r="E227">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F227" t="s">
         <v>28</v>
@@ -13834,7 +13834,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F228" t="s">
         <v>31</v>
@@ -13857,7 +13857,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -13880,7 +13880,7 @@
         <v>27</v>
       </c>
       <c r="E230">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F230" t="s">
         <v>34</v>
@@ -13903,7 +13903,7 @@
         <v>27</v>
       </c>
       <c r="E231">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F231" t="s">
         <v>28</v>
@@ -13926,7 +13926,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F232" t="s">
         <v>31</v>
@@ -13949,7 +13949,7 @@
         <v>27</v>
       </c>
       <c r="E233">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F233" t="s">
         <v>28</v>
@@ -13972,7 +13972,7 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F234" t="s">
         <v>34</v>
@@ -13995,7 +13995,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -14018,7 +14018,7 @@
         <v>27</v>
       </c>
       <c r="E236">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F236" t="s">
         <v>31</v>
@@ -14041,7 +14041,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -14064,7 +14064,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F238" t="s">
         <v>34</v>
@@ -14087,7 +14087,7 @@
         <v>27</v>
       </c>
       <c r="E239">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F239" t="s">
         <v>28</v>
@@ -14133,7 +14133,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -14156,7 +14156,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F242" t="s">
         <v>34</v>
@@ -14179,7 +14179,7 @@
         <v>27</v>
       </c>
       <c r="E243">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -14202,7 +14202,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F244" t="s">
         <v>31</v>
@@ -14225,7 +14225,7 @@
         <v>27</v>
       </c>
       <c r="E245">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F245" t="s">
         <v>28</v>
@@ -14248,7 +14248,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F246" t="s">
         <v>34</v>
@@ -14271,7 +14271,7 @@
         <v>27</v>
       </c>
       <c r="E247">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F247" t="s">
         <v>28</v>
@@ -14294,7 +14294,7 @@
         <v>27</v>
       </c>
       <c r="E248">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F248" t="s">
         <v>31</v>
@@ -14317,7 +14317,7 @@
         <v>27</v>
       </c>
       <c r="E249">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F249" t="s">
         <v>28</v>
@@ -14340,7 +14340,7 @@
         <v>27</v>
       </c>
       <c r="E250">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F250" t="s">
         <v>34</v>
@@ -14363,7 +14363,7 @@
         <v>27</v>
       </c>
       <c r="E251">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F251" t="s">
         <v>28</v>
@@ -14386,7 +14386,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -14409,7 +14409,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F253" t="s">
         <v>31</v>
@@ -14432,7 +14432,7 @@
         <v>27</v>
       </c>
       <c r="E254">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F254" t="s">
         <v>28</v>
@@ -14478,7 +14478,7 @@
         <v>27</v>
       </c>
       <c r="E256">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F256" t="s">
         <v>28</v>
@@ -14501,7 +14501,7 @@
         <v>27</v>
       </c>
       <c r="E257">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F257" t="s">
         <v>31</v>
@@ -14524,7 +14524,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -14547,7 +14547,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F259" t="s">
         <v>34</v>
@@ -14570,7 +14570,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -14616,7 +14616,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -14639,7 +14639,7 @@
         <v>27</v>
       </c>
       <c r="E263">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F263" t="s">
         <v>34</v>
@@ -14662,7 +14662,7 @@
         <v>27</v>
       </c>
       <c r="E264">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -14685,7 +14685,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F265" t="s">
         <v>31</v>
@@ -14708,7 +14708,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -14731,7 +14731,7 @@
         <v>27</v>
       </c>
       <c r="E267">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F267" t="s">
         <v>34</v>
@@ -14754,7 +14754,7 @@
         <v>27</v>
       </c>
       <c r="E268">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F268" t="s">
         <v>28</v>
@@ -14800,7 +14800,7 @@
         <v>27</v>
       </c>
       <c r="E270">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F270" t="s">
         <v>28</v>
@@ -14823,7 +14823,7 @@
         <v>27</v>
       </c>
       <c r="E271">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F271" t="s">
         <v>34</v>
@@ -14846,7 +14846,7 @@
         <v>27</v>
       </c>
       <c r="E272">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F272" t="s">
         <v>28</v>
@@ -14869,7 +14869,7 @@
         <v>27</v>
       </c>
       <c r="E273">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F273" t="s">
         <v>31</v>
@@ -14892,7 +14892,7 @@
         <v>27</v>
       </c>
       <c r="E274">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F274" t="s">
         <v>28</v>
@@ -14915,7 +14915,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F275" t="s">
         <v>34</v>
@@ -14938,7 +14938,7 @@
         <v>27</v>
       </c>
       <c r="E276">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F276" t="s">
         <v>28</v>
@@ -14961,7 +14961,7 @@
         <v>27</v>
       </c>
       <c r="E277">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F277" t="s">
         <v>28</v>
@@ -14984,7 +14984,7 @@
         <v>27</v>
       </c>
       <c r="E278">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F278" t="s">
         <v>31</v>
@@ -15007,7 +15007,7 @@
         <v>27</v>
       </c>
       <c r="E279">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -15030,7 +15030,7 @@
         <v>27</v>
       </c>
       <c r="E280">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F280" t="s">
         <v>34</v>
@@ -15053,7 +15053,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -15076,7 +15076,7 @@
         <v>27</v>
       </c>
       <c r="E282">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F282" t="s">
         <v>31</v>
@@ -15099,7 +15099,7 @@
         <v>27</v>
       </c>
       <c r="E283">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F283" t="s">
         <v>28</v>
@@ -15122,7 +15122,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F284" t="s">
         <v>34</v>
@@ -15145,7 +15145,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -15168,7 +15168,7 @@
         <v>27</v>
       </c>
       <c r="E286">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F286" t="s">
         <v>31</v>
@@ -15191,7 +15191,7 @@
         <v>27</v>
       </c>
       <c r="E287">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F287" t="s">
         <v>28</v>
@@ -15214,7 +15214,7 @@
         <v>27</v>
       </c>
       <c r="E288">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F288" t="s">
         <v>34</v>
@@ -15260,7 +15260,7 @@
         <v>27</v>
       </c>
       <c r="E290">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F290" t="s">
         <v>31</v>
@@ -15283,7 +15283,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -15306,7 +15306,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F292" t="s">
         <v>34</v>
@@ -15329,7 +15329,7 @@
         <v>27</v>
       </c>
       <c r="E293">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -15352,7 +15352,7 @@
         <v>27</v>
       </c>
       <c r="E294">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F294" t="s">
         <v>31</v>
@@ -15375,7 +15375,7 @@
         <v>27</v>
       </c>
       <c r="E295">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F295" t="s">
         <v>28</v>
@@ -15421,7 +15421,7 @@
         <v>27</v>
       </c>
       <c r="E297">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F297" t="s">
         <v>28</v>
@@ -15444,7 +15444,7 @@
         <v>27</v>
       </c>
       <c r="E298">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F298" t="s">
         <v>31</v>
@@ -15467,7 +15467,7 @@
         <v>27</v>
       </c>
       <c r="E299">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F299" t="s">
         <v>28</v>
@@ -15490,7 +15490,7 @@
         <v>27</v>
       </c>
       <c r="E300">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F300" t="s">
         <v>34</v>
@@ -15513,7 +15513,7 @@
         <v>27</v>
       </c>
       <c r="E301">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F301" t="s">
         <v>28</v>

--- a/all-test-reports/vulnerability/vulnerability_test_report.xlsx
+++ b/all-test-reports/vulnerability/vulnerability_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 10:59:39 am</t>
+    <t>28/7/2026, 11:08:30 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1694,7 +1694,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="10">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>28</v>
@@ -1763,7 +1763,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="10">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>34</v>
@@ -1786,7 +1786,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>28</v>
@@ -1809,7 +1809,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="10">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>31</v>
@@ -1832,7 +1832,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="10">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>28</v>
@@ -1855,7 +1855,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="10">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>34</v>
@@ -1878,7 +1878,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="10">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>28</v>
@@ -1901,7 +1901,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="10">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>31</v>
@@ -1924,7 +1924,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="10">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>28</v>
@@ -1947,7 +1947,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="10">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>34</v>
@@ -2016,7 +2016,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="10">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>28</v>
@@ -2039,7 +2039,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="10">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>34</v>
@@ -2062,7 +2062,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>28</v>
@@ -2085,7 +2085,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="10">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>31</v>
@@ -2108,7 +2108,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="10">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>28</v>
@@ -2131,7 +2131,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="10">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>34</v>
@@ -2154,7 +2154,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="10">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>28</v>
@@ -2200,7 +2200,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="10">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>28</v>
@@ -2223,7 +2223,7 @@
         <v>27</v>
       </c>
       <c r="E25" s="10">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>34</v>
@@ -2246,7 +2246,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="10">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>28</v>
@@ -2269,7 +2269,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="10">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>31</v>
@@ -2315,7 +2315,7 @@
         <v>27</v>
       </c>
       <c r="E29" s="10">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>34</v>
@@ -2338,7 +2338,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="10">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>28</v>
@@ -2361,7 +2361,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="10">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>31</v>
@@ -2384,7 +2384,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="10">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>28</v>
@@ -2407,7 +2407,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="10">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>31</v>
@@ -2430,7 +2430,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="10">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>28</v>
@@ -2453,7 +2453,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="10">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>34</v>
@@ -2476,7 +2476,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="10">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>28</v>
@@ -2499,7 +2499,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="10">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>31</v>
@@ -2522,7 +2522,7 @@
         <v>27</v>
       </c>
       <c r="E38" s="10">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>28</v>
@@ -2545,7 +2545,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="10">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>34</v>
@@ -2568,7 +2568,7 @@
         <v>27</v>
       </c>
       <c r="E40" s="10">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>28</v>
@@ -2591,7 +2591,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="10">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>31</v>
@@ -2614,7 +2614,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="10">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>28</v>
@@ -2637,7 +2637,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="10">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>34</v>
@@ -2660,7 +2660,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="10">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>28</v>
@@ -2683,7 +2683,7 @@
         <v>27</v>
       </c>
       <c r="E45" s="10">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>31</v>
@@ -2706,7 +2706,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="10">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>28</v>
@@ -2752,7 +2752,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="10">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>28</v>
@@ -2775,7 +2775,7 @@
         <v>27</v>
       </c>
       <c r="E49" s="10">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>31</v>
@@ -2798,7 +2798,7 @@
         <v>27</v>
       </c>
       <c r="E50" s="10">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>28</v>
@@ -2821,7 +2821,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="10">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>34</v>
@@ -2844,7 +2844,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="10">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>28</v>
@@ -2867,7 +2867,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="10">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>31</v>
@@ -2913,7 +2913,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="10">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>34</v>
@@ -2936,7 +2936,7 @@
         <v>27</v>
       </c>
       <c r="E56" s="10">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>28</v>
@@ -2982,7 +2982,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="10">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>28</v>
@@ -3005,7 +3005,7 @@
         <v>27</v>
       </c>
       <c r="E59" s="10">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>34</v>
@@ -3028,7 +3028,7 @@
         <v>27</v>
       </c>
       <c r="E60" s="10">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>28</v>
@@ -3051,7 +3051,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="10">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>31</v>
@@ -3074,7 +3074,7 @@
         <v>27</v>
       </c>
       <c r="E62" s="10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>28</v>
@@ -3097,7 +3097,7 @@
         <v>27</v>
       </c>
       <c r="E63" s="10">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>31</v>
@@ -3120,7 +3120,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="10">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>28</v>
@@ -3143,7 +3143,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="10">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>34</v>
@@ -3166,7 +3166,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="10">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>28</v>
@@ -3189,7 +3189,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="10">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>31</v>
@@ -3212,7 +3212,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="10">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>28</v>
@@ -3235,7 +3235,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="10">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>34</v>
@@ -3258,7 +3258,7 @@
         <v>27</v>
       </c>
       <c r="E70" s="10">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>28</v>
@@ -3281,7 +3281,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="10">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>31</v>
@@ -3304,7 +3304,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="10">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>28</v>
@@ -3327,7 +3327,7 @@
         <v>27</v>
       </c>
       <c r="E73" s="10">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>34</v>
@@ -3350,7 +3350,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="10">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>28</v>
@@ -3373,7 +3373,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="10">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>31</v>
@@ -3396,7 +3396,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="10">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>28</v>
@@ -3419,7 +3419,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="10">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>34</v>
@@ -3442,7 +3442,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="10">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>28</v>
@@ -3465,7 +3465,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="10">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>31</v>
@@ -3488,7 +3488,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="10">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>28</v>
@@ -3511,7 +3511,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="10">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>34</v>
@@ -3534,7 +3534,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="10">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>28</v>
@@ -3557,7 +3557,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>31</v>
@@ -3603,7 +3603,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="10">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>34</v>
@@ -3626,7 +3626,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="10">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>28</v>
@@ -3649,7 +3649,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="10">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>31</v>
@@ -3672,7 +3672,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="10">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>28</v>
@@ -3695,7 +3695,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="10">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>34</v>
@@ -3718,7 +3718,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="10">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>28</v>
@@ -3741,7 +3741,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="10">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>31</v>
@@ -3764,7 +3764,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="10">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>28</v>
@@ -3787,7 +3787,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="10">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>31</v>
@@ -3810,7 +3810,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="10">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>28</v>
@@ -3833,7 +3833,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="10">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>34</v>
@@ -3856,7 +3856,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="10">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F96" s="8" t="s">
         <v>28</v>
@@ -3879,7 +3879,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="10">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>31</v>
@@ -3902,7 +3902,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="10">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>28</v>
@@ -3925,7 +3925,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="10">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>34</v>
@@ -3948,7 +3948,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>28</v>
@@ -3971,7 +3971,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="10">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>31</v>
@@ -3994,7 +3994,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="10">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>28</v>
@@ -4017,7 +4017,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="10">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>34</v>
@@ -4040,7 +4040,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="10">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>28</v>
@@ -4063,7 +4063,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="10">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>31</v>
@@ -4086,7 +4086,7 @@
         <v>27</v>
       </c>
       <c r="E106" s="10">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>28</v>
@@ -4109,7 +4109,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="10">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>34</v>
@@ -4132,7 +4132,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="10">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>28</v>
@@ -4155,7 +4155,7 @@
         <v>27</v>
       </c>
       <c r="E109" s="10">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>31</v>
@@ -4178,7 +4178,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="10">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>28</v>
@@ -4201,7 +4201,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="10">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>34</v>
@@ -4224,7 +4224,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="10">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>28</v>
@@ -4247,7 +4247,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="10">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F113" s="8" t="s">
         <v>31</v>
@@ -4270,7 +4270,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="10">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>28</v>
@@ -4293,7 +4293,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="10">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>34</v>
@@ -4316,7 +4316,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="10">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>28</v>
@@ -4339,7 +4339,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="10">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F117" s="8" t="s">
         <v>31</v>
@@ -4362,7 +4362,7 @@
         <v>27</v>
       </c>
       <c r="E118" s="10">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F118" s="8" t="s">
         <v>28</v>
@@ -4385,7 +4385,7 @@
         <v>27</v>
       </c>
       <c r="E119" s="10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F119" s="8" t="s">
         <v>34</v>
@@ -4408,7 +4408,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="10">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F120" s="8" t="s">
         <v>28</v>
@@ -4431,7 +4431,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="10">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F121" s="8" t="s">
         <v>31</v>
@@ -4454,7 +4454,7 @@
         <v>27</v>
       </c>
       <c r="E122" s="10">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F122" s="8" t="s">
         <v>28</v>
@@ -4477,7 +4477,7 @@
         <v>27</v>
       </c>
       <c r="E123" s="10">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>31</v>
@@ -4500,7 +4500,7 @@
         <v>27</v>
       </c>
       <c r="E124" s="10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F124" s="8" t="s">
         <v>28</v>
@@ -4523,7 +4523,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="10">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>34</v>
@@ -4546,7 +4546,7 @@
         <v>27</v>
       </c>
       <c r="E126" s="10">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F126" s="8" t="s">
         <v>28</v>
@@ -4592,7 +4592,7 @@
         <v>27</v>
       </c>
       <c r="E128" s="10">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F128" s="8" t="s">
         <v>28</v>
@@ -4615,7 +4615,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="10">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F129" s="8" t="s">
         <v>34</v>
@@ -4638,7 +4638,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="10">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F130" s="8" t="s">
         <v>28</v>
@@ -4661,7 +4661,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F131" s="8" t="s">
         <v>31</v>
@@ -4707,7 +4707,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="10">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F133" s="8" t="s">
         <v>34</v>
@@ -4730,7 +4730,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="10">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F134" s="8" t="s">
         <v>28</v>
@@ -4753,7 +4753,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="10">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F135" s="8" t="s">
         <v>31</v>
@@ -4776,7 +4776,7 @@
         <v>27</v>
       </c>
       <c r="E136" s="10">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F136" s="8" t="s">
         <v>28</v>
@@ -4799,7 +4799,7 @@
         <v>27</v>
       </c>
       <c r="E137" s="10">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F137" s="8" t="s">
         <v>34</v>
@@ -4822,7 +4822,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="10">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F138" s="8" t="s">
         <v>28</v>
@@ -4845,7 +4845,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="10">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F139" s="8" t="s">
         <v>31</v>
@@ -4868,7 +4868,7 @@
         <v>27</v>
       </c>
       <c r="E140" s="10">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F140" s="8" t="s">
         <v>28</v>
@@ -4891,7 +4891,7 @@
         <v>27</v>
       </c>
       <c r="E141" s="10">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F141" s="8" t="s">
         <v>34</v>
@@ -4914,7 +4914,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="10">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F142" s="8" t="s">
         <v>28</v>
@@ -4937,7 +4937,7 @@
         <v>27</v>
       </c>
       <c r="E143" s="10">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F143" s="8" t="s">
         <v>31</v>
@@ -4960,7 +4960,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F144" s="8" t="s">
         <v>28</v>
@@ -4983,7 +4983,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="10">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F145" s="8" t="s">
         <v>34</v>
@@ -5006,7 +5006,7 @@
         <v>27</v>
       </c>
       <c r="E146" s="10">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>28</v>
@@ -5029,7 +5029,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="10">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F147" s="8" t="s">
         <v>31</v>
@@ -5052,7 +5052,7 @@
         <v>27</v>
       </c>
       <c r="E148" s="10">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F148" s="8" t="s">
         <v>28</v>
@@ -5075,7 +5075,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="10">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F149" s="8" t="s">
         <v>34</v>
@@ -5098,7 +5098,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="10">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>28</v>
@@ -5121,7 +5121,7 @@
         <v>27</v>
       </c>
       <c r="E151" s="10">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>31</v>
@@ -5144,7 +5144,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="10">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>28</v>
@@ -5167,7 +5167,7 @@
         <v>27</v>
       </c>
       <c r="E153" s="10">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F153" s="8" t="s">
         <v>31</v>
@@ -5190,7 +5190,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="10">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>28</v>
@@ -5213,7 +5213,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="10">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F155" s="8" t="s">
         <v>34</v>
@@ -5236,7 +5236,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="10">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F156" s="8" t="s">
         <v>28</v>
@@ -5259,7 +5259,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="10">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F157" s="8" t="s">
         <v>31</v>
@@ -5282,7 +5282,7 @@
         <v>27</v>
       </c>
       <c r="E158" s="10">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F158" s="8" t="s">
         <v>28</v>
@@ -5305,7 +5305,7 @@
         <v>27</v>
       </c>
       <c r="E159" s="10">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F159" s="8" t="s">
         <v>34</v>
@@ -5328,7 +5328,7 @@
         <v>27</v>
       </c>
       <c r="E160" s="10">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F160" s="8" t="s">
         <v>28</v>
@@ -5351,7 +5351,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="10">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F161" s="8" t="s">
         <v>31</v>
@@ -5374,7 +5374,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="10">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F162" s="8" t="s">
         <v>28</v>
@@ -5397,7 +5397,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="10">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F163" s="8" t="s">
         <v>34</v>
@@ -5443,7 +5443,7 @@
         <v>27</v>
       </c>
       <c r="E165" s="10">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F165" s="8" t="s">
         <v>31</v>
@@ -5466,7 +5466,7 @@
         <v>27</v>
       </c>
       <c r="E166" s="10">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F166" s="8" t="s">
         <v>28</v>
@@ -5489,7 +5489,7 @@
         <v>27</v>
       </c>
       <c r="E167" s="10">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F167" s="8" t="s">
         <v>34</v>
@@ -5512,7 +5512,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="10">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F168" s="8" t="s">
         <v>28</v>
@@ -5558,7 +5558,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="10">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F170" s="8" t="s">
         <v>28</v>
@@ -5581,7 +5581,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F171" s="8" t="s">
         <v>34</v>
@@ -5604,7 +5604,7 @@
         <v>27</v>
       </c>
       <c r="E172" s="10">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F172" s="8" t="s">
         <v>28</v>
@@ -5627,7 +5627,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="10">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F173" s="8" t="s">
         <v>31</v>
@@ -5650,7 +5650,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="10">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F174" s="8" t="s">
         <v>28</v>
@@ -5673,7 +5673,7 @@
         <v>27</v>
       </c>
       <c r="E175" s="10">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F175" s="8" t="s">
         <v>34</v>
@@ -5696,7 +5696,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="10">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F176" s="8" t="s">
         <v>28</v>
@@ -5719,7 +5719,7 @@
         <v>27</v>
       </c>
       <c r="E177" s="10">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F177" s="8" t="s">
         <v>28</v>
@@ -5742,7 +5742,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="10">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F178" s="8" t="s">
         <v>31</v>
@@ -5765,7 +5765,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="10">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F179" s="8" t="s">
         <v>28</v>
@@ -5811,7 +5811,7 @@
         <v>27</v>
       </c>
       <c r="E181" s="10">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F181" s="8" t="s">
         <v>28</v>
@@ -5834,7 +5834,7 @@
         <v>27</v>
       </c>
       <c r="E182" s="10">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F182" s="8" t="s">
         <v>31</v>
@@ -5857,7 +5857,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="10">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F183" s="8" t="s">
         <v>28</v>
@@ -5880,7 +5880,7 @@
         <v>27</v>
       </c>
       <c r="E184" s="10">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F184" s="8" t="s">
         <v>34</v>
@@ -5903,7 +5903,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="10">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F185" s="8" t="s">
         <v>28</v>
@@ -5926,7 +5926,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="10">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F186" s="8" t="s">
         <v>31</v>
@@ -5949,7 +5949,7 @@
         <v>27</v>
       </c>
       <c r="E187" s="10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F187" s="8" t="s">
         <v>28</v>
@@ -5972,7 +5972,7 @@
         <v>27</v>
       </c>
       <c r="E188" s="10">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F188" s="8" t="s">
         <v>34</v>
@@ -5995,7 +5995,7 @@
         <v>27</v>
       </c>
       <c r="E189" s="10">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F189" s="8" t="s">
         <v>28</v>
@@ -6018,7 +6018,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="10">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F190" s="8" t="s">
         <v>31</v>
@@ -6041,7 +6041,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="10">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F191" s="8" t="s">
         <v>28</v>
@@ -6064,7 +6064,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="10">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F192" s="8" t="s">
         <v>34</v>
@@ -6087,7 +6087,7 @@
         <v>27</v>
       </c>
       <c r="E193" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F193" s="8" t="s">
         <v>28</v>
@@ -6110,7 +6110,7 @@
         <v>27</v>
       </c>
       <c r="E194" s="10">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F194" s="8" t="s">
         <v>31</v>
@@ -6133,7 +6133,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="10">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F195" s="8" t="s">
         <v>28</v>
@@ -6179,7 +6179,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="10">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F197" s="8" t="s">
         <v>28</v>
@@ -6202,7 +6202,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="10">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F198" s="8" t="s">
         <v>31</v>
@@ -6225,7 +6225,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="10">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F199" s="8" t="s">
         <v>28</v>
@@ -6248,7 +6248,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="10">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F200" s="8" t="s">
         <v>34</v>
@@ -6271,7 +6271,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="10">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F201" s="8" t="s">
         <v>28</v>
@@ -6317,7 +6317,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F203" s="8" t="s">
         <v>31</v>
@@ -6340,7 +6340,7 @@
         <v>27</v>
       </c>
       <c r="E204" s="10">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F204" s="8" t="s">
         <v>28</v>
@@ -6363,7 +6363,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="10">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F205" s="8" t="s">
         <v>34</v>
@@ -6386,7 +6386,7 @@
         <v>27</v>
       </c>
       <c r="E206" s="10">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F206" s="8" t="s">
         <v>28</v>
@@ -6409,7 +6409,7 @@
         <v>27</v>
       </c>
       <c r="E207" s="10">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F207" s="8" t="s">
         <v>31</v>
@@ -6432,7 +6432,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="10">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F208" s="8" t="s">
         <v>28</v>
@@ -6455,7 +6455,7 @@
         <v>27</v>
       </c>
       <c r="E209" s="10">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F209" s="8" t="s">
         <v>34</v>
@@ -6478,7 +6478,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="10">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F210" s="8" t="s">
         <v>28</v>
@@ -6501,7 +6501,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="10">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F211" s="8" t="s">
         <v>31</v>
@@ -6524,7 +6524,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="10">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F212" s="8" t="s">
         <v>28</v>
@@ -6547,7 +6547,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="10">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F213" s="8" t="s">
         <v>34</v>
@@ -6570,7 +6570,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="10">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F214" s="8" t="s">
         <v>28</v>
@@ -6593,7 +6593,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="10">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F215" s="8" t="s">
         <v>31</v>
@@ -6616,7 +6616,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="10">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F216" s="8" t="s">
         <v>28</v>
@@ -6639,7 +6639,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="10">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F217" s="8" t="s">
         <v>34</v>
@@ -6662,7 +6662,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="10">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F218" s="8" t="s">
         <v>28</v>
@@ -6685,7 +6685,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="10">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F219" s="8" t="s">
         <v>31</v>
@@ -6708,7 +6708,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="10">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F220" s="8" t="s">
         <v>28</v>
@@ -6731,7 +6731,7 @@
         <v>27</v>
       </c>
       <c r="E221" s="10">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F221" s="8" t="s">
         <v>34</v>
@@ -6754,7 +6754,7 @@
         <v>27</v>
       </c>
       <c r="E222" s="10">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F222" s="8" t="s">
         <v>28</v>
@@ -6777,7 +6777,7 @@
         <v>27</v>
       </c>
       <c r="E223" s="10">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F223" s="8" t="s">
         <v>31</v>
@@ -6800,7 +6800,7 @@
         <v>27</v>
       </c>
       <c r="E224" s="10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F224" s="8" t="s">
         <v>28</v>
@@ -6846,7 +6846,7 @@
         <v>27</v>
       </c>
       <c r="E226" s="10">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F226" s="8" t="s">
         <v>28</v>
@@ -6869,7 +6869,7 @@
         <v>27</v>
       </c>
       <c r="E227" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F227" s="8" t="s">
         <v>28</v>
@@ -6892,7 +6892,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="10">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F228" s="8" t="s">
         <v>31</v>
@@ -6915,7 +6915,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="10">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F229" s="8" t="s">
         <v>28</v>
@@ -6938,7 +6938,7 @@
         <v>27</v>
       </c>
       <c r="E230" s="10">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F230" s="8" t="s">
         <v>34</v>
@@ -6961,7 +6961,7 @@
         <v>27</v>
       </c>
       <c r="E231" s="10">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F231" s="8" t="s">
         <v>28</v>
@@ -6984,7 +6984,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="10">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F232" s="8" t="s">
         <v>31</v>
@@ -7007,7 +7007,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="10">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F233" s="8" t="s">
         <v>28</v>
@@ -7030,7 +7030,7 @@
         <v>27</v>
       </c>
       <c r="E234" s="10">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F234" s="8" t="s">
         <v>34</v>
@@ -7053,7 +7053,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="10">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F235" s="8" t="s">
         <v>28</v>
@@ -7076,7 +7076,7 @@
         <v>27</v>
       </c>
       <c r="E236" s="10">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F236" s="8" t="s">
         <v>31</v>
@@ -7099,7 +7099,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="10">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F237" s="8" t="s">
         <v>28</v>
@@ -7122,7 +7122,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="10">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F238" s="8" t="s">
         <v>34</v>
@@ -7145,7 +7145,7 @@
         <v>27</v>
       </c>
       <c r="E239" s="10">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F239" s="8" t="s">
         <v>28</v>
@@ -7168,7 +7168,7 @@
         <v>27</v>
       </c>
       <c r="E240" s="10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F240" s="8" t="s">
         <v>31</v>
@@ -7191,7 +7191,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="10">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F241" s="8" t="s">
         <v>28</v>
@@ -7214,7 +7214,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="10">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F242" s="8" t="s">
         <v>34</v>
@@ -7237,7 +7237,7 @@
         <v>27</v>
       </c>
       <c r="E243" s="10">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F243" s="8" t="s">
         <v>28</v>
@@ -7260,7 +7260,7 @@
         <v>27</v>
       </c>
       <c r="E244" s="10">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F244" s="8" t="s">
         <v>31</v>
@@ -7283,7 +7283,7 @@
         <v>27</v>
       </c>
       <c r="E245" s="10">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F245" s="8" t="s">
         <v>28</v>
@@ -7306,7 +7306,7 @@
         <v>27</v>
       </c>
       <c r="E246" s="10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F246" s="8" t="s">
         <v>34</v>
@@ -7329,7 +7329,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="10">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F247" s="8" t="s">
         <v>28</v>
@@ -7352,7 +7352,7 @@
         <v>27</v>
       </c>
       <c r="E248" s="10">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F248" s="8" t="s">
         <v>31</v>
@@ -7398,7 +7398,7 @@
         <v>27</v>
       </c>
       <c r="E250" s="10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F250" s="8" t="s">
         <v>34</v>
@@ -7444,7 +7444,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="10">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F252" s="8" t="s">
         <v>28</v>
@@ -7467,7 +7467,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="10">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F253" s="8" t="s">
         <v>31</v>
@@ -7513,7 +7513,7 @@
         <v>27</v>
       </c>
       <c r="E255" s="10">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F255" s="8" t="s">
         <v>34</v>
@@ -7559,7 +7559,7 @@
         <v>27</v>
       </c>
       <c r="E257" s="10">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F257" s="8" t="s">
         <v>31</v>
@@ -7582,7 +7582,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="10">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F258" s="8" t="s">
         <v>28</v>
@@ -7605,7 +7605,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="10">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F259" s="8" t="s">
         <v>34</v>
@@ -7628,7 +7628,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="10">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F260" s="8" t="s">
         <v>28</v>
@@ -7651,7 +7651,7 @@
         <v>27</v>
       </c>
       <c r="E261" s="10">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F261" s="8" t="s">
         <v>31</v>
@@ -7674,7 +7674,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="10">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F262" s="8" t="s">
         <v>28</v>
@@ -7697,7 +7697,7 @@
         <v>27</v>
       </c>
       <c r="E263" s="10">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F263" s="8" t="s">
         <v>34</v>
@@ -7720,7 +7720,7 @@
         <v>27</v>
       </c>
       <c r="E264" s="10">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F264" s="8" t="s">
         <v>28</v>
@@ -7743,7 +7743,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="10">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F265" s="8" t="s">
         <v>31</v>
@@ -7766,7 +7766,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="10">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F266" s="8" t="s">
         <v>28</v>
@@ -7789,7 +7789,7 @@
         <v>27</v>
       </c>
       <c r="E267" s="10">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F267" s="8" t="s">
         <v>34</v>
@@ -7835,7 +7835,7 @@
         <v>27</v>
       </c>
       <c r="E269" s="10">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F269" s="8" t="s">
         <v>31</v>
@@ -7881,7 +7881,7 @@
         <v>27</v>
       </c>
       <c r="E271" s="10">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F271" s="8" t="s">
         <v>34</v>
@@ -7904,7 +7904,7 @@
         <v>27</v>
       </c>
       <c r="E272" s="10">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F272" s="8" t="s">
         <v>28</v>
@@ -7927,7 +7927,7 @@
         <v>27</v>
       </c>
       <c r="E273" s="10">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F273" s="8" t="s">
         <v>31</v>
@@ -7950,7 +7950,7 @@
         <v>27</v>
       </c>
       <c r="E274" s="10">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F274" s="8" t="s">
         <v>28</v>
@@ -7973,7 +7973,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="10">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F275" s="8" t="s">
         <v>34</v>
@@ -7996,7 +7996,7 @@
         <v>27</v>
       </c>
       <c r="E276" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F276" s="8" t="s">
         <v>28</v>
@@ -8019,7 +8019,7 @@
         <v>27</v>
       </c>
       <c r="E277" s="10">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F277" s="8" t="s">
         <v>28</v>
@@ -8042,7 +8042,7 @@
         <v>27</v>
       </c>
       <c r="E278" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F278" s="8" t="s">
         <v>31</v>
@@ -8065,7 +8065,7 @@
         <v>27</v>
       </c>
       <c r="E279" s="10">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F279" s="8" t="s">
         <v>28</v>
@@ -8088,7 +8088,7 @@
         <v>27</v>
       </c>
       <c r="E280" s="10">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F280" s="8" t="s">
         <v>34</v>
@@ -8111,7 +8111,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="10">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F281" s="8" t="s">
         <v>28</v>
@@ -8134,7 +8134,7 @@
         <v>27</v>
       </c>
       <c r="E282" s="10">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F282" s="8" t="s">
         <v>31</v>
@@ -8157,7 +8157,7 @@
         <v>27</v>
       </c>
       <c r="E283" s="10">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F283" s="8" t="s">
         <v>28</v>
@@ -8180,7 +8180,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="10">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F284" s="8" t="s">
         <v>34</v>
@@ -8203,7 +8203,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="10">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F285" s="8" t="s">
         <v>28</v>
@@ -8226,7 +8226,7 @@
         <v>27</v>
       </c>
       <c r="E286" s="10">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F286" s="8" t="s">
         <v>31</v>
@@ -8249,7 +8249,7 @@
         <v>27</v>
       </c>
       <c r="E287" s="10">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F287" s="8" t="s">
         <v>28</v>
@@ -8272,7 +8272,7 @@
         <v>27</v>
       </c>
       <c r="E288" s="10">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F288" s="8" t="s">
         <v>34</v>
@@ -8295,7 +8295,7 @@
         <v>27</v>
       </c>
       <c r="E289" s="10">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F289" s="8" t="s">
         <v>28</v>
@@ -8318,7 +8318,7 @@
         <v>27</v>
       </c>
       <c r="E290" s="10">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F290" s="8" t="s">
         <v>31</v>
@@ -8341,7 +8341,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="10">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F291" s="8" t="s">
         <v>28</v>
@@ -8364,7 +8364,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="10">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F292" s="8" t="s">
         <v>34</v>
@@ -8387,7 +8387,7 @@
         <v>27</v>
       </c>
       <c r="E293" s="10">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F293" s="8" t="s">
         <v>28</v>
@@ -8410,7 +8410,7 @@
         <v>27</v>
       </c>
       <c r="E294" s="10">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F294" s="8" t="s">
         <v>31</v>
@@ -8433,7 +8433,7 @@
         <v>27</v>
       </c>
       <c r="E295" s="10">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F295" s="8" t="s">
         <v>28</v>
@@ -8456,7 +8456,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="10">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F296" s="8" t="s">
         <v>34</v>
@@ -8502,7 +8502,7 @@
         <v>27</v>
       </c>
       <c r="E298" s="10">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F298" s="8" t="s">
         <v>31</v>
@@ -8525,7 +8525,7 @@
         <v>27</v>
       </c>
       <c r="E299" s="10">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F299" s="8" t="s">
         <v>28</v>
@@ -8548,7 +8548,7 @@
         <v>27</v>
       </c>
       <c r="E300" s="10">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F300" s="8" t="s">
         <v>34</v>
@@ -8636,7 +8636,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -8705,7 +8705,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>34</v>
@@ -8728,7 +8728,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -8751,7 +8751,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F7" t="s">
         <v>31</v>
@@ -8774,7 +8774,7 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -8797,7 +8797,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
@@ -8820,7 +8820,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -8843,7 +8843,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F11" t="s">
         <v>31</v>
@@ -8866,7 +8866,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -8889,7 +8889,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
         <v>34</v>
@@ -8958,7 +8958,7 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -8981,7 +8981,7 @@
         <v>27</v>
       </c>
       <c r="E17">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s">
         <v>34</v>
@@ -9004,7 +9004,7 @@
         <v>27</v>
       </c>
       <c r="E18">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -9027,7 +9027,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F19" t="s">
         <v>31</v>
@@ -9050,7 +9050,7 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -9073,7 +9073,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F21" t="s">
         <v>34</v>
@@ -9096,7 +9096,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -9142,7 +9142,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -9165,7 +9165,7 @@
         <v>27</v>
       </c>
       <c r="E25">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F25" t="s">
         <v>34</v>
@@ -9188,7 +9188,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -9211,7 +9211,7 @@
         <v>27</v>
       </c>
       <c r="E27">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F27" t="s">
         <v>31</v>
@@ -9257,7 +9257,7 @@
         <v>27</v>
       </c>
       <c r="E29">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F29" t="s">
         <v>34</v>
@@ -9280,7 +9280,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -9303,7 +9303,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F31" t="s">
         <v>31</v>
@@ -9326,7 +9326,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -9349,7 +9349,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F33" t="s">
         <v>31</v>
@@ -9372,7 +9372,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -9395,7 +9395,7 @@
         <v>27</v>
       </c>
       <c r="E35">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
@@ -9418,7 +9418,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -9441,7 +9441,7 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F37" t="s">
         <v>31</v>
@@ -9464,7 +9464,7 @@
         <v>27</v>
       </c>
       <c r="E38">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -9487,7 +9487,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F39" t="s">
         <v>34</v>
@@ -9510,7 +9510,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -9533,7 +9533,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F41" t="s">
         <v>31</v>
@@ -9556,7 +9556,7 @@
         <v>27</v>
       </c>
       <c r="E42">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -9579,7 +9579,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F43" t="s">
         <v>34</v>
@@ -9602,7 +9602,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -9625,7 +9625,7 @@
         <v>27</v>
       </c>
       <c r="E45">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F45" t="s">
         <v>31</v>
@@ -9648,7 +9648,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -9694,7 +9694,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -9717,7 +9717,7 @@
         <v>27</v>
       </c>
       <c r="E49">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F49" t="s">
         <v>31</v>
@@ -9740,7 +9740,7 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F50" t="s">
         <v>28</v>
@@ -9763,7 +9763,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F51" t="s">
         <v>34</v>
@@ -9786,7 +9786,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -9809,7 +9809,7 @@
         <v>27</v>
       </c>
       <c r="E53">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F53" t="s">
         <v>31</v>
@@ -9855,7 +9855,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F55" t="s">
         <v>34</v>
@@ -9878,7 +9878,7 @@
         <v>27</v>
       </c>
       <c r="E56">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -9924,7 +9924,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -9947,7 +9947,7 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F59" t="s">
         <v>34</v>
@@ -9970,7 +9970,7 @@
         <v>27</v>
       </c>
       <c r="E60">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -9993,7 +9993,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F61" t="s">
         <v>31</v>
@@ -10016,7 +10016,7 @@
         <v>27</v>
       </c>
       <c r="E62">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F62" t="s">
         <v>28</v>
@@ -10039,7 +10039,7 @@
         <v>27</v>
       </c>
       <c r="E63">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F63" t="s">
         <v>31</v>
@@ -10062,7 +10062,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -10085,7 +10085,7 @@
         <v>27</v>
       </c>
       <c r="E65">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F65" t="s">
         <v>34</v>
@@ -10108,7 +10108,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -10131,7 +10131,7 @@
         <v>27</v>
       </c>
       <c r="E67">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F67" t="s">
         <v>31</v>
@@ -10154,7 +10154,7 @@
         <v>27</v>
       </c>
       <c r="E68">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
@@ -10177,7 +10177,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F69" t="s">
         <v>34</v>
@@ -10200,7 +10200,7 @@
         <v>27</v>
       </c>
       <c r="E70">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -10223,7 +10223,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F71" t="s">
         <v>31</v>
@@ -10246,7 +10246,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -10269,7 +10269,7 @@
         <v>27</v>
       </c>
       <c r="E73">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F73" t="s">
         <v>34</v>
@@ -10292,7 +10292,7 @@
         <v>27</v>
       </c>
       <c r="E74">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -10315,7 +10315,7 @@
         <v>27</v>
       </c>
       <c r="E75">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F75" t="s">
         <v>31</v>
@@ -10338,7 +10338,7 @@
         <v>27</v>
       </c>
       <c r="E76">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
@@ -10361,7 +10361,7 @@
         <v>27</v>
       </c>
       <c r="E77">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F77" t="s">
         <v>34</v>
@@ -10384,7 +10384,7 @@
         <v>27</v>
       </c>
       <c r="E78">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
@@ -10407,7 +10407,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F79" t="s">
         <v>31</v>
@@ -10430,7 +10430,7 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
@@ -10453,7 +10453,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F81" t="s">
         <v>34</v>
@@ -10476,7 +10476,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -10499,7 +10499,7 @@
         <v>27</v>
       </c>
       <c r="E83">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F83" t="s">
         <v>31</v>
@@ -10545,7 +10545,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F85" t="s">
         <v>34</v>
@@ -10568,7 +10568,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -10591,7 +10591,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F87" t="s">
         <v>31</v>
@@ -10614,7 +10614,7 @@
         <v>27</v>
       </c>
       <c r="E88">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -10637,7 +10637,7 @@
         <v>27</v>
       </c>
       <c r="E89">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F89" t="s">
         <v>34</v>
@@ -10660,7 +10660,7 @@
         <v>27</v>
       </c>
       <c r="E90">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F90" t="s">
         <v>28</v>
@@ -10683,7 +10683,7 @@
         <v>27</v>
       </c>
       <c r="E91">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F91" t="s">
         <v>31</v>
@@ -10706,7 +10706,7 @@
         <v>27</v>
       </c>
       <c r="E92">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
@@ -10729,7 +10729,7 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F93" t="s">
         <v>31</v>
@@ -10752,7 +10752,7 @@
         <v>27</v>
       </c>
       <c r="E94">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -10775,7 +10775,7 @@
         <v>27</v>
       </c>
       <c r="E95">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F95" t="s">
         <v>34</v>
@@ -10798,7 +10798,7 @@
         <v>27</v>
       </c>
       <c r="E96">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -10821,7 +10821,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F97" t="s">
         <v>31</v>
@@ -10844,7 +10844,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -10867,7 +10867,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F99" t="s">
         <v>34</v>
@@ -10890,7 +10890,7 @@
         <v>27</v>
       </c>
       <c r="E100">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
@@ -10913,7 +10913,7 @@
         <v>27</v>
       </c>
       <c r="E101">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F101" t="s">
         <v>31</v>
@@ -10936,7 +10936,7 @@
         <v>27</v>
       </c>
       <c r="E102">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
@@ -10959,7 +10959,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F103" t="s">
         <v>34</v>
@@ -10982,7 +10982,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -11005,7 +11005,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F105" t="s">
         <v>31</v>
@@ -11028,7 +11028,7 @@
         <v>27</v>
       </c>
       <c r="E106">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
@@ -11051,7 +11051,7 @@
         <v>27</v>
       </c>
       <c r="E107">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F107" t="s">
         <v>34</v>
@@ -11074,7 +11074,7 @@
         <v>27</v>
       </c>
       <c r="E108">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
@@ -11097,7 +11097,7 @@
         <v>27</v>
       </c>
       <c r="E109">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F109" t="s">
         <v>31</v>
@@ -11120,7 +11120,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -11143,7 +11143,7 @@
         <v>27</v>
       </c>
       <c r="E111">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F111" t="s">
         <v>34</v>
@@ -11166,7 +11166,7 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F112" t="s">
         <v>28</v>
@@ -11189,7 +11189,7 @@
         <v>27</v>
       </c>
       <c r="E113">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F113" t="s">
         <v>31</v>
@@ -11212,7 +11212,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -11235,7 +11235,7 @@
         <v>27</v>
       </c>
       <c r="E115">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F115" t="s">
         <v>34</v>
@@ -11258,7 +11258,7 @@
         <v>27</v>
       </c>
       <c r="E116">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F116" t="s">
         <v>28</v>
@@ -11281,7 +11281,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F117" t="s">
         <v>31</v>
@@ -11304,7 +11304,7 @@
         <v>27</v>
       </c>
       <c r="E118">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F118" t="s">
         <v>28</v>
@@ -11327,7 +11327,7 @@
         <v>27</v>
       </c>
       <c r="E119">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F119" t="s">
         <v>34</v>
@@ -11350,7 +11350,7 @@
         <v>27</v>
       </c>
       <c r="E120">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
@@ -11373,7 +11373,7 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F121" t="s">
         <v>31</v>
@@ -11396,7 +11396,7 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -11419,7 +11419,7 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F123" t="s">
         <v>31</v>
@@ -11442,7 +11442,7 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F124" t="s">
         <v>28</v>
@@ -11465,7 +11465,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F125" t="s">
         <v>34</v>
@@ -11488,7 +11488,7 @@
         <v>27</v>
       </c>
       <c r="E126">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
@@ -11534,7 +11534,7 @@
         <v>27</v>
       </c>
       <c r="E128">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -11557,7 +11557,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F129" t="s">
         <v>34</v>
@@ -11580,7 +11580,7 @@
         <v>27</v>
       </c>
       <c r="E130">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
@@ -11603,7 +11603,7 @@
         <v>27</v>
       </c>
       <c r="E131">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F131" t="s">
         <v>31</v>
@@ -11649,7 +11649,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F133" t="s">
         <v>34</v>
@@ -11672,7 +11672,7 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -11695,7 +11695,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F135" t="s">
         <v>31</v>
@@ -11718,7 +11718,7 @@
         <v>27</v>
       </c>
       <c r="E136">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
@@ -11741,7 +11741,7 @@
         <v>27</v>
       </c>
       <c r="E137">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F137" t="s">
         <v>34</v>
@@ -11764,7 +11764,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -11787,7 +11787,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F139" t="s">
         <v>31</v>
@@ -11810,7 +11810,7 @@
         <v>27</v>
       </c>
       <c r="E140">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
@@ -11833,7 +11833,7 @@
         <v>27</v>
       </c>
       <c r="E141">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F141" t="s">
         <v>34</v>
@@ -11856,7 +11856,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -11879,7 +11879,7 @@
         <v>27</v>
       </c>
       <c r="E143">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F143" t="s">
         <v>31</v>
@@ -11902,7 +11902,7 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F144" t="s">
         <v>28</v>
@@ -11925,7 +11925,7 @@
         <v>27</v>
       </c>
       <c r="E145">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F145" t="s">
         <v>34</v>
@@ -11948,7 +11948,7 @@
         <v>27</v>
       </c>
       <c r="E146">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F146" t="s">
         <v>28</v>
@@ -11971,7 +11971,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F147" t="s">
         <v>31</v>
@@ -11994,7 +11994,7 @@
         <v>27</v>
       </c>
       <c r="E148">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
@@ -12017,7 +12017,7 @@
         <v>27</v>
       </c>
       <c r="E149">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F149" t="s">
         <v>34</v>
@@ -12040,7 +12040,7 @@
         <v>27</v>
       </c>
       <c r="E150">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
@@ -12063,7 +12063,7 @@
         <v>27</v>
       </c>
       <c r="E151">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F151" t="s">
         <v>31</v>
@@ -12086,7 +12086,7 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F152" t="s">
         <v>28</v>
@@ -12109,7 +12109,7 @@
         <v>27</v>
       </c>
       <c r="E153">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F153" t="s">
         <v>31</v>
@@ -12132,7 +12132,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -12155,7 +12155,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F155" t="s">
         <v>34</v>
@@ -12178,7 +12178,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -12201,7 +12201,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F157" t="s">
         <v>31</v>
@@ -12224,7 +12224,7 @@
         <v>27</v>
       </c>
       <c r="E158">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F158" t="s">
         <v>28</v>
@@ -12247,7 +12247,7 @@
         <v>27</v>
       </c>
       <c r="E159">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F159" t="s">
         <v>34</v>
@@ -12270,7 +12270,7 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F160" t="s">
         <v>28</v>
@@ -12293,7 +12293,7 @@
         <v>27</v>
       </c>
       <c r="E161">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F161" t="s">
         <v>31</v>
@@ -12316,7 +12316,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -12339,7 +12339,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F163" t="s">
         <v>34</v>
@@ -12385,7 +12385,7 @@
         <v>27</v>
       </c>
       <c r="E165">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F165" t="s">
         <v>31</v>
@@ -12408,7 +12408,7 @@
         <v>27</v>
       </c>
       <c r="E166">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -12431,7 +12431,7 @@
         <v>27</v>
       </c>
       <c r="E167">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F167" t="s">
         <v>34</v>
@@ -12454,7 +12454,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -12500,7 +12500,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -12523,7 +12523,7 @@
         <v>27</v>
       </c>
       <c r="E171">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F171" t="s">
         <v>34</v>
@@ -12546,7 +12546,7 @@
         <v>27</v>
       </c>
       <c r="E172">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
@@ -12569,7 +12569,7 @@
         <v>27</v>
       </c>
       <c r="E173">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F173" t="s">
         <v>31</v>
@@ -12592,7 +12592,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -12615,7 +12615,7 @@
         <v>27</v>
       </c>
       <c r="E175">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F175" t="s">
         <v>34</v>
@@ -12638,7 +12638,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -12661,7 +12661,7 @@
         <v>27</v>
       </c>
       <c r="E177">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
@@ -12684,7 +12684,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F178" t="s">
         <v>31</v>
@@ -12707,7 +12707,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -12753,7 +12753,7 @@
         <v>27</v>
       </c>
       <c r="E181">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F181" t="s">
         <v>28</v>
@@ -12776,7 +12776,7 @@
         <v>27</v>
       </c>
       <c r="E182">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F182" t="s">
         <v>31</v>
@@ -12799,7 +12799,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -12822,7 +12822,7 @@
         <v>27</v>
       </c>
       <c r="E184">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F184" t="s">
         <v>34</v>
@@ -12845,7 +12845,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -12868,7 +12868,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F186" t="s">
         <v>31</v>
@@ -12891,7 +12891,7 @@
         <v>27</v>
       </c>
       <c r="E187">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F187" t="s">
         <v>28</v>
@@ -12914,7 +12914,7 @@
         <v>27</v>
       </c>
       <c r="E188">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F188" t="s">
         <v>34</v>
@@ -12937,7 +12937,7 @@
         <v>27</v>
       </c>
       <c r="E189">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F189" t="s">
         <v>28</v>
@@ -12960,7 +12960,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F190" t="s">
         <v>31</v>
@@ -12983,7 +12983,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -13006,7 +13006,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F192" t="s">
         <v>34</v>
@@ -13029,7 +13029,7 @@
         <v>27</v>
       </c>
       <c r="E193">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -13052,7 +13052,7 @@
         <v>27</v>
       </c>
       <c r="E194">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F194" t="s">
         <v>31</v>
@@ -13075,7 +13075,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -13121,7 +13121,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -13144,7 +13144,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F198" t="s">
         <v>31</v>
@@ -13167,7 +13167,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -13190,7 +13190,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F200" t="s">
         <v>34</v>
@@ -13213,7 +13213,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -13259,7 +13259,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F203" t="s">
         <v>31</v>
@@ -13282,7 +13282,7 @@
         <v>27</v>
       </c>
       <c r="E204">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -13305,7 +13305,7 @@
         <v>27</v>
       </c>
       <c r="E205">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F205" t="s">
         <v>34</v>
@@ -13328,7 +13328,7 @@
         <v>27</v>
       </c>
       <c r="E206">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -13351,7 +13351,7 @@
         <v>27</v>
       </c>
       <c r="E207">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F207" t="s">
         <v>31</v>
@@ -13374,7 +13374,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -13397,7 +13397,7 @@
         <v>27</v>
       </c>
       <c r="E209">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F209" t="s">
         <v>34</v>
@@ -13420,7 +13420,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -13443,7 +13443,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F211" t="s">
         <v>31</v>
@@ -13466,7 +13466,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -13489,7 +13489,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F213" t="s">
         <v>34</v>
@@ -13512,7 +13512,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -13535,7 +13535,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F215" t="s">
         <v>31</v>
@@ -13558,7 +13558,7 @@
         <v>27</v>
       </c>
       <c r="E216">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F216" t="s">
         <v>28</v>
@@ -13581,7 +13581,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F217" t="s">
         <v>34</v>
@@ -13604,7 +13604,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -13627,7 +13627,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F219" t="s">
         <v>31</v>
@@ -13650,7 +13650,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -13673,7 +13673,7 @@
         <v>27</v>
       </c>
       <c r="E221">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F221" t="s">
         <v>34</v>
@@ -13696,7 +13696,7 @@
         <v>27</v>
       </c>
       <c r="E222">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F222" t="s">
         <v>28</v>
@@ -13719,7 +13719,7 @@
         <v>27</v>
       </c>
       <c r="E223">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F223" t="s">
         <v>31</v>
@@ -13742,7 +13742,7 @@
         <v>27</v>
       </c>
       <c r="E224">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F224" t="s">
         <v>28</v>
@@ -13788,7 +13788,7 @@
         <v>27</v>
       </c>
       <c r="E226">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F226" t="s">
         <v>28</v>
@@ -13811,7 +13811,7 @@
         <v>27</v>
       </c>
       <c r="E227">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F227" t="s">
         <v>28</v>
@@ -13834,7 +13834,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F228" t="s">
         <v>31</v>
@@ -13857,7 +13857,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -13880,7 +13880,7 @@
         <v>27</v>
       </c>
       <c r="E230">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F230" t="s">
         <v>34</v>
@@ -13903,7 +13903,7 @@
         <v>27</v>
       </c>
       <c r="E231">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F231" t="s">
         <v>28</v>
@@ -13926,7 +13926,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F232" t="s">
         <v>31</v>
@@ -13949,7 +13949,7 @@
         <v>27</v>
       </c>
       <c r="E233">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F233" t="s">
         <v>28</v>
@@ -13972,7 +13972,7 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F234" t="s">
         <v>34</v>
@@ -13995,7 +13995,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -14018,7 +14018,7 @@
         <v>27</v>
       </c>
       <c r="E236">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F236" t="s">
         <v>31</v>
@@ -14041,7 +14041,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -14064,7 +14064,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F238" t="s">
         <v>34</v>
@@ -14087,7 +14087,7 @@
         <v>27</v>
       </c>
       <c r="E239">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F239" t="s">
         <v>28</v>
@@ -14110,7 +14110,7 @@
         <v>27</v>
       </c>
       <c r="E240">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F240" t="s">
         <v>31</v>
@@ -14133,7 +14133,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -14156,7 +14156,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F242" t="s">
         <v>34</v>
@@ -14179,7 +14179,7 @@
         <v>27</v>
       </c>
       <c r="E243">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -14202,7 +14202,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F244" t="s">
         <v>31</v>
@@ -14225,7 +14225,7 @@
         <v>27</v>
       </c>
       <c r="E245">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F245" t="s">
         <v>28</v>
@@ -14248,7 +14248,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F246" t="s">
         <v>34</v>
@@ -14271,7 +14271,7 @@
         <v>27</v>
       </c>
       <c r="E247">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F247" t="s">
         <v>28</v>
@@ -14294,7 +14294,7 @@
         <v>27</v>
       </c>
       <c r="E248">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F248" t="s">
         <v>31</v>
@@ -14340,7 +14340,7 @@
         <v>27</v>
       </c>
       <c r="E250">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F250" t="s">
         <v>34</v>
@@ -14386,7 +14386,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -14409,7 +14409,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F253" t="s">
         <v>31</v>
@@ -14455,7 +14455,7 @@
         <v>27</v>
       </c>
       <c r="E255">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F255" t="s">
         <v>34</v>
@@ -14501,7 +14501,7 @@
         <v>27</v>
       </c>
       <c r="E257">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F257" t="s">
         <v>31</v>
@@ -14524,7 +14524,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -14547,7 +14547,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F259" t="s">
         <v>34</v>
@@ -14570,7 +14570,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -14593,7 +14593,7 @@
         <v>27</v>
       </c>
       <c r="E261">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F261" t="s">
         <v>31</v>
@@ -14616,7 +14616,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -14639,7 +14639,7 @@
         <v>27</v>
       </c>
       <c r="E263">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F263" t="s">
         <v>34</v>
@@ -14662,7 +14662,7 @@
         <v>27</v>
       </c>
       <c r="E264">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -14685,7 +14685,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F265" t="s">
         <v>31</v>
@@ -14708,7 +14708,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -14731,7 +14731,7 @@
         <v>27</v>
       </c>
       <c r="E267">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F267" t="s">
         <v>34</v>
@@ -14777,7 +14777,7 @@
         <v>27</v>
       </c>
       <c r="E269">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F269" t="s">
         <v>31</v>
@@ -14823,7 +14823,7 @@
         <v>27</v>
       </c>
       <c r="E271">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F271" t="s">
         <v>34</v>
@@ -14846,7 +14846,7 @@
         <v>27</v>
       </c>
       <c r="E272">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F272" t="s">
         <v>28</v>
@@ -14869,7 +14869,7 @@
         <v>27</v>
       </c>
       <c r="E273">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F273" t="s">
         <v>31</v>
@@ -14892,7 +14892,7 @@
         <v>27</v>
       </c>
       <c r="E274">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F274" t="s">
         <v>28</v>
@@ -14915,7 +14915,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F275" t="s">
         <v>34</v>
@@ -14938,7 +14938,7 @@
         <v>27</v>
       </c>
       <c r="E276">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F276" t="s">
         <v>28</v>
@@ -14961,7 +14961,7 @@
         <v>27</v>
       </c>
       <c r="E277">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F277" t="s">
         <v>28</v>
@@ -14984,7 +14984,7 @@
         <v>27</v>
       </c>
       <c r="E278">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F278" t="s">
         <v>31</v>
@@ -15007,7 +15007,7 @@
         <v>27</v>
       </c>
       <c r="E279">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -15030,7 +15030,7 @@
         <v>27</v>
       </c>
       <c r="E280">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F280" t="s">
         <v>34</v>
@@ -15053,7 +15053,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -15076,7 +15076,7 @@
         <v>27</v>
       </c>
       <c r="E282">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F282" t="s">
         <v>31</v>
@@ -15099,7 +15099,7 @@
         <v>27</v>
       </c>
       <c r="E283">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F283" t="s">
         <v>28</v>
@@ -15122,7 +15122,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F284" t="s">
         <v>34</v>
@@ -15145,7 +15145,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -15168,7 +15168,7 @@
         <v>27</v>
       </c>
       <c r="E286">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F286" t="s">
         <v>31</v>
@@ -15191,7 +15191,7 @@
         <v>27</v>
       </c>
       <c r="E287">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F287" t="s">
         <v>28</v>
@@ -15214,7 +15214,7 @@
         <v>27</v>
       </c>
       <c r="E288">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F288" t="s">
         <v>34</v>
@@ -15237,7 +15237,7 @@
         <v>27</v>
       </c>
       <c r="E289">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F289" t="s">
         <v>28</v>
@@ -15260,7 +15260,7 @@
         <v>27</v>
       </c>
       <c r="E290">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F290" t="s">
         <v>31</v>
@@ -15283,7 +15283,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -15306,7 +15306,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F292" t="s">
         <v>34</v>
@@ -15329,7 +15329,7 @@
         <v>27</v>
       </c>
       <c r="E293">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -15352,7 +15352,7 @@
         <v>27</v>
       </c>
       <c r="E294">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F294" t="s">
         <v>31</v>
@@ -15375,7 +15375,7 @@
         <v>27</v>
       </c>
       <c r="E295">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F295" t="s">
         <v>28</v>
@@ -15398,7 +15398,7 @@
         <v>27</v>
       </c>
       <c r="E296">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F296" t="s">
         <v>34</v>
@@ -15444,7 +15444,7 @@
         <v>27</v>
       </c>
       <c r="E298">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F298" t="s">
         <v>31</v>
@@ -15467,7 +15467,7 @@
         <v>27</v>
       </c>
       <c r="E299">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F299" t="s">
         <v>28</v>
@@ -15490,7 +15490,7 @@
         <v>27</v>
       </c>
       <c r="E300">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F300" t="s">
         <v>34</v>

--- a/all-test-reports/vulnerability/vulnerability_test_report.xlsx
+++ b/all-test-reports/vulnerability/vulnerability_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 11:08:30 am</t>
+    <t>28/7/2026, 11:12:56 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1694,7 +1694,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="10">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>28</v>
@@ -1717,7 +1717,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="10">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>31</v>
@@ -1740,7 +1740,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="10">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>28</v>
@@ -1763,7 +1763,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="10">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>34</v>
@@ -1786,7 +1786,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="10">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>28</v>
@@ -1809,7 +1809,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="10">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>31</v>
@@ -1832,7 +1832,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="10">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>28</v>
@@ -1855,7 +1855,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="10">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>34</v>
@@ -1878,7 +1878,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="10">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>28</v>
@@ -1901,7 +1901,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="10">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>31</v>
@@ -1924,7 +1924,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="10">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>28</v>
@@ -1947,7 +1947,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>34</v>
@@ -1970,7 +1970,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="10">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>28</v>
@@ -1993,7 +1993,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="10">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>31</v>
@@ -2016,7 +2016,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="10">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>28</v>
@@ -2039,7 +2039,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="10">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>34</v>
@@ -2062,7 +2062,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="10">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>28</v>
@@ -2108,7 +2108,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="10">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>28</v>
@@ -2131,7 +2131,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="10">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>34</v>
@@ -2154,7 +2154,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="10">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>28</v>
@@ -2177,7 +2177,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="10">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>31</v>
@@ -2200,7 +2200,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="10">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>28</v>
@@ -2223,7 +2223,7 @@
         <v>27</v>
       </c>
       <c r="E25" s="10">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>34</v>
@@ -2246,7 +2246,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="10">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>28</v>
@@ -2269,7 +2269,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="10">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>31</v>
@@ -2292,7 +2292,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="10">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>28</v>
@@ -2315,7 +2315,7 @@
         <v>27</v>
       </c>
       <c r="E29" s="10">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>34</v>
@@ -2338,7 +2338,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="10">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>28</v>
@@ -2361,7 +2361,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="10">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>31</v>
@@ -2384,7 +2384,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="10">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>28</v>
@@ -2407,7 +2407,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="10">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>31</v>
@@ -2430,7 +2430,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="10">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>28</v>
@@ -2453,7 +2453,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="10">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>34</v>
@@ -2476,7 +2476,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="10">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>28</v>
@@ -2522,7 +2522,7 @@
         <v>27</v>
       </c>
       <c r="E38" s="10">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>28</v>
@@ -2545,7 +2545,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="10">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>34</v>
@@ -2568,7 +2568,7 @@
         <v>27</v>
       </c>
       <c r="E40" s="10">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>28</v>
@@ -2591,7 +2591,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="10">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>31</v>
@@ -2614,7 +2614,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="10">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>28</v>
@@ -2637,7 +2637,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="10">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>34</v>
@@ -2660,7 +2660,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="10">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>28</v>
@@ -2683,7 +2683,7 @@
         <v>27</v>
       </c>
       <c r="E45" s="10">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>31</v>
@@ -2706,7 +2706,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="10">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>28</v>
@@ -2729,7 +2729,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>34</v>
@@ -2752,7 +2752,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="10">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>28</v>
@@ -2775,7 +2775,7 @@
         <v>27</v>
       </c>
       <c r="E49" s="10">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>31</v>
@@ -2798,7 +2798,7 @@
         <v>27</v>
       </c>
       <c r="E50" s="10">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>28</v>
@@ -2821,7 +2821,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="10">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>34</v>
@@ -2844,7 +2844,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="10">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>28</v>
@@ -2867,7 +2867,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="10">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>31</v>
@@ -2890,7 +2890,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="10">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>28</v>
@@ -2913,7 +2913,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="10">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>34</v>
@@ -2936,7 +2936,7 @@
         <v>27</v>
       </c>
       <c r="E56" s="10">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>28</v>
@@ -2959,7 +2959,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="10">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>31</v>
@@ -2982,7 +2982,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="10">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>28</v>
@@ -3005,7 +3005,7 @@
         <v>27</v>
       </c>
       <c r="E59" s="10">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>34</v>
@@ -3028,7 +3028,7 @@
         <v>27</v>
       </c>
       <c r="E60" s="10">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>28</v>
@@ -3051,7 +3051,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="10">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>31</v>
@@ -3074,7 +3074,7 @@
         <v>27</v>
       </c>
       <c r="E62" s="10">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>28</v>
@@ -3097,7 +3097,7 @@
         <v>27</v>
       </c>
       <c r="E63" s="10">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>31</v>
@@ -3120,7 +3120,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="10">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>28</v>
@@ -3143,7 +3143,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="10">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>34</v>
@@ -3166,7 +3166,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="10">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>28</v>
@@ -3189,7 +3189,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="10">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>31</v>
@@ -3212,7 +3212,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="10">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>28</v>
@@ -3235,7 +3235,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="10">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>34</v>
@@ -3258,7 +3258,7 @@
         <v>27</v>
       </c>
       <c r="E70" s="10">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>28</v>
@@ -3281,7 +3281,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="10">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>31</v>
@@ -3304,7 +3304,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="10">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>28</v>
@@ -3327,7 +3327,7 @@
         <v>27</v>
       </c>
       <c r="E73" s="10">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>34</v>
@@ -3350,7 +3350,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="10">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>28</v>
@@ -3373,7 +3373,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>31</v>
@@ -3396,7 +3396,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="10">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>28</v>
@@ -3419,7 +3419,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="10">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>34</v>
@@ -3442,7 +3442,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="10">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>28</v>
@@ -3465,7 +3465,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="10">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>31</v>
@@ -3488,7 +3488,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="10">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>28</v>
@@ -3511,7 +3511,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="10">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>34</v>
@@ -3534,7 +3534,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="10">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>28</v>
@@ -3557,7 +3557,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="10">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>31</v>
@@ -3580,7 +3580,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="10">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>28</v>
@@ -3603,7 +3603,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="10">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>34</v>
@@ -3626,7 +3626,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="10">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>28</v>
@@ -3649,7 +3649,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="10">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>31</v>
@@ -3672,7 +3672,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="10">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>28</v>
@@ -3695,7 +3695,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="10">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>34</v>
@@ -3718,7 +3718,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="10">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>28</v>
@@ -3764,7 +3764,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>28</v>
@@ -3787,7 +3787,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="10">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>31</v>
@@ -3810,7 +3810,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="10">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>28</v>
@@ -3833,7 +3833,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="10">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>34</v>
@@ -3856,7 +3856,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="10">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F96" s="8" t="s">
         <v>28</v>
@@ -3879,7 +3879,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>31</v>
@@ -3902,7 +3902,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="10">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>28</v>
@@ -3925,7 +3925,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="10">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>34</v>
@@ -3971,7 +3971,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="10">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>31</v>
@@ -3994,7 +3994,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="10">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>28</v>
@@ -4017,7 +4017,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="10">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>34</v>
@@ -4040,7 +4040,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="10">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>28</v>
@@ -4063,7 +4063,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="10">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>31</v>
@@ -4086,7 +4086,7 @@
         <v>27</v>
       </c>
       <c r="E106" s="10">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>28</v>
@@ -4109,7 +4109,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>34</v>
@@ -4132,7 +4132,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="10">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>28</v>
@@ -4155,7 +4155,7 @@
         <v>27</v>
       </c>
       <c r="E109" s="10">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>31</v>
@@ -4178,7 +4178,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="10">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>28</v>
@@ -4201,7 +4201,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="10">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>34</v>
@@ -4224,7 +4224,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="10">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>28</v>
@@ -4247,7 +4247,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="10">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F113" s="8" t="s">
         <v>31</v>
@@ -4270,7 +4270,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="10">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>28</v>
@@ -4293,7 +4293,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="10">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>34</v>
@@ -4316,7 +4316,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>28</v>
@@ -4339,7 +4339,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="10">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F117" s="8" t="s">
         <v>31</v>
@@ -4362,7 +4362,7 @@
         <v>27</v>
       </c>
       <c r="E118" s="10">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F118" s="8" t="s">
         <v>28</v>
@@ -4385,7 +4385,7 @@
         <v>27</v>
       </c>
       <c r="E119" s="10">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F119" s="8" t="s">
         <v>34</v>
@@ -4408,7 +4408,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="10">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F120" s="8" t="s">
         <v>28</v>
@@ -4431,7 +4431,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="10">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F121" s="8" t="s">
         <v>31</v>
@@ -4454,7 +4454,7 @@
         <v>27</v>
       </c>
       <c r="E122" s="10">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F122" s="8" t="s">
         <v>28</v>
@@ -4477,7 +4477,7 @@
         <v>27</v>
       </c>
       <c r="E123" s="10">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>31</v>
@@ -4500,7 +4500,7 @@
         <v>27</v>
       </c>
       <c r="E124" s="10">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F124" s="8" t="s">
         <v>28</v>
@@ -4523,7 +4523,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="10">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>34</v>
@@ -4546,7 +4546,7 @@
         <v>27</v>
       </c>
       <c r="E126" s="10">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F126" s="8" t="s">
         <v>28</v>
@@ -4569,7 +4569,7 @@
         <v>27</v>
       </c>
       <c r="E127" s="10">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F127" s="8" t="s">
         <v>31</v>
@@ -4615,7 +4615,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="10">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F129" s="8" t="s">
         <v>34</v>
@@ -4638,7 +4638,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="10">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F130" s="8" t="s">
         <v>28</v>
@@ -4661,7 +4661,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="10">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F131" s="8" t="s">
         <v>31</v>
@@ -4684,7 +4684,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="10">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F132" s="8" t="s">
         <v>28</v>
@@ -4707,7 +4707,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="10">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F133" s="8" t="s">
         <v>34</v>
@@ -4730,7 +4730,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="10">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F134" s="8" t="s">
         <v>28</v>
@@ -4753,7 +4753,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="10">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F135" s="8" t="s">
         <v>31</v>
@@ -4776,7 +4776,7 @@
         <v>27</v>
       </c>
       <c r="E136" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F136" s="8" t="s">
         <v>28</v>
@@ -4799,7 +4799,7 @@
         <v>27</v>
       </c>
       <c r="E137" s="10">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F137" s="8" t="s">
         <v>34</v>
@@ -4822,7 +4822,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="10">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F138" s="8" t="s">
         <v>28</v>
@@ -4845,7 +4845,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="10">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F139" s="8" t="s">
         <v>31</v>
@@ -4868,7 +4868,7 @@
         <v>27</v>
       </c>
       <c r="E140" s="10">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F140" s="8" t="s">
         <v>28</v>
@@ -4914,7 +4914,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="10">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F142" s="8" t="s">
         <v>28</v>
@@ -4960,7 +4960,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="10">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F144" s="8" t="s">
         <v>28</v>
@@ -4983,7 +4983,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="10">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F145" s="8" t="s">
         <v>34</v>
@@ -5006,7 +5006,7 @@
         <v>27</v>
       </c>
       <c r="E146" s="10">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>28</v>
@@ -5029,7 +5029,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="10">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F147" s="8" t="s">
         <v>31</v>
@@ -5052,7 +5052,7 @@
         <v>27</v>
       </c>
       <c r="E148" s="10">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F148" s="8" t="s">
         <v>28</v>
@@ -5075,7 +5075,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="10">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F149" s="8" t="s">
         <v>34</v>
@@ -5098,7 +5098,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="10">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>28</v>
@@ -5121,7 +5121,7 @@
         <v>27</v>
       </c>
       <c r="E151" s="10">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>31</v>
@@ -5144,7 +5144,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="10">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>28</v>
@@ -5167,7 +5167,7 @@
         <v>27</v>
       </c>
       <c r="E153" s="10">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F153" s="8" t="s">
         <v>31</v>
@@ -5190,7 +5190,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="10">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>28</v>
@@ -5213,7 +5213,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="10">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F155" s="8" t="s">
         <v>34</v>
@@ -5236,7 +5236,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="10">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F156" s="8" t="s">
         <v>28</v>
@@ -5259,7 +5259,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F157" s="8" t="s">
         <v>31</v>
@@ -5305,7 +5305,7 @@
         <v>27</v>
       </c>
       <c r="E159" s="10">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F159" s="8" t="s">
         <v>34</v>
@@ -5328,7 +5328,7 @@
         <v>27</v>
       </c>
       <c r="E160" s="10">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F160" s="8" t="s">
         <v>28</v>
@@ -5351,7 +5351,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="10">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F161" s="8" t="s">
         <v>31</v>
@@ -5374,7 +5374,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="10">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F162" s="8" t="s">
         <v>28</v>
@@ -5397,7 +5397,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="10">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F163" s="8" t="s">
         <v>34</v>
@@ -5420,7 +5420,7 @@
         <v>27</v>
       </c>
       <c r="E164" s="10">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F164" s="8" t="s">
         <v>28</v>
@@ -5443,7 +5443,7 @@
         <v>27</v>
       </c>
       <c r="E165" s="10">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F165" s="8" t="s">
         <v>31</v>
@@ -5466,7 +5466,7 @@
         <v>27</v>
       </c>
       <c r="E166" s="10">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F166" s="8" t="s">
         <v>28</v>
@@ -5489,7 +5489,7 @@
         <v>27</v>
       </c>
       <c r="E167" s="10">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F167" s="8" t="s">
         <v>34</v>
@@ -5512,7 +5512,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="10">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F168" s="8" t="s">
         <v>28</v>
@@ -5535,7 +5535,7 @@
         <v>27</v>
       </c>
       <c r="E169" s="10">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F169" s="8" t="s">
         <v>31</v>
@@ -5558,7 +5558,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="10">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F170" s="8" t="s">
         <v>28</v>
@@ -5581,7 +5581,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="10">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F171" s="8" t="s">
         <v>34</v>
@@ -5627,7 +5627,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="10">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F173" s="8" t="s">
         <v>31</v>
@@ -5650,7 +5650,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="10">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F174" s="8" t="s">
         <v>28</v>
@@ -5696,7 +5696,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="10">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F176" s="8" t="s">
         <v>28</v>
@@ -5719,7 +5719,7 @@
         <v>27</v>
       </c>
       <c r="E177" s="10">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F177" s="8" t="s">
         <v>28</v>
@@ -5742,7 +5742,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F178" s="8" t="s">
         <v>31</v>
@@ -5765,7 +5765,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="10">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F179" s="8" t="s">
         <v>28</v>
@@ -5788,7 +5788,7 @@
         <v>27</v>
       </c>
       <c r="E180" s="10">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F180" s="8" t="s">
         <v>34</v>
@@ -5811,7 +5811,7 @@
         <v>27</v>
       </c>
       <c r="E181" s="10">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F181" s="8" t="s">
         <v>28</v>
@@ -5834,7 +5834,7 @@
         <v>27</v>
       </c>
       <c r="E182" s="10">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F182" s="8" t="s">
         <v>31</v>
@@ -5857,7 +5857,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="10">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F183" s="8" t="s">
         <v>28</v>
@@ -5880,7 +5880,7 @@
         <v>27</v>
       </c>
       <c r="E184" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F184" s="8" t="s">
         <v>34</v>
@@ -5903,7 +5903,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="10">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F185" s="8" t="s">
         <v>28</v>
@@ -5926,7 +5926,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="10">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F186" s="8" t="s">
         <v>31</v>
@@ -5949,7 +5949,7 @@
         <v>27</v>
       </c>
       <c r="E187" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F187" s="8" t="s">
         <v>28</v>
@@ -5972,7 +5972,7 @@
         <v>27</v>
       </c>
       <c r="E188" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F188" s="8" t="s">
         <v>34</v>
@@ -5995,7 +5995,7 @@
         <v>27</v>
       </c>
       <c r="E189" s="10">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F189" s="8" t="s">
         <v>28</v>
@@ -6018,7 +6018,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="10">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F190" s="8" t="s">
         <v>31</v>
@@ -6041,7 +6041,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="10">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F191" s="8" t="s">
         <v>28</v>
@@ -6064,7 +6064,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F192" s="8" t="s">
         <v>34</v>
@@ -6087,7 +6087,7 @@
         <v>27</v>
       </c>
       <c r="E193" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F193" s="8" t="s">
         <v>28</v>
@@ -6110,7 +6110,7 @@
         <v>27</v>
       </c>
       <c r="E194" s="10">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F194" s="8" t="s">
         <v>31</v>
@@ -6133,7 +6133,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="10">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F195" s="8" t="s">
         <v>28</v>
@@ -6156,7 +6156,7 @@
         <v>27</v>
       </c>
       <c r="E196" s="10">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F196" s="8" t="s">
         <v>34</v>
@@ -6179,7 +6179,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="10">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F197" s="8" t="s">
         <v>28</v>
@@ -6202,7 +6202,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="10">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F198" s="8" t="s">
         <v>31</v>
@@ -6225,7 +6225,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="10">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F199" s="8" t="s">
         <v>28</v>
@@ -6248,7 +6248,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="10">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F200" s="8" t="s">
         <v>34</v>
@@ -6271,7 +6271,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="10">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F201" s="8" t="s">
         <v>28</v>
@@ -6294,7 +6294,7 @@
         <v>27</v>
       </c>
       <c r="E202" s="10">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F202" s="8" t="s">
         <v>28</v>
@@ -6317,7 +6317,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="10">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F203" s="8" t="s">
         <v>31</v>
@@ -6340,7 +6340,7 @@
         <v>27</v>
       </c>
       <c r="E204" s="10">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F204" s="8" t="s">
         <v>28</v>
@@ -6363,7 +6363,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="10">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F205" s="8" t="s">
         <v>34</v>
@@ -6409,7 +6409,7 @@
         <v>27</v>
       </c>
       <c r="E207" s="10">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F207" s="8" t="s">
         <v>31</v>
@@ -6432,7 +6432,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="10">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F208" s="8" t="s">
         <v>28</v>
@@ -6478,7 +6478,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="10">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F210" s="8" t="s">
         <v>28</v>
@@ -6501,7 +6501,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="10">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F211" s="8" t="s">
         <v>31</v>
@@ -6524,7 +6524,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F212" s="8" t="s">
         <v>28</v>
@@ -6547,7 +6547,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="10">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F213" s="8" t="s">
         <v>34</v>
@@ -6570,7 +6570,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="10">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F214" s="8" t="s">
         <v>28</v>
@@ -6593,7 +6593,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="10">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F215" s="8" t="s">
         <v>31</v>
@@ -6616,7 +6616,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="10">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F216" s="8" t="s">
         <v>28</v>
@@ -6639,7 +6639,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="10">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F217" s="8" t="s">
         <v>34</v>
@@ -6662,7 +6662,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F218" s="8" t="s">
         <v>28</v>
@@ -6685,7 +6685,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="10">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F219" s="8" t="s">
         <v>31</v>
@@ -6708,7 +6708,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="10">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F220" s="8" t="s">
         <v>28</v>
@@ -6731,7 +6731,7 @@
         <v>27</v>
       </c>
       <c r="E221" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F221" s="8" t="s">
         <v>34</v>
@@ -6754,7 +6754,7 @@
         <v>27</v>
       </c>
       <c r="E222" s="10">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F222" s="8" t="s">
         <v>28</v>
@@ -6777,7 +6777,7 @@
         <v>27</v>
       </c>
       <c r="E223" s="10">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F223" s="8" t="s">
         <v>31</v>
@@ -6800,7 +6800,7 @@
         <v>27</v>
       </c>
       <c r="E224" s="10">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F224" s="8" t="s">
         <v>28</v>
@@ -6823,7 +6823,7 @@
         <v>27</v>
       </c>
       <c r="E225" s="10">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F225" s="8" t="s">
         <v>34</v>
@@ -6846,7 +6846,7 @@
         <v>27</v>
       </c>
       <c r="E226" s="10">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F226" s="8" t="s">
         <v>28</v>
@@ -6869,7 +6869,7 @@
         <v>27</v>
       </c>
       <c r="E227" s="10">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F227" s="8" t="s">
         <v>28</v>
@@ -6892,7 +6892,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="10">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F228" s="8" t="s">
         <v>31</v>
@@ -6915,7 +6915,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="10">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F229" s="8" t="s">
         <v>28</v>
@@ -6938,7 +6938,7 @@
         <v>27</v>
       </c>
       <c r="E230" s="10">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F230" s="8" t="s">
         <v>34</v>
@@ -6961,7 +6961,7 @@
         <v>27</v>
       </c>
       <c r="E231" s="10">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F231" s="8" t="s">
         <v>28</v>
@@ -6984,7 +6984,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="10">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F232" s="8" t="s">
         <v>31</v>
@@ -7007,7 +7007,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="10">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F233" s="8" t="s">
         <v>28</v>
@@ -7030,7 +7030,7 @@
         <v>27</v>
       </c>
       <c r="E234" s="10">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F234" s="8" t="s">
         <v>34</v>
@@ -7053,7 +7053,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="10">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F235" s="8" t="s">
         <v>28</v>
@@ -7099,7 +7099,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="10">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F237" s="8" t="s">
         <v>28</v>
@@ -7122,7 +7122,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="10">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F238" s="8" t="s">
         <v>34</v>
@@ -7145,7 +7145,7 @@
         <v>27</v>
       </c>
       <c r="E239" s="10">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F239" s="8" t="s">
         <v>28</v>
@@ -7168,7 +7168,7 @@
         <v>27</v>
       </c>
       <c r="E240" s="10">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F240" s="8" t="s">
         <v>31</v>
@@ -7191,7 +7191,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="10">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F241" s="8" t="s">
         <v>28</v>
@@ -7214,7 +7214,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="10">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F242" s="8" t="s">
         <v>34</v>
@@ -7237,7 +7237,7 @@
         <v>27</v>
       </c>
       <c r="E243" s="10">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F243" s="8" t="s">
         <v>28</v>
@@ -7260,7 +7260,7 @@
         <v>27</v>
       </c>
       <c r="E244" s="10">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F244" s="8" t="s">
         <v>31</v>
@@ -7283,7 +7283,7 @@
         <v>27</v>
       </c>
       <c r="E245" s="10">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F245" s="8" t="s">
         <v>28</v>
@@ -7306,7 +7306,7 @@
         <v>27</v>
       </c>
       <c r="E246" s="10">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F246" s="8" t="s">
         <v>34</v>
@@ -7329,7 +7329,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="10">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F247" s="8" t="s">
         <v>28</v>
@@ -7352,7 +7352,7 @@
         <v>27</v>
       </c>
       <c r="E248" s="10">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F248" s="8" t="s">
         <v>31</v>
@@ -7375,7 +7375,7 @@
         <v>27</v>
       </c>
       <c r="E249" s="10">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F249" s="8" t="s">
         <v>28</v>
@@ -7398,7 +7398,7 @@
         <v>27</v>
       </c>
       <c r="E250" s="10">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F250" s="8" t="s">
         <v>34</v>
@@ -7421,7 +7421,7 @@
         <v>27</v>
       </c>
       <c r="E251" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F251" s="8" t="s">
         <v>28</v>
@@ -7444,7 +7444,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="10">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F252" s="8" t="s">
         <v>28</v>
@@ -7467,7 +7467,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="10">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F253" s="8" t="s">
         <v>31</v>
@@ -7490,7 +7490,7 @@
         <v>27</v>
       </c>
       <c r="E254" s="10">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F254" s="8" t="s">
         <v>28</v>
@@ -7513,7 +7513,7 @@
         <v>27</v>
       </c>
       <c r="E255" s="10">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F255" s="8" t="s">
         <v>34</v>
@@ -7536,7 +7536,7 @@
         <v>27</v>
       </c>
       <c r="E256" s="10">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F256" s="8" t="s">
         <v>28</v>
@@ -7559,7 +7559,7 @@
         <v>27</v>
       </c>
       <c r="E257" s="10">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F257" s="8" t="s">
         <v>31</v>
@@ -7582,7 +7582,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="10">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F258" s="8" t="s">
         <v>28</v>
@@ -7605,7 +7605,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F259" s="8" t="s">
         <v>34</v>
@@ -7628,7 +7628,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="10">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F260" s="8" t="s">
         <v>28</v>
@@ -7651,7 +7651,7 @@
         <v>27</v>
       </c>
       <c r="E261" s="10">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F261" s="8" t="s">
         <v>31</v>
@@ -7674,7 +7674,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="10">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F262" s="8" t="s">
         <v>28</v>
@@ -7697,7 +7697,7 @@
         <v>27</v>
       </c>
       <c r="E263" s="10">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F263" s="8" t="s">
         <v>34</v>
@@ -7720,7 +7720,7 @@
         <v>27</v>
       </c>
       <c r="E264" s="10">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F264" s="8" t="s">
         <v>28</v>
@@ -7743,7 +7743,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="10">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F265" s="8" t="s">
         <v>31</v>
@@ -7766,7 +7766,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="10">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F266" s="8" t="s">
         <v>28</v>
@@ -7789,7 +7789,7 @@
         <v>27</v>
       </c>
       <c r="E267" s="10">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F267" s="8" t="s">
         <v>34</v>
@@ -7812,7 +7812,7 @@
         <v>27</v>
       </c>
       <c r="E268" s="10">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F268" s="8" t="s">
         <v>28</v>
@@ -7835,7 +7835,7 @@
         <v>27</v>
       </c>
       <c r="E269" s="10">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F269" s="8" t="s">
         <v>31</v>
@@ -7858,7 +7858,7 @@
         <v>27</v>
       </c>
       <c r="E270" s="10">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F270" s="8" t="s">
         <v>28</v>
@@ -7881,7 +7881,7 @@
         <v>27</v>
       </c>
       <c r="E271" s="10">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F271" s="8" t="s">
         <v>34</v>
@@ -7904,7 +7904,7 @@
         <v>27</v>
       </c>
       <c r="E272" s="10">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F272" s="8" t="s">
         <v>28</v>
@@ -7927,7 +7927,7 @@
         <v>27</v>
       </c>
       <c r="E273" s="10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F273" s="8" t="s">
         <v>31</v>
@@ -7950,7 +7950,7 @@
         <v>27</v>
       </c>
       <c r="E274" s="10">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F274" s="8" t="s">
         <v>28</v>
@@ -7973,7 +7973,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="10">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F275" s="8" t="s">
         <v>34</v>
@@ -7996,7 +7996,7 @@
         <v>27</v>
       </c>
       <c r="E276" s="10">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F276" s="8" t="s">
         <v>28</v>
@@ -8019,7 +8019,7 @@
         <v>27</v>
       </c>
       <c r="E277" s="10">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F277" s="8" t="s">
         <v>28</v>
@@ -8042,7 +8042,7 @@
         <v>27</v>
       </c>
       <c r="E278" s="10">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F278" s="8" t="s">
         <v>31</v>
@@ -8065,7 +8065,7 @@
         <v>27</v>
       </c>
       <c r="E279" s="10">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F279" s="8" t="s">
         <v>28</v>
@@ -8088,7 +8088,7 @@
         <v>27</v>
       </c>
       <c r="E280" s="10">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F280" s="8" t="s">
         <v>34</v>
@@ -8111,7 +8111,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="10">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F281" s="8" t="s">
         <v>28</v>
@@ -8157,7 +8157,7 @@
         <v>27</v>
       </c>
       <c r="E283" s="10">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F283" s="8" t="s">
         <v>28</v>
@@ -8180,7 +8180,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="10">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F284" s="8" t="s">
         <v>34</v>
@@ -8203,7 +8203,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="10">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F285" s="8" t="s">
         <v>28</v>
@@ -8226,7 +8226,7 @@
         <v>27</v>
       </c>
       <c r="E286" s="10">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F286" s="8" t="s">
         <v>31</v>
@@ -8249,7 +8249,7 @@
         <v>27</v>
       </c>
       <c r="E287" s="10">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F287" s="8" t="s">
         <v>28</v>
@@ -8272,7 +8272,7 @@
         <v>27</v>
       </c>
       <c r="E288" s="10">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F288" s="8" t="s">
         <v>34</v>
@@ -8295,7 +8295,7 @@
         <v>27</v>
       </c>
       <c r="E289" s="10">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F289" s="8" t="s">
         <v>28</v>
@@ -8318,7 +8318,7 @@
         <v>27</v>
       </c>
       <c r="E290" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F290" s="8" t="s">
         <v>31</v>
@@ -8341,7 +8341,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="10">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F291" s="8" t="s">
         <v>28</v>
@@ -8364,7 +8364,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="10">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F292" s="8" t="s">
         <v>34</v>
@@ -8387,7 +8387,7 @@
         <v>27</v>
       </c>
       <c r="E293" s="10">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F293" s="8" t="s">
         <v>28</v>
@@ -8410,7 +8410,7 @@
         <v>27</v>
       </c>
       <c r="E294" s="10">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F294" s="8" t="s">
         <v>31</v>
@@ -8433,7 +8433,7 @@
         <v>27</v>
       </c>
       <c r="E295" s="10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F295" s="8" t="s">
         <v>28</v>
@@ -8456,7 +8456,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F296" s="8" t="s">
         <v>34</v>
@@ -8479,7 +8479,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F297" s="8" t="s">
         <v>28</v>
@@ -8502,7 +8502,7 @@
         <v>27</v>
       </c>
       <c r="E298" s="10">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F298" s="8" t="s">
         <v>31</v>
@@ -8525,7 +8525,7 @@
         <v>27</v>
       </c>
       <c r="E299" s="10">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F299" s="8" t="s">
         <v>28</v>
@@ -8548,7 +8548,7 @@
         <v>27</v>
       </c>
       <c r="E300" s="10">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F300" s="8" t="s">
         <v>34</v>
@@ -8571,7 +8571,7 @@
         <v>27</v>
       </c>
       <c r="E301" s="10">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F301" s="8" t="s">
         <v>28</v>
@@ -8636,7 +8636,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -8659,7 +8659,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
         <v>31</v>
@@ -8682,7 +8682,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -8705,7 +8705,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
         <v>34</v>
@@ -8728,7 +8728,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -8751,7 +8751,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
         <v>31</v>
@@ -8774,7 +8774,7 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -8797,7 +8797,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
@@ -8820,7 +8820,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -8843,7 +8843,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
         <v>31</v>
@@ -8866,7 +8866,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -8889,7 +8889,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
         <v>34</v>
@@ -8912,7 +8912,7 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -8935,7 +8935,7 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F15" t="s">
         <v>31</v>
@@ -8958,7 +8958,7 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -8981,7 +8981,7 @@
         <v>27</v>
       </c>
       <c r="E17">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F17" t="s">
         <v>34</v>
@@ -9004,7 +9004,7 @@
         <v>27</v>
       </c>
       <c r="E18">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -9050,7 +9050,7 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -9073,7 +9073,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F21" t="s">
         <v>34</v>
@@ -9096,7 +9096,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -9119,7 +9119,7 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F23" t="s">
         <v>31</v>
@@ -9142,7 +9142,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -9165,7 +9165,7 @@
         <v>27</v>
       </c>
       <c r="E25">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F25" t="s">
         <v>34</v>
@@ -9188,7 +9188,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -9211,7 +9211,7 @@
         <v>27</v>
       </c>
       <c r="E27">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F27" t="s">
         <v>31</v>
@@ -9234,7 +9234,7 @@
         <v>27</v>
       </c>
       <c r="E28">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -9257,7 +9257,7 @@
         <v>27</v>
       </c>
       <c r="E29">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F29" t="s">
         <v>34</v>
@@ -9280,7 +9280,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -9303,7 +9303,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F31" t="s">
         <v>31</v>
@@ -9326,7 +9326,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -9349,7 +9349,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F33" t="s">
         <v>31</v>
@@ -9372,7 +9372,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -9395,7 +9395,7 @@
         <v>27</v>
       </c>
       <c r="E35">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
@@ -9418,7 +9418,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -9464,7 +9464,7 @@
         <v>27</v>
       </c>
       <c r="E38">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -9487,7 +9487,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F39" t="s">
         <v>34</v>
@@ -9510,7 +9510,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -9533,7 +9533,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F41" t="s">
         <v>31</v>
@@ -9556,7 +9556,7 @@
         <v>27</v>
       </c>
       <c r="E42">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -9579,7 +9579,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F43" t="s">
         <v>34</v>
@@ -9602,7 +9602,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -9625,7 +9625,7 @@
         <v>27</v>
       </c>
       <c r="E45">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F45" t="s">
         <v>31</v>
@@ -9648,7 +9648,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -9671,7 +9671,7 @@
         <v>27</v>
       </c>
       <c r="E47">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F47" t="s">
         <v>34</v>
@@ -9694,7 +9694,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -9717,7 +9717,7 @@
         <v>27</v>
       </c>
       <c r="E49">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F49" t="s">
         <v>31</v>
@@ -9740,7 +9740,7 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F50" t="s">
         <v>28</v>
@@ -9763,7 +9763,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F51" t="s">
         <v>34</v>
@@ -9786,7 +9786,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -9809,7 +9809,7 @@
         <v>27</v>
       </c>
       <c r="E53">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F53" t="s">
         <v>31</v>
@@ -9832,7 +9832,7 @@
         <v>27</v>
       </c>
       <c r="E54">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -9855,7 +9855,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F55" t="s">
         <v>34</v>
@@ -9878,7 +9878,7 @@
         <v>27</v>
       </c>
       <c r="E56">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -9901,7 +9901,7 @@
         <v>27</v>
       </c>
       <c r="E57">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F57" t="s">
         <v>31</v>
@@ -9924,7 +9924,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -9947,7 +9947,7 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F59" t="s">
         <v>34</v>
@@ -9970,7 +9970,7 @@
         <v>27</v>
       </c>
       <c r="E60">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -9993,7 +9993,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F61" t="s">
         <v>31</v>
@@ -10016,7 +10016,7 @@
         <v>27</v>
       </c>
       <c r="E62">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F62" t="s">
         <v>28</v>
@@ -10039,7 +10039,7 @@
         <v>27</v>
       </c>
       <c r="E63">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F63" t="s">
         <v>31</v>
@@ -10062,7 +10062,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -10085,7 +10085,7 @@
         <v>27</v>
       </c>
       <c r="E65">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F65" t="s">
         <v>34</v>
@@ -10108,7 +10108,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -10131,7 +10131,7 @@
         <v>27</v>
       </c>
       <c r="E67">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F67" t="s">
         <v>31</v>
@@ -10154,7 +10154,7 @@
         <v>27</v>
       </c>
       <c r="E68">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
@@ -10177,7 +10177,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F69" t="s">
         <v>34</v>
@@ -10200,7 +10200,7 @@
         <v>27</v>
       </c>
       <c r="E70">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -10223,7 +10223,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F71" t="s">
         <v>31</v>
@@ -10246,7 +10246,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -10269,7 +10269,7 @@
         <v>27</v>
       </c>
       <c r="E73">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F73" t="s">
         <v>34</v>
@@ -10292,7 +10292,7 @@
         <v>27</v>
       </c>
       <c r="E74">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -10315,7 +10315,7 @@
         <v>27</v>
       </c>
       <c r="E75">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F75" t="s">
         <v>31</v>
@@ -10338,7 +10338,7 @@
         <v>27</v>
       </c>
       <c r="E76">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
@@ -10361,7 +10361,7 @@
         <v>27</v>
       </c>
       <c r="E77">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F77" t="s">
         <v>34</v>
@@ -10384,7 +10384,7 @@
         <v>27</v>
       </c>
       <c r="E78">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
@@ -10407,7 +10407,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F79" t="s">
         <v>31</v>
@@ -10430,7 +10430,7 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
@@ -10453,7 +10453,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F81" t="s">
         <v>34</v>
@@ -10476,7 +10476,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -10499,7 +10499,7 @@
         <v>27</v>
       </c>
       <c r="E83">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F83" t="s">
         <v>31</v>
@@ -10522,7 +10522,7 @@
         <v>27</v>
       </c>
       <c r="E84">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
@@ -10545,7 +10545,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F85" t="s">
         <v>34</v>
@@ -10568,7 +10568,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -10591,7 +10591,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F87" t="s">
         <v>31</v>
@@ -10614,7 +10614,7 @@
         <v>27</v>
       </c>
       <c r="E88">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -10637,7 +10637,7 @@
         <v>27</v>
       </c>
       <c r="E89">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F89" t="s">
         <v>34</v>
@@ -10660,7 +10660,7 @@
         <v>27</v>
       </c>
       <c r="E90">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F90" t="s">
         <v>28</v>
@@ -10706,7 +10706,7 @@
         <v>27</v>
       </c>
       <c r="E92">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
@@ -10729,7 +10729,7 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F93" t="s">
         <v>31</v>
@@ -10752,7 +10752,7 @@
         <v>27</v>
       </c>
       <c r="E94">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -10775,7 +10775,7 @@
         <v>27</v>
       </c>
       <c r="E95">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F95" t="s">
         <v>34</v>
@@ -10798,7 +10798,7 @@
         <v>27</v>
       </c>
       <c r="E96">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -10821,7 +10821,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F97" t="s">
         <v>31</v>
@@ -10844,7 +10844,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -10867,7 +10867,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F99" t="s">
         <v>34</v>
@@ -10913,7 +10913,7 @@
         <v>27</v>
       </c>
       <c r="E101">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F101" t="s">
         <v>31</v>
@@ -10936,7 +10936,7 @@
         <v>27</v>
       </c>
       <c r="E102">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
@@ -10959,7 +10959,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F103" t="s">
         <v>34</v>
@@ -10982,7 +10982,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -11005,7 +11005,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F105" t="s">
         <v>31</v>
@@ -11028,7 +11028,7 @@
         <v>27</v>
       </c>
       <c r="E106">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
@@ -11051,7 +11051,7 @@
         <v>27</v>
       </c>
       <c r="E107">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F107" t="s">
         <v>34</v>
@@ -11074,7 +11074,7 @@
         <v>27</v>
       </c>
       <c r="E108">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
@@ -11097,7 +11097,7 @@
         <v>27</v>
       </c>
       <c r="E109">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F109" t="s">
         <v>31</v>
@@ -11120,7 +11120,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -11143,7 +11143,7 @@
         <v>27</v>
       </c>
       <c r="E111">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F111" t="s">
         <v>34</v>
@@ -11166,7 +11166,7 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F112" t="s">
         <v>28</v>
@@ -11189,7 +11189,7 @@
         <v>27</v>
       </c>
       <c r="E113">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F113" t="s">
         <v>31</v>
@@ -11212,7 +11212,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -11235,7 +11235,7 @@
         <v>27</v>
       </c>
       <c r="E115">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F115" t="s">
         <v>34</v>
@@ -11258,7 +11258,7 @@
         <v>27</v>
       </c>
       <c r="E116">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F116" t="s">
         <v>28</v>
@@ -11281,7 +11281,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F117" t="s">
         <v>31</v>
@@ -11304,7 +11304,7 @@
         <v>27</v>
       </c>
       <c r="E118">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F118" t="s">
         <v>28</v>
@@ -11327,7 +11327,7 @@
         <v>27</v>
       </c>
       <c r="E119">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F119" t="s">
         <v>34</v>
@@ -11350,7 +11350,7 @@
         <v>27</v>
       </c>
       <c r="E120">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
@@ -11373,7 +11373,7 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F121" t="s">
         <v>31</v>
@@ -11396,7 +11396,7 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -11419,7 +11419,7 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F123" t="s">
         <v>31</v>
@@ -11442,7 +11442,7 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F124" t="s">
         <v>28</v>
@@ -11465,7 +11465,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F125" t="s">
         <v>34</v>
@@ -11488,7 +11488,7 @@
         <v>27</v>
       </c>
       <c r="E126">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
@@ -11511,7 +11511,7 @@
         <v>27</v>
       </c>
       <c r="E127">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F127" t="s">
         <v>31</v>
@@ -11557,7 +11557,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F129" t="s">
         <v>34</v>
@@ -11580,7 +11580,7 @@
         <v>27</v>
       </c>
       <c r="E130">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
@@ -11603,7 +11603,7 @@
         <v>27</v>
       </c>
       <c r="E131">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F131" t="s">
         <v>31</v>
@@ -11626,7 +11626,7 @@
         <v>27</v>
       </c>
       <c r="E132">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F132" t="s">
         <v>28</v>
@@ -11649,7 +11649,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F133" t="s">
         <v>34</v>
@@ -11672,7 +11672,7 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -11695,7 +11695,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F135" t="s">
         <v>31</v>
@@ -11718,7 +11718,7 @@
         <v>27</v>
       </c>
       <c r="E136">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
@@ -11741,7 +11741,7 @@
         <v>27</v>
       </c>
       <c r="E137">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F137" t="s">
         <v>34</v>
@@ -11764,7 +11764,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -11787,7 +11787,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F139" t="s">
         <v>31</v>
@@ -11810,7 +11810,7 @@
         <v>27</v>
       </c>
       <c r="E140">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
@@ -11856,7 +11856,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -11902,7 +11902,7 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F144" t="s">
         <v>28</v>
@@ -11925,7 +11925,7 @@
         <v>27</v>
       </c>
       <c r="E145">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F145" t="s">
         <v>34</v>
@@ -11948,7 +11948,7 @@
         <v>27</v>
       </c>
       <c r="E146">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F146" t="s">
         <v>28</v>
@@ -11971,7 +11971,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F147" t="s">
         <v>31</v>
@@ -11994,7 +11994,7 @@
         <v>27</v>
       </c>
       <c r="E148">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
@@ -12017,7 +12017,7 @@
         <v>27</v>
       </c>
       <c r="E149">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F149" t="s">
         <v>34</v>
@@ -12040,7 +12040,7 @@
         <v>27</v>
       </c>
       <c r="E150">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
@@ -12063,7 +12063,7 @@
         <v>27</v>
       </c>
       <c r="E151">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F151" t="s">
         <v>31</v>
@@ -12086,7 +12086,7 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F152" t="s">
         <v>28</v>
@@ -12109,7 +12109,7 @@
         <v>27</v>
       </c>
       <c r="E153">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F153" t="s">
         <v>31</v>
@@ -12132,7 +12132,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -12155,7 +12155,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F155" t="s">
         <v>34</v>
@@ -12178,7 +12178,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -12201,7 +12201,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F157" t="s">
         <v>31</v>
@@ -12247,7 +12247,7 @@
         <v>27</v>
       </c>
       <c r="E159">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F159" t="s">
         <v>34</v>
@@ -12270,7 +12270,7 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F160" t="s">
         <v>28</v>
@@ -12293,7 +12293,7 @@
         <v>27</v>
       </c>
       <c r="E161">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F161" t="s">
         <v>31</v>
@@ -12316,7 +12316,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -12339,7 +12339,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F163" t="s">
         <v>34</v>
@@ -12362,7 +12362,7 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
@@ -12385,7 +12385,7 @@
         <v>27</v>
       </c>
       <c r="E165">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F165" t="s">
         <v>31</v>
@@ -12408,7 +12408,7 @@
         <v>27</v>
       </c>
       <c r="E166">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -12431,7 +12431,7 @@
         <v>27</v>
       </c>
       <c r="E167">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F167" t="s">
         <v>34</v>
@@ -12454,7 +12454,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -12477,7 +12477,7 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F169" t="s">
         <v>31</v>
@@ -12500,7 +12500,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -12523,7 +12523,7 @@
         <v>27</v>
       </c>
       <c r="E171">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F171" t="s">
         <v>34</v>
@@ -12569,7 +12569,7 @@
         <v>27</v>
       </c>
       <c r="E173">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F173" t="s">
         <v>31</v>
@@ -12592,7 +12592,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -12638,7 +12638,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -12661,7 +12661,7 @@
         <v>27</v>
       </c>
       <c r="E177">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
@@ -12684,7 +12684,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F178" t="s">
         <v>31</v>
@@ -12707,7 +12707,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -12730,7 +12730,7 @@
         <v>27</v>
       </c>
       <c r="E180">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F180" t="s">
         <v>34</v>
@@ -12753,7 +12753,7 @@
         <v>27</v>
       </c>
       <c r="E181">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F181" t="s">
         <v>28</v>
@@ -12776,7 +12776,7 @@
         <v>27</v>
       </c>
       <c r="E182">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F182" t="s">
         <v>31</v>
@@ -12799,7 +12799,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -12822,7 +12822,7 @@
         <v>27</v>
       </c>
       <c r="E184">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F184" t="s">
         <v>34</v>
@@ -12845,7 +12845,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -12868,7 +12868,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F186" t="s">
         <v>31</v>
@@ -12891,7 +12891,7 @@
         <v>27</v>
       </c>
       <c r="E187">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F187" t="s">
         <v>28</v>
@@ -12914,7 +12914,7 @@
         <v>27</v>
       </c>
       <c r="E188">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F188" t="s">
         <v>34</v>
@@ -12937,7 +12937,7 @@
         <v>27</v>
       </c>
       <c r="E189">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F189" t="s">
         <v>28</v>
@@ -12960,7 +12960,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F190" t="s">
         <v>31</v>
@@ -12983,7 +12983,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -13006,7 +13006,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F192" t="s">
         <v>34</v>
@@ -13029,7 +13029,7 @@
         <v>27</v>
       </c>
       <c r="E193">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -13052,7 +13052,7 @@
         <v>27</v>
       </c>
       <c r="E194">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F194" t="s">
         <v>31</v>
@@ -13075,7 +13075,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -13098,7 +13098,7 @@
         <v>27</v>
       </c>
       <c r="E196">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F196" t="s">
         <v>34</v>
@@ -13121,7 +13121,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -13144,7 +13144,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F198" t="s">
         <v>31</v>
@@ -13167,7 +13167,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -13190,7 +13190,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F200" t="s">
         <v>34</v>
@@ -13213,7 +13213,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -13236,7 +13236,7 @@
         <v>27</v>
       </c>
       <c r="E202">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -13259,7 +13259,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F203" t="s">
         <v>31</v>
@@ -13282,7 +13282,7 @@
         <v>27</v>
       </c>
       <c r="E204">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -13305,7 +13305,7 @@
         <v>27</v>
       </c>
       <c r="E205">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F205" t="s">
         <v>34</v>
@@ -13351,7 +13351,7 @@
         <v>27</v>
       </c>
       <c r="E207">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F207" t="s">
         <v>31</v>
@@ -13374,7 +13374,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -13420,7 +13420,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -13443,7 +13443,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F211" t="s">
         <v>31</v>
@@ -13466,7 +13466,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -13489,7 +13489,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F213" t="s">
         <v>34</v>
@@ -13512,7 +13512,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -13535,7 +13535,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F215" t="s">
         <v>31</v>
@@ -13558,7 +13558,7 @@
         <v>27</v>
       </c>
       <c r="E216">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F216" t="s">
         <v>28</v>
@@ -13581,7 +13581,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F217" t="s">
         <v>34</v>
@@ -13604,7 +13604,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -13627,7 +13627,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F219" t="s">
         <v>31</v>
@@ -13650,7 +13650,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -13673,7 +13673,7 @@
         <v>27</v>
       </c>
       <c r="E221">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F221" t="s">
         <v>34</v>
@@ -13696,7 +13696,7 @@
         <v>27</v>
       </c>
       <c r="E222">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F222" t="s">
         <v>28</v>
@@ -13719,7 +13719,7 @@
         <v>27</v>
       </c>
       <c r="E223">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F223" t="s">
         <v>31</v>
@@ -13742,7 +13742,7 @@
         <v>27</v>
       </c>
       <c r="E224">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F224" t="s">
         <v>28</v>
@@ -13765,7 +13765,7 @@
         <v>27</v>
       </c>
       <c r="E225">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F225" t="s">
         <v>34</v>
@@ -13788,7 +13788,7 @@
         <v>27</v>
       </c>
       <c r="E226">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F226" t="s">
         <v>28</v>
@@ -13811,7 +13811,7 @@
         <v>27</v>
       </c>
       <c r="E227">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F227" t="s">
         <v>28</v>
@@ -13834,7 +13834,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F228" t="s">
         <v>31</v>
@@ -13857,7 +13857,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -13880,7 +13880,7 @@
         <v>27</v>
       </c>
       <c r="E230">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F230" t="s">
         <v>34</v>
@@ -13903,7 +13903,7 @@
         <v>27</v>
       </c>
       <c r="E231">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F231" t="s">
         <v>28</v>
@@ -13926,7 +13926,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F232" t="s">
         <v>31</v>
@@ -13949,7 +13949,7 @@
         <v>27</v>
       </c>
       <c r="E233">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F233" t="s">
         <v>28</v>
@@ -13972,7 +13972,7 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F234" t="s">
         <v>34</v>
@@ -13995,7 +13995,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -14041,7 +14041,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -14064,7 +14064,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F238" t="s">
         <v>34</v>
@@ -14087,7 +14087,7 @@
         <v>27</v>
       </c>
       <c r="E239">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F239" t="s">
         <v>28</v>
@@ -14110,7 +14110,7 @@
         <v>27</v>
       </c>
       <c r="E240">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F240" t="s">
         <v>31</v>
@@ -14133,7 +14133,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -14156,7 +14156,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F242" t="s">
         <v>34</v>
@@ -14179,7 +14179,7 @@
         <v>27</v>
       </c>
       <c r="E243">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -14202,7 +14202,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F244" t="s">
         <v>31</v>
@@ -14225,7 +14225,7 @@
         <v>27</v>
       </c>
       <c r="E245">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F245" t="s">
         <v>28</v>
@@ -14248,7 +14248,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F246" t="s">
         <v>34</v>
@@ -14271,7 +14271,7 @@
         <v>27</v>
       </c>
       <c r="E247">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F247" t="s">
         <v>28</v>
@@ -14294,7 +14294,7 @@
         <v>27</v>
       </c>
       <c r="E248">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F248" t="s">
         <v>31</v>
@@ -14317,7 +14317,7 @@
         <v>27</v>
       </c>
       <c r="E249">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F249" t="s">
         <v>28</v>
@@ -14340,7 +14340,7 @@
         <v>27</v>
       </c>
       <c r="E250">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F250" t="s">
         <v>34</v>
@@ -14363,7 +14363,7 @@
         <v>27</v>
       </c>
       <c r="E251">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F251" t="s">
         <v>28</v>
@@ -14386,7 +14386,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -14409,7 +14409,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F253" t="s">
         <v>31</v>
@@ -14432,7 +14432,7 @@
         <v>27</v>
       </c>
       <c r="E254">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F254" t="s">
         <v>28</v>
@@ -14455,7 +14455,7 @@
         <v>27</v>
       </c>
       <c r="E255">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F255" t="s">
         <v>34</v>
@@ -14478,7 +14478,7 @@
         <v>27</v>
       </c>
       <c r="E256">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F256" t="s">
         <v>28</v>
@@ -14501,7 +14501,7 @@
         <v>27</v>
       </c>
       <c r="E257">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F257" t="s">
         <v>31</v>
@@ -14524,7 +14524,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -14547,7 +14547,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F259" t="s">
         <v>34</v>
@@ -14570,7 +14570,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -14593,7 +14593,7 @@
         <v>27</v>
       </c>
       <c r="E261">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F261" t="s">
         <v>31</v>
@@ -14616,7 +14616,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -14639,7 +14639,7 @@
         <v>27</v>
       </c>
       <c r="E263">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F263" t="s">
         <v>34</v>
@@ -14662,7 +14662,7 @@
         <v>27</v>
       </c>
       <c r="E264">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -14685,7 +14685,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F265" t="s">
         <v>31</v>
@@ -14708,7 +14708,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -14731,7 +14731,7 @@
         <v>27</v>
       </c>
       <c r="E267">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F267" t="s">
         <v>34</v>
@@ -14754,7 +14754,7 @@
         <v>27</v>
       </c>
       <c r="E268">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F268" t="s">
         <v>28</v>
@@ -14777,7 +14777,7 @@
         <v>27</v>
       </c>
       <c r="E269">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F269" t="s">
         <v>31</v>
@@ -14800,7 +14800,7 @@
         <v>27</v>
       </c>
       <c r="E270">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F270" t="s">
         <v>28</v>
@@ -14823,7 +14823,7 @@
         <v>27</v>
       </c>
       <c r="E271">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F271" t="s">
         <v>34</v>
@@ -14846,7 +14846,7 @@
         <v>27</v>
       </c>
       <c r="E272">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F272" t="s">
         <v>28</v>
@@ -14869,7 +14869,7 @@
         <v>27</v>
       </c>
       <c r="E273">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F273" t="s">
         <v>31</v>
@@ -14892,7 +14892,7 @@
         <v>27</v>
       </c>
       <c r="E274">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F274" t="s">
         <v>28</v>
@@ -14915,7 +14915,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F275" t="s">
         <v>34</v>
@@ -14938,7 +14938,7 @@
         <v>27</v>
       </c>
       <c r="E276">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F276" t="s">
         <v>28</v>
@@ -14961,7 +14961,7 @@
         <v>27</v>
       </c>
       <c r="E277">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F277" t="s">
         <v>28</v>
@@ -14984,7 +14984,7 @@
         <v>27</v>
       </c>
       <c r="E278">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F278" t="s">
         <v>31</v>
@@ -15007,7 +15007,7 @@
         <v>27</v>
       </c>
       <c r="E279">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -15030,7 +15030,7 @@
         <v>27</v>
       </c>
       <c r="E280">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F280" t="s">
         <v>34</v>
@@ -15053,7 +15053,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -15099,7 +15099,7 @@
         <v>27</v>
       </c>
       <c r="E283">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F283" t="s">
         <v>28</v>
@@ -15122,7 +15122,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F284" t="s">
         <v>34</v>
@@ -15145,7 +15145,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -15168,7 +15168,7 @@
         <v>27</v>
       </c>
       <c r="E286">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F286" t="s">
         <v>31</v>
@@ -15191,7 +15191,7 @@
         <v>27</v>
       </c>
       <c r="E287">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F287" t="s">
         <v>28</v>
@@ -15214,7 +15214,7 @@
         <v>27</v>
       </c>
       <c r="E288">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F288" t="s">
         <v>34</v>
@@ -15237,7 +15237,7 @@
         <v>27</v>
       </c>
       <c r="E289">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F289" t="s">
         <v>28</v>
@@ -15260,7 +15260,7 @@
         <v>27</v>
       </c>
       <c r="E290">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F290" t="s">
         <v>31</v>
@@ -15283,7 +15283,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -15306,7 +15306,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F292" t="s">
         <v>34</v>
@@ -15329,7 +15329,7 @@
         <v>27</v>
       </c>
       <c r="E293">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -15352,7 +15352,7 @@
         <v>27</v>
       </c>
       <c r="E294">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F294" t="s">
         <v>31</v>
@@ -15375,7 +15375,7 @@
         <v>27</v>
       </c>
       <c r="E295">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F295" t="s">
         <v>28</v>
@@ -15398,7 +15398,7 @@
         <v>27</v>
       </c>
       <c r="E296">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F296" t="s">
         <v>34</v>
@@ -15421,7 +15421,7 @@
         <v>27</v>
       </c>
       <c r="E297">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F297" t="s">
         <v>28</v>
@@ -15444,7 +15444,7 @@
         <v>27</v>
       </c>
       <c r="E298">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F298" t="s">
         <v>31</v>
@@ -15467,7 +15467,7 @@
         <v>27</v>
       </c>
       <c r="E299">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F299" t="s">
         <v>28</v>
@@ -15490,7 +15490,7 @@
         <v>27</v>
       </c>
       <c r="E300">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F300" t="s">
         <v>34</v>
@@ -15513,7 +15513,7 @@
         <v>27</v>
       </c>
       <c r="E301">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F301" t="s">
         <v>28</v>

--- a/all-test-reports/vulnerability/vulnerability_test_report.xlsx
+++ b/all-test-reports/vulnerability/vulnerability_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 11:12:56 am</t>
+    <t>28/7/2026, 11:17:40 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1694,7 +1694,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="10">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>28</v>
@@ -1717,7 +1717,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="10">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>31</v>
@@ -1740,7 +1740,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="10">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>28</v>
@@ -1763,7 +1763,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="10">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>34</v>
@@ -1786,7 +1786,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="10">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>28</v>
@@ -1809,7 +1809,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="10">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>31</v>
@@ -1832,7 +1832,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="10">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>28</v>
@@ -1855,7 +1855,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="10">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>34</v>
@@ -1878,7 +1878,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="10">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>28</v>
@@ -1901,7 +1901,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="10">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>31</v>
@@ -1924,7 +1924,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="10">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>28</v>
@@ -1947,7 +1947,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="10">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>34</v>
@@ -1970,7 +1970,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="10">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>28</v>
@@ -1993,7 +1993,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="10">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>31</v>
@@ -2016,7 +2016,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="10">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>28</v>
@@ -2039,7 +2039,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="10">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>34</v>
@@ -2062,7 +2062,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="10">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>28</v>
@@ -2085,7 +2085,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="10">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>31</v>
@@ -2108,7 +2108,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="10">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>28</v>
@@ -2131,7 +2131,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="10">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>34</v>
@@ -2154,7 +2154,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="10">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>28</v>
@@ -2177,7 +2177,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>31</v>
@@ -2200,7 +2200,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="10">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>28</v>
@@ -2246,7 +2246,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>28</v>
@@ -2269,7 +2269,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="10">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>31</v>
@@ -2292,7 +2292,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="10">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>28</v>
@@ -2315,7 +2315,7 @@
         <v>27</v>
       </c>
       <c r="E29" s="10">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>34</v>
@@ -2338,7 +2338,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="10">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>28</v>
@@ -2361,7 +2361,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="10">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>31</v>
@@ -2384,7 +2384,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="10">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>28</v>
@@ -2407,7 +2407,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="10">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>31</v>
@@ -2430,7 +2430,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="10">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>28</v>
@@ -2453,7 +2453,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="10">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>34</v>
@@ -2476,7 +2476,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="10">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>28</v>
@@ -2499,7 +2499,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="10">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>31</v>
@@ -2545,7 +2545,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="10">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>34</v>
@@ -2591,7 +2591,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="10">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>31</v>
@@ -2614,7 +2614,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="10">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>28</v>
@@ -2637,7 +2637,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="10">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>34</v>
@@ -2660,7 +2660,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="10">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>28</v>
@@ -2683,7 +2683,7 @@
         <v>27</v>
       </c>
       <c r="E45" s="10">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>31</v>
@@ -2706,7 +2706,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="10">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>28</v>
@@ -2729,7 +2729,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="10">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>34</v>
@@ -2752,7 +2752,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="10">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>28</v>
@@ -2775,7 +2775,7 @@
         <v>27</v>
       </c>
       <c r="E49" s="10">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>31</v>
@@ -2798,7 +2798,7 @@
         <v>27</v>
       </c>
       <c r="E50" s="10">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>28</v>
@@ -2821,7 +2821,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="10">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>34</v>
@@ -2844,7 +2844,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>28</v>
@@ -2867,7 +2867,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="10">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>31</v>
@@ -2890,7 +2890,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="10">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>28</v>
@@ -2913,7 +2913,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="10">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>34</v>
@@ -2936,7 +2936,7 @@
         <v>27</v>
       </c>
       <c r="E56" s="10">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>28</v>
@@ -2959,7 +2959,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="10">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>31</v>
@@ -2982,7 +2982,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="10">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>28</v>
@@ -3005,7 +3005,7 @@
         <v>27</v>
       </c>
       <c r="E59" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>34</v>
@@ -3028,7 +3028,7 @@
         <v>27</v>
       </c>
       <c r="E60" s="10">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>28</v>
@@ -3051,7 +3051,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="10">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>31</v>
@@ -3074,7 +3074,7 @@
         <v>27</v>
       </c>
       <c r="E62" s="10">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>28</v>
@@ -3097,7 +3097,7 @@
         <v>27</v>
       </c>
       <c r="E63" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>31</v>
@@ -3120,7 +3120,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="10">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>28</v>
@@ -3143,7 +3143,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="10">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>34</v>
@@ -3166,7 +3166,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="10">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>28</v>
@@ -3189,7 +3189,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="10">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>31</v>
@@ -3212,7 +3212,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="10">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>28</v>
@@ -3235,7 +3235,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="10">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>34</v>
@@ -3281,7 +3281,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="10">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>31</v>
@@ -3304,7 +3304,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="10">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>28</v>
@@ -3327,7 +3327,7 @@
         <v>27</v>
       </c>
       <c r="E73" s="10">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>34</v>
@@ -3350,7 +3350,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="10">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>28</v>
@@ -3396,7 +3396,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="10">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>28</v>
@@ -3419,7 +3419,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="10">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>34</v>
@@ -3442,7 +3442,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="10">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>28</v>
@@ -3465,7 +3465,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="10">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>31</v>
@@ -3488,7 +3488,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="10">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>28</v>
@@ -3511,7 +3511,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="10">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>34</v>
@@ -3534,7 +3534,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="10">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>28</v>
@@ -3557,7 +3557,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="10">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>31</v>
@@ -3580,7 +3580,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="10">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>28</v>
@@ -3603,7 +3603,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="10">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>34</v>
@@ -3626,7 +3626,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="10">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>28</v>
@@ -3649,7 +3649,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="10">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>31</v>
@@ -3672,7 +3672,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="10">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>28</v>
@@ -3695,7 +3695,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="10">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>34</v>
@@ -3718,7 +3718,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="10">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>28</v>
@@ -3764,7 +3764,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>28</v>
@@ -3833,7 +3833,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="10">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>34</v>
@@ -3856,7 +3856,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="10">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F96" s="8" t="s">
         <v>28</v>
@@ -3879,7 +3879,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="10">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>31</v>
@@ -3902,7 +3902,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>28</v>
@@ -3925,7 +3925,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="10">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>34</v>
@@ -3948,7 +3948,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="10">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>28</v>
@@ -3971,7 +3971,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="10">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>31</v>
@@ -3994,7 +3994,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="10">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>28</v>
@@ -4017,7 +4017,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="10">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>34</v>
@@ -4040,7 +4040,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="10">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>28</v>
@@ -4063,7 +4063,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="10">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>31</v>
@@ -4086,7 +4086,7 @@
         <v>27</v>
       </c>
       <c r="E106" s="10">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>28</v>
@@ -4109,7 +4109,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="10">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>34</v>
@@ -4132,7 +4132,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="10">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>28</v>
@@ -4178,7 +4178,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="10">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>28</v>
@@ -4201,7 +4201,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="10">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>34</v>
@@ -4224,7 +4224,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="10">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>28</v>
@@ -4247,7 +4247,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="10">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F113" s="8" t="s">
         <v>31</v>
@@ -4270,7 +4270,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="10">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>28</v>
@@ -4293,7 +4293,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="10">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>34</v>
@@ -4316,7 +4316,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="10">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>28</v>
@@ -4339,7 +4339,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="10">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F117" s="8" t="s">
         <v>31</v>
@@ -4362,7 +4362,7 @@
         <v>27</v>
       </c>
       <c r="E118" s="10">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F118" s="8" t="s">
         <v>28</v>
@@ -4408,7 +4408,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="10">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F120" s="8" t="s">
         <v>28</v>
@@ -4431,7 +4431,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="10">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F121" s="8" t="s">
         <v>31</v>
@@ -4454,7 +4454,7 @@
         <v>27</v>
       </c>
       <c r="E122" s="10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F122" s="8" t="s">
         <v>28</v>
@@ -4477,7 +4477,7 @@
         <v>27</v>
       </c>
       <c r="E123" s="10">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>31</v>
@@ -4500,7 +4500,7 @@
         <v>27</v>
       </c>
       <c r="E124" s="10">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F124" s="8" t="s">
         <v>28</v>
@@ -4523,7 +4523,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="10">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>34</v>
@@ -4546,7 +4546,7 @@
         <v>27</v>
       </c>
       <c r="E126" s="10">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F126" s="8" t="s">
         <v>28</v>
@@ -4569,7 +4569,7 @@
         <v>27</v>
       </c>
       <c r="E127" s="10">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F127" s="8" t="s">
         <v>31</v>
@@ -4592,7 +4592,7 @@
         <v>27</v>
       </c>
       <c r="E128" s="10">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F128" s="8" t="s">
         <v>28</v>
@@ -4615,7 +4615,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="10">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F129" s="8" t="s">
         <v>34</v>
@@ -4638,7 +4638,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="10">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F130" s="8" t="s">
         <v>28</v>
@@ -4661,7 +4661,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="10">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F131" s="8" t="s">
         <v>31</v>
@@ -4684,7 +4684,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="10">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F132" s="8" t="s">
         <v>28</v>
@@ -4707,7 +4707,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="10">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F133" s="8" t="s">
         <v>34</v>
@@ -4730,7 +4730,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="10">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F134" s="8" t="s">
         <v>28</v>
@@ -4753,7 +4753,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="10">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F135" s="8" t="s">
         <v>31</v>
@@ -4799,7 +4799,7 @@
         <v>27</v>
       </c>
       <c r="E137" s="10">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F137" s="8" t="s">
         <v>34</v>
@@ -4822,7 +4822,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F138" s="8" t="s">
         <v>28</v>
@@ -4845,7 +4845,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="10">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F139" s="8" t="s">
         <v>31</v>
@@ -4868,7 +4868,7 @@
         <v>27</v>
       </c>
       <c r="E140" s="10">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F140" s="8" t="s">
         <v>28</v>
@@ -4891,7 +4891,7 @@
         <v>27</v>
       </c>
       <c r="E141" s="10">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F141" s="8" t="s">
         <v>34</v>
@@ -4914,7 +4914,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="10">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F142" s="8" t="s">
         <v>28</v>
@@ -4937,7 +4937,7 @@
         <v>27</v>
       </c>
       <c r="E143" s="10">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F143" s="8" t="s">
         <v>31</v>
@@ -4983,7 +4983,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="10">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F145" s="8" t="s">
         <v>34</v>
@@ -5006,7 +5006,7 @@
         <v>27</v>
       </c>
       <c r="E146" s="10">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>28</v>
@@ -5029,7 +5029,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="10">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F147" s="8" t="s">
         <v>31</v>
@@ -5052,7 +5052,7 @@
         <v>27</v>
       </c>
       <c r="E148" s="10">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F148" s="8" t="s">
         <v>28</v>
@@ -5075,7 +5075,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="10">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F149" s="8" t="s">
         <v>34</v>
@@ -5098,7 +5098,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="10">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>28</v>
@@ -5121,7 +5121,7 @@
         <v>27</v>
       </c>
       <c r="E151" s="10">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>31</v>
@@ -5144,7 +5144,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="10">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>28</v>
@@ -5167,7 +5167,7 @@
         <v>27</v>
       </c>
       <c r="E153" s="10">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F153" s="8" t="s">
         <v>31</v>
@@ -5190,7 +5190,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="10">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>28</v>
@@ -5213,7 +5213,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="10">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F155" s="8" t="s">
         <v>34</v>
@@ -5236,7 +5236,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="10">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F156" s="8" t="s">
         <v>28</v>
@@ -5259,7 +5259,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="10">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F157" s="8" t="s">
         <v>31</v>
@@ -5282,7 +5282,7 @@
         <v>27</v>
       </c>
       <c r="E158" s="10">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F158" s="8" t="s">
         <v>28</v>
@@ -5305,7 +5305,7 @@
         <v>27</v>
       </c>
       <c r="E159" s="10">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F159" s="8" t="s">
         <v>34</v>
@@ -5328,7 +5328,7 @@
         <v>27</v>
       </c>
       <c r="E160" s="10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F160" s="8" t="s">
         <v>28</v>
@@ -5351,7 +5351,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="10">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F161" s="8" t="s">
         <v>31</v>
@@ -5374,7 +5374,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="10">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F162" s="8" t="s">
         <v>28</v>
@@ -5397,7 +5397,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="10">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F163" s="8" t="s">
         <v>34</v>
@@ -5420,7 +5420,7 @@
         <v>27</v>
       </c>
       <c r="E164" s="10">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F164" s="8" t="s">
         <v>28</v>
@@ -5443,7 +5443,7 @@
         <v>27</v>
       </c>
       <c r="E165" s="10">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F165" s="8" t="s">
         <v>31</v>
@@ -5466,7 +5466,7 @@
         <v>27</v>
       </c>
       <c r="E166" s="10">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F166" s="8" t="s">
         <v>28</v>
@@ -5489,7 +5489,7 @@
         <v>27</v>
       </c>
       <c r="E167" s="10">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F167" s="8" t="s">
         <v>34</v>
@@ -5512,7 +5512,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="10">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F168" s="8" t="s">
         <v>28</v>
@@ -5535,7 +5535,7 @@
         <v>27</v>
       </c>
       <c r="E169" s="10">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F169" s="8" t="s">
         <v>31</v>
@@ -5558,7 +5558,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="10">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F170" s="8" t="s">
         <v>28</v>
@@ -5581,7 +5581,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="10">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F171" s="8" t="s">
         <v>34</v>
@@ -5604,7 +5604,7 @@
         <v>27</v>
       </c>
       <c r="E172" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F172" s="8" t="s">
         <v>28</v>
@@ -5627,7 +5627,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="10">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F173" s="8" t="s">
         <v>31</v>
@@ -5650,7 +5650,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="10">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F174" s="8" t="s">
         <v>28</v>
@@ -5673,7 +5673,7 @@
         <v>27</v>
       </c>
       <c r="E175" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F175" s="8" t="s">
         <v>34</v>
@@ -5696,7 +5696,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="10">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F176" s="8" t="s">
         <v>28</v>
@@ -5719,7 +5719,7 @@
         <v>27</v>
       </c>
       <c r="E177" s="10">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F177" s="8" t="s">
         <v>28</v>
@@ -5742,7 +5742,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="10">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F178" s="8" t="s">
         <v>31</v>
@@ -5765,7 +5765,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="10">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F179" s="8" t="s">
         <v>28</v>
@@ -5788,7 +5788,7 @@
         <v>27</v>
       </c>
       <c r="E180" s="10">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F180" s="8" t="s">
         <v>34</v>
@@ -5811,7 +5811,7 @@
         <v>27</v>
       </c>
       <c r="E181" s="10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F181" s="8" t="s">
         <v>28</v>
@@ -5834,7 +5834,7 @@
         <v>27</v>
       </c>
       <c r="E182" s="10">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F182" s="8" t="s">
         <v>31</v>
@@ -5857,7 +5857,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="10">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F183" s="8" t="s">
         <v>28</v>
@@ -5880,7 +5880,7 @@
         <v>27</v>
       </c>
       <c r="E184" s="10">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F184" s="8" t="s">
         <v>34</v>
@@ -5903,7 +5903,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F185" s="8" t="s">
         <v>28</v>
@@ -5926,7 +5926,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="10">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F186" s="8" t="s">
         <v>31</v>
@@ -5949,7 +5949,7 @@
         <v>27</v>
       </c>
       <c r="E187" s="10">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F187" s="8" t="s">
         <v>28</v>
@@ -5972,7 +5972,7 @@
         <v>27</v>
       </c>
       <c r="E188" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F188" s="8" t="s">
         <v>34</v>
@@ -5995,7 +5995,7 @@
         <v>27</v>
       </c>
       <c r="E189" s="10">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F189" s="8" t="s">
         <v>28</v>
@@ -6018,7 +6018,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="10">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F190" s="8" t="s">
         <v>31</v>
@@ -6041,7 +6041,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="10">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F191" s="8" t="s">
         <v>28</v>
@@ -6064,7 +6064,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="10">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F192" s="8" t="s">
         <v>34</v>
@@ -6087,7 +6087,7 @@
         <v>27</v>
       </c>
       <c r="E193" s="10">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F193" s="8" t="s">
         <v>28</v>
@@ -6110,7 +6110,7 @@
         <v>27</v>
       </c>
       <c r="E194" s="10">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F194" s="8" t="s">
         <v>31</v>
@@ -6133,7 +6133,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="10">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F195" s="8" t="s">
         <v>28</v>
@@ -6156,7 +6156,7 @@
         <v>27</v>
       </c>
       <c r="E196" s="10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F196" s="8" t="s">
         <v>34</v>
@@ -6179,7 +6179,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="10">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F197" s="8" t="s">
         <v>28</v>
@@ -6202,7 +6202,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F198" s="8" t="s">
         <v>31</v>
@@ -6225,7 +6225,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="10">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F199" s="8" t="s">
         <v>28</v>
@@ -6248,7 +6248,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="10">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F200" s="8" t="s">
         <v>34</v>
@@ -6271,7 +6271,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="10">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F201" s="8" t="s">
         <v>28</v>
@@ -6294,7 +6294,7 @@
         <v>27</v>
       </c>
       <c r="E202" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F202" s="8" t="s">
         <v>28</v>
@@ -6317,7 +6317,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="10">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F203" s="8" t="s">
         <v>31</v>
@@ -6340,7 +6340,7 @@
         <v>27</v>
       </c>
       <c r="E204" s="10">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F204" s="8" t="s">
         <v>28</v>
@@ -6363,7 +6363,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="10">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F205" s="8" t="s">
         <v>34</v>
@@ -6386,7 +6386,7 @@
         <v>27</v>
       </c>
       <c r="E206" s="10">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F206" s="8" t="s">
         <v>28</v>
@@ -6409,7 +6409,7 @@
         <v>27</v>
       </c>
       <c r="E207" s="10">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F207" s="8" t="s">
         <v>31</v>
@@ -6432,7 +6432,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="10">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F208" s="8" t="s">
         <v>28</v>
@@ -6455,7 +6455,7 @@
         <v>27</v>
       </c>
       <c r="E209" s="10">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F209" s="8" t="s">
         <v>34</v>
@@ -6478,7 +6478,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="10">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F210" s="8" t="s">
         <v>28</v>
@@ -6501,7 +6501,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="10">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F211" s="8" t="s">
         <v>31</v>
@@ -6524,7 +6524,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="10">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F212" s="8" t="s">
         <v>28</v>
@@ -6547,7 +6547,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F213" s="8" t="s">
         <v>34</v>
@@ -6570,7 +6570,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="10">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F214" s="8" t="s">
         <v>28</v>
@@ -6593,7 +6593,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="10">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F215" s="8" t="s">
         <v>31</v>
@@ -6616,7 +6616,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="10">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F216" s="8" t="s">
         <v>28</v>
@@ -6639,7 +6639,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F217" s="8" t="s">
         <v>34</v>
@@ -6662,7 +6662,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="10">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F218" s="8" t="s">
         <v>28</v>
@@ -6685,7 +6685,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="10">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F219" s="8" t="s">
         <v>31</v>
@@ -6708,7 +6708,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="10">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F220" s="8" t="s">
         <v>28</v>
@@ -6731,7 +6731,7 @@
         <v>27</v>
       </c>
       <c r="E221" s="10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F221" s="8" t="s">
         <v>34</v>
@@ -6754,7 +6754,7 @@
         <v>27</v>
       </c>
       <c r="E222" s="10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F222" s="8" t="s">
         <v>28</v>
@@ -6777,7 +6777,7 @@
         <v>27</v>
       </c>
       <c r="E223" s="10">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F223" s="8" t="s">
         <v>31</v>
@@ -6800,7 +6800,7 @@
         <v>27</v>
       </c>
       <c r="E224" s="10">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F224" s="8" t="s">
         <v>28</v>
@@ -6823,7 +6823,7 @@
         <v>27</v>
       </c>
       <c r="E225" s="10">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F225" s="8" t="s">
         <v>34</v>
@@ -6846,7 +6846,7 @@
         <v>27</v>
       </c>
       <c r="E226" s="10">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F226" s="8" t="s">
         <v>28</v>
@@ -6869,7 +6869,7 @@
         <v>27</v>
       </c>
       <c r="E227" s="10">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F227" s="8" t="s">
         <v>28</v>
@@ -6892,7 +6892,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="10">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F228" s="8" t="s">
         <v>31</v>
@@ -6915,7 +6915,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="10">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F229" s="8" t="s">
         <v>28</v>
@@ -6938,7 +6938,7 @@
         <v>27</v>
       </c>
       <c r="E230" s="10">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F230" s="8" t="s">
         <v>34</v>
@@ -6984,7 +6984,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F232" s="8" t="s">
         <v>31</v>
@@ -7007,7 +7007,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="10">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F233" s="8" t="s">
         <v>28</v>
@@ -7030,7 +7030,7 @@
         <v>27</v>
       </c>
       <c r="E234" s="10">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F234" s="8" t="s">
         <v>34</v>
@@ -7053,7 +7053,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F235" s="8" t="s">
         <v>28</v>
@@ -7076,7 +7076,7 @@
         <v>27</v>
       </c>
       <c r="E236" s="10">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F236" s="8" t="s">
         <v>31</v>
@@ -7099,7 +7099,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="10">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F237" s="8" t="s">
         <v>28</v>
@@ -7122,7 +7122,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="10">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F238" s="8" t="s">
         <v>34</v>
@@ -7145,7 +7145,7 @@
         <v>27</v>
       </c>
       <c r="E239" s="10">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F239" s="8" t="s">
         <v>28</v>
@@ -7168,7 +7168,7 @@
         <v>27</v>
       </c>
       <c r="E240" s="10">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F240" s="8" t="s">
         <v>31</v>
@@ -7191,7 +7191,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="10">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F241" s="8" t="s">
         <v>28</v>
@@ -7214,7 +7214,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="10">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F242" s="8" t="s">
         <v>34</v>
@@ -7237,7 +7237,7 @@
         <v>27</v>
       </c>
       <c r="E243" s="10">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F243" s="8" t="s">
         <v>28</v>
@@ -7260,7 +7260,7 @@
         <v>27</v>
       </c>
       <c r="E244" s="10">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F244" s="8" t="s">
         <v>31</v>
@@ -7283,7 +7283,7 @@
         <v>27</v>
       </c>
       <c r="E245" s="10">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F245" s="8" t="s">
         <v>28</v>
@@ -7306,7 +7306,7 @@
         <v>27</v>
       </c>
       <c r="E246" s="10">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F246" s="8" t="s">
         <v>34</v>
@@ -7329,7 +7329,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="10">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F247" s="8" t="s">
         <v>28</v>
@@ -7352,7 +7352,7 @@
         <v>27</v>
       </c>
       <c r="E248" s="10">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F248" s="8" t="s">
         <v>31</v>
@@ -7375,7 +7375,7 @@
         <v>27</v>
       </c>
       <c r="E249" s="10">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F249" s="8" t="s">
         <v>28</v>
@@ -7398,7 +7398,7 @@
         <v>27</v>
       </c>
       <c r="E250" s="10">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F250" s="8" t="s">
         <v>34</v>
@@ -7421,7 +7421,7 @@
         <v>27</v>
       </c>
       <c r="E251" s="10">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F251" s="8" t="s">
         <v>28</v>
@@ -7444,7 +7444,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="10">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F252" s="8" t="s">
         <v>28</v>
@@ -7467,7 +7467,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="10">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F253" s="8" t="s">
         <v>31</v>
@@ -7490,7 +7490,7 @@
         <v>27</v>
       </c>
       <c r="E254" s="10">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F254" s="8" t="s">
         <v>28</v>
@@ -7513,7 +7513,7 @@
         <v>27</v>
       </c>
       <c r="E255" s="10">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F255" s="8" t="s">
         <v>34</v>
@@ -7536,7 +7536,7 @@
         <v>27</v>
       </c>
       <c r="E256" s="10">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F256" s="8" t="s">
         <v>28</v>
@@ -7559,7 +7559,7 @@
         <v>27</v>
       </c>
       <c r="E257" s="10">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F257" s="8" t="s">
         <v>31</v>
@@ -7582,7 +7582,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="10">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F258" s="8" t="s">
         <v>28</v>
@@ -7605,7 +7605,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="10">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F259" s="8" t="s">
         <v>34</v>
@@ -7628,7 +7628,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="10">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F260" s="8" t="s">
         <v>28</v>
@@ -7651,7 +7651,7 @@
         <v>27</v>
       </c>
       <c r="E261" s="10">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F261" s="8" t="s">
         <v>31</v>
@@ -7674,7 +7674,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="10">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F262" s="8" t="s">
         <v>28</v>
@@ -7697,7 +7697,7 @@
         <v>27</v>
       </c>
       <c r="E263" s="10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F263" s="8" t="s">
         <v>34</v>
@@ -7720,7 +7720,7 @@
         <v>27</v>
       </c>
       <c r="E264" s="10">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F264" s="8" t="s">
         <v>28</v>
@@ -7743,7 +7743,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="10">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F265" s="8" t="s">
         <v>31</v>
@@ -7766,7 +7766,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="10">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F266" s="8" t="s">
         <v>28</v>
@@ -7789,7 +7789,7 @@
         <v>27</v>
       </c>
       <c r="E267" s="10">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F267" s="8" t="s">
         <v>34</v>
@@ -7812,7 +7812,7 @@
         <v>27</v>
       </c>
       <c r="E268" s="10">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F268" s="8" t="s">
         <v>28</v>
@@ -7835,7 +7835,7 @@
         <v>27</v>
       </c>
       <c r="E269" s="10">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F269" s="8" t="s">
         <v>31</v>
@@ -7858,7 +7858,7 @@
         <v>27</v>
       </c>
       <c r="E270" s="10">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F270" s="8" t="s">
         <v>28</v>
@@ -7881,7 +7881,7 @@
         <v>27</v>
       </c>
       <c r="E271" s="10">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F271" s="8" t="s">
         <v>34</v>
@@ -7904,7 +7904,7 @@
         <v>27</v>
       </c>
       <c r="E272" s="10">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F272" s="8" t="s">
         <v>28</v>
@@ -7927,7 +7927,7 @@
         <v>27</v>
       </c>
       <c r="E273" s="10">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F273" s="8" t="s">
         <v>31</v>
@@ -7950,7 +7950,7 @@
         <v>27</v>
       </c>
       <c r="E274" s="10">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F274" s="8" t="s">
         <v>28</v>
@@ -7973,7 +7973,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="10">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F275" s="8" t="s">
         <v>34</v>
@@ -7996,7 +7996,7 @@
         <v>27</v>
       </c>
       <c r="E276" s="10">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F276" s="8" t="s">
         <v>28</v>
@@ -8019,7 +8019,7 @@
         <v>27</v>
       </c>
       <c r="E277" s="10">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F277" s="8" t="s">
         <v>28</v>
@@ -8065,7 +8065,7 @@
         <v>27</v>
       </c>
       <c r="E279" s="10">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F279" s="8" t="s">
         <v>28</v>
@@ -8088,7 +8088,7 @@
         <v>27</v>
       </c>
       <c r="E280" s="10">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F280" s="8" t="s">
         <v>34</v>
@@ -8111,7 +8111,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="10">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F281" s="8" t="s">
         <v>28</v>
@@ -8134,7 +8134,7 @@
         <v>27</v>
       </c>
       <c r="E282" s="10">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F282" s="8" t="s">
         <v>31</v>
@@ -8157,7 +8157,7 @@
         <v>27</v>
       </c>
       <c r="E283" s="10">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F283" s="8" t="s">
         <v>28</v>
@@ -8180,7 +8180,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="10">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F284" s="8" t="s">
         <v>34</v>
@@ -8203,7 +8203,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="10">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F285" s="8" t="s">
         <v>28</v>
@@ -8226,7 +8226,7 @@
         <v>27</v>
       </c>
       <c r="E286" s="10">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F286" s="8" t="s">
         <v>31</v>
@@ -8249,7 +8249,7 @@
         <v>27</v>
       </c>
       <c r="E287" s="10">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F287" s="8" t="s">
         <v>28</v>
@@ -8272,7 +8272,7 @@
         <v>27</v>
       </c>
       <c r="E288" s="10">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F288" s="8" t="s">
         <v>34</v>
@@ -8295,7 +8295,7 @@
         <v>27</v>
       </c>
       <c r="E289" s="10">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F289" s="8" t="s">
         <v>28</v>
@@ -8318,7 +8318,7 @@
         <v>27</v>
       </c>
       <c r="E290" s="10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F290" s="8" t="s">
         <v>31</v>
@@ -8341,7 +8341,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="10">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F291" s="8" t="s">
         <v>28</v>
@@ -8364,7 +8364,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F292" s="8" t="s">
         <v>34</v>
@@ -8387,7 +8387,7 @@
         <v>27</v>
       </c>
       <c r="E293" s="10">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F293" s="8" t="s">
         <v>28</v>
@@ -8410,7 +8410,7 @@
         <v>27</v>
       </c>
       <c r="E294" s="10">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F294" s="8" t="s">
         <v>31</v>
@@ -8433,7 +8433,7 @@
         <v>27</v>
       </c>
       <c r="E295" s="10">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F295" s="8" t="s">
         <v>28</v>
@@ -8456,7 +8456,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="10">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F296" s="8" t="s">
         <v>34</v>
@@ -8479,7 +8479,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="10">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F297" s="8" t="s">
         <v>28</v>
@@ -8502,7 +8502,7 @@
         <v>27</v>
       </c>
       <c r="E298" s="10">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F298" s="8" t="s">
         <v>31</v>
@@ -8525,7 +8525,7 @@
         <v>27</v>
       </c>
       <c r="E299" s="10">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F299" s="8" t="s">
         <v>28</v>
@@ -8571,7 +8571,7 @@
         <v>27</v>
       </c>
       <c r="E301" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F301" s="8" t="s">
         <v>28</v>
@@ -8636,7 +8636,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -8659,7 +8659,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
         <v>31</v>
@@ -8682,7 +8682,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -8705,7 +8705,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
         <v>34</v>
@@ -8728,7 +8728,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -8751,7 +8751,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F7" t="s">
         <v>31</v>
@@ -8774,7 +8774,7 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -8797,7 +8797,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
@@ -8820,7 +8820,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -8843,7 +8843,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
         <v>31</v>
@@ -8866,7 +8866,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -8889,7 +8889,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s">
         <v>34</v>
@@ -8912,7 +8912,7 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -8935,7 +8935,7 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F15" t="s">
         <v>31</v>
@@ -8958,7 +8958,7 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -8981,7 +8981,7 @@
         <v>27</v>
       </c>
       <c r="E17">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F17" t="s">
         <v>34</v>
@@ -9004,7 +9004,7 @@
         <v>27</v>
       </c>
       <c r="E18">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -9027,7 +9027,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F19" t="s">
         <v>31</v>
@@ -9050,7 +9050,7 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -9073,7 +9073,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
         <v>34</v>
@@ -9096,7 +9096,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -9119,7 +9119,7 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F23" t="s">
         <v>31</v>
@@ -9142,7 +9142,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -9188,7 +9188,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -9211,7 +9211,7 @@
         <v>27</v>
       </c>
       <c r="E27">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F27" t="s">
         <v>31</v>
@@ -9234,7 +9234,7 @@
         <v>27</v>
       </c>
       <c r="E28">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -9257,7 +9257,7 @@
         <v>27</v>
       </c>
       <c r="E29">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F29" t="s">
         <v>34</v>
@@ -9280,7 +9280,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -9303,7 +9303,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F31" t="s">
         <v>31</v>
@@ -9326,7 +9326,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -9349,7 +9349,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F33" t="s">
         <v>31</v>
@@ -9372,7 +9372,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -9395,7 +9395,7 @@
         <v>27</v>
       </c>
       <c r="E35">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
@@ -9418,7 +9418,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -9441,7 +9441,7 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F37" t="s">
         <v>31</v>
@@ -9487,7 +9487,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F39" t="s">
         <v>34</v>
@@ -9533,7 +9533,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F41" t="s">
         <v>31</v>
@@ -9556,7 +9556,7 @@
         <v>27</v>
       </c>
       <c r="E42">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -9579,7 +9579,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F43" t="s">
         <v>34</v>
@@ -9602,7 +9602,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -9625,7 +9625,7 @@
         <v>27</v>
       </c>
       <c r="E45">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F45" t="s">
         <v>31</v>
@@ -9648,7 +9648,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -9671,7 +9671,7 @@
         <v>27</v>
       </c>
       <c r="E47">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F47" t="s">
         <v>34</v>
@@ -9694,7 +9694,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -9717,7 +9717,7 @@
         <v>27</v>
       </c>
       <c r="E49">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F49" t="s">
         <v>31</v>
@@ -9740,7 +9740,7 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F50" t="s">
         <v>28</v>
@@ -9763,7 +9763,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F51" t="s">
         <v>34</v>
@@ -9786,7 +9786,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -9809,7 +9809,7 @@
         <v>27</v>
       </c>
       <c r="E53">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F53" t="s">
         <v>31</v>
@@ -9832,7 +9832,7 @@
         <v>27</v>
       </c>
       <c r="E54">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -9855,7 +9855,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F55" t="s">
         <v>34</v>
@@ -9878,7 +9878,7 @@
         <v>27</v>
       </c>
       <c r="E56">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -9901,7 +9901,7 @@
         <v>27</v>
       </c>
       <c r="E57">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F57" t="s">
         <v>31</v>
@@ -9924,7 +9924,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -9947,7 +9947,7 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F59" t="s">
         <v>34</v>
@@ -9970,7 +9970,7 @@
         <v>27</v>
       </c>
       <c r="E60">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -9993,7 +9993,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F61" t="s">
         <v>31</v>
@@ -10016,7 +10016,7 @@
         <v>27</v>
       </c>
       <c r="E62">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F62" t="s">
         <v>28</v>
@@ -10039,7 +10039,7 @@
         <v>27</v>
       </c>
       <c r="E63">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F63" t="s">
         <v>31</v>
@@ -10062,7 +10062,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -10085,7 +10085,7 @@
         <v>27</v>
       </c>
       <c r="E65">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F65" t="s">
         <v>34</v>
@@ -10108,7 +10108,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -10131,7 +10131,7 @@
         <v>27</v>
       </c>
       <c r="E67">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F67" t="s">
         <v>31</v>
@@ -10154,7 +10154,7 @@
         <v>27</v>
       </c>
       <c r="E68">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
@@ -10177,7 +10177,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F69" t="s">
         <v>34</v>
@@ -10223,7 +10223,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F71" t="s">
         <v>31</v>
@@ -10246,7 +10246,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -10269,7 +10269,7 @@
         <v>27</v>
       </c>
       <c r="E73">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F73" t="s">
         <v>34</v>
@@ -10292,7 +10292,7 @@
         <v>27</v>
       </c>
       <c r="E74">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -10338,7 +10338,7 @@
         <v>27</v>
       </c>
       <c r="E76">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
@@ -10361,7 +10361,7 @@
         <v>27</v>
       </c>
       <c r="E77">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F77" t="s">
         <v>34</v>
@@ -10384,7 +10384,7 @@
         <v>27</v>
       </c>
       <c r="E78">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
@@ -10407,7 +10407,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F79" t="s">
         <v>31</v>
@@ -10430,7 +10430,7 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
@@ -10453,7 +10453,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F81" t="s">
         <v>34</v>
@@ -10476,7 +10476,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -10499,7 +10499,7 @@
         <v>27</v>
       </c>
       <c r="E83">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F83" t="s">
         <v>31</v>
@@ -10522,7 +10522,7 @@
         <v>27</v>
       </c>
       <c r="E84">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
@@ -10545,7 +10545,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F85" t="s">
         <v>34</v>
@@ -10568,7 +10568,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -10591,7 +10591,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F87" t="s">
         <v>31</v>
@@ -10614,7 +10614,7 @@
         <v>27</v>
       </c>
       <c r="E88">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -10637,7 +10637,7 @@
         <v>27</v>
       </c>
       <c r="E89">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F89" t="s">
         <v>34</v>
@@ -10660,7 +10660,7 @@
         <v>27</v>
       </c>
       <c r="E90">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F90" t="s">
         <v>28</v>
@@ -10706,7 +10706,7 @@
         <v>27</v>
       </c>
       <c r="E92">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
@@ -10775,7 +10775,7 @@
         <v>27</v>
       </c>
       <c r="E95">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F95" t="s">
         <v>34</v>
@@ -10798,7 +10798,7 @@
         <v>27</v>
       </c>
       <c r="E96">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -10821,7 +10821,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F97" t="s">
         <v>31</v>
@@ -10844,7 +10844,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -10867,7 +10867,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F99" t="s">
         <v>34</v>
@@ -10890,7 +10890,7 @@
         <v>27</v>
       </c>
       <c r="E100">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
@@ -10913,7 +10913,7 @@
         <v>27</v>
       </c>
       <c r="E101">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F101" t="s">
         <v>31</v>
@@ -10936,7 +10936,7 @@
         <v>27</v>
       </c>
       <c r="E102">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
@@ -10959,7 +10959,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F103" t="s">
         <v>34</v>
@@ -10982,7 +10982,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -11005,7 +11005,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F105" t="s">
         <v>31</v>
@@ -11028,7 +11028,7 @@
         <v>27</v>
       </c>
       <c r="E106">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
@@ -11051,7 +11051,7 @@
         <v>27</v>
       </c>
       <c r="E107">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F107" t="s">
         <v>34</v>
@@ -11074,7 +11074,7 @@
         <v>27</v>
       </c>
       <c r="E108">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
@@ -11120,7 +11120,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -11143,7 +11143,7 @@
         <v>27</v>
       </c>
       <c r="E111">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F111" t="s">
         <v>34</v>
@@ -11166,7 +11166,7 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F112" t="s">
         <v>28</v>
@@ -11189,7 +11189,7 @@
         <v>27</v>
       </c>
       <c r="E113">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F113" t="s">
         <v>31</v>
@@ -11212,7 +11212,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -11235,7 +11235,7 @@
         <v>27</v>
       </c>
       <c r="E115">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F115" t="s">
         <v>34</v>
@@ -11258,7 +11258,7 @@
         <v>27</v>
       </c>
       <c r="E116">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F116" t="s">
         <v>28</v>
@@ -11281,7 +11281,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F117" t="s">
         <v>31</v>
@@ -11304,7 +11304,7 @@
         <v>27</v>
       </c>
       <c r="E118">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F118" t="s">
         <v>28</v>
@@ -11350,7 +11350,7 @@
         <v>27</v>
       </c>
       <c r="E120">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
@@ -11373,7 +11373,7 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F121" t="s">
         <v>31</v>
@@ -11396,7 +11396,7 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -11419,7 +11419,7 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F123" t="s">
         <v>31</v>
@@ -11442,7 +11442,7 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F124" t="s">
         <v>28</v>
@@ -11465,7 +11465,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F125" t="s">
         <v>34</v>
@@ -11488,7 +11488,7 @@
         <v>27</v>
       </c>
       <c r="E126">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
@@ -11511,7 +11511,7 @@
         <v>27</v>
       </c>
       <c r="E127">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F127" t="s">
         <v>31</v>
@@ -11534,7 +11534,7 @@
         <v>27</v>
       </c>
       <c r="E128">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -11557,7 +11557,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F129" t="s">
         <v>34</v>
@@ -11580,7 +11580,7 @@
         <v>27</v>
       </c>
       <c r="E130">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
@@ -11603,7 +11603,7 @@
         <v>27</v>
       </c>
       <c r="E131">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F131" t="s">
         <v>31</v>
@@ -11626,7 +11626,7 @@
         <v>27</v>
       </c>
       <c r="E132">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F132" t="s">
         <v>28</v>
@@ -11649,7 +11649,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F133" t="s">
         <v>34</v>
@@ -11672,7 +11672,7 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -11695,7 +11695,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F135" t="s">
         <v>31</v>
@@ -11741,7 +11741,7 @@
         <v>27</v>
       </c>
       <c r="E137">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F137" t="s">
         <v>34</v>
@@ -11764,7 +11764,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -11787,7 +11787,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F139" t="s">
         <v>31</v>
@@ -11810,7 +11810,7 @@
         <v>27</v>
       </c>
       <c r="E140">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
@@ -11833,7 +11833,7 @@
         <v>27</v>
       </c>
       <c r="E141">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F141" t="s">
         <v>34</v>
@@ -11856,7 +11856,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -11879,7 +11879,7 @@
         <v>27</v>
       </c>
       <c r="E143">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F143" t="s">
         <v>31</v>
@@ -11925,7 +11925,7 @@
         <v>27</v>
       </c>
       <c r="E145">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F145" t="s">
         <v>34</v>
@@ -11948,7 +11948,7 @@
         <v>27</v>
       </c>
       <c r="E146">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F146" t="s">
         <v>28</v>
@@ -11971,7 +11971,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F147" t="s">
         <v>31</v>
@@ -11994,7 +11994,7 @@
         <v>27</v>
       </c>
       <c r="E148">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
@@ -12017,7 +12017,7 @@
         <v>27</v>
       </c>
       <c r="E149">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F149" t="s">
         <v>34</v>
@@ -12040,7 +12040,7 @@
         <v>27</v>
       </c>
       <c r="E150">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
@@ -12063,7 +12063,7 @@
         <v>27</v>
       </c>
       <c r="E151">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F151" t="s">
         <v>31</v>
@@ -12086,7 +12086,7 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F152" t="s">
         <v>28</v>
@@ -12109,7 +12109,7 @@
         <v>27</v>
       </c>
       <c r="E153">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F153" t="s">
         <v>31</v>
@@ -12132,7 +12132,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -12155,7 +12155,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F155" t="s">
         <v>34</v>
@@ -12178,7 +12178,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -12201,7 +12201,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F157" t="s">
         <v>31</v>
@@ -12224,7 +12224,7 @@
         <v>27</v>
       </c>
       <c r="E158">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F158" t="s">
         <v>28</v>
@@ -12247,7 +12247,7 @@
         <v>27</v>
       </c>
       <c r="E159">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F159" t="s">
         <v>34</v>
@@ -12270,7 +12270,7 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F160" t="s">
         <v>28</v>
@@ -12293,7 +12293,7 @@
         <v>27</v>
       </c>
       <c r="E161">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F161" t="s">
         <v>31</v>
@@ -12316,7 +12316,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -12339,7 +12339,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F163" t="s">
         <v>34</v>
@@ -12362,7 +12362,7 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
@@ -12385,7 +12385,7 @@
         <v>27</v>
       </c>
       <c r="E165">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F165" t="s">
         <v>31</v>
@@ -12408,7 +12408,7 @@
         <v>27</v>
       </c>
       <c r="E166">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -12431,7 +12431,7 @@
         <v>27</v>
       </c>
       <c r="E167">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F167" t="s">
         <v>34</v>
@@ -12454,7 +12454,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -12477,7 +12477,7 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F169" t="s">
         <v>31</v>
@@ -12500,7 +12500,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -12523,7 +12523,7 @@
         <v>27</v>
       </c>
       <c r="E171">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F171" t="s">
         <v>34</v>
@@ -12546,7 +12546,7 @@
         <v>27</v>
       </c>
       <c r="E172">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
@@ -12569,7 +12569,7 @@
         <v>27</v>
       </c>
       <c r="E173">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F173" t="s">
         <v>31</v>
@@ -12592,7 +12592,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -12615,7 +12615,7 @@
         <v>27</v>
       </c>
       <c r="E175">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F175" t="s">
         <v>34</v>
@@ -12638,7 +12638,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -12661,7 +12661,7 @@
         <v>27</v>
       </c>
       <c r="E177">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
@@ -12684,7 +12684,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F178" t="s">
         <v>31</v>
@@ -12707,7 +12707,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -12730,7 +12730,7 @@
         <v>27</v>
       </c>
       <c r="E180">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F180" t="s">
         <v>34</v>
@@ -12753,7 +12753,7 @@
         <v>27</v>
       </c>
       <c r="E181">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F181" t="s">
         <v>28</v>
@@ -12776,7 +12776,7 @@
         <v>27</v>
       </c>
       <c r="E182">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F182" t="s">
         <v>31</v>
@@ -12799,7 +12799,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -12822,7 +12822,7 @@
         <v>27</v>
       </c>
       <c r="E184">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F184" t="s">
         <v>34</v>
@@ -12845,7 +12845,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -12868,7 +12868,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F186" t="s">
         <v>31</v>
@@ -12891,7 +12891,7 @@
         <v>27</v>
       </c>
       <c r="E187">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F187" t="s">
         <v>28</v>
@@ -12914,7 +12914,7 @@
         <v>27</v>
       </c>
       <c r="E188">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F188" t="s">
         <v>34</v>
@@ -12937,7 +12937,7 @@
         <v>27</v>
       </c>
       <c r="E189">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F189" t="s">
         <v>28</v>
@@ -12960,7 +12960,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F190" t="s">
         <v>31</v>
@@ -12983,7 +12983,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -13006,7 +13006,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F192" t="s">
         <v>34</v>
@@ -13029,7 +13029,7 @@
         <v>27</v>
       </c>
       <c r="E193">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -13052,7 +13052,7 @@
         <v>27</v>
       </c>
       <c r="E194">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F194" t="s">
         <v>31</v>
@@ -13075,7 +13075,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -13098,7 +13098,7 @@
         <v>27</v>
       </c>
       <c r="E196">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F196" t="s">
         <v>34</v>
@@ -13121,7 +13121,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -13144,7 +13144,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F198" t="s">
         <v>31</v>
@@ -13167,7 +13167,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -13190,7 +13190,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F200" t="s">
         <v>34</v>
@@ -13213,7 +13213,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -13236,7 +13236,7 @@
         <v>27</v>
       </c>
       <c r="E202">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -13259,7 +13259,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F203" t="s">
         <v>31</v>
@@ -13282,7 +13282,7 @@
         <v>27</v>
       </c>
       <c r="E204">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -13305,7 +13305,7 @@
         <v>27</v>
       </c>
       <c r="E205">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F205" t="s">
         <v>34</v>
@@ -13328,7 +13328,7 @@
         <v>27</v>
       </c>
       <c r="E206">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -13351,7 +13351,7 @@
         <v>27</v>
       </c>
       <c r="E207">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F207" t="s">
         <v>31</v>
@@ -13374,7 +13374,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -13397,7 +13397,7 @@
         <v>27</v>
       </c>
       <c r="E209">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F209" t="s">
         <v>34</v>
@@ -13420,7 +13420,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -13443,7 +13443,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F211" t="s">
         <v>31</v>
@@ -13466,7 +13466,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -13489,7 +13489,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F213" t="s">
         <v>34</v>
@@ -13512,7 +13512,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -13535,7 +13535,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F215" t="s">
         <v>31</v>
@@ -13558,7 +13558,7 @@
         <v>27</v>
       </c>
       <c r="E216">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F216" t="s">
         <v>28</v>
@@ -13581,7 +13581,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F217" t="s">
         <v>34</v>
@@ -13604,7 +13604,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -13627,7 +13627,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F219" t="s">
         <v>31</v>
@@ -13650,7 +13650,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -13673,7 +13673,7 @@
         <v>27</v>
       </c>
       <c r="E221">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F221" t="s">
         <v>34</v>
@@ -13696,7 +13696,7 @@
         <v>27</v>
       </c>
       <c r="E222">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F222" t="s">
         <v>28</v>
@@ -13719,7 +13719,7 @@
         <v>27</v>
       </c>
       <c r="E223">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F223" t="s">
         <v>31</v>
@@ -13742,7 +13742,7 @@
         <v>27</v>
       </c>
       <c r="E224">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F224" t="s">
         <v>28</v>
@@ -13765,7 +13765,7 @@
         <v>27</v>
       </c>
       <c r="E225">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F225" t="s">
         <v>34</v>
@@ -13788,7 +13788,7 @@
         <v>27</v>
       </c>
       <c r="E226">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F226" t="s">
         <v>28</v>
@@ -13811,7 +13811,7 @@
         <v>27</v>
       </c>
       <c r="E227">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F227" t="s">
         <v>28</v>
@@ -13834,7 +13834,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F228" t="s">
         <v>31</v>
@@ -13857,7 +13857,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -13880,7 +13880,7 @@
         <v>27</v>
       </c>
       <c r="E230">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F230" t="s">
         <v>34</v>
@@ -13926,7 +13926,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F232" t="s">
         <v>31</v>
@@ -13949,7 +13949,7 @@
         <v>27</v>
       </c>
       <c r="E233">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F233" t="s">
         <v>28</v>
@@ -13972,7 +13972,7 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F234" t="s">
         <v>34</v>
@@ -13995,7 +13995,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -14018,7 +14018,7 @@
         <v>27</v>
       </c>
       <c r="E236">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F236" t="s">
         <v>31</v>
@@ -14041,7 +14041,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -14064,7 +14064,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F238" t="s">
         <v>34</v>
@@ -14087,7 +14087,7 @@
         <v>27</v>
       </c>
       <c r="E239">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F239" t="s">
         <v>28</v>
@@ -14110,7 +14110,7 @@
         <v>27</v>
       </c>
       <c r="E240">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F240" t="s">
         <v>31</v>
@@ -14133,7 +14133,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -14156,7 +14156,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F242" t="s">
         <v>34</v>
@@ -14179,7 +14179,7 @@
         <v>27</v>
       </c>
       <c r="E243">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -14202,7 +14202,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F244" t="s">
         <v>31</v>
@@ -14225,7 +14225,7 @@
         <v>27</v>
       </c>
       <c r="E245">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F245" t="s">
         <v>28</v>
@@ -14248,7 +14248,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F246" t="s">
         <v>34</v>
@@ -14271,7 +14271,7 @@
         <v>27</v>
       </c>
       <c r="E247">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F247" t="s">
         <v>28</v>
@@ -14294,7 +14294,7 @@
         <v>27</v>
       </c>
       <c r="E248">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F248" t="s">
         <v>31</v>
@@ -14317,7 +14317,7 @@
         <v>27</v>
       </c>
       <c r="E249">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F249" t="s">
         <v>28</v>
@@ -14340,7 +14340,7 @@
         <v>27</v>
       </c>
       <c r="E250">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F250" t="s">
         <v>34</v>
@@ -14363,7 +14363,7 @@
         <v>27</v>
       </c>
       <c r="E251">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F251" t="s">
         <v>28</v>
@@ -14386,7 +14386,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -14409,7 +14409,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F253" t="s">
         <v>31</v>
@@ -14432,7 +14432,7 @@
         <v>27</v>
       </c>
       <c r="E254">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F254" t="s">
         <v>28</v>
@@ -14455,7 +14455,7 @@
         <v>27</v>
       </c>
       <c r="E255">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F255" t="s">
         <v>34</v>
@@ -14478,7 +14478,7 @@
         <v>27</v>
       </c>
       <c r="E256">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F256" t="s">
         <v>28</v>
@@ -14501,7 +14501,7 @@
         <v>27</v>
       </c>
       <c r="E257">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F257" t="s">
         <v>31</v>
@@ -14524,7 +14524,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -14547,7 +14547,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F259" t="s">
         <v>34</v>
@@ -14570,7 +14570,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -14593,7 +14593,7 @@
         <v>27</v>
       </c>
       <c r="E261">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F261" t="s">
         <v>31</v>
@@ -14616,7 +14616,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -14639,7 +14639,7 @@
         <v>27</v>
       </c>
       <c r="E263">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F263" t="s">
         <v>34</v>
@@ -14662,7 +14662,7 @@
         <v>27</v>
       </c>
       <c r="E264">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -14685,7 +14685,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F265" t="s">
         <v>31</v>
@@ -14708,7 +14708,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -14731,7 +14731,7 @@
         <v>27</v>
       </c>
       <c r="E267">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F267" t="s">
         <v>34</v>
@@ -14754,7 +14754,7 @@
         <v>27</v>
       </c>
       <c r="E268">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F268" t="s">
         <v>28</v>
@@ -14777,7 +14777,7 @@
         <v>27</v>
       </c>
       <c r="E269">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F269" t="s">
         <v>31</v>
@@ -14800,7 +14800,7 @@
         <v>27</v>
       </c>
       <c r="E270">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F270" t="s">
         <v>28</v>
@@ -14823,7 +14823,7 @@
         <v>27</v>
       </c>
       <c r="E271">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F271" t="s">
         <v>34</v>
@@ -14846,7 +14846,7 @@
         <v>27</v>
       </c>
       <c r="E272">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F272" t="s">
         <v>28</v>
@@ -14869,7 +14869,7 @@
         <v>27</v>
       </c>
       <c r="E273">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F273" t="s">
         <v>31</v>
@@ -14892,7 +14892,7 @@
         <v>27</v>
       </c>
       <c r="E274">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F274" t="s">
         <v>28</v>
@@ -14915,7 +14915,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F275" t="s">
         <v>34</v>
@@ -14938,7 +14938,7 @@
         <v>27</v>
       </c>
       <c r="E276">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F276" t="s">
         <v>28</v>
@@ -14961,7 +14961,7 @@
         <v>27</v>
       </c>
       <c r="E277">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F277" t="s">
         <v>28</v>
@@ -15007,7 +15007,7 @@
         <v>27</v>
       </c>
       <c r="E279">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -15030,7 +15030,7 @@
         <v>27</v>
       </c>
       <c r="E280">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F280" t="s">
         <v>34</v>
@@ -15053,7 +15053,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -15076,7 +15076,7 @@
         <v>27</v>
       </c>
       <c r="E282">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F282" t="s">
         <v>31</v>
@@ -15099,7 +15099,7 @@
         <v>27</v>
       </c>
       <c r="E283">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F283" t="s">
         <v>28</v>
@@ -15122,7 +15122,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F284" t="s">
         <v>34</v>
@@ -15145,7 +15145,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -15168,7 +15168,7 @@
         <v>27</v>
       </c>
       <c r="E286">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F286" t="s">
         <v>31</v>
@@ -15191,7 +15191,7 @@
         <v>27</v>
       </c>
       <c r="E287">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F287" t="s">
         <v>28</v>
@@ -15214,7 +15214,7 @@
         <v>27</v>
       </c>
       <c r="E288">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F288" t="s">
         <v>34</v>
@@ -15237,7 +15237,7 @@
         <v>27</v>
       </c>
       <c r="E289">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F289" t="s">
         <v>28</v>
@@ -15260,7 +15260,7 @@
         <v>27</v>
       </c>
       <c r="E290">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F290" t="s">
         <v>31</v>
@@ -15283,7 +15283,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -15306,7 +15306,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F292" t="s">
         <v>34</v>
@@ -15329,7 +15329,7 @@
         <v>27</v>
       </c>
       <c r="E293">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -15352,7 +15352,7 @@
         <v>27</v>
       </c>
       <c r="E294">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F294" t="s">
         <v>31</v>
@@ -15375,7 +15375,7 @@
         <v>27</v>
       </c>
       <c r="E295">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F295" t="s">
         <v>28</v>
@@ -15398,7 +15398,7 @@
         <v>27</v>
       </c>
       <c r="E296">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F296" t="s">
         <v>34</v>
@@ -15421,7 +15421,7 @@
         <v>27</v>
       </c>
       <c r="E297">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F297" t="s">
         <v>28</v>
@@ -15444,7 +15444,7 @@
         <v>27</v>
       </c>
       <c r="E298">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F298" t="s">
         <v>31</v>
@@ -15467,7 +15467,7 @@
         <v>27</v>
       </c>
       <c r="E299">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F299" t="s">
         <v>28</v>
@@ -15513,7 +15513,7 @@
         <v>27</v>
       </c>
       <c r="E301">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F301" t="s">
         <v>28</v>

--- a/all-test-reports/vulnerability/vulnerability_test_report.xlsx
+++ b/all-test-reports/vulnerability/vulnerability_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 11:17:40 am</t>
+    <t>28/7/2026, 11:28:00 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1694,7 +1694,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="10">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>28</v>
@@ -1717,7 +1717,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="10">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>31</v>
@@ -1740,7 +1740,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="10">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>28</v>
@@ -1763,7 +1763,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="10">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>34</v>
@@ -1786,7 +1786,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="10">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>28</v>
@@ -1809,7 +1809,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="10">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>31</v>
@@ -1832,7 +1832,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="10">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>28</v>
@@ -1855,7 +1855,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="10">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>34</v>
@@ -1878,7 +1878,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="10">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>28</v>
@@ -1901,7 +1901,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="10">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>31</v>
@@ -1924,7 +1924,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="10">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>28</v>
@@ -1947,7 +1947,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="10">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>34</v>
@@ -1970,7 +1970,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>28</v>
@@ -1993,7 +1993,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="10">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>31</v>
@@ -2016,7 +2016,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="10">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>28</v>
@@ -2039,7 +2039,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="10">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>34</v>
@@ -2062,7 +2062,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="10">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>28</v>
@@ -2085,7 +2085,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="10">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>31</v>
@@ -2108,7 +2108,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="10">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>28</v>
@@ -2131,7 +2131,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="10">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>34</v>
@@ -2154,7 +2154,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="10">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>28</v>
@@ -2177,7 +2177,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="10">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>31</v>
@@ -2200,7 +2200,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="10">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>28</v>
@@ -2223,7 +2223,7 @@
         <v>27</v>
       </c>
       <c r="E25" s="10">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>34</v>
@@ -2246,7 +2246,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="10">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>28</v>
@@ -2269,7 +2269,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="10">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>31</v>
@@ -2292,7 +2292,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="10">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>28</v>
@@ -2315,7 +2315,7 @@
         <v>27</v>
       </c>
       <c r="E29" s="10">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>34</v>
@@ -2338,7 +2338,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="10">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>28</v>
@@ -2361,7 +2361,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="10">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>31</v>
@@ -2384,7 +2384,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="10">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>28</v>
@@ -2407,7 +2407,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="10">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>31</v>
@@ -2430,7 +2430,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="10">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>28</v>
@@ -2453,7 +2453,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="10">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>34</v>
@@ -2476,7 +2476,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="10">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>28</v>
@@ -2499,7 +2499,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="10">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>31</v>
@@ -2522,7 +2522,7 @@
         <v>27</v>
       </c>
       <c r="E38" s="10">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>28</v>
@@ -2545,7 +2545,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="10">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>34</v>
@@ -2568,7 +2568,7 @@
         <v>27</v>
       </c>
       <c r="E40" s="10">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>28</v>
@@ -2591,7 +2591,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="10">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>31</v>
@@ -2614,7 +2614,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="10">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>28</v>
@@ -2637,7 +2637,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="10">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>34</v>
@@ -2660,7 +2660,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="10">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>28</v>
@@ -2683,7 +2683,7 @@
         <v>27</v>
       </c>
       <c r="E45" s="10">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>31</v>
@@ -2706,7 +2706,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="10">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>28</v>
@@ -2729,7 +2729,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="10">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>34</v>
@@ -2752,7 +2752,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="10">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>28</v>
@@ -2775,7 +2775,7 @@
         <v>27</v>
       </c>
       <c r="E49" s="10">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>31</v>
@@ -2798,7 +2798,7 @@
         <v>27</v>
       </c>
       <c r="E50" s="10">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>28</v>
@@ -2821,7 +2821,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>34</v>
@@ -2844,7 +2844,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>28</v>
@@ -2867,7 +2867,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="10">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>31</v>
@@ -2890,7 +2890,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>28</v>
@@ -2913,7 +2913,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="10">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>34</v>
@@ -2936,7 +2936,7 @@
         <v>27</v>
       </c>
       <c r="E56" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>28</v>
@@ -2959,7 +2959,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="10">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>31</v>
@@ -2982,7 +2982,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="10">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>28</v>
@@ -3005,7 +3005,7 @@
         <v>27</v>
       </c>
       <c r="E59" s="10">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>34</v>
@@ -3028,7 +3028,7 @@
         <v>27</v>
       </c>
       <c r="E60" s="10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>28</v>
@@ -3051,7 +3051,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="10">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>31</v>
@@ -3074,7 +3074,7 @@
         <v>27</v>
       </c>
       <c r="E62" s="10">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>28</v>
@@ -3097,7 +3097,7 @@
         <v>27</v>
       </c>
       <c r="E63" s="10">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>31</v>
@@ -3120,7 +3120,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="10">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>28</v>
@@ -3143,7 +3143,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="10">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>34</v>
@@ -3166,7 +3166,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="10">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>28</v>
@@ -3189,7 +3189,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>31</v>
@@ -3212,7 +3212,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="10">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>28</v>
@@ -3235,7 +3235,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>34</v>
@@ -3258,7 +3258,7 @@
         <v>27</v>
       </c>
       <c r="E70" s="10">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>28</v>
@@ -3281,7 +3281,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="10">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>31</v>
@@ -3304,7 +3304,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="10">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>28</v>
@@ -3327,7 +3327,7 @@
         <v>27</v>
       </c>
       <c r="E73" s="10">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>34</v>
@@ -3350,7 +3350,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="10">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>28</v>
@@ -3373,7 +3373,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="10">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>31</v>
@@ -3396,7 +3396,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="10">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>28</v>
@@ -3419,7 +3419,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="10">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>34</v>
@@ -3442,7 +3442,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="10">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>28</v>
@@ -3465,7 +3465,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>31</v>
@@ -3511,7 +3511,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="10">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>34</v>
@@ -3534,7 +3534,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="10">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>28</v>
@@ -3557,7 +3557,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="10">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>31</v>
@@ -3580,7 +3580,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="10">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>28</v>
@@ -3603,7 +3603,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="10">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>34</v>
@@ -3626,7 +3626,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="10">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>28</v>
@@ -3649,7 +3649,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="10">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>31</v>
@@ -3672,7 +3672,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>28</v>
@@ -3695,7 +3695,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="10">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>34</v>
@@ -3718,7 +3718,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="10">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>28</v>
@@ -3741,7 +3741,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="10">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>31</v>
@@ -3764,7 +3764,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="10">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>28</v>
@@ -3787,7 +3787,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="10">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>31</v>
@@ -3810,7 +3810,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="10">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>28</v>
@@ -3833,7 +3833,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="10">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>34</v>
@@ -3856,7 +3856,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="10">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F96" s="8" t="s">
         <v>28</v>
@@ -3879,7 +3879,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="10">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>31</v>
@@ -3902,7 +3902,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="10">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>28</v>
@@ -3925,7 +3925,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="10">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>34</v>
@@ -3948,7 +3948,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="10">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>28</v>
@@ -3971,7 +3971,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="10">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>31</v>
@@ -3994,7 +3994,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="10">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>28</v>
@@ -4017,7 +4017,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="10">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>34</v>
@@ -4040,7 +4040,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="10">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>28</v>
@@ -4063,7 +4063,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="10">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>31</v>
@@ -4086,7 +4086,7 @@
         <v>27</v>
       </c>
       <c r="E106" s="10">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>28</v>
@@ -4109,7 +4109,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="10">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>34</v>
@@ -4132,7 +4132,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="10">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>28</v>
@@ -4155,7 +4155,7 @@
         <v>27</v>
       </c>
       <c r="E109" s="10">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>31</v>
@@ -4178,7 +4178,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="10">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>28</v>
@@ -4201,7 +4201,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="10">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>34</v>
@@ -4224,7 +4224,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="10">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>28</v>
@@ -4247,7 +4247,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F113" s="8" t="s">
         <v>31</v>
@@ -4270,7 +4270,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="10">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>28</v>
@@ -4293,7 +4293,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="10">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>34</v>
@@ -4316,7 +4316,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="10">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>28</v>
@@ -4339,7 +4339,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="10">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F117" s="8" t="s">
         <v>31</v>
@@ -4362,7 +4362,7 @@
         <v>27</v>
       </c>
       <c r="E118" s="10">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F118" s="8" t="s">
         <v>28</v>
@@ -4385,7 +4385,7 @@
         <v>27</v>
       </c>
       <c r="E119" s="10">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F119" s="8" t="s">
         <v>34</v>
@@ -4408,7 +4408,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F120" s="8" t="s">
         <v>28</v>
@@ -4431,7 +4431,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="10">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F121" s="8" t="s">
         <v>31</v>
@@ -4454,7 +4454,7 @@
         <v>27</v>
       </c>
       <c r="E122" s="10">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F122" s="8" t="s">
         <v>28</v>
@@ -4477,7 +4477,7 @@
         <v>27</v>
       </c>
       <c r="E123" s="10">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>31</v>
@@ -4500,7 +4500,7 @@
         <v>27</v>
       </c>
       <c r="E124" s="10">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F124" s="8" t="s">
         <v>28</v>
@@ -4523,7 +4523,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="10">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>34</v>
@@ -4546,7 +4546,7 @@
         <v>27</v>
       </c>
       <c r="E126" s="10">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F126" s="8" t="s">
         <v>28</v>
@@ -4569,7 +4569,7 @@
         <v>27</v>
       </c>
       <c r="E127" s="10">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F127" s="8" t="s">
         <v>31</v>
@@ -4592,7 +4592,7 @@
         <v>27</v>
       </c>
       <c r="E128" s="10">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F128" s="8" t="s">
         <v>28</v>
@@ -4615,7 +4615,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="10">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F129" s="8" t="s">
         <v>34</v>
@@ -4638,7 +4638,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="10">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F130" s="8" t="s">
         <v>28</v>
@@ -4684,7 +4684,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="10">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F132" s="8" t="s">
         <v>28</v>
@@ -4707,7 +4707,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="10">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F133" s="8" t="s">
         <v>34</v>
@@ -4730,7 +4730,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="10">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F134" s="8" t="s">
         <v>28</v>
@@ -4753,7 +4753,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="10">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F135" s="8" t="s">
         <v>31</v>
@@ -4776,7 +4776,7 @@
         <v>27</v>
       </c>
       <c r="E136" s="10">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F136" s="8" t="s">
         <v>28</v>
@@ -4799,7 +4799,7 @@
         <v>27</v>
       </c>
       <c r="E137" s="10">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F137" s="8" t="s">
         <v>34</v>
@@ -4822,7 +4822,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F138" s="8" t="s">
         <v>28</v>
@@ -4845,7 +4845,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="10">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F139" s="8" t="s">
         <v>31</v>
@@ -4868,7 +4868,7 @@
         <v>27</v>
       </c>
       <c r="E140" s="10">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F140" s="8" t="s">
         <v>28</v>
@@ -4891,7 +4891,7 @@
         <v>27</v>
       </c>
       <c r="E141" s="10">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F141" s="8" t="s">
         <v>34</v>
@@ -4914,7 +4914,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="10">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F142" s="8" t="s">
         <v>28</v>
@@ -4937,7 +4937,7 @@
         <v>27</v>
       </c>
       <c r="E143" s="10">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F143" s="8" t="s">
         <v>31</v>
@@ -4960,7 +4960,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="10">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F144" s="8" t="s">
         <v>28</v>
@@ -4983,7 +4983,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="10">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F145" s="8" t="s">
         <v>34</v>
@@ -5029,7 +5029,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="10">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F147" s="8" t="s">
         <v>31</v>
@@ -5052,7 +5052,7 @@
         <v>27</v>
       </c>
       <c r="E148" s="10">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F148" s="8" t="s">
         <v>28</v>
@@ -5075,7 +5075,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="10">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F149" s="8" t="s">
         <v>34</v>
@@ -5144,7 +5144,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="10">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>28</v>
@@ -5167,7 +5167,7 @@
         <v>27</v>
       </c>
       <c r="E153" s="10">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F153" s="8" t="s">
         <v>31</v>
@@ -5190,7 +5190,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="10">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>28</v>
@@ -5213,7 +5213,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="10">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F155" s="8" t="s">
         <v>34</v>
@@ -5236,7 +5236,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="10">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F156" s="8" t="s">
         <v>28</v>
@@ -5259,7 +5259,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="10">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F157" s="8" t="s">
         <v>31</v>
@@ -5305,7 +5305,7 @@
         <v>27</v>
       </c>
       <c r="E159" s="10">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F159" s="8" t="s">
         <v>34</v>
@@ -5328,7 +5328,7 @@
         <v>27</v>
       </c>
       <c r="E160" s="10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F160" s="8" t="s">
         <v>28</v>
@@ -5351,7 +5351,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="10">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F161" s="8" t="s">
         <v>31</v>
@@ -5374,7 +5374,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="10">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F162" s="8" t="s">
         <v>28</v>
@@ -5397,7 +5397,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="10">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F163" s="8" t="s">
         <v>34</v>
@@ -5420,7 +5420,7 @@
         <v>27</v>
       </c>
       <c r="E164" s="10">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F164" s="8" t="s">
         <v>28</v>
@@ -5466,7 +5466,7 @@
         <v>27</v>
       </c>
       <c r="E166" s="10">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F166" s="8" t="s">
         <v>28</v>
@@ -5489,7 +5489,7 @@
         <v>27</v>
       </c>
       <c r="E167" s="10">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F167" s="8" t="s">
         <v>34</v>
@@ -5512,7 +5512,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="10">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F168" s="8" t="s">
         <v>28</v>
@@ -5535,7 +5535,7 @@
         <v>27</v>
       </c>
       <c r="E169" s="10">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F169" s="8" t="s">
         <v>31</v>
@@ -5558,7 +5558,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="10">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F170" s="8" t="s">
         <v>28</v>
@@ -5581,7 +5581,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="10">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F171" s="8" t="s">
         <v>34</v>
@@ -5604,7 +5604,7 @@
         <v>27</v>
       </c>
       <c r="E172" s="10">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F172" s="8" t="s">
         <v>28</v>
@@ -5627,7 +5627,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="10">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F173" s="8" t="s">
         <v>31</v>
@@ -5650,7 +5650,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F174" s="8" t="s">
         <v>28</v>
@@ -5673,7 +5673,7 @@
         <v>27</v>
       </c>
       <c r="E175" s="10">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F175" s="8" t="s">
         <v>34</v>
@@ -5696,7 +5696,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="10">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F176" s="8" t="s">
         <v>28</v>
@@ -5719,7 +5719,7 @@
         <v>27</v>
       </c>
       <c r="E177" s="10">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F177" s="8" t="s">
         <v>28</v>
@@ -5742,7 +5742,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="10">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F178" s="8" t="s">
         <v>31</v>
@@ -5765,7 +5765,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="10">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F179" s="8" t="s">
         <v>28</v>
@@ -5788,7 +5788,7 @@
         <v>27</v>
       </c>
       <c r="E180" s="10">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F180" s="8" t="s">
         <v>34</v>
@@ -5811,7 +5811,7 @@
         <v>27</v>
       </c>
       <c r="E181" s="10">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F181" s="8" t="s">
         <v>28</v>
@@ -5834,7 +5834,7 @@
         <v>27</v>
       </c>
       <c r="E182" s="10">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F182" s="8" t="s">
         <v>31</v>
@@ -5857,7 +5857,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="10">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F183" s="8" t="s">
         <v>28</v>
@@ -5880,7 +5880,7 @@
         <v>27</v>
       </c>
       <c r="E184" s="10">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F184" s="8" t="s">
         <v>34</v>
@@ -5903,7 +5903,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="10">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F185" s="8" t="s">
         <v>28</v>
@@ -5926,7 +5926,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="10">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F186" s="8" t="s">
         <v>31</v>
@@ -5972,7 +5972,7 @@
         <v>27</v>
       </c>
       <c r="E188" s="10">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F188" s="8" t="s">
         <v>34</v>
@@ -5995,7 +5995,7 @@
         <v>27</v>
       </c>
       <c r="E189" s="10">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F189" s="8" t="s">
         <v>28</v>
@@ -6018,7 +6018,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="10">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F190" s="8" t="s">
         <v>31</v>
@@ -6041,7 +6041,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="10">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F191" s="8" t="s">
         <v>28</v>
@@ -6064,7 +6064,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="10">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F192" s="8" t="s">
         <v>34</v>
@@ -6087,7 +6087,7 @@
         <v>27</v>
       </c>
       <c r="E193" s="10">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F193" s="8" t="s">
         <v>28</v>
@@ -6110,7 +6110,7 @@
         <v>27</v>
       </c>
       <c r="E194" s="10">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F194" s="8" t="s">
         <v>31</v>
@@ -6133,7 +6133,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="10">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F195" s="8" t="s">
         <v>28</v>
@@ -6156,7 +6156,7 @@
         <v>27</v>
       </c>
       <c r="E196" s="10">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F196" s="8" t="s">
         <v>34</v>
@@ -6179,7 +6179,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="10">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F197" s="8" t="s">
         <v>28</v>
@@ -6202,7 +6202,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="10">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F198" s="8" t="s">
         <v>31</v>
@@ -6225,7 +6225,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="10">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F199" s="8" t="s">
         <v>28</v>
@@ -6248,7 +6248,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="10">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F200" s="8" t="s">
         <v>34</v>
@@ -6271,7 +6271,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="10">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F201" s="8" t="s">
         <v>28</v>
@@ -6294,7 +6294,7 @@
         <v>27</v>
       </c>
       <c r="E202" s="10">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F202" s="8" t="s">
         <v>28</v>
@@ -6317,7 +6317,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="10">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F203" s="8" t="s">
         <v>31</v>
@@ -6340,7 +6340,7 @@
         <v>27</v>
       </c>
       <c r="E204" s="10">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F204" s="8" t="s">
         <v>28</v>
@@ -6363,7 +6363,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F205" s="8" t="s">
         <v>34</v>
@@ -6386,7 +6386,7 @@
         <v>27</v>
       </c>
       <c r="E206" s="10">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F206" s="8" t="s">
         <v>28</v>
@@ -6409,7 +6409,7 @@
         <v>27</v>
       </c>
       <c r="E207" s="10">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F207" s="8" t="s">
         <v>31</v>
@@ -6432,7 +6432,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="10">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F208" s="8" t="s">
         <v>28</v>
@@ -6455,7 +6455,7 @@
         <v>27</v>
       </c>
       <c r="E209" s="10">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F209" s="8" t="s">
         <v>34</v>
@@ -6478,7 +6478,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="10">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F210" s="8" t="s">
         <v>28</v>
@@ -6501,7 +6501,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="10">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F211" s="8" t="s">
         <v>31</v>
@@ -6524,7 +6524,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="10">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F212" s="8" t="s">
         <v>28</v>
@@ -6547,7 +6547,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="10">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F213" s="8" t="s">
         <v>34</v>
@@ -6570,7 +6570,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="10">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F214" s="8" t="s">
         <v>28</v>
@@ -6593,7 +6593,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="10">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F215" s="8" t="s">
         <v>31</v>
@@ -6616,7 +6616,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="10">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F216" s="8" t="s">
         <v>28</v>
@@ -6639,7 +6639,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="10">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F217" s="8" t="s">
         <v>34</v>
@@ -6662,7 +6662,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="10">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F218" s="8" t="s">
         <v>28</v>
@@ -6685,7 +6685,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="10">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F219" s="8" t="s">
         <v>31</v>
@@ -6708,7 +6708,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="10">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F220" s="8" t="s">
         <v>28</v>
@@ -6731,7 +6731,7 @@
         <v>27</v>
       </c>
       <c r="E221" s="10">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F221" s="8" t="s">
         <v>34</v>
@@ -6754,7 +6754,7 @@
         <v>27</v>
       </c>
       <c r="E222" s="10">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F222" s="8" t="s">
         <v>28</v>
@@ -6777,7 +6777,7 @@
         <v>27</v>
       </c>
       <c r="E223" s="10">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F223" s="8" t="s">
         <v>31</v>
@@ -6800,7 +6800,7 @@
         <v>27</v>
       </c>
       <c r="E224" s="10">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F224" s="8" t="s">
         <v>28</v>
@@ -6823,7 +6823,7 @@
         <v>27</v>
       </c>
       <c r="E225" s="10">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F225" s="8" t="s">
         <v>34</v>
@@ -6846,7 +6846,7 @@
         <v>27</v>
       </c>
       <c r="E226" s="10">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F226" s="8" t="s">
         <v>28</v>
@@ -6869,7 +6869,7 @@
         <v>27</v>
       </c>
       <c r="E227" s="10">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F227" s="8" t="s">
         <v>28</v>
@@ -6892,7 +6892,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="10">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F228" s="8" t="s">
         <v>31</v>
@@ -6915,7 +6915,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="10">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F229" s="8" t="s">
         <v>28</v>
@@ -6938,7 +6938,7 @@
         <v>27</v>
       </c>
       <c r="E230" s="10">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F230" s="8" t="s">
         <v>34</v>
@@ -6961,7 +6961,7 @@
         <v>27</v>
       </c>
       <c r="E231" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F231" s="8" t="s">
         <v>28</v>
@@ -6984,7 +6984,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="10">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F232" s="8" t="s">
         <v>31</v>
@@ -7007,7 +7007,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="10">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F233" s="8" t="s">
         <v>28</v>
@@ -7030,7 +7030,7 @@
         <v>27</v>
       </c>
       <c r="E234" s="10">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F234" s="8" t="s">
         <v>34</v>
@@ -7053,7 +7053,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="10">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F235" s="8" t="s">
         <v>28</v>
@@ -7076,7 +7076,7 @@
         <v>27</v>
       </c>
       <c r="E236" s="10">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F236" s="8" t="s">
         <v>31</v>
@@ -7099,7 +7099,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="10">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F237" s="8" t="s">
         <v>28</v>
@@ -7122,7 +7122,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="10">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F238" s="8" t="s">
         <v>34</v>
@@ -7168,7 +7168,7 @@
         <v>27</v>
       </c>
       <c r="E240" s="10">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F240" s="8" t="s">
         <v>31</v>
@@ -7191,7 +7191,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="10">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F241" s="8" t="s">
         <v>28</v>
@@ -7214,7 +7214,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="10">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F242" s="8" t="s">
         <v>34</v>
@@ -7237,7 +7237,7 @@
         <v>27</v>
       </c>
       <c r="E243" s="10">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F243" s="8" t="s">
         <v>28</v>
@@ -7260,7 +7260,7 @@
         <v>27</v>
       </c>
       <c r="E244" s="10">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F244" s="8" t="s">
         <v>31</v>
@@ -7306,7 +7306,7 @@
         <v>27</v>
       </c>
       <c r="E246" s="10">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F246" s="8" t="s">
         <v>34</v>
@@ -7329,7 +7329,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="10">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F247" s="8" t="s">
         <v>28</v>
@@ -7352,7 +7352,7 @@
         <v>27</v>
       </c>
       <c r="E248" s="10">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F248" s="8" t="s">
         <v>31</v>
@@ -7375,7 +7375,7 @@
         <v>27</v>
       </c>
       <c r="E249" s="10">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F249" s="8" t="s">
         <v>28</v>
@@ -7398,7 +7398,7 @@
         <v>27</v>
       </c>
       <c r="E250" s="10">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F250" s="8" t="s">
         <v>34</v>
@@ -7421,7 +7421,7 @@
         <v>27</v>
       </c>
       <c r="E251" s="10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F251" s="8" t="s">
         <v>28</v>
@@ -7444,7 +7444,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="10">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F252" s="8" t="s">
         <v>28</v>
@@ -7467,7 +7467,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="10">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F253" s="8" t="s">
         <v>31</v>
@@ -7490,7 +7490,7 @@
         <v>27</v>
       </c>
       <c r="E254" s="10">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F254" s="8" t="s">
         <v>28</v>
@@ -7513,7 +7513,7 @@
         <v>27</v>
       </c>
       <c r="E255" s="10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F255" s="8" t="s">
         <v>34</v>
@@ -7536,7 +7536,7 @@
         <v>27</v>
       </c>
       <c r="E256" s="10">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F256" s="8" t="s">
         <v>28</v>
@@ -7559,7 +7559,7 @@
         <v>27</v>
       </c>
       <c r="E257" s="10">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F257" s="8" t="s">
         <v>31</v>
@@ -7582,7 +7582,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="10">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F258" s="8" t="s">
         <v>28</v>
@@ -7605,7 +7605,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="10">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F259" s="8" t="s">
         <v>34</v>
@@ -7628,7 +7628,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="10">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F260" s="8" t="s">
         <v>28</v>
@@ -7651,7 +7651,7 @@
         <v>27</v>
       </c>
       <c r="E261" s="10">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F261" s="8" t="s">
         <v>31</v>
@@ -7674,7 +7674,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="10">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F262" s="8" t="s">
         <v>28</v>
@@ -7697,7 +7697,7 @@
         <v>27</v>
       </c>
       <c r="E263" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F263" s="8" t="s">
         <v>34</v>
@@ -7720,7 +7720,7 @@
         <v>27</v>
       </c>
       <c r="E264" s="10">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F264" s="8" t="s">
         <v>28</v>
@@ -7743,7 +7743,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="10">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F265" s="8" t="s">
         <v>31</v>
@@ -7766,7 +7766,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F266" s="8" t="s">
         <v>28</v>
@@ -7789,7 +7789,7 @@
         <v>27</v>
       </c>
       <c r="E267" s="10">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F267" s="8" t="s">
         <v>34</v>
@@ -7812,7 +7812,7 @@
         <v>27</v>
       </c>
       <c r="E268" s="10">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F268" s="8" t="s">
         <v>28</v>
@@ -7835,7 +7835,7 @@
         <v>27</v>
       </c>
       <c r="E269" s="10">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F269" s="8" t="s">
         <v>31</v>
@@ -7858,7 +7858,7 @@
         <v>27</v>
       </c>
       <c r="E270" s="10">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F270" s="8" t="s">
         <v>28</v>
@@ -7881,7 +7881,7 @@
         <v>27</v>
       </c>
       <c r="E271" s="10">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F271" s="8" t="s">
         <v>34</v>
@@ -7904,7 +7904,7 @@
         <v>27</v>
       </c>
       <c r="E272" s="10">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F272" s="8" t="s">
         <v>28</v>
@@ -7927,7 +7927,7 @@
         <v>27</v>
       </c>
       <c r="E273" s="10">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F273" s="8" t="s">
         <v>31</v>
@@ -7973,7 +7973,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="10">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F275" s="8" t="s">
         <v>34</v>
@@ -7996,7 +7996,7 @@
         <v>27</v>
       </c>
       <c r="E276" s="10">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F276" s="8" t="s">
         <v>28</v>
@@ -8019,7 +8019,7 @@
         <v>27</v>
       </c>
       <c r="E277" s="10">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F277" s="8" t="s">
         <v>28</v>
@@ -8042,7 +8042,7 @@
         <v>27</v>
       </c>
       <c r="E278" s="10">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F278" s="8" t="s">
         <v>31</v>
@@ -8065,7 +8065,7 @@
         <v>27</v>
       </c>
       <c r="E279" s="10">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F279" s="8" t="s">
         <v>28</v>
@@ -8088,7 +8088,7 @@
         <v>27</v>
       </c>
       <c r="E280" s="10">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F280" s="8" t="s">
         <v>34</v>
@@ -8111,7 +8111,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="10">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F281" s="8" t="s">
         <v>28</v>
@@ -8134,7 +8134,7 @@
         <v>27</v>
       </c>
       <c r="E282" s="10">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F282" s="8" t="s">
         <v>31</v>
@@ -8157,7 +8157,7 @@
         <v>27</v>
       </c>
       <c r="E283" s="10">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F283" s="8" t="s">
         <v>28</v>
@@ -8180,7 +8180,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="10">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F284" s="8" t="s">
         <v>34</v>
@@ -8203,7 +8203,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="10">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F285" s="8" t="s">
         <v>28</v>
@@ -8226,7 +8226,7 @@
         <v>27</v>
       </c>
       <c r="E286" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F286" s="8" t="s">
         <v>31</v>
@@ -8249,7 +8249,7 @@
         <v>27</v>
       </c>
       <c r="E287" s="10">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F287" s="8" t="s">
         <v>28</v>
@@ -8272,7 +8272,7 @@
         <v>27</v>
       </c>
       <c r="E288" s="10">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F288" s="8" t="s">
         <v>34</v>
@@ -8295,7 +8295,7 @@
         <v>27</v>
       </c>
       <c r="E289" s="10">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F289" s="8" t="s">
         <v>28</v>
@@ -8318,7 +8318,7 @@
         <v>27</v>
       </c>
       <c r="E290" s="10">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F290" s="8" t="s">
         <v>31</v>
@@ -8341,7 +8341,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="10">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F291" s="8" t="s">
         <v>28</v>
@@ -8364,7 +8364,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="10">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F292" s="8" t="s">
         <v>34</v>
@@ -8387,7 +8387,7 @@
         <v>27</v>
       </c>
       <c r="E293" s="10">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F293" s="8" t="s">
         <v>28</v>
@@ -8410,7 +8410,7 @@
         <v>27</v>
       </c>
       <c r="E294" s="10">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F294" s="8" t="s">
         <v>31</v>
@@ -8433,7 +8433,7 @@
         <v>27</v>
       </c>
       <c r="E295" s="10">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F295" s="8" t="s">
         <v>28</v>
@@ -8456,7 +8456,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="10">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F296" s="8" t="s">
         <v>34</v>
@@ -8479,7 +8479,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="10">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F297" s="8" t="s">
         <v>28</v>
@@ -8502,7 +8502,7 @@
         <v>27</v>
       </c>
       <c r="E298" s="10">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F298" s="8" t="s">
         <v>31</v>
@@ -8548,7 +8548,7 @@
         <v>27</v>
       </c>
       <c r="E300" s="10">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F300" s="8" t="s">
         <v>34</v>
@@ -8571,7 +8571,7 @@
         <v>27</v>
       </c>
       <c r="E301" s="10">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F301" s="8" t="s">
         <v>28</v>
@@ -8636,7 +8636,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -8659,7 +8659,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
         <v>31</v>
@@ -8682,7 +8682,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -8705,7 +8705,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F5" t="s">
         <v>34</v>
@@ -8728,7 +8728,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -8751,7 +8751,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F7" t="s">
         <v>31</v>
@@ -8774,7 +8774,7 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -8797,7 +8797,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
@@ -8820,7 +8820,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -8843,7 +8843,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F11" t="s">
         <v>31</v>
@@ -8866,7 +8866,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -8889,7 +8889,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F13" t="s">
         <v>34</v>
@@ -8912,7 +8912,7 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -8935,7 +8935,7 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F15" t="s">
         <v>31</v>
@@ -8958,7 +8958,7 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -8981,7 +8981,7 @@
         <v>27</v>
       </c>
       <c r="E17">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F17" t="s">
         <v>34</v>
@@ -9004,7 +9004,7 @@
         <v>27</v>
       </c>
       <c r="E18">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -9027,7 +9027,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F19" t="s">
         <v>31</v>
@@ -9050,7 +9050,7 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -9073,7 +9073,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F21" t="s">
         <v>34</v>
@@ -9096,7 +9096,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -9119,7 +9119,7 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F23" t="s">
         <v>31</v>
@@ -9142,7 +9142,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -9165,7 +9165,7 @@
         <v>27</v>
       </c>
       <c r="E25">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F25" t="s">
         <v>34</v>
@@ -9188,7 +9188,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -9211,7 +9211,7 @@
         <v>27</v>
       </c>
       <c r="E27">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F27" t="s">
         <v>31</v>
@@ -9234,7 +9234,7 @@
         <v>27</v>
       </c>
       <c r="E28">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -9257,7 +9257,7 @@
         <v>27</v>
       </c>
       <c r="E29">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F29" t="s">
         <v>34</v>
@@ -9280,7 +9280,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -9303,7 +9303,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F31" t="s">
         <v>31</v>
@@ -9326,7 +9326,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -9349,7 +9349,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F33" t="s">
         <v>31</v>
@@ -9372,7 +9372,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -9395,7 +9395,7 @@
         <v>27</v>
       </c>
       <c r="E35">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
@@ -9418,7 +9418,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -9441,7 +9441,7 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F37" t="s">
         <v>31</v>
@@ -9464,7 +9464,7 @@
         <v>27</v>
       </c>
       <c r="E38">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -9487,7 +9487,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F39" t="s">
         <v>34</v>
@@ -9510,7 +9510,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -9533,7 +9533,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F41" t="s">
         <v>31</v>
@@ -9556,7 +9556,7 @@
         <v>27</v>
       </c>
       <c r="E42">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -9579,7 +9579,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F43" t="s">
         <v>34</v>
@@ -9602,7 +9602,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -9625,7 +9625,7 @@
         <v>27</v>
       </c>
       <c r="E45">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F45" t="s">
         <v>31</v>
@@ -9648,7 +9648,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -9671,7 +9671,7 @@
         <v>27</v>
       </c>
       <c r="E47">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F47" t="s">
         <v>34</v>
@@ -9694,7 +9694,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -9717,7 +9717,7 @@
         <v>27</v>
       </c>
       <c r="E49">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F49" t="s">
         <v>31</v>
@@ -9740,7 +9740,7 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F50" t="s">
         <v>28</v>
@@ -9763,7 +9763,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F51" t="s">
         <v>34</v>
@@ -9786,7 +9786,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -9809,7 +9809,7 @@
         <v>27</v>
       </c>
       <c r="E53">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F53" t="s">
         <v>31</v>
@@ -9832,7 +9832,7 @@
         <v>27</v>
       </c>
       <c r="E54">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -9855,7 +9855,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F55" t="s">
         <v>34</v>
@@ -9878,7 +9878,7 @@
         <v>27</v>
       </c>
       <c r="E56">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -9901,7 +9901,7 @@
         <v>27</v>
       </c>
       <c r="E57">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F57" t="s">
         <v>31</v>
@@ -9924,7 +9924,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -9947,7 +9947,7 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F59" t="s">
         <v>34</v>
@@ -9970,7 +9970,7 @@
         <v>27</v>
       </c>
       <c r="E60">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -9993,7 +9993,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F61" t="s">
         <v>31</v>
@@ -10016,7 +10016,7 @@
         <v>27</v>
       </c>
       <c r="E62">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F62" t="s">
         <v>28</v>
@@ -10039,7 +10039,7 @@
         <v>27</v>
       </c>
       <c r="E63">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F63" t="s">
         <v>31</v>
@@ -10062,7 +10062,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -10085,7 +10085,7 @@
         <v>27</v>
       </c>
       <c r="E65">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F65" t="s">
         <v>34</v>
@@ -10108,7 +10108,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -10131,7 +10131,7 @@
         <v>27</v>
       </c>
       <c r="E67">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F67" t="s">
         <v>31</v>
@@ -10154,7 +10154,7 @@
         <v>27</v>
       </c>
       <c r="E68">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
@@ -10177,7 +10177,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F69" t="s">
         <v>34</v>
@@ -10200,7 +10200,7 @@
         <v>27</v>
       </c>
       <c r="E70">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -10223,7 +10223,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F71" t="s">
         <v>31</v>
@@ -10246,7 +10246,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -10269,7 +10269,7 @@
         <v>27</v>
       </c>
       <c r="E73">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F73" t="s">
         <v>34</v>
@@ -10292,7 +10292,7 @@
         <v>27</v>
       </c>
       <c r="E74">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -10315,7 +10315,7 @@
         <v>27</v>
       </c>
       <c r="E75">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F75" t="s">
         <v>31</v>
@@ -10338,7 +10338,7 @@
         <v>27</v>
       </c>
       <c r="E76">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
@@ -10361,7 +10361,7 @@
         <v>27</v>
       </c>
       <c r="E77">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F77" t="s">
         <v>34</v>
@@ -10384,7 +10384,7 @@
         <v>27</v>
       </c>
       <c r="E78">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
@@ -10407,7 +10407,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F79" t="s">
         <v>31</v>
@@ -10453,7 +10453,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F81" t="s">
         <v>34</v>
@@ -10476,7 +10476,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -10499,7 +10499,7 @@
         <v>27</v>
       </c>
       <c r="E83">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F83" t="s">
         <v>31</v>
@@ -10522,7 +10522,7 @@
         <v>27</v>
       </c>
       <c r="E84">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
@@ -10545,7 +10545,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F85" t="s">
         <v>34</v>
@@ -10568,7 +10568,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -10591,7 +10591,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F87" t="s">
         <v>31</v>
@@ -10614,7 +10614,7 @@
         <v>27</v>
       </c>
       <c r="E88">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -10637,7 +10637,7 @@
         <v>27</v>
       </c>
       <c r="E89">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F89" t="s">
         <v>34</v>
@@ -10660,7 +10660,7 @@
         <v>27</v>
       </c>
       <c r="E90">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F90" t="s">
         <v>28</v>
@@ -10683,7 +10683,7 @@
         <v>27</v>
       </c>
       <c r="E91">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F91" t="s">
         <v>31</v>
@@ -10706,7 +10706,7 @@
         <v>27</v>
       </c>
       <c r="E92">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
@@ -10729,7 +10729,7 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F93" t="s">
         <v>31</v>
@@ -10752,7 +10752,7 @@
         <v>27</v>
       </c>
       <c r="E94">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -10775,7 +10775,7 @@
         <v>27</v>
       </c>
       <c r="E95">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F95" t="s">
         <v>34</v>
@@ -10798,7 +10798,7 @@
         <v>27</v>
       </c>
       <c r="E96">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -10821,7 +10821,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F97" t="s">
         <v>31</v>
@@ -10844,7 +10844,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -10867,7 +10867,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F99" t="s">
         <v>34</v>
@@ -10890,7 +10890,7 @@
         <v>27</v>
       </c>
       <c r="E100">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
@@ -10913,7 +10913,7 @@
         <v>27</v>
       </c>
       <c r="E101">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F101" t="s">
         <v>31</v>
@@ -10936,7 +10936,7 @@
         <v>27</v>
       </c>
       <c r="E102">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
@@ -10959,7 +10959,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F103" t="s">
         <v>34</v>
@@ -10982,7 +10982,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -11005,7 +11005,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F105" t="s">
         <v>31</v>
@@ -11028,7 +11028,7 @@
         <v>27</v>
       </c>
       <c r="E106">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
@@ -11051,7 +11051,7 @@
         <v>27</v>
       </c>
       <c r="E107">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F107" t="s">
         <v>34</v>
@@ -11074,7 +11074,7 @@
         <v>27</v>
       </c>
       <c r="E108">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
@@ -11097,7 +11097,7 @@
         <v>27</v>
       </c>
       <c r="E109">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F109" t="s">
         <v>31</v>
@@ -11120,7 +11120,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -11143,7 +11143,7 @@
         <v>27</v>
       </c>
       <c r="E111">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F111" t="s">
         <v>34</v>
@@ -11166,7 +11166,7 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F112" t="s">
         <v>28</v>
@@ -11189,7 +11189,7 @@
         <v>27</v>
       </c>
       <c r="E113">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F113" t="s">
         <v>31</v>
@@ -11212,7 +11212,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -11235,7 +11235,7 @@
         <v>27</v>
       </c>
       <c r="E115">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F115" t="s">
         <v>34</v>
@@ -11258,7 +11258,7 @@
         <v>27</v>
       </c>
       <c r="E116">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F116" t="s">
         <v>28</v>
@@ -11281,7 +11281,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F117" t="s">
         <v>31</v>
@@ -11304,7 +11304,7 @@
         <v>27</v>
       </c>
       <c r="E118">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F118" t="s">
         <v>28</v>
@@ -11327,7 +11327,7 @@
         <v>27</v>
       </c>
       <c r="E119">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F119" t="s">
         <v>34</v>
@@ -11350,7 +11350,7 @@
         <v>27</v>
       </c>
       <c r="E120">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
@@ -11373,7 +11373,7 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F121" t="s">
         <v>31</v>
@@ -11396,7 +11396,7 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -11419,7 +11419,7 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F123" t="s">
         <v>31</v>
@@ -11442,7 +11442,7 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F124" t="s">
         <v>28</v>
@@ -11465,7 +11465,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F125" t="s">
         <v>34</v>
@@ -11488,7 +11488,7 @@
         <v>27</v>
       </c>
       <c r="E126">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
@@ -11511,7 +11511,7 @@
         <v>27</v>
       </c>
       <c r="E127">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F127" t="s">
         <v>31</v>
@@ -11534,7 +11534,7 @@
         <v>27</v>
       </c>
       <c r="E128">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -11557,7 +11557,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F129" t="s">
         <v>34</v>
@@ -11580,7 +11580,7 @@
         <v>27</v>
       </c>
       <c r="E130">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
@@ -11626,7 +11626,7 @@
         <v>27</v>
       </c>
       <c r="E132">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F132" t="s">
         <v>28</v>
@@ -11649,7 +11649,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F133" t="s">
         <v>34</v>
@@ -11672,7 +11672,7 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -11695,7 +11695,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F135" t="s">
         <v>31</v>
@@ -11718,7 +11718,7 @@
         <v>27</v>
       </c>
       <c r="E136">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
@@ -11741,7 +11741,7 @@
         <v>27</v>
       </c>
       <c r="E137">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F137" t="s">
         <v>34</v>
@@ -11764,7 +11764,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -11787,7 +11787,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F139" t="s">
         <v>31</v>
@@ -11810,7 +11810,7 @@
         <v>27</v>
       </c>
       <c r="E140">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
@@ -11833,7 +11833,7 @@
         <v>27</v>
       </c>
       <c r="E141">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F141" t="s">
         <v>34</v>
@@ -11856,7 +11856,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -11879,7 +11879,7 @@
         <v>27</v>
       </c>
       <c r="E143">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F143" t="s">
         <v>31</v>
@@ -11902,7 +11902,7 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F144" t="s">
         <v>28</v>
@@ -11925,7 +11925,7 @@
         <v>27</v>
       </c>
       <c r="E145">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F145" t="s">
         <v>34</v>
@@ -11971,7 +11971,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F147" t="s">
         <v>31</v>
@@ -11994,7 +11994,7 @@
         <v>27</v>
       </c>
       <c r="E148">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
@@ -12017,7 +12017,7 @@
         <v>27</v>
       </c>
       <c r="E149">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F149" t="s">
         <v>34</v>
@@ -12086,7 +12086,7 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F152" t="s">
         <v>28</v>
@@ -12109,7 +12109,7 @@
         <v>27</v>
       </c>
       <c r="E153">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F153" t="s">
         <v>31</v>
@@ -12132,7 +12132,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -12155,7 +12155,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F155" t="s">
         <v>34</v>
@@ -12178,7 +12178,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -12201,7 +12201,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F157" t="s">
         <v>31</v>
@@ -12247,7 +12247,7 @@
         <v>27</v>
       </c>
       <c r="E159">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F159" t="s">
         <v>34</v>
@@ -12270,7 +12270,7 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F160" t="s">
         <v>28</v>
@@ -12293,7 +12293,7 @@
         <v>27</v>
       </c>
       <c r="E161">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F161" t="s">
         <v>31</v>
@@ -12316,7 +12316,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -12339,7 +12339,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F163" t="s">
         <v>34</v>
@@ -12362,7 +12362,7 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
@@ -12408,7 +12408,7 @@
         <v>27</v>
       </c>
       <c r="E166">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -12431,7 +12431,7 @@
         <v>27</v>
       </c>
       <c r="E167">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F167" t="s">
         <v>34</v>
@@ -12454,7 +12454,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -12477,7 +12477,7 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F169" t="s">
         <v>31</v>
@@ -12500,7 +12500,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -12523,7 +12523,7 @@
         <v>27</v>
       </c>
       <c r="E171">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F171" t="s">
         <v>34</v>
@@ -12546,7 +12546,7 @@
         <v>27</v>
       </c>
       <c r="E172">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
@@ -12569,7 +12569,7 @@
         <v>27</v>
       </c>
       <c r="E173">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F173" t="s">
         <v>31</v>
@@ -12592,7 +12592,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -12615,7 +12615,7 @@
         <v>27</v>
       </c>
       <c r="E175">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F175" t="s">
         <v>34</v>
@@ -12638,7 +12638,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -12661,7 +12661,7 @@
         <v>27</v>
       </c>
       <c r="E177">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
@@ -12684,7 +12684,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F178" t="s">
         <v>31</v>
@@ -12707,7 +12707,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -12730,7 +12730,7 @@
         <v>27</v>
       </c>
       <c r="E180">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F180" t="s">
         <v>34</v>
@@ -12753,7 +12753,7 @@
         <v>27</v>
       </c>
       <c r="E181">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F181" t="s">
         <v>28</v>
@@ -12776,7 +12776,7 @@
         <v>27</v>
       </c>
       <c r="E182">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F182" t="s">
         <v>31</v>
@@ -12799,7 +12799,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -12822,7 +12822,7 @@
         <v>27</v>
       </c>
       <c r="E184">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F184" t="s">
         <v>34</v>
@@ -12845,7 +12845,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -12868,7 +12868,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F186" t="s">
         <v>31</v>
@@ -12914,7 +12914,7 @@
         <v>27</v>
       </c>
       <c r="E188">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F188" t="s">
         <v>34</v>
@@ -12937,7 +12937,7 @@
         <v>27</v>
       </c>
       <c r="E189">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F189" t="s">
         <v>28</v>
@@ -12960,7 +12960,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F190" t="s">
         <v>31</v>
@@ -12983,7 +12983,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -13006,7 +13006,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F192" t="s">
         <v>34</v>
@@ -13029,7 +13029,7 @@
         <v>27</v>
       </c>
       <c r="E193">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -13052,7 +13052,7 @@
         <v>27</v>
       </c>
       <c r="E194">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F194" t="s">
         <v>31</v>
@@ -13075,7 +13075,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -13098,7 +13098,7 @@
         <v>27</v>
       </c>
       <c r="E196">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F196" t="s">
         <v>34</v>
@@ -13121,7 +13121,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -13144,7 +13144,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F198" t="s">
         <v>31</v>
@@ -13167,7 +13167,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -13190,7 +13190,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F200" t="s">
         <v>34</v>
@@ -13213,7 +13213,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -13236,7 +13236,7 @@
         <v>27</v>
       </c>
       <c r="E202">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -13259,7 +13259,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F203" t="s">
         <v>31</v>
@@ -13282,7 +13282,7 @@
         <v>27</v>
       </c>
       <c r="E204">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -13305,7 +13305,7 @@
         <v>27</v>
       </c>
       <c r="E205">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F205" t="s">
         <v>34</v>
@@ -13328,7 +13328,7 @@
         <v>27</v>
       </c>
       <c r="E206">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -13351,7 +13351,7 @@
         <v>27</v>
       </c>
       <c r="E207">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F207" t="s">
         <v>31</v>
@@ -13374,7 +13374,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -13397,7 +13397,7 @@
         <v>27</v>
       </c>
       <c r="E209">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F209" t="s">
         <v>34</v>
@@ -13420,7 +13420,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -13443,7 +13443,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F211" t="s">
         <v>31</v>
@@ -13466,7 +13466,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -13489,7 +13489,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F213" t="s">
         <v>34</v>
@@ -13512,7 +13512,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -13535,7 +13535,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F215" t="s">
         <v>31</v>
@@ -13558,7 +13558,7 @@
         <v>27</v>
       </c>
       <c r="E216">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F216" t="s">
         <v>28</v>
@@ -13581,7 +13581,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F217" t="s">
         <v>34</v>
@@ -13604,7 +13604,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -13627,7 +13627,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F219" t="s">
         <v>31</v>
@@ -13650,7 +13650,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -13673,7 +13673,7 @@
         <v>27</v>
       </c>
       <c r="E221">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F221" t="s">
         <v>34</v>
@@ -13696,7 +13696,7 @@
         <v>27</v>
       </c>
       <c r="E222">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F222" t="s">
         <v>28</v>
@@ -13719,7 +13719,7 @@
         <v>27</v>
       </c>
       <c r="E223">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F223" t="s">
         <v>31</v>
@@ -13742,7 +13742,7 @@
         <v>27</v>
       </c>
       <c r="E224">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F224" t="s">
         <v>28</v>
@@ -13765,7 +13765,7 @@
         <v>27</v>
       </c>
       <c r="E225">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F225" t="s">
         <v>34</v>
@@ -13788,7 +13788,7 @@
         <v>27</v>
       </c>
       <c r="E226">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F226" t="s">
         <v>28</v>
@@ -13811,7 +13811,7 @@
         <v>27</v>
       </c>
       <c r="E227">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F227" t="s">
         <v>28</v>
@@ -13834,7 +13834,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F228" t="s">
         <v>31</v>
@@ -13857,7 +13857,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -13880,7 +13880,7 @@
         <v>27</v>
       </c>
       <c r="E230">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F230" t="s">
         <v>34</v>
@@ -13903,7 +13903,7 @@
         <v>27</v>
       </c>
       <c r="E231">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F231" t="s">
         <v>28</v>
@@ -13926,7 +13926,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F232" t="s">
         <v>31</v>
@@ -13949,7 +13949,7 @@
         <v>27</v>
       </c>
       <c r="E233">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F233" t="s">
         <v>28</v>
@@ -13972,7 +13972,7 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F234" t="s">
         <v>34</v>
@@ -13995,7 +13995,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -14018,7 +14018,7 @@
         <v>27</v>
       </c>
       <c r="E236">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F236" t="s">
         <v>31</v>
@@ -14041,7 +14041,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -14064,7 +14064,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F238" t="s">
         <v>34</v>
@@ -14110,7 +14110,7 @@
         <v>27</v>
       </c>
       <c r="E240">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F240" t="s">
         <v>31</v>
@@ -14133,7 +14133,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -14156,7 +14156,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F242" t="s">
         <v>34</v>
@@ -14179,7 +14179,7 @@
         <v>27</v>
       </c>
       <c r="E243">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -14202,7 +14202,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F244" t="s">
         <v>31</v>
@@ -14248,7 +14248,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F246" t="s">
         <v>34</v>
@@ -14271,7 +14271,7 @@
         <v>27</v>
       </c>
       <c r="E247">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F247" t="s">
         <v>28</v>
@@ -14294,7 +14294,7 @@
         <v>27</v>
       </c>
       <c r="E248">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F248" t="s">
         <v>31</v>
@@ -14317,7 +14317,7 @@
         <v>27</v>
       </c>
       <c r="E249">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F249" t="s">
         <v>28</v>
@@ -14340,7 +14340,7 @@
         <v>27</v>
       </c>
       <c r="E250">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F250" t="s">
         <v>34</v>
@@ -14363,7 +14363,7 @@
         <v>27</v>
       </c>
       <c r="E251">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F251" t="s">
         <v>28</v>
@@ -14386,7 +14386,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -14409,7 +14409,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F253" t="s">
         <v>31</v>
@@ -14432,7 +14432,7 @@
         <v>27</v>
       </c>
       <c r="E254">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F254" t="s">
         <v>28</v>
@@ -14455,7 +14455,7 @@
         <v>27</v>
       </c>
       <c r="E255">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F255" t="s">
         <v>34</v>
@@ -14478,7 +14478,7 @@
         <v>27</v>
       </c>
       <c r="E256">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F256" t="s">
         <v>28</v>
@@ -14501,7 +14501,7 @@
         <v>27</v>
       </c>
       <c r="E257">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F257" t="s">
         <v>31</v>
@@ -14524,7 +14524,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -14547,7 +14547,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F259" t="s">
         <v>34</v>
@@ -14570,7 +14570,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -14593,7 +14593,7 @@
         <v>27</v>
       </c>
       <c r="E261">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F261" t="s">
         <v>31</v>
@@ -14616,7 +14616,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -14639,7 +14639,7 @@
         <v>27</v>
       </c>
       <c r="E263">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F263" t="s">
         <v>34</v>
@@ -14662,7 +14662,7 @@
         <v>27</v>
       </c>
       <c r="E264">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -14685,7 +14685,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F265" t="s">
         <v>31</v>
@@ -14708,7 +14708,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -14731,7 +14731,7 @@
         <v>27</v>
       </c>
       <c r="E267">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F267" t="s">
         <v>34</v>
@@ -14754,7 +14754,7 @@
         <v>27</v>
       </c>
       <c r="E268">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F268" t="s">
         <v>28</v>
@@ -14777,7 +14777,7 @@
         <v>27</v>
       </c>
       <c r="E269">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F269" t="s">
         <v>31</v>
@@ -14800,7 +14800,7 @@
         <v>27</v>
       </c>
       <c r="E270">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F270" t="s">
         <v>28</v>
@@ -14823,7 +14823,7 @@
         <v>27</v>
       </c>
       <c r="E271">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F271" t="s">
         <v>34</v>
@@ -14846,7 +14846,7 @@
         <v>27</v>
       </c>
       <c r="E272">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F272" t="s">
         <v>28</v>
@@ -14869,7 +14869,7 @@
         <v>27</v>
       </c>
       <c r="E273">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F273" t="s">
         <v>31</v>
@@ -14915,7 +14915,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F275" t="s">
         <v>34</v>
@@ -14938,7 +14938,7 @@
         <v>27</v>
       </c>
       <c r="E276">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F276" t="s">
         <v>28</v>
@@ -14961,7 +14961,7 @@
         <v>27</v>
       </c>
       <c r="E277">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F277" t="s">
         <v>28</v>
@@ -14984,7 +14984,7 @@
         <v>27</v>
       </c>
       <c r="E278">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F278" t="s">
         <v>31</v>
@@ -15007,7 +15007,7 @@
         <v>27</v>
       </c>
       <c r="E279">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -15030,7 +15030,7 @@
         <v>27</v>
       </c>
       <c r="E280">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F280" t="s">
         <v>34</v>
@@ -15053,7 +15053,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -15076,7 +15076,7 @@
         <v>27</v>
       </c>
       <c r="E282">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F282" t="s">
         <v>31</v>
@@ -15099,7 +15099,7 @@
         <v>27</v>
       </c>
       <c r="E283">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F283" t="s">
         <v>28</v>
@@ -15122,7 +15122,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F284" t="s">
         <v>34</v>
@@ -15145,7 +15145,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -15168,7 +15168,7 @@
         <v>27</v>
       </c>
       <c r="E286">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F286" t="s">
         <v>31</v>
@@ -15191,7 +15191,7 @@
         <v>27</v>
       </c>
       <c r="E287">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F287" t="s">
         <v>28</v>
@@ -15214,7 +15214,7 @@
         <v>27</v>
       </c>
       <c r="E288">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F288" t="s">
         <v>34</v>
@@ -15237,7 +15237,7 @@
         <v>27</v>
       </c>
       <c r="E289">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F289" t="s">
         <v>28</v>
@@ -15260,7 +15260,7 @@
         <v>27</v>
       </c>
       <c r="E290">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F290" t="s">
         <v>31</v>
@@ -15283,7 +15283,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -15306,7 +15306,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F292" t="s">
         <v>34</v>
@@ -15329,7 +15329,7 @@
         <v>27</v>
       </c>
       <c r="E293">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -15352,7 +15352,7 @@
         <v>27</v>
       </c>
       <c r="E294">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F294" t="s">
         <v>31</v>
@@ -15375,7 +15375,7 @@
         <v>27</v>
       </c>
       <c r="E295">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F295" t="s">
         <v>28</v>
@@ -15398,7 +15398,7 @@
         <v>27</v>
       </c>
       <c r="E296">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F296" t="s">
         <v>34</v>
@@ -15421,7 +15421,7 @@
         <v>27</v>
       </c>
       <c r="E297">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F297" t="s">
         <v>28</v>
@@ -15444,7 +15444,7 @@
         <v>27</v>
       </c>
       <c r="E298">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F298" t="s">
         <v>31</v>
@@ -15490,7 +15490,7 @@
         <v>27</v>
       </c>
       <c r="E300">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F300" t="s">
         <v>34</v>
@@ -15513,7 +15513,7 @@
         <v>27</v>
       </c>
       <c r="E301">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F301" t="s">
         <v>28</v>

--- a/all-test-reports/vulnerability/vulnerability_test_report.xlsx
+++ b/all-test-reports/vulnerability/vulnerability_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 11:28:00 am</t>
+    <t>28/7/2026, 11:31:47 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1694,7 +1694,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="10">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>28</v>
@@ -1717,7 +1717,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="10">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>31</v>
@@ -1740,7 +1740,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="10">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>28</v>
@@ -1763,7 +1763,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="10">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>34</v>
@@ -1786,7 +1786,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="10">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>28</v>
@@ -1809,7 +1809,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="10">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>31</v>
@@ -1855,7 +1855,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>34</v>
@@ -1878,7 +1878,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="10">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>28</v>
@@ -1901,7 +1901,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="10">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>31</v>
@@ -1924,7 +1924,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="10">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>28</v>
@@ -1947,7 +1947,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="10">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>34</v>
@@ -1970,7 +1970,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="10">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>28</v>
@@ -1993,7 +1993,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="10">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>31</v>
@@ -2016,7 +2016,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="10">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>28</v>
@@ -2039,7 +2039,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="10">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>34</v>
@@ -2062,7 +2062,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>28</v>
@@ -2085,7 +2085,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="10">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>31</v>
@@ -2108,7 +2108,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="10">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>28</v>
@@ -2131,7 +2131,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="10">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>34</v>
@@ -2154,7 +2154,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="10">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>28</v>
@@ -2200,7 +2200,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="10">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>28</v>
@@ -2223,7 +2223,7 @@
         <v>27</v>
       </c>
       <c r="E25" s="10">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>34</v>
@@ -2246,7 +2246,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="10">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>28</v>
@@ -2269,7 +2269,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="10">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>31</v>
@@ -2292,7 +2292,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="10">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>28</v>
@@ -2315,7 +2315,7 @@
         <v>27</v>
       </c>
       <c r="E29" s="10">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>34</v>
@@ -2338,7 +2338,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="10">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>28</v>
@@ -2361,7 +2361,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="10">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>31</v>
@@ -2384,7 +2384,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="10">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>28</v>
@@ -2407,7 +2407,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="10">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>31</v>
@@ -2430,7 +2430,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="10">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>28</v>
@@ -2453,7 +2453,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="10">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>34</v>
@@ -2476,7 +2476,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="10">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>28</v>
@@ -2522,7 +2522,7 @@
         <v>27</v>
       </c>
       <c r="E38" s="10">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>28</v>
@@ -2545,7 +2545,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="10">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>34</v>
@@ -2568,7 +2568,7 @@
         <v>27</v>
       </c>
       <c r="E40" s="10">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>28</v>
@@ -2591,7 +2591,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="10">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>31</v>
@@ -2614,7 +2614,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="10">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>28</v>
@@ -2637,7 +2637,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="10">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>34</v>
@@ -2660,7 +2660,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="10">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>28</v>
@@ -2683,7 +2683,7 @@
         <v>27</v>
       </c>
       <c r="E45" s="10">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>31</v>
@@ -2706,7 +2706,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="10">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>28</v>
@@ -2729,7 +2729,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="10">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>34</v>
@@ -2752,7 +2752,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="10">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>28</v>
@@ -2775,7 +2775,7 @@
         <v>27</v>
       </c>
       <c r="E49" s="10">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>31</v>
@@ -2798,7 +2798,7 @@
         <v>27</v>
       </c>
       <c r="E50" s="10">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>28</v>
@@ -2821,7 +2821,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="10">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>34</v>
@@ -2844,7 +2844,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="10">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>28</v>
@@ -2867,7 +2867,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="10">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>31</v>
@@ -2890,7 +2890,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="10">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>28</v>
@@ -2913,7 +2913,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="10">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>34</v>
@@ -2936,7 +2936,7 @@
         <v>27</v>
       </c>
       <c r="E56" s="10">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>28</v>
@@ -2959,7 +2959,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="10">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>31</v>
@@ -2982,7 +2982,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="10">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>28</v>
@@ -3005,7 +3005,7 @@
         <v>27</v>
       </c>
       <c r="E59" s="10">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>34</v>
@@ -3028,7 +3028,7 @@
         <v>27</v>
       </c>
       <c r="E60" s="10">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>28</v>
@@ -3051,7 +3051,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="10">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>31</v>
@@ -3074,7 +3074,7 @@
         <v>27</v>
       </c>
       <c r="E62" s="10">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>28</v>
@@ -3097,7 +3097,7 @@
         <v>27</v>
       </c>
       <c r="E63" s="10">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>31</v>
@@ -3120,7 +3120,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="10">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>28</v>
@@ -3143,7 +3143,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="10">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>34</v>
@@ -3166,7 +3166,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="10">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>28</v>
@@ -3189,7 +3189,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="10">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>31</v>
@@ -3212,7 +3212,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>28</v>
@@ -3235,7 +3235,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="10">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>34</v>
@@ -3258,7 +3258,7 @@
         <v>27</v>
       </c>
       <c r="E70" s="10">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>28</v>
@@ -3281,7 +3281,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="10">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>31</v>
@@ -3304,7 +3304,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="10">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>28</v>
@@ -3327,7 +3327,7 @@
         <v>27</v>
       </c>
       <c r="E73" s="10">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>34</v>
@@ -3350,7 +3350,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="10">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>28</v>
@@ -3373,7 +3373,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="10">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>31</v>
@@ -3396,7 +3396,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="10">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>28</v>
@@ -3419,7 +3419,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="10">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>34</v>
@@ -3442,7 +3442,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="10">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>28</v>
@@ -3465,7 +3465,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="10">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>31</v>
@@ -3488,7 +3488,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="10">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>28</v>
@@ -3511,7 +3511,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="10">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>34</v>
@@ -3534,7 +3534,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="10">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>28</v>
@@ -3557,7 +3557,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="10">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>31</v>
@@ -3580,7 +3580,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="10">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>28</v>
@@ -3603,7 +3603,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="10">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>34</v>
@@ -3626,7 +3626,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="10">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>28</v>
@@ -3649,7 +3649,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="10">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>31</v>
@@ -3672,7 +3672,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="10">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>28</v>
@@ -3695,7 +3695,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="10">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>34</v>
@@ -3718,7 +3718,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>28</v>
@@ -3741,7 +3741,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="10">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>31</v>
@@ -3764,7 +3764,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="10">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>28</v>
@@ -3787,7 +3787,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="10">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>31</v>
@@ -3810,7 +3810,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="10">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>28</v>
@@ -3833,7 +3833,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="10">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>34</v>
@@ -3856,7 +3856,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="10">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F96" s="8" t="s">
         <v>28</v>
@@ -3879,7 +3879,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="10">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>31</v>
@@ -3902,7 +3902,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>28</v>
@@ -3925,7 +3925,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="10">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>34</v>
@@ -3948,7 +3948,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="10">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>28</v>
@@ -3971,7 +3971,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="10">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>31</v>
@@ -3994,7 +3994,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="10">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>28</v>
@@ -4017,7 +4017,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="10">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>34</v>
@@ -4040,7 +4040,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="10">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>28</v>
@@ -4063,7 +4063,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>31</v>
@@ -4086,7 +4086,7 @@
         <v>27</v>
       </c>
       <c r="E106" s="10">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>28</v>
@@ -4132,7 +4132,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="10">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>28</v>
@@ -4155,7 +4155,7 @@
         <v>27</v>
       </c>
       <c r="E109" s="10">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>31</v>
@@ -4178,7 +4178,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="10">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>28</v>
@@ -4201,7 +4201,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="10">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>34</v>
@@ -4224,7 +4224,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="10">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>28</v>
@@ -4247,7 +4247,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="10">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F113" s="8" t="s">
         <v>31</v>
@@ -4270,7 +4270,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>28</v>
@@ -4293,7 +4293,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="10">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>34</v>
@@ -4316,7 +4316,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="10">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>28</v>
@@ -4339,7 +4339,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="10">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F117" s="8" t="s">
         <v>31</v>
@@ -4362,7 +4362,7 @@
         <v>27</v>
       </c>
       <c r="E118" s="10">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F118" s="8" t="s">
         <v>28</v>
@@ -4385,7 +4385,7 @@
         <v>27</v>
       </c>
       <c r="E119" s="10">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F119" s="8" t="s">
         <v>34</v>
@@ -4408,7 +4408,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="10">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F120" s="8" t="s">
         <v>28</v>
@@ -4431,7 +4431,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="10">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F121" s="8" t="s">
         <v>31</v>
@@ -4454,7 +4454,7 @@
         <v>27</v>
       </c>
       <c r="E122" s="10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F122" s="8" t="s">
         <v>28</v>
@@ -4500,7 +4500,7 @@
         <v>27</v>
       </c>
       <c r="E124" s="10">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F124" s="8" t="s">
         <v>28</v>
@@ -4523,7 +4523,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="10">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>34</v>
@@ -4546,7 +4546,7 @@
         <v>27</v>
       </c>
       <c r="E126" s="10">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F126" s="8" t="s">
         <v>28</v>
@@ -4569,7 +4569,7 @@
         <v>27</v>
       </c>
       <c r="E127" s="10">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F127" s="8" t="s">
         <v>31</v>
@@ -4592,7 +4592,7 @@
         <v>27</v>
       </c>
       <c r="E128" s="10">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F128" s="8" t="s">
         <v>28</v>
@@ -4615,7 +4615,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="10">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F129" s="8" t="s">
         <v>34</v>
@@ -4638,7 +4638,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="10">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F130" s="8" t="s">
         <v>28</v>
@@ -4661,7 +4661,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="10">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F131" s="8" t="s">
         <v>31</v>
@@ -4684,7 +4684,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="10">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F132" s="8" t="s">
         <v>28</v>
@@ -4707,7 +4707,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="10">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F133" s="8" t="s">
         <v>34</v>
@@ -4730,7 +4730,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="10">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F134" s="8" t="s">
         <v>28</v>
@@ -4776,7 +4776,7 @@
         <v>27</v>
       </c>
       <c r="E136" s="10">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F136" s="8" t="s">
         <v>28</v>
@@ -4799,7 +4799,7 @@
         <v>27</v>
       </c>
       <c r="E137" s="10">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F137" s="8" t="s">
         <v>34</v>
@@ -4822,7 +4822,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="10">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F138" s="8" t="s">
         <v>28</v>
@@ -4845,7 +4845,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="10">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F139" s="8" t="s">
         <v>31</v>
@@ -4868,7 +4868,7 @@
         <v>27</v>
       </c>
       <c r="E140" s="10">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F140" s="8" t="s">
         <v>28</v>
@@ -4891,7 +4891,7 @@
         <v>27</v>
       </c>
       <c r="E141" s="10">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F141" s="8" t="s">
         <v>34</v>
@@ -4914,7 +4914,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="10">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F142" s="8" t="s">
         <v>28</v>
@@ -4937,7 +4937,7 @@
         <v>27</v>
       </c>
       <c r="E143" s="10">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F143" s="8" t="s">
         <v>31</v>
@@ -4960,7 +4960,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="10">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F144" s="8" t="s">
         <v>28</v>
@@ -4983,7 +4983,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="10">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F145" s="8" t="s">
         <v>34</v>
@@ -5006,7 +5006,7 @@
         <v>27</v>
       </c>
       <c r="E146" s="10">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>28</v>
@@ -5029,7 +5029,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="10">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F147" s="8" t="s">
         <v>31</v>
@@ -5052,7 +5052,7 @@
         <v>27</v>
       </c>
       <c r="E148" s="10">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F148" s="8" t="s">
         <v>28</v>
@@ -5098,7 +5098,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>28</v>
@@ -5121,7 +5121,7 @@
         <v>27</v>
       </c>
       <c r="E151" s="10">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>31</v>
@@ -5144,7 +5144,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="10">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>28</v>
@@ -5167,7 +5167,7 @@
         <v>27</v>
       </c>
       <c r="E153" s="10">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F153" s="8" t="s">
         <v>31</v>
@@ -5190,7 +5190,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="10">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>28</v>
@@ -5213,7 +5213,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="10">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F155" s="8" t="s">
         <v>34</v>
@@ -5236,7 +5236,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="10">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F156" s="8" t="s">
         <v>28</v>
@@ -5259,7 +5259,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="10">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F157" s="8" t="s">
         <v>31</v>
@@ -5282,7 +5282,7 @@
         <v>27</v>
       </c>
       <c r="E158" s="10">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F158" s="8" t="s">
         <v>28</v>
@@ -5305,7 +5305,7 @@
         <v>27</v>
       </c>
       <c r="E159" s="10">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F159" s="8" t="s">
         <v>34</v>
@@ -5328,7 +5328,7 @@
         <v>27</v>
       </c>
       <c r="E160" s="10">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F160" s="8" t="s">
         <v>28</v>
@@ -5351,7 +5351,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="10">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F161" s="8" t="s">
         <v>31</v>
@@ -5374,7 +5374,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="10">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F162" s="8" t="s">
         <v>28</v>
@@ -5397,7 +5397,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="10">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F163" s="8" t="s">
         <v>34</v>
@@ -5420,7 +5420,7 @@
         <v>27</v>
       </c>
       <c r="E164" s="10">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F164" s="8" t="s">
         <v>28</v>
@@ -5443,7 +5443,7 @@
         <v>27</v>
       </c>
       <c r="E165" s="10">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F165" s="8" t="s">
         <v>31</v>
@@ -5466,7 +5466,7 @@
         <v>27</v>
       </c>
       <c r="E166" s="10">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F166" s="8" t="s">
         <v>28</v>
@@ -5489,7 +5489,7 @@
         <v>27</v>
       </c>
       <c r="E167" s="10">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F167" s="8" t="s">
         <v>34</v>
@@ -5512,7 +5512,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="10">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F168" s="8" t="s">
         <v>28</v>
@@ -5535,7 +5535,7 @@
         <v>27</v>
       </c>
       <c r="E169" s="10">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F169" s="8" t="s">
         <v>31</v>
@@ -5558,7 +5558,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="10">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F170" s="8" t="s">
         <v>28</v>
@@ -5581,7 +5581,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F171" s="8" t="s">
         <v>34</v>
@@ -5604,7 +5604,7 @@
         <v>27</v>
       </c>
       <c r="E172" s="10">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F172" s="8" t="s">
         <v>28</v>
@@ -5627,7 +5627,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="10">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F173" s="8" t="s">
         <v>31</v>
@@ -5650,7 +5650,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="10">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="F174" s="8" t="s">
         <v>28</v>
@@ -5673,7 +5673,7 @@
         <v>27</v>
       </c>
       <c r="E175" s="10">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F175" s="8" t="s">
         <v>34</v>
@@ -5696,7 +5696,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="10">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F176" s="8" t="s">
         <v>28</v>
@@ -5719,7 +5719,7 @@
         <v>27</v>
       </c>
       <c r="E177" s="10">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F177" s="8" t="s">
         <v>28</v>
@@ -5742,7 +5742,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="10">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F178" s="8" t="s">
         <v>31</v>
@@ -5765,7 +5765,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="10">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F179" s="8" t="s">
         <v>28</v>
@@ -5788,7 +5788,7 @@
         <v>27</v>
       </c>
       <c r="E180" s="10">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F180" s="8" t="s">
         <v>34</v>
@@ -5811,7 +5811,7 @@
         <v>27</v>
       </c>
       <c r="E181" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F181" s="8" t="s">
         <v>28</v>
@@ -5834,7 +5834,7 @@
         <v>27</v>
       </c>
       <c r="E182" s="10">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F182" s="8" t="s">
         <v>31</v>
@@ -5857,7 +5857,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="10">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F183" s="8" t="s">
         <v>28</v>
@@ -5880,7 +5880,7 @@
         <v>27</v>
       </c>
       <c r="E184" s="10">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F184" s="8" t="s">
         <v>34</v>
@@ -5903,7 +5903,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="10">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F185" s="8" t="s">
         <v>28</v>
@@ -5926,7 +5926,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="10">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F186" s="8" t="s">
         <v>31</v>
@@ -5949,7 +5949,7 @@
         <v>27</v>
       </c>
       <c r="E187" s="10">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F187" s="8" t="s">
         <v>28</v>
@@ -5972,7 +5972,7 @@
         <v>27</v>
       </c>
       <c r="E188" s="10">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F188" s="8" t="s">
         <v>34</v>
@@ -5995,7 +5995,7 @@
         <v>27</v>
       </c>
       <c r="E189" s="10">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F189" s="8" t="s">
         <v>28</v>
@@ -6018,7 +6018,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="10">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F190" s="8" t="s">
         <v>31</v>
@@ -6041,7 +6041,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F191" s="8" t="s">
         <v>28</v>
@@ -6064,7 +6064,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="10">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F192" s="8" t="s">
         <v>34</v>
@@ -6087,7 +6087,7 @@
         <v>27</v>
       </c>
       <c r="E193" s="10">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F193" s="8" t="s">
         <v>28</v>
@@ -6110,7 +6110,7 @@
         <v>27</v>
       </c>
       <c r="E194" s="10">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F194" s="8" t="s">
         <v>31</v>
@@ -6133,7 +6133,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="10">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F195" s="8" t="s">
         <v>28</v>
@@ -6156,7 +6156,7 @@
         <v>27</v>
       </c>
       <c r="E196" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F196" s="8" t="s">
         <v>34</v>
@@ -6179,7 +6179,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="10">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F197" s="8" t="s">
         <v>28</v>
@@ -6202,7 +6202,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="10">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F198" s="8" t="s">
         <v>31</v>
@@ -6225,7 +6225,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="10">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F199" s="8" t="s">
         <v>28</v>
@@ -6248,7 +6248,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="10">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F200" s="8" t="s">
         <v>34</v>
@@ -6271,7 +6271,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="10">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F201" s="8" t="s">
         <v>28</v>
@@ -6294,7 +6294,7 @@
         <v>27</v>
       </c>
       <c r="E202" s="10">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F202" s="8" t="s">
         <v>28</v>
@@ -6317,7 +6317,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="10">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F203" s="8" t="s">
         <v>31</v>
@@ -6340,7 +6340,7 @@
         <v>27</v>
       </c>
       <c r="E204" s="10">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F204" s="8" t="s">
         <v>28</v>
@@ -6363,7 +6363,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F205" s="8" t="s">
         <v>34</v>
@@ -6386,7 +6386,7 @@
         <v>27</v>
       </c>
       <c r="E206" s="10">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F206" s="8" t="s">
         <v>28</v>
@@ -6409,7 +6409,7 @@
         <v>27</v>
       </c>
       <c r="E207" s="10">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F207" s="8" t="s">
         <v>31</v>
@@ -6432,7 +6432,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="10">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F208" s="8" t="s">
         <v>28</v>
@@ -6455,7 +6455,7 @@
         <v>27</v>
       </c>
       <c r="E209" s="10">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F209" s="8" t="s">
         <v>34</v>
@@ -6478,7 +6478,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="10">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F210" s="8" t="s">
         <v>28</v>
@@ -6501,7 +6501,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="10">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F211" s="8" t="s">
         <v>31</v>
@@ -6524,7 +6524,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="10">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F212" s="8" t="s">
         <v>28</v>
@@ -6547,7 +6547,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="10">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F213" s="8" t="s">
         <v>34</v>
@@ -6570,7 +6570,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="10">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F214" s="8" t="s">
         <v>28</v>
@@ -6593,7 +6593,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="10">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F215" s="8" t="s">
         <v>31</v>
@@ -6616,7 +6616,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="10">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F216" s="8" t="s">
         <v>28</v>
@@ -6639,7 +6639,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="10">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F217" s="8" t="s">
         <v>34</v>
@@ -6662,7 +6662,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="10">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F218" s="8" t="s">
         <v>28</v>
@@ -6685,7 +6685,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="10">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F219" s="8" t="s">
         <v>31</v>
@@ -6708,7 +6708,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="10">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F220" s="8" t="s">
         <v>28</v>
@@ -6731,7 +6731,7 @@
         <v>27</v>
       </c>
       <c r="E221" s="10">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F221" s="8" t="s">
         <v>34</v>
@@ -6777,7 +6777,7 @@
         <v>27</v>
       </c>
       <c r="E223" s="10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F223" s="8" t="s">
         <v>31</v>
@@ -6800,7 +6800,7 @@
         <v>27</v>
       </c>
       <c r="E224" s="10">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F224" s="8" t="s">
         <v>28</v>
@@ -6823,7 +6823,7 @@
         <v>27</v>
       </c>
       <c r="E225" s="10">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F225" s="8" t="s">
         <v>34</v>
@@ -6846,7 +6846,7 @@
         <v>27</v>
       </c>
       <c r="E226" s="10">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F226" s="8" t="s">
         <v>28</v>
@@ -6869,7 +6869,7 @@
         <v>27</v>
       </c>
       <c r="E227" s="10">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F227" s="8" t="s">
         <v>28</v>
@@ -6892,7 +6892,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="10">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F228" s="8" t="s">
         <v>31</v>
@@ -6915,7 +6915,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="10">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F229" s="8" t="s">
         <v>28</v>
@@ -6938,7 +6938,7 @@
         <v>27</v>
       </c>
       <c r="E230" s="10">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="F230" s="8" t="s">
         <v>34</v>
@@ -6961,7 +6961,7 @@
         <v>27</v>
       </c>
       <c r="E231" s="10">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F231" s="8" t="s">
         <v>28</v>
@@ -6984,7 +6984,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="10">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F232" s="8" t="s">
         <v>31</v>
@@ -7007,7 +7007,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="10">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F233" s="8" t="s">
         <v>28</v>
@@ -7053,7 +7053,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="10">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F235" s="8" t="s">
         <v>28</v>
@@ -7076,7 +7076,7 @@
         <v>27</v>
       </c>
       <c r="E236" s="10">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F236" s="8" t="s">
         <v>31</v>
@@ -7099,7 +7099,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="10">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F237" s="8" t="s">
         <v>28</v>
@@ -7122,7 +7122,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="10">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F238" s="8" t="s">
         <v>34</v>
@@ -7145,7 +7145,7 @@
         <v>27</v>
       </c>
       <c r="E239" s="10">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F239" s="8" t="s">
         <v>28</v>
@@ -7168,7 +7168,7 @@
         <v>27</v>
       </c>
       <c r="E240" s="10">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F240" s="8" t="s">
         <v>31</v>
@@ -7191,7 +7191,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="10">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F241" s="8" t="s">
         <v>28</v>
@@ -7214,7 +7214,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="10">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F242" s="8" t="s">
         <v>34</v>
@@ -7237,7 +7237,7 @@
         <v>27</v>
       </c>
       <c r="E243" s="10">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F243" s="8" t="s">
         <v>28</v>
@@ -7260,7 +7260,7 @@
         <v>27</v>
       </c>
       <c r="E244" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F244" s="8" t="s">
         <v>31</v>
@@ -7283,7 +7283,7 @@
         <v>27</v>
       </c>
       <c r="E245" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F245" s="8" t="s">
         <v>28</v>
@@ -7306,7 +7306,7 @@
         <v>27</v>
       </c>
       <c r="E246" s="10">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F246" s="8" t="s">
         <v>34</v>
@@ -7329,7 +7329,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="10">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F247" s="8" t="s">
         <v>28</v>
@@ -7352,7 +7352,7 @@
         <v>27</v>
       </c>
       <c r="E248" s="10">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F248" s="8" t="s">
         <v>31</v>
@@ -7375,7 +7375,7 @@
         <v>27</v>
       </c>
       <c r="E249" s="10">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F249" s="8" t="s">
         <v>28</v>
@@ -7398,7 +7398,7 @@
         <v>27</v>
       </c>
       <c r="E250" s="10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F250" s="8" t="s">
         <v>34</v>
@@ -7421,7 +7421,7 @@
         <v>27</v>
       </c>
       <c r="E251" s="10">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F251" s="8" t="s">
         <v>28</v>
@@ -7444,7 +7444,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F252" s="8" t="s">
         <v>28</v>
@@ -7467,7 +7467,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="10">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F253" s="8" t="s">
         <v>31</v>
@@ -7490,7 +7490,7 @@
         <v>27</v>
       </c>
       <c r="E254" s="10">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F254" s="8" t="s">
         <v>28</v>
@@ -7513,7 +7513,7 @@
         <v>27</v>
       </c>
       <c r="E255" s="10">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F255" s="8" t="s">
         <v>34</v>
@@ -7536,7 +7536,7 @@
         <v>27</v>
       </c>
       <c r="E256" s="10">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F256" s="8" t="s">
         <v>28</v>
@@ -7559,7 +7559,7 @@
         <v>27</v>
       </c>
       <c r="E257" s="10">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F257" s="8" t="s">
         <v>31</v>
@@ -7582,7 +7582,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="10">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F258" s="8" t="s">
         <v>28</v>
@@ -7605,7 +7605,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="10">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F259" s="8" t="s">
         <v>34</v>
@@ -7628,7 +7628,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="10">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F260" s="8" t="s">
         <v>28</v>
@@ -7651,7 +7651,7 @@
         <v>27</v>
       </c>
       <c r="E261" s="10">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F261" s="8" t="s">
         <v>31</v>
@@ -7674,7 +7674,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="10">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F262" s="8" t="s">
         <v>28</v>
@@ -7720,7 +7720,7 @@
         <v>27</v>
       </c>
       <c r="E264" s="10">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F264" s="8" t="s">
         <v>28</v>
@@ -7743,7 +7743,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F265" s="8" t="s">
         <v>31</v>
@@ -7766,7 +7766,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="10">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F266" s="8" t="s">
         <v>28</v>
@@ -7812,7 +7812,7 @@
         <v>27</v>
       </c>
       <c r="E268" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F268" s="8" t="s">
         <v>28</v>
@@ -7835,7 +7835,7 @@
         <v>27</v>
       </c>
       <c r="E269" s="10">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F269" s="8" t="s">
         <v>31</v>
@@ -7858,7 +7858,7 @@
         <v>27</v>
       </c>
       <c r="E270" s="10">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F270" s="8" t="s">
         <v>28</v>
@@ -7881,7 +7881,7 @@
         <v>27</v>
       </c>
       <c r="E271" s="10">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F271" s="8" t="s">
         <v>34</v>
@@ -7904,7 +7904,7 @@
         <v>27</v>
       </c>
       <c r="E272" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F272" s="8" t="s">
         <v>28</v>
@@ -7927,7 +7927,7 @@
         <v>27</v>
       </c>
       <c r="E273" s="10">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F273" s="8" t="s">
         <v>31</v>
@@ -7950,7 +7950,7 @@
         <v>27</v>
       </c>
       <c r="E274" s="10">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F274" s="8" t="s">
         <v>28</v>
@@ -7973,7 +7973,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="10">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F275" s="8" t="s">
         <v>34</v>
@@ -7996,7 +7996,7 @@
         <v>27</v>
       </c>
       <c r="E276" s="10">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F276" s="8" t="s">
         <v>28</v>
@@ -8019,7 +8019,7 @@
         <v>27</v>
       </c>
       <c r="E277" s="10">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F277" s="8" t="s">
         <v>28</v>
@@ -8042,7 +8042,7 @@
         <v>27</v>
       </c>
       <c r="E278" s="10">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F278" s="8" t="s">
         <v>31</v>
@@ -8065,7 +8065,7 @@
         <v>27</v>
       </c>
       <c r="E279" s="10">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F279" s="8" t="s">
         <v>28</v>
@@ -8088,7 +8088,7 @@
         <v>27</v>
       </c>
       <c r="E280" s="10">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F280" s="8" t="s">
         <v>34</v>
@@ -8111,7 +8111,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="10">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F281" s="8" t="s">
         <v>28</v>
@@ -8134,7 +8134,7 @@
         <v>27</v>
       </c>
       <c r="E282" s="10">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F282" s="8" t="s">
         <v>31</v>
@@ -8180,7 +8180,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="10">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F284" s="8" t="s">
         <v>34</v>
@@ -8203,7 +8203,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="10">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F285" s="8" t="s">
         <v>28</v>
@@ -8226,7 +8226,7 @@
         <v>27</v>
       </c>
       <c r="E286" s="10">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F286" s="8" t="s">
         <v>31</v>
@@ -8249,7 +8249,7 @@
         <v>27</v>
       </c>
       <c r="E287" s="10">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F287" s="8" t="s">
         <v>28</v>
@@ -8272,7 +8272,7 @@
         <v>27</v>
       </c>
       <c r="E288" s="10">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F288" s="8" t="s">
         <v>34</v>
@@ -8295,7 +8295,7 @@
         <v>27</v>
       </c>
       <c r="E289" s="10">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F289" s="8" t="s">
         <v>28</v>
@@ -8318,7 +8318,7 @@
         <v>27</v>
       </c>
       <c r="E290" s="10">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F290" s="8" t="s">
         <v>31</v>
@@ -8341,7 +8341,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="10">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F291" s="8" t="s">
         <v>28</v>
@@ -8364,7 +8364,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="10">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F292" s="8" t="s">
         <v>34</v>
@@ -8387,7 +8387,7 @@
         <v>27</v>
       </c>
       <c r="E293" s="10">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F293" s="8" t="s">
         <v>28</v>
@@ -8410,7 +8410,7 @@
         <v>27</v>
       </c>
       <c r="E294" s="10">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F294" s="8" t="s">
         <v>31</v>
@@ -8433,7 +8433,7 @@
         <v>27</v>
       </c>
       <c r="E295" s="10">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F295" s="8" t="s">
         <v>28</v>
@@ -8456,7 +8456,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="10">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F296" s="8" t="s">
         <v>34</v>
@@ -8479,7 +8479,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="10">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F297" s="8" t="s">
         <v>28</v>
@@ -8502,7 +8502,7 @@
         <v>27</v>
       </c>
       <c r="E298" s="10">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F298" s="8" t="s">
         <v>31</v>
@@ -8525,7 +8525,7 @@
         <v>27</v>
       </c>
       <c r="E299" s="10">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F299" s="8" t="s">
         <v>28</v>
@@ -8548,7 +8548,7 @@
         <v>27</v>
       </c>
       <c r="E300" s="10">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F300" s="8" t="s">
         <v>34</v>
@@ -8571,7 +8571,7 @@
         <v>27</v>
       </c>
       <c r="E301" s="10">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F301" s="8" t="s">
         <v>28</v>
@@ -8636,7 +8636,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -8659,7 +8659,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
         <v>31</v>
@@ -8682,7 +8682,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -8705,7 +8705,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
         <v>34</v>
@@ -8728,7 +8728,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -8751,7 +8751,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
         <v>31</v>
@@ -8797,7 +8797,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
@@ -8820,7 +8820,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -8843,7 +8843,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F11" t="s">
         <v>31</v>
@@ -8866,7 +8866,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -8889,7 +8889,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
         <v>34</v>
@@ -8912,7 +8912,7 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -8935,7 +8935,7 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
         <v>31</v>
@@ -8958,7 +8958,7 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -8981,7 +8981,7 @@
         <v>27</v>
       </c>
       <c r="E17">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
         <v>34</v>
@@ -9004,7 +9004,7 @@
         <v>27</v>
       </c>
       <c r="E18">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -9027,7 +9027,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F19" t="s">
         <v>31</v>
@@ -9050,7 +9050,7 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -9073,7 +9073,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F21" t="s">
         <v>34</v>
@@ -9096,7 +9096,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -9142,7 +9142,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -9165,7 +9165,7 @@
         <v>27</v>
       </c>
       <c r="E25">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F25" t="s">
         <v>34</v>
@@ -9188,7 +9188,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -9211,7 +9211,7 @@
         <v>27</v>
       </c>
       <c r="E27">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F27" t="s">
         <v>31</v>
@@ -9234,7 +9234,7 @@
         <v>27</v>
       </c>
       <c r="E28">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -9257,7 +9257,7 @@
         <v>27</v>
       </c>
       <c r="E29">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F29" t="s">
         <v>34</v>
@@ -9280,7 +9280,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -9303,7 +9303,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F31" t="s">
         <v>31</v>
@@ -9326,7 +9326,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -9349,7 +9349,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F33" t="s">
         <v>31</v>
@@ -9372,7 +9372,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -9395,7 +9395,7 @@
         <v>27</v>
       </c>
       <c r="E35">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
@@ -9418,7 +9418,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -9464,7 +9464,7 @@
         <v>27</v>
       </c>
       <c r="E38">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -9487,7 +9487,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F39" t="s">
         <v>34</v>
@@ -9510,7 +9510,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -9533,7 +9533,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F41" t="s">
         <v>31</v>
@@ -9556,7 +9556,7 @@
         <v>27</v>
       </c>
       <c r="E42">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -9579,7 +9579,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F43" t="s">
         <v>34</v>
@@ -9602,7 +9602,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -9625,7 +9625,7 @@
         <v>27</v>
       </c>
       <c r="E45">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F45" t="s">
         <v>31</v>
@@ -9648,7 +9648,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -9671,7 +9671,7 @@
         <v>27</v>
       </c>
       <c r="E47">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F47" t="s">
         <v>34</v>
@@ -9694,7 +9694,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -9717,7 +9717,7 @@
         <v>27</v>
       </c>
       <c r="E49">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F49" t="s">
         <v>31</v>
@@ -9740,7 +9740,7 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F50" t="s">
         <v>28</v>
@@ -9763,7 +9763,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F51" t="s">
         <v>34</v>
@@ -9786,7 +9786,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -9809,7 +9809,7 @@
         <v>27</v>
       </c>
       <c r="E53">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F53" t="s">
         <v>31</v>
@@ -9832,7 +9832,7 @@
         <v>27</v>
       </c>
       <c r="E54">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -9855,7 +9855,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F55" t="s">
         <v>34</v>
@@ -9878,7 +9878,7 @@
         <v>27</v>
       </c>
       <c r="E56">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -9901,7 +9901,7 @@
         <v>27</v>
       </c>
       <c r="E57">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F57" t="s">
         <v>31</v>
@@ -9924,7 +9924,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -9947,7 +9947,7 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F59" t="s">
         <v>34</v>
@@ -9970,7 +9970,7 @@
         <v>27</v>
       </c>
       <c r="E60">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -9993,7 +9993,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F61" t="s">
         <v>31</v>
@@ -10016,7 +10016,7 @@
         <v>27</v>
       </c>
       <c r="E62">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F62" t="s">
         <v>28</v>
@@ -10039,7 +10039,7 @@
         <v>27</v>
       </c>
       <c r="E63">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F63" t="s">
         <v>31</v>
@@ -10062,7 +10062,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -10085,7 +10085,7 @@
         <v>27</v>
       </c>
       <c r="E65">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F65" t="s">
         <v>34</v>
@@ -10108,7 +10108,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -10131,7 +10131,7 @@
         <v>27</v>
       </c>
       <c r="E67">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F67" t="s">
         <v>31</v>
@@ -10154,7 +10154,7 @@
         <v>27</v>
       </c>
       <c r="E68">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
@@ -10177,7 +10177,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F69" t="s">
         <v>34</v>
@@ -10200,7 +10200,7 @@
         <v>27</v>
       </c>
       <c r="E70">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -10223,7 +10223,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F71" t="s">
         <v>31</v>
@@ -10246,7 +10246,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -10269,7 +10269,7 @@
         <v>27</v>
       </c>
       <c r="E73">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F73" t="s">
         <v>34</v>
@@ -10292,7 +10292,7 @@
         <v>27</v>
       </c>
       <c r="E74">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -10315,7 +10315,7 @@
         <v>27</v>
       </c>
       <c r="E75">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F75" t="s">
         <v>31</v>
@@ -10338,7 +10338,7 @@
         <v>27</v>
       </c>
       <c r="E76">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
@@ -10361,7 +10361,7 @@
         <v>27</v>
       </c>
       <c r="E77">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F77" t="s">
         <v>34</v>
@@ -10384,7 +10384,7 @@
         <v>27</v>
       </c>
       <c r="E78">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
@@ -10407,7 +10407,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F79" t="s">
         <v>31</v>
@@ -10430,7 +10430,7 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
@@ -10453,7 +10453,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F81" t="s">
         <v>34</v>
@@ -10476,7 +10476,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -10499,7 +10499,7 @@
         <v>27</v>
       </c>
       <c r="E83">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F83" t="s">
         <v>31</v>
@@ -10522,7 +10522,7 @@
         <v>27</v>
       </c>
       <c r="E84">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
@@ -10545,7 +10545,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F85" t="s">
         <v>34</v>
@@ -10568,7 +10568,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -10591,7 +10591,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F87" t="s">
         <v>31</v>
@@ -10614,7 +10614,7 @@
         <v>27</v>
       </c>
       <c r="E88">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -10637,7 +10637,7 @@
         <v>27</v>
       </c>
       <c r="E89">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F89" t="s">
         <v>34</v>
@@ -10660,7 +10660,7 @@
         <v>27</v>
       </c>
       <c r="E90">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F90" t="s">
         <v>28</v>
@@ -10683,7 +10683,7 @@
         <v>27</v>
       </c>
       <c r="E91">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F91" t="s">
         <v>31</v>
@@ -10706,7 +10706,7 @@
         <v>27</v>
       </c>
       <c r="E92">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
@@ -10729,7 +10729,7 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F93" t="s">
         <v>31</v>
@@ -10752,7 +10752,7 @@
         <v>27</v>
       </c>
       <c r="E94">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -10775,7 +10775,7 @@
         <v>27</v>
       </c>
       <c r="E95">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F95" t="s">
         <v>34</v>
@@ -10798,7 +10798,7 @@
         <v>27</v>
       </c>
       <c r="E96">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -10821,7 +10821,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F97" t="s">
         <v>31</v>
@@ -10844,7 +10844,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -10867,7 +10867,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F99" t="s">
         <v>34</v>
@@ -10890,7 +10890,7 @@
         <v>27</v>
       </c>
       <c r="E100">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
@@ -10913,7 +10913,7 @@
         <v>27</v>
       </c>
       <c r="E101">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F101" t="s">
         <v>31</v>
@@ -10936,7 +10936,7 @@
         <v>27</v>
       </c>
       <c r="E102">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
@@ -10959,7 +10959,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F103" t="s">
         <v>34</v>
@@ -10982,7 +10982,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -11005,7 +11005,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F105" t="s">
         <v>31</v>
@@ -11028,7 +11028,7 @@
         <v>27</v>
       </c>
       <c r="E106">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
@@ -11074,7 +11074,7 @@
         <v>27</v>
       </c>
       <c r="E108">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
@@ -11097,7 +11097,7 @@
         <v>27</v>
       </c>
       <c r="E109">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F109" t="s">
         <v>31</v>
@@ -11120,7 +11120,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -11143,7 +11143,7 @@
         <v>27</v>
       </c>
       <c r="E111">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F111" t="s">
         <v>34</v>
@@ -11166,7 +11166,7 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F112" t="s">
         <v>28</v>
@@ -11189,7 +11189,7 @@
         <v>27</v>
       </c>
       <c r="E113">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F113" t="s">
         <v>31</v>
@@ -11212,7 +11212,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -11235,7 +11235,7 @@
         <v>27</v>
       </c>
       <c r="E115">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F115" t="s">
         <v>34</v>
@@ -11258,7 +11258,7 @@
         <v>27</v>
       </c>
       <c r="E116">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F116" t="s">
         <v>28</v>
@@ -11281,7 +11281,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F117" t="s">
         <v>31</v>
@@ -11304,7 +11304,7 @@
         <v>27</v>
       </c>
       <c r="E118">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F118" t="s">
         <v>28</v>
@@ -11327,7 +11327,7 @@
         <v>27</v>
       </c>
       <c r="E119">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F119" t="s">
         <v>34</v>
@@ -11350,7 +11350,7 @@
         <v>27</v>
       </c>
       <c r="E120">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
@@ -11373,7 +11373,7 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F121" t="s">
         <v>31</v>
@@ -11396,7 +11396,7 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -11442,7 +11442,7 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F124" t="s">
         <v>28</v>
@@ -11465,7 +11465,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F125" t="s">
         <v>34</v>
@@ -11488,7 +11488,7 @@
         <v>27</v>
       </c>
       <c r="E126">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
@@ -11511,7 +11511,7 @@
         <v>27</v>
       </c>
       <c r="E127">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F127" t="s">
         <v>31</v>
@@ -11534,7 +11534,7 @@
         <v>27</v>
       </c>
       <c r="E128">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -11557,7 +11557,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F129" t="s">
         <v>34</v>
@@ -11580,7 +11580,7 @@
         <v>27</v>
       </c>
       <c r="E130">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
@@ -11603,7 +11603,7 @@
         <v>27</v>
       </c>
       <c r="E131">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F131" t="s">
         <v>31</v>
@@ -11626,7 +11626,7 @@
         <v>27</v>
       </c>
       <c r="E132">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F132" t="s">
         <v>28</v>
@@ -11649,7 +11649,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F133" t="s">
         <v>34</v>
@@ -11672,7 +11672,7 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -11718,7 +11718,7 @@
         <v>27</v>
       </c>
       <c r="E136">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
@@ -11741,7 +11741,7 @@
         <v>27</v>
       </c>
       <c r="E137">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F137" t="s">
         <v>34</v>
@@ -11764,7 +11764,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -11787,7 +11787,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F139" t="s">
         <v>31</v>
@@ -11810,7 +11810,7 @@
         <v>27</v>
       </c>
       <c r="E140">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
@@ -11833,7 +11833,7 @@
         <v>27</v>
       </c>
       <c r="E141">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F141" t="s">
         <v>34</v>
@@ -11856,7 +11856,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -11879,7 +11879,7 @@
         <v>27</v>
       </c>
       <c r="E143">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F143" t="s">
         <v>31</v>
@@ -11902,7 +11902,7 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F144" t="s">
         <v>28</v>
@@ -11925,7 +11925,7 @@
         <v>27</v>
       </c>
       <c r="E145">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F145" t="s">
         <v>34</v>
@@ -11948,7 +11948,7 @@
         <v>27</v>
       </c>
       <c r="E146">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F146" t="s">
         <v>28</v>
@@ -11971,7 +11971,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F147" t="s">
         <v>31</v>
@@ -11994,7 +11994,7 @@
         <v>27</v>
       </c>
       <c r="E148">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
@@ -12040,7 +12040,7 @@
         <v>27</v>
       </c>
       <c r="E150">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
@@ -12063,7 +12063,7 @@
         <v>27</v>
       </c>
       <c r="E151">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F151" t="s">
         <v>31</v>
@@ -12086,7 +12086,7 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F152" t="s">
         <v>28</v>
@@ -12109,7 +12109,7 @@
         <v>27</v>
       </c>
       <c r="E153">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F153" t="s">
         <v>31</v>
@@ -12132,7 +12132,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -12155,7 +12155,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F155" t="s">
         <v>34</v>
@@ -12178,7 +12178,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -12201,7 +12201,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F157" t="s">
         <v>31</v>
@@ -12224,7 +12224,7 @@
         <v>27</v>
       </c>
       <c r="E158">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F158" t="s">
         <v>28</v>
@@ -12247,7 +12247,7 @@
         <v>27</v>
       </c>
       <c r="E159">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F159" t="s">
         <v>34</v>
@@ -12270,7 +12270,7 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F160" t="s">
         <v>28</v>
@@ -12293,7 +12293,7 @@
         <v>27</v>
       </c>
       <c r="E161">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F161" t="s">
         <v>31</v>
@@ -12316,7 +12316,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -12339,7 +12339,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F163" t="s">
         <v>34</v>
@@ -12362,7 +12362,7 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
@@ -12385,7 +12385,7 @@
         <v>27</v>
       </c>
       <c r="E165">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F165" t="s">
         <v>31</v>
@@ -12408,7 +12408,7 @@
         <v>27</v>
       </c>
       <c r="E166">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -12431,7 +12431,7 @@
         <v>27</v>
       </c>
       <c r="E167">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F167" t="s">
         <v>34</v>
@@ -12454,7 +12454,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -12477,7 +12477,7 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F169" t="s">
         <v>31</v>
@@ -12500,7 +12500,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -12523,7 +12523,7 @@
         <v>27</v>
       </c>
       <c r="E171">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F171" t="s">
         <v>34</v>
@@ -12546,7 +12546,7 @@
         <v>27</v>
       </c>
       <c r="E172">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
@@ -12569,7 +12569,7 @@
         <v>27</v>
       </c>
       <c r="E173">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F173" t="s">
         <v>31</v>
@@ -12592,7 +12592,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -12615,7 +12615,7 @@
         <v>27</v>
       </c>
       <c r="E175">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F175" t="s">
         <v>34</v>
@@ -12638,7 +12638,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -12661,7 +12661,7 @@
         <v>27</v>
       </c>
       <c r="E177">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
@@ -12684,7 +12684,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F178" t="s">
         <v>31</v>
@@ -12707,7 +12707,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -12730,7 +12730,7 @@
         <v>27</v>
       </c>
       <c r="E180">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F180" t="s">
         <v>34</v>
@@ -12753,7 +12753,7 @@
         <v>27</v>
       </c>
       <c r="E181">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F181" t="s">
         <v>28</v>
@@ -12776,7 +12776,7 @@
         <v>27</v>
       </c>
       <c r="E182">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F182" t="s">
         <v>31</v>
@@ -12799,7 +12799,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -12822,7 +12822,7 @@
         <v>27</v>
       </c>
       <c r="E184">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F184" t="s">
         <v>34</v>
@@ -12845,7 +12845,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -12868,7 +12868,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F186" t="s">
         <v>31</v>
@@ -12891,7 +12891,7 @@
         <v>27</v>
       </c>
       <c r="E187">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F187" t="s">
         <v>28</v>
@@ -12914,7 +12914,7 @@
         <v>27</v>
       </c>
       <c r="E188">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F188" t="s">
         <v>34</v>
@@ -12937,7 +12937,7 @@
         <v>27</v>
       </c>
       <c r="E189">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F189" t="s">
         <v>28</v>
@@ -12960,7 +12960,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F190" t="s">
         <v>31</v>
@@ -12983,7 +12983,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -13006,7 +13006,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F192" t="s">
         <v>34</v>
@@ -13029,7 +13029,7 @@
         <v>27</v>
       </c>
       <c r="E193">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -13052,7 +13052,7 @@
         <v>27</v>
       </c>
       <c r="E194">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F194" t="s">
         <v>31</v>
@@ -13075,7 +13075,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -13098,7 +13098,7 @@
         <v>27</v>
       </c>
       <c r="E196">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F196" t="s">
         <v>34</v>
@@ -13121,7 +13121,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -13144,7 +13144,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F198" t="s">
         <v>31</v>
@@ -13167,7 +13167,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -13190,7 +13190,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F200" t="s">
         <v>34</v>
@@ -13213,7 +13213,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -13236,7 +13236,7 @@
         <v>27</v>
       </c>
       <c r="E202">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -13259,7 +13259,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F203" t="s">
         <v>31</v>
@@ -13282,7 +13282,7 @@
         <v>27</v>
       </c>
       <c r="E204">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -13305,7 +13305,7 @@
         <v>27</v>
       </c>
       <c r="E205">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F205" t="s">
         <v>34</v>
@@ -13328,7 +13328,7 @@
         <v>27</v>
       </c>
       <c r="E206">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -13351,7 +13351,7 @@
         <v>27</v>
       </c>
       <c r="E207">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F207" t="s">
         <v>31</v>
@@ -13374,7 +13374,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -13397,7 +13397,7 @@
         <v>27</v>
       </c>
       <c r="E209">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F209" t="s">
         <v>34</v>
@@ -13420,7 +13420,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -13443,7 +13443,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F211" t="s">
         <v>31</v>
@@ -13466,7 +13466,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -13489,7 +13489,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F213" t="s">
         <v>34</v>
@@ -13512,7 +13512,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -13535,7 +13535,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F215" t="s">
         <v>31</v>
@@ -13558,7 +13558,7 @@
         <v>27</v>
       </c>
       <c r="E216">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F216" t="s">
         <v>28</v>
@@ -13581,7 +13581,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F217" t="s">
         <v>34</v>
@@ -13604,7 +13604,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -13627,7 +13627,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F219" t="s">
         <v>31</v>
@@ -13650,7 +13650,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -13673,7 +13673,7 @@
         <v>27</v>
       </c>
       <c r="E221">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F221" t="s">
         <v>34</v>
@@ -13719,7 +13719,7 @@
         <v>27</v>
       </c>
       <c r="E223">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F223" t="s">
         <v>31</v>
@@ -13742,7 +13742,7 @@
         <v>27</v>
       </c>
       <c r="E224">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F224" t="s">
         <v>28</v>
@@ -13765,7 +13765,7 @@
         <v>27</v>
       </c>
       <c r="E225">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F225" t="s">
         <v>34</v>
@@ -13788,7 +13788,7 @@
         <v>27</v>
       </c>
       <c r="E226">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F226" t="s">
         <v>28</v>
@@ -13811,7 +13811,7 @@
         <v>27</v>
       </c>
       <c r="E227">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F227" t="s">
         <v>28</v>
@@ -13834,7 +13834,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F228" t="s">
         <v>31</v>
@@ -13857,7 +13857,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -13880,7 +13880,7 @@
         <v>27</v>
       </c>
       <c r="E230">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="F230" t="s">
         <v>34</v>
@@ -13903,7 +13903,7 @@
         <v>27</v>
       </c>
       <c r="E231">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F231" t="s">
         <v>28</v>
@@ -13926,7 +13926,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F232" t="s">
         <v>31</v>
@@ -13949,7 +13949,7 @@
         <v>27</v>
       </c>
       <c r="E233">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F233" t="s">
         <v>28</v>
@@ -13995,7 +13995,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -14018,7 +14018,7 @@
         <v>27</v>
       </c>
       <c r="E236">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F236" t="s">
         <v>31</v>
@@ -14041,7 +14041,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -14064,7 +14064,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F238" t="s">
         <v>34</v>
@@ -14087,7 +14087,7 @@
         <v>27</v>
       </c>
       <c r="E239">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F239" t="s">
         <v>28</v>
@@ -14110,7 +14110,7 @@
         <v>27</v>
       </c>
       <c r="E240">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F240" t="s">
         <v>31</v>
@@ -14133,7 +14133,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -14156,7 +14156,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F242" t="s">
         <v>34</v>
@@ -14179,7 +14179,7 @@
         <v>27</v>
       </c>
       <c r="E243">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -14202,7 +14202,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F244" t="s">
         <v>31</v>
@@ -14225,7 +14225,7 @@
         <v>27</v>
       </c>
       <c r="E245">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F245" t="s">
         <v>28</v>
@@ -14248,7 +14248,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F246" t="s">
         <v>34</v>
@@ -14271,7 +14271,7 @@
         <v>27</v>
       </c>
       <c r="E247">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F247" t="s">
         <v>28</v>
@@ -14294,7 +14294,7 @@
         <v>27</v>
       </c>
       <c r="E248">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F248" t="s">
         <v>31</v>
@@ -14317,7 +14317,7 @@
         <v>27</v>
       </c>
       <c r="E249">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F249" t="s">
         <v>28</v>
@@ -14340,7 +14340,7 @@
         <v>27</v>
       </c>
       <c r="E250">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F250" t="s">
         <v>34</v>
@@ -14363,7 +14363,7 @@
         <v>27</v>
       </c>
       <c r="E251">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F251" t="s">
         <v>28</v>
@@ -14386,7 +14386,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -14409,7 +14409,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F253" t="s">
         <v>31</v>
@@ -14432,7 +14432,7 @@
         <v>27</v>
       </c>
       <c r="E254">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F254" t="s">
         <v>28</v>
@@ -14455,7 +14455,7 @@
         <v>27</v>
       </c>
       <c r="E255">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F255" t="s">
         <v>34</v>
@@ -14478,7 +14478,7 @@
         <v>27</v>
       </c>
       <c r="E256">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F256" t="s">
         <v>28</v>
@@ -14501,7 +14501,7 @@
         <v>27</v>
       </c>
       <c r="E257">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F257" t="s">
         <v>31</v>
@@ -14524,7 +14524,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -14547,7 +14547,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F259" t="s">
         <v>34</v>
@@ -14570,7 +14570,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -14593,7 +14593,7 @@
         <v>27</v>
       </c>
       <c r="E261">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F261" t="s">
         <v>31</v>
@@ -14616,7 +14616,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -14662,7 +14662,7 @@
         <v>27</v>
       </c>
       <c r="E264">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -14685,7 +14685,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F265" t="s">
         <v>31</v>
@@ -14708,7 +14708,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -14754,7 +14754,7 @@
         <v>27</v>
       </c>
       <c r="E268">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F268" t="s">
         <v>28</v>
@@ -14777,7 +14777,7 @@
         <v>27</v>
       </c>
       <c r="E269">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F269" t="s">
         <v>31</v>
@@ -14800,7 +14800,7 @@
         <v>27</v>
       </c>
       <c r="E270">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F270" t="s">
         <v>28</v>
@@ -14823,7 +14823,7 @@
         <v>27</v>
       </c>
       <c r="E271">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F271" t="s">
         <v>34</v>
@@ -14846,7 +14846,7 @@
         <v>27</v>
       </c>
       <c r="E272">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F272" t="s">
         <v>28</v>
@@ -14869,7 +14869,7 @@
         <v>27</v>
       </c>
       <c r="E273">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F273" t="s">
         <v>31</v>
@@ -14892,7 +14892,7 @@
         <v>27</v>
       </c>
       <c r="E274">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F274" t="s">
         <v>28</v>
@@ -14915,7 +14915,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F275" t="s">
         <v>34</v>
@@ -14938,7 +14938,7 @@
         <v>27</v>
       </c>
       <c r="E276">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F276" t="s">
         <v>28</v>
@@ -14961,7 +14961,7 @@
         <v>27</v>
       </c>
       <c r="E277">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F277" t="s">
         <v>28</v>
@@ -14984,7 +14984,7 @@
         <v>27</v>
       </c>
       <c r="E278">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F278" t="s">
         <v>31</v>
@@ -15007,7 +15007,7 @@
         <v>27</v>
       </c>
       <c r="E279">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -15030,7 +15030,7 @@
         <v>27</v>
       </c>
       <c r="E280">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F280" t="s">
         <v>34</v>
@@ -15053,7 +15053,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -15076,7 +15076,7 @@
         <v>27</v>
       </c>
       <c r="E282">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F282" t="s">
         <v>31</v>
@@ -15122,7 +15122,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F284" t="s">
         <v>34</v>
@@ -15145,7 +15145,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -15168,7 +15168,7 @@
         <v>27</v>
       </c>
       <c r="E286">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F286" t="s">
         <v>31</v>
@@ -15191,7 +15191,7 @@
         <v>27</v>
       </c>
       <c r="E287">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F287" t="s">
         <v>28</v>
@@ -15214,7 +15214,7 @@
         <v>27</v>
       </c>
       <c r="E288">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F288" t="s">
         <v>34</v>
@@ -15237,7 +15237,7 @@
         <v>27</v>
       </c>
       <c r="E289">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F289" t="s">
         <v>28</v>
@@ -15260,7 +15260,7 @@
         <v>27</v>
       </c>
       <c r="E290">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F290" t="s">
         <v>31</v>
@@ -15283,7 +15283,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -15306,7 +15306,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F292" t="s">
         <v>34</v>
@@ -15329,7 +15329,7 @@
         <v>27</v>
       </c>
       <c r="E293">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -15352,7 +15352,7 @@
         <v>27</v>
       </c>
       <c r="E294">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F294" t="s">
         <v>31</v>
@@ -15375,7 +15375,7 @@
         <v>27</v>
       </c>
       <c r="E295">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F295" t="s">
         <v>28</v>
@@ -15398,7 +15398,7 @@
         <v>27</v>
       </c>
       <c r="E296">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F296" t="s">
         <v>34</v>
@@ -15421,7 +15421,7 @@
         <v>27</v>
       </c>
       <c r="E297">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F297" t="s">
         <v>28</v>
@@ -15444,7 +15444,7 @@
         <v>27</v>
       </c>
       <c r="E298">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F298" t="s">
         <v>31</v>
@@ -15467,7 +15467,7 @@
         <v>27</v>
       </c>
       <c r="E299">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F299" t="s">
         <v>28</v>
@@ -15490,7 +15490,7 @@
         <v>27</v>
       </c>
       <c r="E300">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F300" t="s">
         <v>34</v>
@@ -15513,7 +15513,7 @@
         <v>27</v>
       </c>
       <c r="E301">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F301" t="s">
         <v>28</v>

--- a/all-test-reports/vulnerability/vulnerability_test_report.xlsx
+++ b/all-test-reports/vulnerability/vulnerability_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 11:31:47 am</t>
+    <t>28/7/2026, 11:37:59 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1694,7 +1694,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="10">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>28</v>
@@ -1717,7 +1717,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="10">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>31</v>
@@ -1740,7 +1740,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="10">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>28</v>
@@ -1763,7 +1763,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="10">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>34</v>
@@ -1786,7 +1786,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="10">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>28</v>
@@ -1809,7 +1809,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="10">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>31</v>
@@ -1832,7 +1832,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="10">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>28</v>
@@ -1855,7 +1855,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="10">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>34</v>
@@ -1878,7 +1878,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="10">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>28</v>
@@ -1901,7 +1901,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="10">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>31</v>
@@ -1924,7 +1924,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="10">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>28</v>
@@ -1947,7 +1947,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="10">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>34</v>
@@ -1970,7 +1970,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="10">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>28</v>
@@ -1993,7 +1993,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>31</v>
@@ -2016,7 +2016,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="10">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>28</v>
@@ -2039,7 +2039,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="10">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>34</v>
@@ -2062,7 +2062,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="10">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>28</v>
@@ -2085,7 +2085,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="10">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>31</v>
@@ -2108,7 +2108,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="10">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>28</v>
@@ -2131,7 +2131,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>34</v>
@@ -2154,7 +2154,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="10">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>28</v>
@@ -2177,7 +2177,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="10">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>31</v>
@@ -2200,7 +2200,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="10">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>28</v>
@@ -2223,7 +2223,7 @@
         <v>27</v>
       </c>
       <c r="E25" s="10">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>34</v>
@@ -2246,7 +2246,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="10">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>28</v>
@@ -2269,7 +2269,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="10">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>31</v>
@@ -2292,7 +2292,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="10">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>28</v>
@@ -2315,7 +2315,7 @@
         <v>27</v>
       </c>
       <c r="E29" s="10">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>34</v>
@@ -2338,7 +2338,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="10">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>28</v>
@@ -2361,7 +2361,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="10">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>31</v>
@@ -2384,7 +2384,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="10">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>28</v>
@@ -2407,7 +2407,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="10">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>31</v>
@@ -2430,7 +2430,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="10">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>28</v>
@@ -2453,7 +2453,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="10">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>34</v>
@@ -2476,7 +2476,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="10">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>28</v>
@@ -2499,7 +2499,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="10">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>31</v>
@@ -2522,7 +2522,7 @@
         <v>27</v>
       </c>
       <c r="E38" s="10">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>28</v>
@@ -2545,7 +2545,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="10">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>34</v>
@@ -2568,7 +2568,7 @@
         <v>27</v>
       </c>
       <c r="E40" s="10">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>28</v>
@@ -2591,7 +2591,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="10">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>31</v>
@@ -2614,7 +2614,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="10">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>28</v>
@@ -2637,7 +2637,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>34</v>
@@ -2660,7 +2660,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>28</v>
@@ -2683,7 +2683,7 @@
         <v>27</v>
       </c>
       <c r="E45" s="10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>31</v>
@@ -2706,7 +2706,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="10">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>28</v>
@@ -2729,7 +2729,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="10">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>34</v>
@@ -2752,7 +2752,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="10">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>28</v>
@@ -2775,7 +2775,7 @@
         <v>27</v>
       </c>
       <c r="E49" s="10">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>31</v>
@@ -2798,7 +2798,7 @@
         <v>27</v>
       </c>
       <c r="E50" s="10">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>28</v>
@@ -2821,7 +2821,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="10">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>34</v>
@@ -2844,7 +2844,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>28</v>
@@ -2867,7 +2867,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="10">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>31</v>
@@ -2890,7 +2890,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="10">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>28</v>
@@ -2913,7 +2913,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="10">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>34</v>
@@ -2936,7 +2936,7 @@
         <v>27</v>
       </c>
       <c r="E56" s="10">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>28</v>
@@ -2959,7 +2959,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>31</v>
@@ -2982,7 +2982,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="10">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>28</v>
@@ -3005,7 +3005,7 @@
         <v>27</v>
       </c>
       <c r="E59" s="10">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>34</v>
@@ -3028,7 +3028,7 @@
         <v>27</v>
       </c>
       <c r="E60" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>28</v>
@@ -3051,7 +3051,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="10">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>31</v>
@@ -3074,7 +3074,7 @@
         <v>27</v>
       </c>
       <c r="E62" s="10">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>28</v>
@@ -3097,7 +3097,7 @@
         <v>27</v>
       </c>
       <c r="E63" s="10">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>31</v>
@@ -3120,7 +3120,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="10">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>28</v>
@@ -3143,7 +3143,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="10">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>34</v>
@@ -3166,7 +3166,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="10">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>28</v>
@@ -3189,7 +3189,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="10">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>31</v>
@@ -3212,7 +3212,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="10">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>28</v>
@@ -3235,7 +3235,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>34</v>
@@ -3258,7 +3258,7 @@
         <v>27</v>
       </c>
       <c r="E70" s="10">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>28</v>
@@ -3281,7 +3281,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="10">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>31</v>
@@ -3304,7 +3304,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="10">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>28</v>
@@ -3327,7 +3327,7 @@
         <v>27</v>
       </c>
       <c r="E73" s="10">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>34</v>
@@ -3350,7 +3350,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="10">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>28</v>
@@ -3373,7 +3373,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="10">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>31</v>
@@ -3396,7 +3396,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="10">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>28</v>
@@ -3419,7 +3419,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="10">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>34</v>
@@ -3442,7 +3442,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="10">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>28</v>
@@ -3465,7 +3465,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="10">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>31</v>
@@ -3488,7 +3488,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>28</v>
@@ -3511,7 +3511,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="10">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>34</v>
@@ -3534,7 +3534,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="10">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>28</v>
@@ -3557,7 +3557,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="10">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>31</v>
@@ -3580,7 +3580,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="10">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>28</v>
@@ -3603,7 +3603,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="10">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>34</v>
@@ -3626,7 +3626,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="10">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>28</v>
@@ -3649,7 +3649,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="10">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>31</v>
@@ -3672,7 +3672,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="10">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>28</v>
@@ -3695,7 +3695,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="10">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>34</v>
@@ -3718,7 +3718,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="10">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>28</v>
@@ -3741,7 +3741,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="10">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>31</v>
@@ -3787,7 +3787,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="10">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>31</v>
@@ -3810,7 +3810,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="10">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>28</v>
@@ -3833,7 +3833,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="10">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>34</v>
@@ -3856,7 +3856,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="10">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F96" s="8" t="s">
         <v>28</v>
@@ -3879,7 +3879,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>31</v>
@@ -3902,7 +3902,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="10">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>28</v>
@@ -3925,7 +3925,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="10">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>34</v>
@@ -3948,7 +3948,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="10">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>28</v>
@@ -3971,7 +3971,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>31</v>
@@ -3994,7 +3994,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="10">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>28</v>
@@ -4017,7 +4017,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="10">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>34</v>
@@ -4040,7 +4040,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="10">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>28</v>
@@ -4063,7 +4063,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="10">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>31</v>
@@ -4086,7 +4086,7 @@
         <v>27</v>
       </c>
       <c r="E106" s="10">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>28</v>
@@ -4109,7 +4109,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="10">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>34</v>
@@ -4132,7 +4132,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="10">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>28</v>
@@ -4155,7 +4155,7 @@
         <v>27</v>
       </c>
       <c r="E109" s="10">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>31</v>
@@ -4178,7 +4178,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>28</v>
@@ -4201,7 +4201,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="10">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>34</v>
@@ -4224,7 +4224,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>28</v>
@@ -4247,7 +4247,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F113" s="8" t="s">
         <v>31</v>
@@ -4270,7 +4270,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="10">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>28</v>
@@ -4293,7 +4293,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="10">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>34</v>
@@ -4316,7 +4316,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="10">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>28</v>
@@ -4339,7 +4339,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="10">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F117" s="8" t="s">
         <v>31</v>
@@ -4362,7 +4362,7 @@
         <v>27</v>
       </c>
       <c r="E118" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F118" s="8" t="s">
         <v>28</v>
@@ -4385,7 +4385,7 @@
         <v>27</v>
       </c>
       <c r="E119" s="10">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F119" s="8" t="s">
         <v>34</v>
@@ -4408,7 +4408,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="10">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F120" s="8" t="s">
         <v>28</v>
@@ -4431,7 +4431,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="10">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F121" s="8" t="s">
         <v>31</v>
@@ -4454,7 +4454,7 @@
         <v>27</v>
       </c>
       <c r="E122" s="10">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F122" s="8" t="s">
         <v>28</v>
@@ -4477,7 +4477,7 @@
         <v>27</v>
       </c>
       <c r="E123" s="10">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>31</v>
@@ -4500,7 +4500,7 @@
         <v>27</v>
       </c>
       <c r="E124" s="10">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F124" s="8" t="s">
         <v>28</v>
@@ -4523,7 +4523,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="10">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>34</v>
@@ -4546,7 +4546,7 @@
         <v>27</v>
       </c>
       <c r="E126" s="10">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F126" s="8" t="s">
         <v>28</v>
@@ -4569,7 +4569,7 @@
         <v>27</v>
       </c>
       <c r="E127" s="10">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F127" s="8" t="s">
         <v>31</v>
@@ -4592,7 +4592,7 @@
         <v>27</v>
       </c>
       <c r="E128" s="10">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F128" s="8" t="s">
         <v>28</v>
@@ -4615,7 +4615,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F129" s="8" t="s">
         <v>34</v>
@@ -4638,7 +4638,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="10">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F130" s="8" t="s">
         <v>28</v>
@@ -4661,7 +4661,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F131" s="8" t="s">
         <v>31</v>
@@ -4684,7 +4684,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="10">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F132" s="8" t="s">
         <v>28</v>
@@ -4707,7 +4707,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="10">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F133" s="8" t="s">
         <v>34</v>
@@ -4730,7 +4730,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="10">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F134" s="8" t="s">
         <v>28</v>
@@ -4753,7 +4753,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="10">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F135" s="8" t="s">
         <v>31</v>
@@ -4776,7 +4776,7 @@
         <v>27</v>
       </c>
       <c r="E136" s="10">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F136" s="8" t="s">
         <v>28</v>
@@ -4799,7 +4799,7 @@
         <v>27</v>
       </c>
       <c r="E137" s="10">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F137" s="8" t="s">
         <v>34</v>
@@ -4822,7 +4822,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="10">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F138" s="8" t="s">
         <v>28</v>
@@ -4845,7 +4845,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="10">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F139" s="8" t="s">
         <v>31</v>
@@ -4868,7 +4868,7 @@
         <v>27</v>
       </c>
       <c r="E140" s="10">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F140" s="8" t="s">
         <v>28</v>
@@ -4891,7 +4891,7 @@
         <v>27</v>
       </c>
       <c r="E141" s="10">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F141" s="8" t="s">
         <v>34</v>
@@ -4914,7 +4914,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="10">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F142" s="8" t="s">
         <v>28</v>
@@ -4937,7 +4937,7 @@
         <v>27</v>
       </c>
       <c r="E143" s="10">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F143" s="8" t="s">
         <v>31</v>
@@ -4960,7 +4960,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="10">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F144" s="8" t="s">
         <v>28</v>
@@ -4983,7 +4983,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="10">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F145" s="8" t="s">
         <v>34</v>
@@ -5006,7 +5006,7 @@
         <v>27</v>
       </c>
       <c r="E146" s="10">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>28</v>
@@ -5029,7 +5029,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="10">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F147" s="8" t="s">
         <v>31</v>
@@ -5075,7 +5075,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="10">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F149" s="8" t="s">
         <v>34</v>
@@ -5098,7 +5098,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="10">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>28</v>
@@ -5121,7 +5121,7 @@
         <v>27</v>
       </c>
       <c r="E151" s="10">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>31</v>
@@ -5144,7 +5144,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="10">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>28</v>
@@ -5167,7 +5167,7 @@
         <v>27</v>
       </c>
       <c r="E153" s="10">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F153" s="8" t="s">
         <v>31</v>
@@ -5190,7 +5190,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="10">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>28</v>
@@ -5213,7 +5213,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="10">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F155" s="8" t="s">
         <v>34</v>
@@ -5236,7 +5236,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F156" s="8" t="s">
         <v>28</v>
@@ -5259,7 +5259,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="10">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F157" s="8" t="s">
         <v>31</v>
@@ -5282,7 +5282,7 @@
         <v>27</v>
       </c>
       <c r="E158" s="10">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F158" s="8" t="s">
         <v>28</v>
@@ -5305,7 +5305,7 @@
         <v>27</v>
       </c>
       <c r="E159" s="10">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F159" s="8" t="s">
         <v>34</v>
@@ -5328,7 +5328,7 @@
         <v>27</v>
       </c>
       <c r="E160" s="10">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F160" s="8" t="s">
         <v>28</v>
@@ -5351,7 +5351,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="10">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F161" s="8" t="s">
         <v>31</v>
@@ -5374,7 +5374,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F162" s="8" t="s">
         <v>28</v>
@@ -5397,7 +5397,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="10">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F163" s="8" t="s">
         <v>34</v>
@@ -5420,7 +5420,7 @@
         <v>27</v>
       </c>
       <c r="E164" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F164" s="8" t="s">
         <v>28</v>
@@ -5443,7 +5443,7 @@
         <v>27</v>
       </c>
       <c r="E165" s="10">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F165" s="8" t="s">
         <v>31</v>
@@ -5466,7 +5466,7 @@
         <v>27</v>
       </c>
       <c r="E166" s="10">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F166" s="8" t="s">
         <v>28</v>
@@ -5489,7 +5489,7 @@
         <v>27</v>
       </c>
       <c r="E167" s="10">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F167" s="8" t="s">
         <v>34</v>
@@ -5512,7 +5512,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="10">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F168" s="8" t="s">
         <v>28</v>
@@ -5535,7 +5535,7 @@
         <v>27</v>
       </c>
       <c r="E169" s="10">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F169" s="8" t="s">
         <v>31</v>
@@ -5558,7 +5558,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="10">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F170" s="8" t="s">
         <v>28</v>
@@ -5581,7 +5581,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="10">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F171" s="8" t="s">
         <v>34</v>
@@ -5604,7 +5604,7 @@
         <v>27</v>
       </c>
       <c r="E172" s="10">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F172" s="8" t="s">
         <v>28</v>
@@ -5627,7 +5627,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="10">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F173" s="8" t="s">
         <v>31</v>
@@ -5650,7 +5650,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="10">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F174" s="8" t="s">
         <v>28</v>
@@ -5673,7 +5673,7 @@
         <v>27</v>
       </c>
       <c r="E175" s="10">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F175" s="8" t="s">
         <v>34</v>
@@ -5696,7 +5696,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="10">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F176" s="8" t="s">
         <v>28</v>
@@ -5719,7 +5719,7 @@
         <v>27</v>
       </c>
       <c r="E177" s="10">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F177" s="8" t="s">
         <v>28</v>
@@ -5742,7 +5742,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="10">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F178" s="8" t="s">
         <v>31</v>
@@ -5765,7 +5765,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="10">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F179" s="8" t="s">
         <v>28</v>
@@ -5788,7 +5788,7 @@
         <v>27</v>
       </c>
       <c r="E180" s="10">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F180" s="8" t="s">
         <v>34</v>
@@ -5811,7 +5811,7 @@
         <v>27</v>
       </c>
       <c r="E181" s="10">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F181" s="8" t="s">
         <v>28</v>
@@ -5834,7 +5834,7 @@
         <v>27</v>
       </c>
       <c r="E182" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F182" s="8" t="s">
         <v>31</v>
@@ -5857,7 +5857,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="10">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F183" s="8" t="s">
         <v>28</v>
@@ -5880,7 +5880,7 @@
         <v>27</v>
       </c>
       <c r="E184" s="10">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F184" s="8" t="s">
         <v>34</v>
@@ -5903,7 +5903,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="10">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F185" s="8" t="s">
         <v>28</v>
@@ -5926,7 +5926,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="10">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F186" s="8" t="s">
         <v>31</v>
@@ -5949,7 +5949,7 @@
         <v>27</v>
       </c>
       <c r="E187" s="10">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F187" s="8" t="s">
         <v>28</v>
@@ -5972,7 +5972,7 @@
         <v>27</v>
       </c>
       <c r="E188" s="10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F188" s="8" t="s">
         <v>34</v>
@@ -5995,7 +5995,7 @@
         <v>27</v>
       </c>
       <c r="E189" s="10">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F189" s="8" t="s">
         <v>28</v>
@@ -6018,7 +6018,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="10">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F190" s="8" t="s">
         <v>31</v>
@@ -6041,7 +6041,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="10">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F191" s="8" t="s">
         <v>28</v>
@@ -6064,7 +6064,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="10">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F192" s="8" t="s">
         <v>34</v>
@@ -6087,7 +6087,7 @@
         <v>27</v>
       </c>
       <c r="E193" s="10">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F193" s="8" t="s">
         <v>28</v>
@@ -6110,7 +6110,7 @@
         <v>27</v>
       </c>
       <c r="E194" s="10">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F194" s="8" t="s">
         <v>31</v>
@@ -6133,7 +6133,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="10">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F195" s="8" t="s">
         <v>28</v>
@@ -6156,7 +6156,7 @@
         <v>27</v>
       </c>
       <c r="E196" s="10">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F196" s="8" t="s">
         <v>34</v>
@@ -6179,7 +6179,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="10">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F197" s="8" t="s">
         <v>28</v>
@@ -6202,7 +6202,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="10">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F198" s="8" t="s">
         <v>31</v>
@@ -6225,7 +6225,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="10">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F199" s="8" t="s">
         <v>28</v>
@@ -6248,7 +6248,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="10">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F200" s="8" t="s">
         <v>34</v>
@@ -6271,7 +6271,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="10">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F201" s="8" t="s">
         <v>28</v>
@@ -6294,7 +6294,7 @@
         <v>27</v>
       </c>
       <c r="E202" s="10">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F202" s="8" t="s">
         <v>28</v>
@@ -6317,7 +6317,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="10">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F203" s="8" t="s">
         <v>31</v>
@@ -6340,7 +6340,7 @@
         <v>27</v>
       </c>
       <c r="E204" s="10">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F204" s="8" t="s">
         <v>28</v>
@@ -6363,7 +6363,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="10">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F205" s="8" t="s">
         <v>34</v>
@@ -6386,7 +6386,7 @@
         <v>27</v>
       </c>
       <c r="E206" s="10">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F206" s="8" t="s">
         <v>28</v>
@@ -6409,7 +6409,7 @@
         <v>27</v>
       </c>
       <c r="E207" s="10">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F207" s="8" t="s">
         <v>31</v>
@@ -6432,7 +6432,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="10">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F208" s="8" t="s">
         <v>28</v>
@@ -6455,7 +6455,7 @@
         <v>27</v>
       </c>
       <c r="E209" s="10">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F209" s="8" t="s">
         <v>34</v>
@@ -6478,7 +6478,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="10">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F210" s="8" t="s">
         <v>28</v>
@@ -6501,7 +6501,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="10">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F211" s="8" t="s">
         <v>31</v>
@@ -6524,7 +6524,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="10">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F212" s="8" t="s">
         <v>28</v>
@@ -6547,7 +6547,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="10">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F213" s="8" t="s">
         <v>34</v>
@@ -6570,7 +6570,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="10">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F214" s="8" t="s">
         <v>28</v>
@@ -6593,7 +6593,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="10">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F215" s="8" t="s">
         <v>31</v>
@@ -6616,7 +6616,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="10">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F216" s="8" t="s">
         <v>28</v>
@@ -6639,7 +6639,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="10">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F217" s="8" t="s">
         <v>34</v>
@@ -6662,7 +6662,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="10">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F218" s="8" t="s">
         <v>28</v>
@@ -6685,7 +6685,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="10">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F219" s="8" t="s">
         <v>31</v>
@@ -6708,7 +6708,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="10">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F220" s="8" t="s">
         <v>28</v>
@@ -6731,7 +6731,7 @@
         <v>27</v>
       </c>
       <c r="E221" s="10">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F221" s="8" t="s">
         <v>34</v>
@@ -6754,7 +6754,7 @@
         <v>27</v>
       </c>
       <c r="E222" s="10">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F222" s="8" t="s">
         <v>28</v>
@@ -6777,7 +6777,7 @@
         <v>27</v>
       </c>
       <c r="E223" s="10">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F223" s="8" t="s">
         <v>31</v>
@@ -6800,7 +6800,7 @@
         <v>27</v>
       </c>
       <c r="E224" s="10">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F224" s="8" t="s">
         <v>28</v>
@@ -6823,7 +6823,7 @@
         <v>27</v>
       </c>
       <c r="E225" s="10">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F225" s="8" t="s">
         <v>34</v>
@@ -6846,7 +6846,7 @@
         <v>27</v>
       </c>
       <c r="E226" s="10">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F226" s="8" t="s">
         <v>28</v>
@@ -6869,7 +6869,7 @@
         <v>27</v>
       </c>
       <c r="E227" s="10">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F227" s="8" t="s">
         <v>28</v>
@@ -6892,7 +6892,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="10">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F228" s="8" t="s">
         <v>31</v>
@@ -6915,7 +6915,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="10">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F229" s="8" t="s">
         <v>28</v>
@@ -6938,7 +6938,7 @@
         <v>27</v>
       </c>
       <c r="E230" s="10">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F230" s="8" t="s">
         <v>34</v>
@@ -6961,7 +6961,7 @@
         <v>27</v>
       </c>
       <c r="E231" s="10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F231" s="8" t="s">
         <v>28</v>
@@ -6984,7 +6984,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="10">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F232" s="8" t="s">
         <v>31</v>
@@ -7007,7 +7007,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="10">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F233" s="8" t="s">
         <v>28</v>
@@ -7030,7 +7030,7 @@
         <v>27</v>
       </c>
       <c r="E234" s="10">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F234" s="8" t="s">
         <v>34</v>
@@ -7053,7 +7053,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F235" s="8" t="s">
         <v>28</v>
@@ -7076,7 +7076,7 @@
         <v>27</v>
       </c>
       <c r="E236" s="10">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F236" s="8" t="s">
         <v>31</v>
@@ -7099,7 +7099,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F237" s="8" t="s">
         <v>28</v>
@@ -7122,7 +7122,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="10">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F238" s="8" t="s">
         <v>34</v>
@@ -7145,7 +7145,7 @@
         <v>27</v>
       </c>
       <c r="E239" s="10">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F239" s="8" t="s">
         <v>28</v>
@@ -7168,7 +7168,7 @@
         <v>27</v>
       </c>
       <c r="E240" s="10">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F240" s="8" t="s">
         <v>31</v>
@@ -7191,7 +7191,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="10">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F241" s="8" t="s">
         <v>28</v>
@@ -7214,7 +7214,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="10">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F242" s="8" t="s">
         <v>34</v>
@@ -7237,7 +7237,7 @@
         <v>27</v>
       </c>
       <c r="E243" s="10">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F243" s="8" t="s">
         <v>28</v>
@@ -7260,7 +7260,7 @@
         <v>27</v>
       </c>
       <c r="E244" s="10">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F244" s="8" t="s">
         <v>31</v>
@@ -7283,7 +7283,7 @@
         <v>27</v>
       </c>
       <c r="E245" s="10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F245" s="8" t="s">
         <v>28</v>
@@ -7306,7 +7306,7 @@
         <v>27</v>
       </c>
       <c r="E246" s="10">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F246" s="8" t="s">
         <v>34</v>
@@ -7352,7 +7352,7 @@
         <v>27</v>
       </c>
       <c r="E248" s="10">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F248" s="8" t="s">
         <v>31</v>
@@ -7375,7 +7375,7 @@
         <v>27</v>
       </c>
       <c r="E249" s="10">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F249" s="8" t="s">
         <v>28</v>
@@ -7398,7 +7398,7 @@
         <v>27</v>
       </c>
       <c r="E250" s="10">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F250" s="8" t="s">
         <v>34</v>
@@ -7421,7 +7421,7 @@
         <v>27</v>
       </c>
       <c r="E251" s="10">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F251" s="8" t="s">
         <v>28</v>
@@ -7444,7 +7444,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="10">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F252" s="8" t="s">
         <v>28</v>
@@ -7467,7 +7467,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="10">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F253" s="8" t="s">
         <v>31</v>
@@ -7490,7 +7490,7 @@
         <v>27</v>
       </c>
       <c r="E254" s="10">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F254" s="8" t="s">
         <v>28</v>
@@ -7513,7 +7513,7 @@
         <v>27</v>
       </c>
       <c r="E255" s="10">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F255" s="8" t="s">
         <v>34</v>
@@ -7536,7 +7536,7 @@
         <v>27</v>
       </c>
       <c r="E256" s="10">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F256" s="8" t="s">
         <v>28</v>
@@ -7559,7 +7559,7 @@
         <v>27</v>
       </c>
       <c r="E257" s="10">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F257" s="8" t="s">
         <v>31</v>
@@ -7582,7 +7582,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="10">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F258" s="8" t="s">
         <v>28</v>
@@ -7605,7 +7605,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F259" s="8" t="s">
         <v>34</v>
@@ -7628,7 +7628,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="10">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F260" s="8" t="s">
         <v>28</v>
@@ -7651,7 +7651,7 @@
         <v>27</v>
       </c>
       <c r="E261" s="10">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F261" s="8" t="s">
         <v>31</v>
@@ -7674,7 +7674,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="10">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F262" s="8" t="s">
         <v>28</v>
@@ -7697,7 +7697,7 @@
         <v>27</v>
       </c>
       <c r="E263" s="10">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F263" s="8" t="s">
         <v>34</v>
@@ -7743,7 +7743,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="10">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F265" s="8" t="s">
         <v>31</v>
@@ -7766,7 +7766,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F266" s="8" t="s">
         <v>28</v>
@@ -7789,7 +7789,7 @@
         <v>27</v>
       </c>
       <c r="E267" s="10">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F267" s="8" t="s">
         <v>34</v>
@@ -7812,7 +7812,7 @@
         <v>27</v>
       </c>
       <c r="E268" s="10">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F268" s="8" t="s">
         <v>28</v>
@@ -7835,7 +7835,7 @@
         <v>27</v>
       </c>
       <c r="E269" s="10">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F269" s="8" t="s">
         <v>31</v>
@@ -7858,7 +7858,7 @@
         <v>27</v>
       </c>
       <c r="E270" s="10">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F270" s="8" t="s">
         <v>28</v>
@@ -7881,7 +7881,7 @@
         <v>27</v>
       </c>
       <c r="E271" s="10">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F271" s="8" t="s">
         <v>34</v>
@@ -7904,7 +7904,7 @@
         <v>27</v>
       </c>
       <c r="E272" s="10">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F272" s="8" t="s">
         <v>28</v>
@@ -7927,7 +7927,7 @@
         <v>27</v>
       </c>
       <c r="E273" s="10">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F273" s="8" t="s">
         <v>31</v>
@@ -7950,7 +7950,7 @@
         <v>27</v>
       </c>
       <c r="E274" s="10">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F274" s="8" t="s">
         <v>28</v>
@@ -7973,7 +7973,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="10">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F275" s="8" t="s">
         <v>34</v>
@@ -7996,7 +7996,7 @@
         <v>27</v>
       </c>
       <c r="E276" s="10">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F276" s="8" t="s">
         <v>28</v>
@@ -8019,7 +8019,7 @@
         <v>27</v>
       </c>
       <c r="E277" s="10">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F277" s="8" t="s">
         <v>28</v>
@@ -8042,7 +8042,7 @@
         <v>27</v>
       </c>
       <c r="E278" s="10">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F278" s="8" t="s">
         <v>31</v>
@@ -8065,7 +8065,7 @@
         <v>27</v>
       </c>
       <c r="E279" s="10">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F279" s="8" t="s">
         <v>28</v>
@@ -8088,7 +8088,7 @@
         <v>27</v>
       </c>
       <c r="E280" s="10">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F280" s="8" t="s">
         <v>34</v>
@@ -8111,7 +8111,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="10">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F281" s="8" t="s">
         <v>28</v>
@@ -8134,7 +8134,7 @@
         <v>27</v>
       </c>
       <c r="E282" s="10">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F282" s="8" t="s">
         <v>31</v>
@@ -8157,7 +8157,7 @@
         <v>27</v>
       </c>
       <c r="E283" s="10">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F283" s="8" t="s">
         <v>28</v>
@@ -8180,7 +8180,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="10">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F284" s="8" t="s">
         <v>34</v>
@@ -8203,7 +8203,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="10">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F285" s="8" t="s">
         <v>28</v>
@@ -8226,7 +8226,7 @@
         <v>27</v>
       </c>
       <c r="E286" s="10">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F286" s="8" t="s">
         <v>31</v>
@@ -8249,7 +8249,7 @@
         <v>27</v>
       </c>
       <c r="E287" s="10">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F287" s="8" t="s">
         <v>28</v>
@@ -8272,7 +8272,7 @@
         <v>27</v>
       </c>
       <c r="E288" s="10">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F288" s="8" t="s">
         <v>34</v>
@@ -8295,7 +8295,7 @@
         <v>27</v>
       </c>
       <c r="E289" s="10">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F289" s="8" t="s">
         <v>28</v>
@@ -8318,7 +8318,7 @@
         <v>27</v>
       </c>
       <c r="E290" s="10">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F290" s="8" t="s">
         <v>31</v>
@@ -8341,7 +8341,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="10">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F291" s="8" t="s">
         <v>28</v>
@@ -8364,7 +8364,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="10">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F292" s="8" t="s">
         <v>34</v>
@@ -8387,7 +8387,7 @@
         <v>27</v>
       </c>
       <c r="E293" s="10">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F293" s="8" t="s">
         <v>28</v>
@@ -8410,7 +8410,7 @@
         <v>27</v>
       </c>
       <c r="E294" s="10">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F294" s="8" t="s">
         <v>31</v>
@@ -8433,7 +8433,7 @@
         <v>27</v>
       </c>
       <c r="E295" s="10">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F295" s="8" t="s">
         <v>28</v>
@@ -8456,7 +8456,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="10">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F296" s="8" t="s">
         <v>34</v>
@@ -8479,7 +8479,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="10">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F297" s="8" t="s">
         <v>28</v>
@@ -8502,7 +8502,7 @@
         <v>27</v>
       </c>
       <c r="E298" s="10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F298" s="8" t="s">
         <v>31</v>
@@ -8525,7 +8525,7 @@
         <v>27</v>
       </c>
       <c r="E299" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F299" s="8" t="s">
         <v>28</v>
@@ -8548,7 +8548,7 @@
         <v>27</v>
       </c>
       <c r="E300" s="10">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F300" s="8" t="s">
         <v>34</v>
@@ -8571,7 +8571,7 @@
         <v>27</v>
       </c>
       <c r="E301" s="10">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F301" s="8" t="s">
         <v>28</v>
@@ -8636,7 +8636,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -8659,7 +8659,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
         <v>31</v>
@@ -8682,7 +8682,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -8705,7 +8705,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
         <v>34</v>
@@ -8728,7 +8728,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -8751,7 +8751,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F7" t="s">
         <v>31</v>
@@ -8774,7 +8774,7 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -8797,7 +8797,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
@@ -8820,7 +8820,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -8843,7 +8843,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
         <v>31</v>
@@ -8866,7 +8866,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -8889,7 +8889,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F13" t="s">
         <v>34</v>
@@ -8912,7 +8912,7 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -8935,7 +8935,7 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F15" t="s">
         <v>31</v>
@@ -8958,7 +8958,7 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -8981,7 +8981,7 @@
         <v>27</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F17" t="s">
         <v>34</v>
@@ -9004,7 +9004,7 @@
         <v>27</v>
       </c>
       <c r="E18">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -9027,7 +9027,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F19" t="s">
         <v>31</v>
@@ -9050,7 +9050,7 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -9073,7 +9073,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F21" t="s">
         <v>34</v>
@@ -9096,7 +9096,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -9119,7 +9119,7 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F23" t="s">
         <v>31</v>
@@ -9142,7 +9142,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -9165,7 +9165,7 @@
         <v>27</v>
       </c>
       <c r="E25">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F25" t="s">
         <v>34</v>
@@ -9188,7 +9188,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -9211,7 +9211,7 @@
         <v>27</v>
       </c>
       <c r="E27">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F27" t="s">
         <v>31</v>
@@ -9234,7 +9234,7 @@
         <v>27</v>
       </c>
       <c r="E28">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -9257,7 +9257,7 @@
         <v>27</v>
       </c>
       <c r="E29">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F29" t="s">
         <v>34</v>
@@ -9280,7 +9280,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -9303,7 +9303,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F31" t="s">
         <v>31</v>
@@ -9326,7 +9326,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -9349,7 +9349,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F33" t="s">
         <v>31</v>
@@ -9372,7 +9372,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -9395,7 +9395,7 @@
         <v>27</v>
       </c>
       <c r="E35">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
@@ -9418,7 +9418,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -9441,7 +9441,7 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F37" t="s">
         <v>31</v>
@@ -9464,7 +9464,7 @@
         <v>27</v>
       </c>
       <c r="E38">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -9487,7 +9487,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F39" t="s">
         <v>34</v>
@@ -9510,7 +9510,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -9533,7 +9533,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F41" t="s">
         <v>31</v>
@@ -9556,7 +9556,7 @@
         <v>27</v>
       </c>
       <c r="E42">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -9579,7 +9579,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F43" t="s">
         <v>34</v>
@@ -9602,7 +9602,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -9625,7 +9625,7 @@
         <v>27</v>
       </c>
       <c r="E45">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F45" t="s">
         <v>31</v>
@@ -9648,7 +9648,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -9671,7 +9671,7 @@
         <v>27</v>
       </c>
       <c r="E47">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F47" t="s">
         <v>34</v>
@@ -9694,7 +9694,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -9717,7 +9717,7 @@
         <v>27</v>
       </c>
       <c r="E49">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F49" t="s">
         <v>31</v>
@@ -9740,7 +9740,7 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F50" t="s">
         <v>28</v>
@@ -9763,7 +9763,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F51" t="s">
         <v>34</v>
@@ -9786,7 +9786,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -9809,7 +9809,7 @@
         <v>27</v>
       </c>
       <c r="E53">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F53" t="s">
         <v>31</v>
@@ -9832,7 +9832,7 @@
         <v>27</v>
       </c>
       <c r="E54">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -9855,7 +9855,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F55" t="s">
         <v>34</v>
@@ -9878,7 +9878,7 @@
         <v>27</v>
       </c>
       <c r="E56">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -9901,7 +9901,7 @@
         <v>27</v>
       </c>
       <c r="E57">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F57" t="s">
         <v>31</v>
@@ -9924,7 +9924,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -9947,7 +9947,7 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F59" t="s">
         <v>34</v>
@@ -9970,7 +9970,7 @@
         <v>27</v>
       </c>
       <c r="E60">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -9993,7 +9993,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F61" t="s">
         <v>31</v>
@@ -10016,7 +10016,7 @@
         <v>27</v>
       </c>
       <c r="E62">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F62" t="s">
         <v>28</v>
@@ -10039,7 +10039,7 @@
         <v>27</v>
       </c>
       <c r="E63">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F63" t="s">
         <v>31</v>
@@ -10062,7 +10062,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -10085,7 +10085,7 @@
         <v>27</v>
       </c>
       <c r="E65">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F65" t="s">
         <v>34</v>
@@ -10108,7 +10108,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -10131,7 +10131,7 @@
         <v>27</v>
       </c>
       <c r="E67">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F67" t="s">
         <v>31</v>
@@ -10154,7 +10154,7 @@
         <v>27</v>
       </c>
       <c r="E68">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
@@ -10177,7 +10177,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F69" t="s">
         <v>34</v>
@@ -10200,7 +10200,7 @@
         <v>27</v>
       </c>
       <c r="E70">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -10223,7 +10223,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F71" t="s">
         <v>31</v>
@@ -10246,7 +10246,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -10269,7 +10269,7 @@
         <v>27</v>
       </c>
       <c r="E73">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F73" t="s">
         <v>34</v>
@@ -10292,7 +10292,7 @@
         <v>27</v>
       </c>
       <c r="E74">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -10315,7 +10315,7 @@
         <v>27</v>
       </c>
       <c r="E75">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F75" t="s">
         <v>31</v>
@@ -10338,7 +10338,7 @@
         <v>27</v>
       </c>
       <c r="E76">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
@@ -10361,7 +10361,7 @@
         <v>27</v>
       </c>
       <c r="E77">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F77" t="s">
         <v>34</v>
@@ -10384,7 +10384,7 @@
         <v>27</v>
       </c>
       <c r="E78">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
@@ -10407,7 +10407,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F79" t="s">
         <v>31</v>
@@ -10430,7 +10430,7 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
@@ -10453,7 +10453,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F81" t="s">
         <v>34</v>
@@ -10476,7 +10476,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -10499,7 +10499,7 @@
         <v>27</v>
       </c>
       <c r="E83">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F83" t="s">
         <v>31</v>
@@ -10522,7 +10522,7 @@
         <v>27</v>
       </c>
       <c r="E84">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
@@ -10545,7 +10545,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F85" t="s">
         <v>34</v>
@@ -10568,7 +10568,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -10591,7 +10591,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F87" t="s">
         <v>31</v>
@@ -10614,7 +10614,7 @@
         <v>27</v>
       </c>
       <c r="E88">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -10637,7 +10637,7 @@
         <v>27</v>
       </c>
       <c r="E89">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F89" t="s">
         <v>34</v>
@@ -10660,7 +10660,7 @@
         <v>27</v>
       </c>
       <c r="E90">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F90" t="s">
         <v>28</v>
@@ -10683,7 +10683,7 @@
         <v>27</v>
       </c>
       <c r="E91">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F91" t="s">
         <v>31</v>
@@ -10729,7 +10729,7 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F93" t="s">
         <v>31</v>
@@ -10752,7 +10752,7 @@
         <v>27</v>
       </c>
       <c r="E94">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -10775,7 +10775,7 @@
         <v>27</v>
       </c>
       <c r="E95">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F95" t="s">
         <v>34</v>
@@ -10798,7 +10798,7 @@
         <v>27</v>
       </c>
       <c r="E96">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -10821,7 +10821,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F97" t="s">
         <v>31</v>
@@ -10844,7 +10844,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -10867,7 +10867,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F99" t="s">
         <v>34</v>
@@ -10890,7 +10890,7 @@
         <v>27</v>
       </c>
       <c r="E100">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
@@ -10913,7 +10913,7 @@
         <v>27</v>
       </c>
       <c r="E101">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F101" t="s">
         <v>31</v>
@@ -10936,7 +10936,7 @@
         <v>27</v>
       </c>
       <c r="E102">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
@@ -10959,7 +10959,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F103" t="s">
         <v>34</v>
@@ -10982,7 +10982,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -11005,7 +11005,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F105" t="s">
         <v>31</v>
@@ -11028,7 +11028,7 @@
         <v>27</v>
       </c>
       <c r="E106">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
@@ -11051,7 +11051,7 @@
         <v>27</v>
       </c>
       <c r="E107">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F107" t="s">
         <v>34</v>
@@ -11074,7 +11074,7 @@
         <v>27</v>
       </c>
       <c r="E108">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
@@ -11097,7 +11097,7 @@
         <v>27</v>
       </c>
       <c r="E109">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F109" t="s">
         <v>31</v>
@@ -11120,7 +11120,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -11143,7 +11143,7 @@
         <v>27</v>
       </c>
       <c r="E111">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F111" t="s">
         <v>34</v>
@@ -11166,7 +11166,7 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F112" t="s">
         <v>28</v>
@@ -11189,7 +11189,7 @@
         <v>27</v>
       </c>
       <c r="E113">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F113" t="s">
         <v>31</v>
@@ -11212,7 +11212,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -11235,7 +11235,7 @@
         <v>27</v>
       </c>
       <c r="E115">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F115" t="s">
         <v>34</v>
@@ -11258,7 +11258,7 @@
         <v>27</v>
       </c>
       <c r="E116">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F116" t="s">
         <v>28</v>
@@ -11281,7 +11281,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F117" t="s">
         <v>31</v>
@@ -11304,7 +11304,7 @@
         <v>27</v>
       </c>
       <c r="E118">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F118" t="s">
         <v>28</v>
@@ -11327,7 +11327,7 @@
         <v>27</v>
       </c>
       <c r="E119">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F119" t="s">
         <v>34</v>
@@ -11350,7 +11350,7 @@
         <v>27</v>
       </c>
       <c r="E120">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
@@ -11373,7 +11373,7 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F121" t="s">
         <v>31</v>
@@ -11396,7 +11396,7 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -11419,7 +11419,7 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F123" t="s">
         <v>31</v>
@@ -11442,7 +11442,7 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F124" t="s">
         <v>28</v>
@@ -11465,7 +11465,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F125" t="s">
         <v>34</v>
@@ -11488,7 +11488,7 @@
         <v>27</v>
       </c>
       <c r="E126">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
@@ -11511,7 +11511,7 @@
         <v>27</v>
       </c>
       <c r="E127">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F127" t="s">
         <v>31</v>
@@ -11534,7 +11534,7 @@
         <v>27</v>
       </c>
       <c r="E128">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -11557,7 +11557,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F129" t="s">
         <v>34</v>
@@ -11580,7 +11580,7 @@
         <v>27</v>
       </c>
       <c r="E130">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
@@ -11603,7 +11603,7 @@
         <v>27</v>
       </c>
       <c r="E131">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F131" t="s">
         <v>31</v>
@@ -11626,7 +11626,7 @@
         <v>27</v>
       </c>
       <c r="E132">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F132" t="s">
         <v>28</v>
@@ -11649,7 +11649,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F133" t="s">
         <v>34</v>
@@ -11672,7 +11672,7 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -11695,7 +11695,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F135" t="s">
         <v>31</v>
@@ -11718,7 +11718,7 @@
         <v>27</v>
       </c>
       <c r="E136">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
@@ -11741,7 +11741,7 @@
         <v>27</v>
       </c>
       <c r="E137">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F137" t="s">
         <v>34</v>
@@ -11764,7 +11764,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -11787,7 +11787,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F139" t="s">
         <v>31</v>
@@ -11810,7 +11810,7 @@
         <v>27</v>
       </c>
       <c r="E140">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
@@ -11833,7 +11833,7 @@
         <v>27</v>
       </c>
       <c r="E141">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F141" t="s">
         <v>34</v>
@@ -11856,7 +11856,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -11879,7 +11879,7 @@
         <v>27</v>
       </c>
       <c r="E143">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F143" t="s">
         <v>31</v>
@@ -11902,7 +11902,7 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F144" t="s">
         <v>28</v>
@@ -11925,7 +11925,7 @@
         <v>27</v>
       </c>
       <c r="E145">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F145" t="s">
         <v>34</v>
@@ -11948,7 +11948,7 @@
         <v>27</v>
       </c>
       <c r="E146">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F146" t="s">
         <v>28</v>
@@ -11971,7 +11971,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F147" t="s">
         <v>31</v>
@@ -12017,7 +12017,7 @@
         <v>27</v>
       </c>
       <c r="E149">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F149" t="s">
         <v>34</v>
@@ -12040,7 +12040,7 @@
         <v>27</v>
       </c>
       <c r="E150">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
@@ -12063,7 +12063,7 @@
         <v>27</v>
       </c>
       <c r="E151">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F151" t="s">
         <v>31</v>
@@ -12086,7 +12086,7 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F152" t="s">
         <v>28</v>
@@ -12109,7 +12109,7 @@
         <v>27</v>
       </c>
       <c r="E153">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F153" t="s">
         <v>31</v>
@@ -12132,7 +12132,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -12155,7 +12155,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F155" t="s">
         <v>34</v>
@@ -12178,7 +12178,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -12201,7 +12201,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F157" t="s">
         <v>31</v>
@@ -12224,7 +12224,7 @@
         <v>27</v>
       </c>
       <c r="E158">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F158" t="s">
         <v>28</v>
@@ -12247,7 +12247,7 @@
         <v>27</v>
       </c>
       <c r="E159">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F159" t="s">
         <v>34</v>
@@ -12270,7 +12270,7 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F160" t="s">
         <v>28</v>
@@ -12293,7 +12293,7 @@
         <v>27</v>
       </c>
       <c r="E161">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F161" t="s">
         <v>31</v>
@@ -12316,7 +12316,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -12339,7 +12339,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F163" t="s">
         <v>34</v>
@@ -12362,7 +12362,7 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
@@ -12385,7 +12385,7 @@
         <v>27</v>
       </c>
       <c r="E165">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F165" t="s">
         <v>31</v>
@@ -12408,7 +12408,7 @@
         <v>27</v>
       </c>
       <c r="E166">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -12431,7 +12431,7 @@
         <v>27</v>
       </c>
       <c r="E167">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F167" t="s">
         <v>34</v>
@@ -12454,7 +12454,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -12477,7 +12477,7 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F169" t="s">
         <v>31</v>
@@ -12500,7 +12500,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -12523,7 +12523,7 @@
         <v>27</v>
       </c>
       <c r="E171">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F171" t="s">
         <v>34</v>
@@ -12546,7 +12546,7 @@
         <v>27</v>
       </c>
       <c r="E172">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
@@ -12569,7 +12569,7 @@
         <v>27</v>
       </c>
       <c r="E173">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F173" t="s">
         <v>31</v>
@@ -12592,7 +12592,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -12615,7 +12615,7 @@
         <v>27</v>
       </c>
       <c r="E175">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F175" t="s">
         <v>34</v>
@@ -12638,7 +12638,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -12661,7 +12661,7 @@
         <v>27</v>
       </c>
       <c r="E177">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
@@ -12684,7 +12684,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F178" t="s">
         <v>31</v>
@@ -12707,7 +12707,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -12730,7 +12730,7 @@
         <v>27</v>
       </c>
       <c r="E180">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F180" t="s">
         <v>34</v>
@@ -12753,7 +12753,7 @@
         <v>27</v>
       </c>
       <c r="E181">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F181" t="s">
         <v>28</v>
@@ -12776,7 +12776,7 @@
         <v>27</v>
       </c>
       <c r="E182">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F182" t="s">
         <v>31</v>
@@ -12799,7 +12799,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -12822,7 +12822,7 @@
         <v>27</v>
       </c>
       <c r="E184">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F184" t="s">
         <v>34</v>
@@ -12845,7 +12845,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -12868,7 +12868,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F186" t="s">
         <v>31</v>
@@ -12891,7 +12891,7 @@
         <v>27</v>
       </c>
       <c r="E187">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F187" t="s">
         <v>28</v>
@@ -12914,7 +12914,7 @@
         <v>27</v>
       </c>
       <c r="E188">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F188" t="s">
         <v>34</v>
@@ -12937,7 +12937,7 @@
         <v>27</v>
       </c>
       <c r="E189">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F189" t="s">
         <v>28</v>
@@ -12960,7 +12960,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F190" t="s">
         <v>31</v>
@@ -12983,7 +12983,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -13006,7 +13006,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F192" t="s">
         <v>34</v>
@@ -13029,7 +13029,7 @@
         <v>27</v>
       </c>
       <c r="E193">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -13052,7 +13052,7 @@
         <v>27</v>
       </c>
       <c r="E194">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F194" t="s">
         <v>31</v>
@@ -13075,7 +13075,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -13098,7 +13098,7 @@
         <v>27</v>
       </c>
       <c r="E196">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F196" t="s">
         <v>34</v>
@@ -13121,7 +13121,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -13144,7 +13144,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F198" t="s">
         <v>31</v>
@@ -13167,7 +13167,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -13190,7 +13190,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F200" t="s">
         <v>34</v>
@@ -13213,7 +13213,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -13236,7 +13236,7 @@
         <v>27</v>
       </c>
       <c r="E202">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -13259,7 +13259,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F203" t="s">
         <v>31</v>
@@ -13282,7 +13282,7 @@
         <v>27</v>
       </c>
       <c r="E204">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -13305,7 +13305,7 @@
         <v>27</v>
       </c>
       <c r="E205">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F205" t="s">
         <v>34</v>
@@ -13328,7 +13328,7 @@
         <v>27</v>
       </c>
       <c r="E206">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -13351,7 +13351,7 @@
         <v>27</v>
       </c>
       <c r="E207">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F207" t="s">
         <v>31</v>
@@ -13374,7 +13374,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -13397,7 +13397,7 @@
         <v>27</v>
       </c>
       <c r="E209">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F209" t="s">
         <v>34</v>
@@ -13420,7 +13420,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -13443,7 +13443,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F211" t="s">
         <v>31</v>
@@ -13466,7 +13466,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -13489,7 +13489,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F213" t="s">
         <v>34</v>
@@ -13512,7 +13512,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -13535,7 +13535,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F215" t="s">
         <v>31</v>
@@ -13558,7 +13558,7 @@
         <v>27</v>
       </c>
       <c r="E216">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F216" t="s">
         <v>28</v>
@@ -13581,7 +13581,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F217" t="s">
         <v>34</v>
@@ -13604,7 +13604,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -13627,7 +13627,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F219" t="s">
         <v>31</v>
@@ -13650,7 +13650,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -13673,7 +13673,7 @@
         <v>27</v>
       </c>
       <c r="E221">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F221" t="s">
         <v>34</v>
@@ -13696,7 +13696,7 @@
         <v>27</v>
       </c>
       <c r="E222">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F222" t="s">
         <v>28</v>
@@ -13719,7 +13719,7 @@
         <v>27</v>
       </c>
       <c r="E223">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F223" t="s">
         <v>31</v>
@@ -13742,7 +13742,7 @@
         <v>27</v>
       </c>
       <c r="E224">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F224" t="s">
         <v>28</v>
@@ -13765,7 +13765,7 @@
         <v>27</v>
       </c>
       <c r="E225">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F225" t="s">
         <v>34</v>
@@ -13788,7 +13788,7 @@
         <v>27</v>
       </c>
       <c r="E226">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F226" t="s">
         <v>28</v>
@@ -13811,7 +13811,7 @@
         <v>27</v>
       </c>
       <c r="E227">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F227" t="s">
         <v>28</v>
@@ -13834,7 +13834,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F228" t="s">
         <v>31</v>
@@ -13857,7 +13857,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -13880,7 +13880,7 @@
         <v>27</v>
       </c>
       <c r="E230">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F230" t="s">
         <v>34</v>
@@ -13903,7 +13903,7 @@
         <v>27</v>
       </c>
       <c r="E231">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F231" t="s">
         <v>28</v>
@@ -13926,7 +13926,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F232" t="s">
         <v>31</v>
@@ -13949,7 +13949,7 @@
         <v>27</v>
       </c>
       <c r="E233">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F233" t="s">
         <v>28</v>
@@ -13972,7 +13972,7 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F234" t="s">
         <v>34</v>
@@ -13995,7 +13995,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -14018,7 +14018,7 @@
         <v>27</v>
       </c>
       <c r="E236">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F236" t="s">
         <v>31</v>
@@ -14041,7 +14041,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -14064,7 +14064,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F238" t="s">
         <v>34</v>
@@ -14087,7 +14087,7 @@
         <v>27</v>
       </c>
       <c r="E239">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F239" t="s">
         <v>28</v>
@@ -14110,7 +14110,7 @@
         <v>27</v>
       </c>
       <c r="E240">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F240" t="s">
         <v>31</v>
@@ -14133,7 +14133,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -14156,7 +14156,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F242" t="s">
         <v>34</v>
@@ -14179,7 +14179,7 @@
         <v>27</v>
       </c>
       <c r="E243">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -14202,7 +14202,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F244" t="s">
         <v>31</v>
@@ -14225,7 +14225,7 @@
         <v>27</v>
       </c>
       <c r="E245">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F245" t="s">
         <v>28</v>
@@ -14248,7 +14248,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F246" t="s">
         <v>34</v>
@@ -14294,7 +14294,7 @@
         <v>27</v>
       </c>
       <c r="E248">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F248" t="s">
         <v>31</v>
@@ -14317,7 +14317,7 @@
         <v>27</v>
       </c>
       <c r="E249">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F249" t="s">
         <v>28</v>
@@ -14340,7 +14340,7 @@
         <v>27</v>
       </c>
       <c r="E250">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F250" t="s">
         <v>34</v>
@@ -14363,7 +14363,7 @@
         <v>27</v>
       </c>
       <c r="E251">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F251" t="s">
         <v>28</v>
@@ -14386,7 +14386,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -14409,7 +14409,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F253" t="s">
         <v>31</v>
@@ -14432,7 +14432,7 @@
         <v>27</v>
       </c>
       <c r="E254">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F254" t="s">
         <v>28</v>
@@ -14455,7 +14455,7 @@
         <v>27</v>
       </c>
       <c r="E255">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F255" t="s">
         <v>34</v>
@@ -14478,7 +14478,7 @@
         <v>27</v>
       </c>
       <c r="E256">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F256" t="s">
         <v>28</v>
@@ -14501,7 +14501,7 @@
         <v>27</v>
       </c>
       <c r="E257">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F257" t="s">
         <v>31</v>
@@ -14524,7 +14524,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -14547,7 +14547,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F259" t="s">
         <v>34</v>
@@ -14570,7 +14570,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -14593,7 +14593,7 @@
         <v>27</v>
       </c>
       <c r="E261">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F261" t="s">
         <v>31</v>
@@ -14616,7 +14616,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -14639,7 +14639,7 @@
         <v>27</v>
       </c>
       <c r="E263">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F263" t="s">
         <v>34</v>
@@ -14685,7 +14685,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F265" t="s">
         <v>31</v>
@@ -14708,7 +14708,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -14731,7 +14731,7 @@
         <v>27</v>
       </c>
       <c r="E267">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F267" t="s">
         <v>34</v>
@@ -14754,7 +14754,7 @@
         <v>27</v>
       </c>
       <c r="E268">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F268" t="s">
         <v>28</v>
@@ -14777,7 +14777,7 @@
         <v>27</v>
       </c>
       <c r="E269">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F269" t="s">
         <v>31</v>
@@ -14800,7 +14800,7 @@
         <v>27</v>
       </c>
       <c r="E270">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F270" t="s">
         <v>28</v>
@@ -14823,7 +14823,7 @@
         <v>27</v>
       </c>
       <c r="E271">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F271" t="s">
         <v>34</v>
@@ -14846,7 +14846,7 @@
         <v>27</v>
       </c>
       <c r="E272">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F272" t="s">
         <v>28</v>
@@ -14869,7 +14869,7 @@
         <v>27</v>
       </c>
       <c r="E273">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F273" t="s">
         <v>31</v>
@@ -14892,7 +14892,7 @@
         <v>27</v>
       </c>
       <c r="E274">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F274" t="s">
         <v>28</v>
@@ -14915,7 +14915,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F275" t="s">
         <v>34</v>
@@ -14938,7 +14938,7 @@
         <v>27</v>
       </c>
       <c r="E276">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F276" t="s">
         <v>28</v>
@@ -14961,7 +14961,7 @@
         <v>27</v>
       </c>
       <c r="E277">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F277" t="s">
         <v>28</v>
@@ -14984,7 +14984,7 @@
         <v>27</v>
       </c>
       <c r="E278">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F278" t="s">
         <v>31</v>
@@ -15007,7 +15007,7 @@
         <v>27</v>
       </c>
       <c r="E279">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -15030,7 +15030,7 @@
         <v>27</v>
       </c>
       <c r="E280">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F280" t="s">
         <v>34</v>
@@ -15053,7 +15053,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -15076,7 +15076,7 @@
         <v>27</v>
       </c>
       <c r="E282">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F282" t="s">
         <v>31</v>
@@ -15099,7 +15099,7 @@
         <v>27</v>
       </c>
       <c r="E283">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F283" t="s">
         <v>28</v>
@@ -15122,7 +15122,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F284" t="s">
         <v>34</v>
@@ -15145,7 +15145,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -15168,7 +15168,7 @@
         <v>27</v>
       </c>
       <c r="E286">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F286" t="s">
         <v>31</v>
@@ -15191,7 +15191,7 @@
         <v>27</v>
       </c>
       <c r="E287">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F287" t="s">
         <v>28</v>
@@ -15214,7 +15214,7 @@
         <v>27</v>
       </c>
       <c r="E288">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F288" t="s">
         <v>34</v>
@@ -15237,7 +15237,7 @@
         <v>27</v>
       </c>
       <c r="E289">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F289" t="s">
         <v>28</v>
@@ -15260,7 +15260,7 @@
         <v>27</v>
       </c>
       <c r="E290">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F290" t="s">
         <v>31</v>
@@ -15283,7 +15283,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -15306,7 +15306,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F292" t="s">
         <v>34</v>
@@ -15329,7 +15329,7 @@
         <v>27</v>
       </c>
       <c r="E293">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -15352,7 +15352,7 @@
         <v>27</v>
       </c>
       <c r="E294">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F294" t="s">
         <v>31</v>
@@ -15375,7 +15375,7 @@
         <v>27</v>
       </c>
       <c r="E295">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F295" t="s">
         <v>28</v>
@@ -15398,7 +15398,7 @@
         <v>27</v>
       </c>
       <c r="E296">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F296" t="s">
         <v>34</v>
@@ -15421,7 +15421,7 @@
         <v>27</v>
       </c>
       <c r="E297">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F297" t="s">
         <v>28</v>
@@ -15444,7 +15444,7 @@
         <v>27</v>
       </c>
       <c r="E298">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F298" t="s">
         <v>31</v>
@@ -15467,7 +15467,7 @@
         <v>27</v>
       </c>
       <c r="E299">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F299" t="s">
         <v>28</v>
@@ -15490,7 +15490,7 @@
         <v>27</v>
       </c>
       <c r="E300">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F300" t="s">
         <v>34</v>
@@ -15513,7 +15513,7 @@
         <v>27</v>
       </c>
       <c r="E301">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F301" t="s">
         <v>28</v>

--- a/all-test-reports/vulnerability/vulnerability_test_report.xlsx
+++ b/all-test-reports/vulnerability/vulnerability_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 11:37:59 am</t>
+    <t>28/7/2026, 11:40:42 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1694,7 +1694,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="10">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>28</v>
@@ -1717,7 +1717,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="10">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>31</v>
@@ -1740,7 +1740,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="10">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>28</v>
@@ -1763,7 +1763,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="10">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>34</v>
@@ -1786,7 +1786,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="10">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>28</v>
@@ -1809,7 +1809,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="10">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>31</v>
@@ -1832,7 +1832,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="10">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>28</v>
@@ -1855,7 +1855,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="10">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>34</v>
@@ -1878,7 +1878,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="10">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>28</v>
@@ -1901,7 +1901,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="10">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>31</v>
@@ -1924,7 +1924,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="10">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>28</v>
@@ -1947,7 +1947,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="10">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>34</v>
@@ -1970,7 +1970,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>28</v>
@@ -1993,7 +1993,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="10">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>31</v>
@@ -2016,7 +2016,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="10">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>28</v>
@@ -2062,7 +2062,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="10">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>28</v>
@@ -2085,7 +2085,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="10">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>31</v>
@@ -2108,7 +2108,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="10">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>28</v>
@@ -2131,7 +2131,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="10">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>34</v>
@@ -2154,7 +2154,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="10">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>28</v>
@@ -2177,7 +2177,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="10">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>31</v>
@@ -2200,7 +2200,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="10">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>28</v>
@@ -2223,7 +2223,7 @@
         <v>27</v>
       </c>
       <c r="E25" s="10">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>34</v>
@@ -2246,7 +2246,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="10">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>28</v>
@@ -2269,7 +2269,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="10">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>31</v>
@@ -2292,7 +2292,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="10">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>28</v>
@@ -2315,7 +2315,7 @@
         <v>27</v>
       </c>
       <c r="E29" s="10">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>34</v>
@@ -2361,7 +2361,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="10">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>31</v>
@@ -2384,7 +2384,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="10">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>28</v>
@@ -2407,7 +2407,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="10">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>31</v>
@@ -2430,7 +2430,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>28</v>
@@ -2453,7 +2453,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="10">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>34</v>
@@ -2499,7 +2499,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="10">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>31</v>
@@ -2545,7 +2545,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="10">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>34</v>
@@ -2568,7 +2568,7 @@
         <v>27</v>
       </c>
       <c r="E40" s="10">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>28</v>
@@ -2591,7 +2591,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="10">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>31</v>
@@ -2614,7 +2614,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="10">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>28</v>
@@ -2637,7 +2637,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="10">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>34</v>
@@ -2660,7 +2660,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="10">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>28</v>
@@ -2706,7 +2706,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="10">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>28</v>
@@ -2729,7 +2729,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="10">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>34</v>
@@ -2752,7 +2752,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="10">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>28</v>
@@ -2775,7 +2775,7 @@
         <v>27</v>
       </c>
       <c r="E49" s="10">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>31</v>
@@ -2798,7 +2798,7 @@
         <v>27</v>
       </c>
       <c r="E50" s="10">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>28</v>
@@ -2821,7 +2821,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="10">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>34</v>
@@ -2844,7 +2844,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="10">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>28</v>
@@ -2867,7 +2867,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="10">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>31</v>
@@ -2890,7 +2890,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="10">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>28</v>
@@ -2913,7 +2913,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="10">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>34</v>
@@ -2936,7 +2936,7 @@
         <v>27</v>
       </c>
       <c r="E56" s="10">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>28</v>
@@ -2959,7 +2959,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="10">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>31</v>
@@ -2982,7 +2982,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="10">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>28</v>
@@ -3005,7 +3005,7 @@
         <v>27</v>
       </c>
       <c r="E59" s="10">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>34</v>
@@ -3028,7 +3028,7 @@
         <v>27</v>
       </c>
       <c r="E60" s="10">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>28</v>
@@ -3051,7 +3051,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="10">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>31</v>
@@ -3074,7 +3074,7 @@
         <v>27</v>
       </c>
       <c r="E62" s="10">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>28</v>
@@ -3097,7 +3097,7 @@
         <v>27</v>
       </c>
       <c r="E63" s="10">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>31</v>
@@ -3120,7 +3120,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="10">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>28</v>
@@ -3143,7 +3143,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="10">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>34</v>
@@ -3166,7 +3166,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="10">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>28</v>
@@ -3189,7 +3189,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="10">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>31</v>
@@ -3212,7 +3212,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="10">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>28</v>
@@ -3235,7 +3235,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>34</v>
@@ -3258,7 +3258,7 @@
         <v>27</v>
       </c>
       <c r="E70" s="10">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>28</v>
@@ -3281,7 +3281,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="10">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>31</v>
@@ -3304,7 +3304,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="10">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>28</v>
@@ -3327,7 +3327,7 @@
         <v>27</v>
       </c>
       <c r="E73" s="10">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>34</v>
@@ -3350,7 +3350,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="10">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>28</v>
@@ -3373,7 +3373,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="10">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>31</v>
@@ -3396,7 +3396,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="10">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>28</v>
@@ -3419,7 +3419,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="10">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>34</v>
@@ -3442,7 +3442,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="10">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>28</v>
@@ -3465,7 +3465,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="10">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>31</v>
@@ -3488,7 +3488,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="10">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>28</v>
@@ -3511,7 +3511,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="10">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>34</v>
@@ -3534,7 +3534,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>28</v>
@@ -3557,7 +3557,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="10">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>31</v>
@@ -3603,7 +3603,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="10">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>34</v>
@@ -3626,7 +3626,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="10">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>28</v>
@@ -3649,7 +3649,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="10">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>31</v>
@@ -3672,7 +3672,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="10">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>28</v>
@@ -3695,7 +3695,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="10">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>34</v>
@@ -3741,7 +3741,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="10">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>31</v>
@@ -3764,7 +3764,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="10">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>28</v>
@@ -3787,7 +3787,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>31</v>
@@ -3810,7 +3810,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="10">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>28</v>
@@ -3833,7 +3833,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="10">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>34</v>
@@ -3856,7 +3856,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="10">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F96" s="8" t="s">
         <v>28</v>
@@ -3879,7 +3879,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="10">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>31</v>
@@ -3902,7 +3902,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="10">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>28</v>
@@ -3925,7 +3925,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="10">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>34</v>
@@ -3948,7 +3948,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="10">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>28</v>
@@ -3971,7 +3971,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="10">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>31</v>
@@ -3994,7 +3994,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="10">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>28</v>
@@ -4017,7 +4017,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="10">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>34</v>
@@ -4040,7 +4040,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="10">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>28</v>
@@ -4063,7 +4063,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="10">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>31</v>
@@ -4086,7 +4086,7 @@
         <v>27</v>
       </c>
       <c r="E106" s="10">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>28</v>
@@ -4109,7 +4109,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="10">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>34</v>
@@ -4132,7 +4132,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="10">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>28</v>
@@ -4155,7 +4155,7 @@
         <v>27</v>
       </c>
       <c r="E109" s="10">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>31</v>
@@ -4178,7 +4178,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="10">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>28</v>
@@ -4201,7 +4201,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="10">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>34</v>
@@ -4224,7 +4224,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="10">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>28</v>
@@ -4247,7 +4247,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F113" s="8" t="s">
         <v>31</v>
@@ -4270,7 +4270,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="10">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>28</v>
@@ -4293,7 +4293,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="10">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>34</v>
@@ -4316,7 +4316,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="10">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>28</v>
@@ -4339,7 +4339,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="10">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F117" s="8" t="s">
         <v>31</v>
@@ -4362,7 +4362,7 @@
         <v>27</v>
       </c>
       <c r="E118" s="10">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F118" s="8" t="s">
         <v>28</v>
@@ -4385,7 +4385,7 @@
         <v>27</v>
       </c>
       <c r="E119" s="10">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F119" s="8" t="s">
         <v>34</v>
@@ -4408,7 +4408,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="10">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F120" s="8" t="s">
         <v>28</v>
@@ -4454,7 +4454,7 @@
         <v>27</v>
       </c>
       <c r="E122" s="10">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F122" s="8" t="s">
         <v>28</v>
@@ -4477,7 +4477,7 @@
         <v>27</v>
       </c>
       <c r="E123" s="10">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>31</v>
@@ -4523,7 +4523,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="10">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>34</v>
@@ -4546,7 +4546,7 @@
         <v>27</v>
       </c>
       <c r="E126" s="10">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F126" s="8" t="s">
         <v>28</v>
@@ -4569,7 +4569,7 @@
         <v>27</v>
       </c>
       <c r="E127" s="10">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F127" s="8" t="s">
         <v>31</v>
@@ -4592,7 +4592,7 @@
         <v>27</v>
       </c>
       <c r="E128" s="10">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F128" s="8" t="s">
         <v>28</v>
@@ -4615,7 +4615,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="10">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F129" s="8" t="s">
         <v>34</v>
@@ -4638,7 +4638,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="10">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F130" s="8" t="s">
         <v>28</v>
@@ -4661,7 +4661,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="10">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F131" s="8" t="s">
         <v>31</v>
@@ -4684,7 +4684,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="10">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F132" s="8" t="s">
         <v>28</v>
@@ -4707,7 +4707,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="10">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F133" s="8" t="s">
         <v>34</v>
@@ -4730,7 +4730,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="10">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F134" s="8" t="s">
         <v>28</v>
@@ -4753,7 +4753,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="10">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F135" s="8" t="s">
         <v>31</v>
@@ -4776,7 +4776,7 @@
         <v>27</v>
       </c>
       <c r="E136" s="10">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F136" s="8" t="s">
         <v>28</v>
@@ -4799,7 +4799,7 @@
         <v>27</v>
       </c>
       <c r="E137" s="10">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F137" s="8" t="s">
         <v>34</v>
@@ -4822,7 +4822,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="10">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F138" s="8" t="s">
         <v>28</v>
@@ -4845,7 +4845,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="10">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F139" s="8" t="s">
         <v>31</v>
@@ -4868,7 +4868,7 @@
         <v>27</v>
       </c>
       <c r="E140" s="10">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F140" s="8" t="s">
         <v>28</v>
@@ -4891,7 +4891,7 @@
         <v>27</v>
       </c>
       <c r="E141" s="10">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F141" s="8" t="s">
         <v>34</v>
@@ -4914,7 +4914,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="10">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F142" s="8" t="s">
         <v>28</v>
@@ -4937,7 +4937,7 @@
         <v>27</v>
       </c>
       <c r="E143" s="10">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F143" s="8" t="s">
         <v>31</v>
@@ -4960,7 +4960,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="10">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F144" s="8" t="s">
         <v>28</v>
@@ -4983,7 +4983,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="10">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F145" s="8" t="s">
         <v>34</v>
@@ -5006,7 +5006,7 @@
         <v>27</v>
       </c>
       <c r="E146" s="10">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>28</v>
@@ -5029,7 +5029,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="10">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F147" s="8" t="s">
         <v>31</v>
@@ -5052,7 +5052,7 @@
         <v>27</v>
       </c>
       <c r="E148" s="10">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F148" s="8" t="s">
         <v>28</v>
@@ -5075,7 +5075,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="10">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F149" s="8" t="s">
         <v>34</v>
@@ -5098,7 +5098,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="10">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>28</v>
@@ -5121,7 +5121,7 @@
         <v>27</v>
       </c>
       <c r="E151" s="10">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>31</v>
@@ -5144,7 +5144,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="10">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>28</v>
@@ -5167,7 +5167,7 @@
         <v>27</v>
       </c>
       <c r="E153" s="10">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F153" s="8" t="s">
         <v>31</v>
@@ -5190,7 +5190,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="10">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>28</v>
@@ -5213,7 +5213,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F155" s="8" t="s">
         <v>34</v>
@@ -5236,7 +5236,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="10">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F156" s="8" t="s">
         <v>28</v>
@@ -5259,7 +5259,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="10">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F157" s="8" t="s">
         <v>31</v>
@@ -5282,7 +5282,7 @@
         <v>27</v>
       </c>
       <c r="E158" s="10">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F158" s="8" t="s">
         <v>28</v>
@@ -5305,7 +5305,7 @@
         <v>27</v>
       </c>
       <c r="E159" s="10">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F159" s="8" t="s">
         <v>34</v>
@@ -5328,7 +5328,7 @@
         <v>27</v>
       </c>
       <c r="E160" s="10">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F160" s="8" t="s">
         <v>28</v>
@@ -5351,7 +5351,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="10">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F161" s="8" t="s">
         <v>31</v>
@@ -5374,7 +5374,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="10">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F162" s="8" t="s">
         <v>28</v>
@@ -5397,7 +5397,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="10">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F163" s="8" t="s">
         <v>34</v>
@@ -5420,7 +5420,7 @@
         <v>27</v>
       </c>
       <c r="E164" s="10">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F164" s="8" t="s">
         <v>28</v>
@@ -5443,7 +5443,7 @@
         <v>27</v>
       </c>
       <c r="E165" s="10">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F165" s="8" t="s">
         <v>31</v>
@@ -5466,7 +5466,7 @@
         <v>27</v>
       </c>
       <c r="E166" s="10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F166" s="8" t="s">
         <v>28</v>
@@ -5489,7 +5489,7 @@
         <v>27</v>
       </c>
       <c r="E167" s="10">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F167" s="8" t="s">
         <v>34</v>
@@ -5512,7 +5512,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="10">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F168" s="8" t="s">
         <v>28</v>
@@ -5535,7 +5535,7 @@
         <v>27</v>
       </c>
       <c r="E169" s="10">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F169" s="8" t="s">
         <v>31</v>
@@ -5558,7 +5558,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="10">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F170" s="8" t="s">
         <v>28</v>
@@ -5581,7 +5581,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="10">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F171" s="8" t="s">
         <v>34</v>
@@ -5604,7 +5604,7 @@
         <v>27</v>
       </c>
       <c r="E172" s="10">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F172" s="8" t="s">
         <v>28</v>
@@ -5627,7 +5627,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="10">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F173" s="8" t="s">
         <v>31</v>
@@ -5650,7 +5650,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="10">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F174" s="8" t="s">
         <v>28</v>
@@ -5673,7 +5673,7 @@
         <v>27</v>
       </c>
       <c r="E175" s="10">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F175" s="8" t="s">
         <v>34</v>
@@ -5696,7 +5696,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="10">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F176" s="8" t="s">
         <v>28</v>
@@ -5719,7 +5719,7 @@
         <v>27</v>
       </c>
       <c r="E177" s="10">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F177" s="8" t="s">
         <v>28</v>
@@ -5742,7 +5742,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="10">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F178" s="8" t="s">
         <v>31</v>
@@ -5765,7 +5765,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="10">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F179" s="8" t="s">
         <v>28</v>
@@ -5788,7 +5788,7 @@
         <v>27</v>
       </c>
       <c r="E180" s="10">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F180" s="8" t="s">
         <v>34</v>
@@ -5811,7 +5811,7 @@
         <v>27</v>
       </c>
       <c r="E181" s="10">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F181" s="8" t="s">
         <v>28</v>
@@ -5834,7 +5834,7 @@
         <v>27</v>
       </c>
       <c r="E182" s="10">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F182" s="8" t="s">
         <v>31</v>
@@ -5857,7 +5857,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="10">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F183" s="8" t="s">
         <v>28</v>
@@ -5880,7 +5880,7 @@
         <v>27</v>
       </c>
       <c r="E184" s="10">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F184" s="8" t="s">
         <v>34</v>
@@ -5903,7 +5903,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="10">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F185" s="8" t="s">
         <v>28</v>
@@ -5926,7 +5926,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="10">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F186" s="8" t="s">
         <v>31</v>
@@ -5949,7 +5949,7 @@
         <v>27</v>
       </c>
       <c r="E187" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F187" s="8" t="s">
         <v>28</v>
@@ -5972,7 +5972,7 @@
         <v>27</v>
       </c>
       <c r="E188" s="10">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F188" s="8" t="s">
         <v>34</v>
@@ -5995,7 +5995,7 @@
         <v>27</v>
       </c>
       <c r="E189" s="10">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F189" s="8" t="s">
         <v>28</v>
@@ -6018,7 +6018,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="10">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F190" s="8" t="s">
         <v>31</v>
@@ -6041,7 +6041,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="10">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F191" s="8" t="s">
         <v>28</v>
@@ -6064,7 +6064,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="10">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F192" s="8" t="s">
         <v>34</v>
@@ -6087,7 +6087,7 @@
         <v>27</v>
       </c>
       <c r="E193" s="10">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F193" s="8" t="s">
         <v>28</v>
@@ -6110,7 +6110,7 @@
         <v>27</v>
       </c>
       <c r="E194" s="10">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F194" s="8" t="s">
         <v>31</v>
@@ -6133,7 +6133,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="10">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F195" s="8" t="s">
         <v>28</v>
@@ -6156,7 +6156,7 @@
         <v>27</v>
       </c>
       <c r="E196" s="10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F196" s="8" t="s">
         <v>34</v>
@@ -6179,7 +6179,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="10">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F197" s="8" t="s">
         <v>28</v>
@@ -6202,7 +6202,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="10">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F198" s="8" t="s">
         <v>31</v>
@@ -6225,7 +6225,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="10">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F199" s="8" t="s">
         <v>28</v>
@@ -6248,7 +6248,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="10">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F200" s="8" t="s">
         <v>34</v>
@@ -6271,7 +6271,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="10">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F201" s="8" t="s">
         <v>28</v>
@@ -6294,7 +6294,7 @@
         <v>27</v>
       </c>
       <c r="E202" s="10">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F202" s="8" t="s">
         <v>28</v>
@@ -6317,7 +6317,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="10">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F203" s="8" t="s">
         <v>31</v>
@@ -6340,7 +6340,7 @@
         <v>27</v>
       </c>
       <c r="E204" s="10">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F204" s="8" t="s">
         <v>28</v>
@@ -6363,7 +6363,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="10">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F205" s="8" t="s">
         <v>34</v>
@@ -6386,7 +6386,7 @@
         <v>27</v>
       </c>
       <c r="E206" s="10">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F206" s="8" t="s">
         <v>28</v>
@@ -6409,7 +6409,7 @@
         <v>27</v>
       </c>
       <c r="E207" s="10">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F207" s="8" t="s">
         <v>31</v>
@@ -6432,7 +6432,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="10">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F208" s="8" t="s">
         <v>28</v>
@@ -6455,7 +6455,7 @@
         <v>27</v>
       </c>
       <c r="E209" s="10">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F209" s="8" t="s">
         <v>34</v>
@@ -6478,7 +6478,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="10">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F210" s="8" t="s">
         <v>28</v>
@@ -6501,7 +6501,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="10">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F211" s="8" t="s">
         <v>31</v>
@@ -6524,7 +6524,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="10">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F212" s="8" t="s">
         <v>28</v>
@@ -6547,7 +6547,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="10">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F213" s="8" t="s">
         <v>34</v>
@@ -6570,7 +6570,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="10">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F214" s="8" t="s">
         <v>28</v>
@@ -6593,7 +6593,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="10">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F215" s="8" t="s">
         <v>31</v>
@@ -6616,7 +6616,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="10">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F216" s="8" t="s">
         <v>28</v>
@@ -6639,7 +6639,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="10">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F217" s="8" t="s">
         <v>34</v>
@@ -6662,7 +6662,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="10">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F218" s="8" t="s">
         <v>28</v>
@@ -6685,7 +6685,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="10">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F219" s="8" t="s">
         <v>31</v>
@@ -6708,7 +6708,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="10">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F220" s="8" t="s">
         <v>28</v>
@@ -6731,7 +6731,7 @@
         <v>27</v>
       </c>
       <c r="E221" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F221" s="8" t="s">
         <v>34</v>
@@ -6754,7 +6754,7 @@
         <v>27</v>
       </c>
       <c r="E222" s="10">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F222" s="8" t="s">
         <v>28</v>
@@ -6777,7 +6777,7 @@
         <v>27</v>
       </c>
       <c r="E223" s="10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F223" s="8" t="s">
         <v>31</v>
@@ -6823,7 +6823,7 @@
         <v>27</v>
       </c>
       <c r="E225" s="10">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F225" s="8" t="s">
         <v>34</v>
@@ -6846,7 +6846,7 @@
         <v>27</v>
       </c>
       <c r="E226" s="10">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F226" s="8" t="s">
         <v>28</v>
@@ -6869,7 +6869,7 @@
         <v>27</v>
       </c>
       <c r="E227" s="10">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F227" s="8" t="s">
         <v>28</v>
@@ -6892,7 +6892,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="10">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F228" s="8" t="s">
         <v>31</v>
@@ -6915,7 +6915,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="10">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F229" s="8" t="s">
         <v>28</v>
@@ -6938,7 +6938,7 @@
         <v>27</v>
       </c>
       <c r="E230" s="10">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F230" s="8" t="s">
         <v>34</v>
@@ -6961,7 +6961,7 @@
         <v>27</v>
       </c>
       <c r="E231" s="10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F231" s="8" t="s">
         <v>28</v>
@@ -6984,7 +6984,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="10">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F232" s="8" t="s">
         <v>31</v>
@@ -7007,7 +7007,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="10">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F233" s="8" t="s">
         <v>28</v>
@@ -7030,7 +7030,7 @@
         <v>27</v>
       </c>
       <c r="E234" s="10">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F234" s="8" t="s">
         <v>34</v>
@@ -7053,7 +7053,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="10">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F235" s="8" t="s">
         <v>28</v>
@@ -7076,7 +7076,7 @@
         <v>27</v>
       </c>
       <c r="E236" s="10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F236" s="8" t="s">
         <v>31</v>
@@ -7099,7 +7099,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="10">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F237" s="8" t="s">
         <v>28</v>
@@ -7122,7 +7122,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="10">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F238" s="8" t="s">
         <v>34</v>
@@ -7145,7 +7145,7 @@
         <v>27</v>
       </c>
       <c r="E239" s="10">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F239" s="8" t="s">
         <v>28</v>
@@ -7168,7 +7168,7 @@
         <v>27</v>
       </c>
       <c r="E240" s="10">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F240" s="8" t="s">
         <v>31</v>
@@ -7191,7 +7191,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F241" s="8" t="s">
         <v>28</v>
@@ -7214,7 +7214,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="10">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F242" s="8" t="s">
         <v>34</v>
@@ -7237,7 +7237,7 @@
         <v>27</v>
       </c>
       <c r="E243" s="10">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F243" s="8" t="s">
         <v>28</v>
@@ -7260,7 +7260,7 @@
         <v>27</v>
       </c>
       <c r="E244" s="10">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F244" s="8" t="s">
         <v>31</v>
@@ -7283,7 +7283,7 @@
         <v>27</v>
       </c>
       <c r="E245" s="10">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F245" s="8" t="s">
         <v>28</v>
@@ -7306,7 +7306,7 @@
         <v>27</v>
       </c>
       <c r="E246" s="10">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F246" s="8" t="s">
         <v>34</v>
@@ -7329,7 +7329,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="10">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F247" s="8" t="s">
         <v>28</v>
@@ -7352,7 +7352,7 @@
         <v>27</v>
       </c>
       <c r="E248" s="10">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F248" s="8" t="s">
         <v>31</v>
@@ -7375,7 +7375,7 @@
         <v>27</v>
       </c>
       <c r="E249" s="10">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F249" s="8" t="s">
         <v>28</v>
@@ -7398,7 +7398,7 @@
         <v>27</v>
       </c>
       <c r="E250" s="10">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F250" s="8" t="s">
         <v>34</v>
@@ -7421,7 +7421,7 @@
         <v>27</v>
       </c>
       <c r="E251" s="10">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F251" s="8" t="s">
         <v>28</v>
@@ -7444,7 +7444,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="10">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F252" s="8" t="s">
         <v>28</v>
@@ -7467,7 +7467,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="10">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F253" s="8" t="s">
         <v>31</v>
@@ -7490,7 +7490,7 @@
         <v>27</v>
       </c>
       <c r="E254" s="10">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F254" s="8" t="s">
         <v>28</v>
@@ -7513,7 +7513,7 @@
         <v>27</v>
       </c>
       <c r="E255" s="10">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F255" s="8" t="s">
         <v>34</v>
@@ -7536,7 +7536,7 @@
         <v>27</v>
       </c>
       <c r="E256" s="10">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F256" s="8" t="s">
         <v>28</v>
@@ -7559,7 +7559,7 @@
         <v>27</v>
       </c>
       <c r="E257" s="10">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F257" s="8" t="s">
         <v>31</v>
@@ -7582,7 +7582,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="10">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F258" s="8" t="s">
         <v>28</v>
@@ -7605,7 +7605,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="10">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F259" s="8" t="s">
         <v>34</v>
@@ -7628,7 +7628,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="10">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F260" s="8" t="s">
         <v>28</v>
@@ -7651,7 +7651,7 @@
         <v>27</v>
       </c>
       <c r="E261" s="10">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F261" s="8" t="s">
         <v>31</v>
@@ -7674,7 +7674,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="10">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F262" s="8" t="s">
         <v>28</v>
@@ -7697,7 +7697,7 @@
         <v>27</v>
       </c>
       <c r="E263" s="10">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F263" s="8" t="s">
         <v>34</v>
@@ -7720,7 +7720,7 @@
         <v>27</v>
       </c>
       <c r="E264" s="10">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F264" s="8" t="s">
         <v>28</v>
@@ -7743,7 +7743,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="10">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F265" s="8" t="s">
         <v>31</v>
@@ -7766,7 +7766,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="10">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F266" s="8" t="s">
         <v>28</v>
@@ -7789,7 +7789,7 @@
         <v>27</v>
       </c>
       <c r="E267" s="10">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F267" s="8" t="s">
         <v>34</v>
@@ -7812,7 +7812,7 @@
         <v>27</v>
       </c>
       <c r="E268" s="10">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F268" s="8" t="s">
         <v>28</v>
@@ -7835,7 +7835,7 @@
         <v>27</v>
       </c>
       <c r="E269" s="10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F269" s="8" t="s">
         <v>31</v>
@@ -7858,7 +7858,7 @@
         <v>27</v>
       </c>
       <c r="E270" s="10">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F270" s="8" t="s">
         <v>28</v>
@@ -7881,7 +7881,7 @@
         <v>27</v>
       </c>
       <c r="E271" s="10">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F271" s="8" t="s">
         <v>34</v>
@@ -7904,7 +7904,7 @@
         <v>27</v>
       </c>
       <c r="E272" s="10">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F272" s="8" t="s">
         <v>28</v>
@@ -7927,7 +7927,7 @@
         <v>27</v>
       </c>
       <c r="E273" s="10">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F273" s="8" t="s">
         <v>31</v>
@@ -7950,7 +7950,7 @@
         <v>27</v>
       </c>
       <c r="E274" s="10">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F274" s="8" t="s">
         <v>28</v>
@@ -7973,7 +7973,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="10">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F275" s="8" t="s">
         <v>34</v>
@@ -7996,7 +7996,7 @@
         <v>27</v>
       </c>
       <c r="E276" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F276" s="8" t="s">
         <v>28</v>
@@ -8019,7 +8019,7 @@
         <v>27</v>
       </c>
       <c r="E277" s="10">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F277" s="8" t="s">
         <v>28</v>
@@ -8042,7 +8042,7 @@
         <v>27</v>
       </c>
       <c r="E278" s="10">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F278" s="8" t="s">
         <v>31</v>
@@ -8065,7 +8065,7 @@
         <v>27</v>
       </c>
       <c r="E279" s="10">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F279" s="8" t="s">
         <v>28</v>
@@ -8088,7 +8088,7 @@
         <v>27</v>
       </c>
       <c r="E280" s="10">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F280" s="8" t="s">
         <v>34</v>
@@ -8111,7 +8111,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="10">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F281" s="8" t="s">
         <v>28</v>
@@ -8134,7 +8134,7 @@
         <v>27</v>
       </c>
       <c r="E282" s="10">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F282" s="8" t="s">
         <v>31</v>
@@ -8157,7 +8157,7 @@
         <v>27</v>
       </c>
       <c r="E283" s="10">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F283" s="8" t="s">
         <v>28</v>
@@ -8180,7 +8180,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="10">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F284" s="8" t="s">
         <v>34</v>
@@ -8203,7 +8203,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="10">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F285" s="8" t="s">
         <v>28</v>
@@ -8226,7 +8226,7 @@
         <v>27</v>
       </c>
       <c r="E286" s="10">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F286" s="8" t="s">
         <v>31</v>
@@ -8249,7 +8249,7 @@
         <v>27</v>
       </c>
       <c r="E287" s="10">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F287" s="8" t="s">
         <v>28</v>
@@ -8272,7 +8272,7 @@
         <v>27</v>
       </c>
       <c r="E288" s="10">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F288" s="8" t="s">
         <v>34</v>
@@ -8295,7 +8295,7 @@
         <v>27</v>
       </c>
       <c r="E289" s="10">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F289" s="8" t="s">
         <v>28</v>
@@ -8318,7 +8318,7 @@
         <v>27</v>
       </c>
       <c r="E290" s="10">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F290" s="8" t="s">
         <v>31</v>
@@ -8341,7 +8341,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="10">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F291" s="8" t="s">
         <v>28</v>
@@ -8364,7 +8364,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="10">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F292" s="8" t="s">
         <v>34</v>
@@ -8387,7 +8387,7 @@
         <v>27</v>
       </c>
       <c r="E293" s="10">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F293" s="8" t="s">
         <v>28</v>
@@ -8410,7 +8410,7 @@
         <v>27</v>
       </c>
       <c r="E294" s="10">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F294" s="8" t="s">
         <v>31</v>
@@ -8433,7 +8433,7 @@
         <v>27</v>
       </c>
       <c r="E295" s="10">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F295" s="8" t="s">
         <v>28</v>
@@ -8456,7 +8456,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="10">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F296" s="8" t="s">
         <v>34</v>
@@ -8479,7 +8479,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="10">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F297" s="8" t="s">
         <v>28</v>
@@ -8502,7 +8502,7 @@
         <v>27</v>
       </c>
       <c r="E298" s="10">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F298" s="8" t="s">
         <v>31</v>
@@ -8525,7 +8525,7 @@
         <v>27</v>
       </c>
       <c r="E299" s="10">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F299" s="8" t="s">
         <v>28</v>
@@ -8548,7 +8548,7 @@
         <v>27</v>
       </c>
       <c r="E300" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F300" s="8" t="s">
         <v>34</v>
@@ -8571,7 +8571,7 @@
         <v>27</v>
       </c>
       <c r="E301" s="10">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F301" s="8" t="s">
         <v>28</v>
@@ -8636,7 +8636,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -8659,7 +8659,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
         <v>31</v>
@@ -8682,7 +8682,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -8705,7 +8705,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
         <v>34</v>
@@ -8728,7 +8728,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -8751,7 +8751,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
         <v>31</v>
@@ -8774,7 +8774,7 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -8797,7 +8797,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
@@ -8820,7 +8820,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -8843,7 +8843,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F11" t="s">
         <v>31</v>
@@ -8866,7 +8866,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -8889,7 +8889,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s">
         <v>34</v>
@@ -8912,7 +8912,7 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -8935,7 +8935,7 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s">
         <v>31</v>
@@ -8958,7 +8958,7 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -9004,7 +9004,7 @@
         <v>27</v>
       </c>
       <c r="E18">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -9027,7 +9027,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F19" t="s">
         <v>31</v>
@@ -9050,7 +9050,7 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -9073,7 +9073,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F21" t="s">
         <v>34</v>
@@ -9096,7 +9096,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -9119,7 +9119,7 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F23" t="s">
         <v>31</v>
@@ -9142,7 +9142,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -9165,7 +9165,7 @@
         <v>27</v>
       </c>
       <c r="E25">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F25" t="s">
         <v>34</v>
@@ -9188,7 +9188,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -9211,7 +9211,7 @@
         <v>27</v>
       </c>
       <c r="E27">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F27" t="s">
         <v>31</v>
@@ -9234,7 +9234,7 @@
         <v>27</v>
       </c>
       <c r="E28">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -9257,7 +9257,7 @@
         <v>27</v>
       </c>
       <c r="E29">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F29" t="s">
         <v>34</v>
@@ -9303,7 +9303,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F31" t="s">
         <v>31</v>
@@ -9326,7 +9326,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -9349,7 +9349,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F33" t="s">
         <v>31</v>
@@ -9372,7 +9372,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -9395,7 +9395,7 @@
         <v>27</v>
       </c>
       <c r="E35">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
@@ -9441,7 +9441,7 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F37" t="s">
         <v>31</v>
@@ -9487,7 +9487,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F39" t="s">
         <v>34</v>
@@ -9510,7 +9510,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -9533,7 +9533,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F41" t="s">
         <v>31</v>
@@ -9556,7 +9556,7 @@
         <v>27</v>
       </c>
       <c r="E42">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -9579,7 +9579,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F43" t="s">
         <v>34</v>
@@ -9602,7 +9602,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -9648,7 +9648,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -9671,7 +9671,7 @@
         <v>27</v>
       </c>
       <c r="E47">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F47" t="s">
         <v>34</v>
@@ -9694,7 +9694,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -9717,7 +9717,7 @@
         <v>27</v>
       </c>
       <c r="E49">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F49" t="s">
         <v>31</v>
@@ -9740,7 +9740,7 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F50" t="s">
         <v>28</v>
@@ -9763,7 +9763,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F51" t="s">
         <v>34</v>
@@ -9786,7 +9786,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -9809,7 +9809,7 @@
         <v>27</v>
       </c>
       <c r="E53">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F53" t="s">
         <v>31</v>
@@ -9832,7 +9832,7 @@
         <v>27</v>
       </c>
       <c r="E54">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -9855,7 +9855,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F55" t="s">
         <v>34</v>
@@ -9878,7 +9878,7 @@
         <v>27</v>
       </c>
       <c r="E56">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -9901,7 +9901,7 @@
         <v>27</v>
       </c>
       <c r="E57">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F57" t="s">
         <v>31</v>
@@ -9924,7 +9924,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -9947,7 +9947,7 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F59" t="s">
         <v>34</v>
@@ -9970,7 +9970,7 @@
         <v>27</v>
       </c>
       <c r="E60">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -9993,7 +9993,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F61" t="s">
         <v>31</v>
@@ -10016,7 +10016,7 @@
         <v>27</v>
       </c>
       <c r="E62">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F62" t="s">
         <v>28</v>
@@ -10039,7 +10039,7 @@
         <v>27</v>
       </c>
       <c r="E63">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F63" t="s">
         <v>31</v>
@@ -10062,7 +10062,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -10085,7 +10085,7 @@
         <v>27</v>
       </c>
       <c r="E65">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F65" t="s">
         <v>34</v>
@@ -10108,7 +10108,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -10131,7 +10131,7 @@
         <v>27</v>
       </c>
       <c r="E67">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F67" t="s">
         <v>31</v>
@@ -10154,7 +10154,7 @@
         <v>27</v>
       </c>
       <c r="E68">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
@@ -10177,7 +10177,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F69" t="s">
         <v>34</v>
@@ -10200,7 +10200,7 @@
         <v>27</v>
       </c>
       <c r="E70">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -10223,7 +10223,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F71" t="s">
         <v>31</v>
@@ -10246,7 +10246,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -10269,7 +10269,7 @@
         <v>27</v>
       </c>
       <c r="E73">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F73" t="s">
         <v>34</v>
@@ -10292,7 +10292,7 @@
         <v>27</v>
       </c>
       <c r="E74">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -10315,7 +10315,7 @@
         <v>27</v>
       </c>
       <c r="E75">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F75" t="s">
         <v>31</v>
@@ -10338,7 +10338,7 @@
         <v>27</v>
       </c>
       <c r="E76">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
@@ -10361,7 +10361,7 @@
         <v>27</v>
       </c>
       <c r="E77">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F77" t="s">
         <v>34</v>
@@ -10384,7 +10384,7 @@
         <v>27</v>
       </c>
       <c r="E78">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
@@ -10407,7 +10407,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F79" t="s">
         <v>31</v>
@@ -10430,7 +10430,7 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
@@ -10453,7 +10453,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F81" t="s">
         <v>34</v>
@@ -10476,7 +10476,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -10499,7 +10499,7 @@
         <v>27</v>
       </c>
       <c r="E83">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F83" t="s">
         <v>31</v>
@@ -10545,7 +10545,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F85" t="s">
         <v>34</v>
@@ -10568,7 +10568,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -10591,7 +10591,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F87" t="s">
         <v>31</v>
@@ -10614,7 +10614,7 @@
         <v>27</v>
       </c>
       <c r="E88">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -10637,7 +10637,7 @@
         <v>27</v>
       </c>
       <c r="E89">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F89" t="s">
         <v>34</v>
@@ -10683,7 +10683,7 @@
         <v>27</v>
       </c>
       <c r="E91">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F91" t="s">
         <v>31</v>
@@ -10706,7 +10706,7 @@
         <v>27</v>
       </c>
       <c r="E92">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
@@ -10729,7 +10729,7 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F93" t="s">
         <v>31</v>
@@ -10752,7 +10752,7 @@
         <v>27</v>
       </c>
       <c r="E94">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -10775,7 +10775,7 @@
         <v>27</v>
       </c>
       <c r="E95">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F95" t="s">
         <v>34</v>
@@ -10798,7 +10798,7 @@
         <v>27</v>
       </c>
       <c r="E96">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -10821,7 +10821,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F97" t="s">
         <v>31</v>
@@ -10844,7 +10844,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -10867,7 +10867,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F99" t="s">
         <v>34</v>
@@ -10890,7 +10890,7 @@
         <v>27</v>
       </c>
       <c r="E100">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
@@ -10913,7 +10913,7 @@
         <v>27</v>
       </c>
       <c r="E101">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F101" t="s">
         <v>31</v>
@@ -10936,7 +10936,7 @@
         <v>27</v>
       </c>
       <c r="E102">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
@@ -10959,7 +10959,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F103" t="s">
         <v>34</v>
@@ -10982,7 +10982,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -11005,7 +11005,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F105" t="s">
         <v>31</v>
@@ -11028,7 +11028,7 @@
         <v>27</v>
       </c>
       <c r="E106">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
@@ -11051,7 +11051,7 @@
         <v>27</v>
       </c>
       <c r="E107">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F107" t="s">
         <v>34</v>
@@ -11074,7 +11074,7 @@
         <v>27</v>
       </c>
       <c r="E108">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
@@ -11097,7 +11097,7 @@
         <v>27</v>
       </c>
       <c r="E109">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F109" t="s">
         <v>31</v>
@@ -11120,7 +11120,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -11143,7 +11143,7 @@
         <v>27</v>
       </c>
       <c r="E111">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F111" t="s">
         <v>34</v>
@@ -11166,7 +11166,7 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F112" t="s">
         <v>28</v>
@@ -11189,7 +11189,7 @@
         <v>27</v>
       </c>
       <c r="E113">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F113" t="s">
         <v>31</v>
@@ -11212,7 +11212,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -11235,7 +11235,7 @@
         <v>27</v>
       </c>
       <c r="E115">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F115" t="s">
         <v>34</v>
@@ -11258,7 +11258,7 @@
         <v>27</v>
       </c>
       <c r="E116">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F116" t="s">
         <v>28</v>
@@ -11281,7 +11281,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F117" t="s">
         <v>31</v>
@@ -11304,7 +11304,7 @@
         <v>27</v>
       </c>
       <c r="E118">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F118" t="s">
         <v>28</v>
@@ -11327,7 +11327,7 @@
         <v>27</v>
       </c>
       <c r="E119">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F119" t="s">
         <v>34</v>
@@ -11350,7 +11350,7 @@
         <v>27</v>
       </c>
       <c r="E120">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
@@ -11396,7 +11396,7 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -11419,7 +11419,7 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F123" t="s">
         <v>31</v>
@@ -11465,7 +11465,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F125" t="s">
         <v>34</v>
@@ -11488,7 +11488,7 @@
         <v>27</v>
       </c>
       <c r="E126">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
@@ -11511,7 +11511,7 @@
         <v>27</v>
       </c>
       <c r="E127">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F127" t="s">
         <v>31</v>
@@ -11534,7 +11534,7 @@
         <v>27</v>
       </c>
       <c r="E128">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -11557,7 +11557,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F129" t="s">
         <v>34</v>
@@ -11580,7 +11580,7 @@
         <v>27</v>
       </c>
       <c r="E130">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
@@ -11603,7 +11603,7 @@
         <v>27</v>
       </c>
       <c r="E131">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F131" t="s">
         <v>31</v>
@@ -11626,7 +11626,7 @@
         <v>27</v>
       </c>
       <c r="E132">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F132" t="s">
         <v>28</v>
@@ -11649,7 +11649,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F133" t="s">
         <v>34</v>
@@ -11672,7 +11672,7 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -11695,7 +11695,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F135" t="s">
         <v>31</v>
@@ -11718,7 +11718,7 @@
         <v>27</v>
       </c>
       <c r="E136">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
@@ -11741,7 +11741,7 @@
         <v>27</v>
       </c>
       <c r="E137">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F137" t="s">
         <v>34</v>
@@ -11764,7 +11764,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -11787,7 +11787,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F139" t="s">
         <v>31</v>
@@ -11810,7 +11810,7 @@
         <v>27</v>
       </c>
       <c r="E140">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
@@ -11833,7 +11833,7 @@
         <v>27</v>
       </c>
       <c r="E141">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F141" t="s">
         <v>34</v>
@@ -11856,7 +11856,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -11879,7 +11879,7 @@
         <v>27</v>
       </c>
       <c r="E143">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F143" t="s">
         <v>31</v>
@@ -11902,7 +11902,7 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F144" t="s">
         <v>28</v>
@@ -11925,7 +11925,7 @@
         <v>27</v>
       </c>
       <c r="E145">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F145" t="s">
         <v>34</v>
@@ -11948,7 +11948,7 @@
         <v>27</v>
       </c>
       <c r="E146">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F146" t="s">
         <v>28</v>
@@ -11971,7 +11971,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F147" t="s">
         <v>31</v>
@@ -11994,7 +11994,7 @@
         <v>27</v>
       </c>
       <c r="E148">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
@@ -12017,7 +12017,7 @@
         <v>27</v>
       </c>
       <c r="E149">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F149" t="s">
         <v>34</v>
@@ -12040,7 +12040,7 @@
         <v>27</v>
       </c>
       <c r="E150">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
@@ -12063,7 +12063,7 @@
         <v>27</v>
       </c>
       <c r="E151">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F151" t="s">
         <v>31</v>
@@ -12086,7 +12086,7 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F152" t="s">
         <v>28</v>
@@ -12109,7 +12109,7 @@
         <v>27</v>
       </c>
       <c r="E153">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F153" t="s">
         <v>31</v>
@@ -12132,7 +12132,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -12155,7 +12155,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F155" t="s">
         <v>34</v>
@@ -12178,7 +12178,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -12201,7 +12201,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F157" t="s">
         <v>31</v>
@@ -12224,7 +12224,7 @@
         <v>27</v>
       </c>
       <c r="E158">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F158" t="s">
         <v>28</v>
@@ -12247,7 +12247,7 @@
         <v>27</v>
       </c>
       <c r="E159">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F159" t="s">
         <v>34</v>
@@ -12270,7 +12270,7 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F160" t="s">
         <v>28</v>
@@ -12293,7 +12293,7 @@
         <v>27</v>
       </c>
       <c r="E161">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F161" t="s">
         <v>31</v>
@@ -12316,7 +12316,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -12339,7 +12339,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F163" t="s">
         <v>34</v>
@@ -12362,7 +12362,7 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
@@ -12385,7 +12385,7 @@
         <v>27</v>
       </c>
       <c r="E165">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F165" t="s">
         <v>31</v>
@@ -12408,7 +12408,7 @@
         <v>27</v>
       </c>
       <c r="E166">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -12431,7 +12431,7 @@
         <v>27</v>
       </c>
       <c r="E167">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F167" t="s">
         <v>34</v>
@@ -12454,7 +12454,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -12477,7 +12477,7 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F169" t="s">
         <v>31</v>
@@ -12500,7 +12500,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -12523,7 +12523,7 @@
         <v>27</v>
       </c>
       <c r="E171">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F171" t="s">
         <v>34</v>
@@ -12546,7 +12546,7 @@
         <v>27</v>
       </c>
       <c r="E172">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
@@ -12569,7 +12569,7 @@
         <v>27</v>
       </c>
       <c r="E173">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F173" t="s">
         <v>31</v>
@@ -12592,7 +12592,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -12615,7 +12615,7 @@
         <v>27</v>
       </c>
       <c r="E175">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F175" t="s">
         <v>34</v>
@@ -12638,7 +12638,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -12661,7 +12661,7 @@
         <v>27</v>
       </c>
       <c r="E177">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
@@ -12684,7 +12684,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F178" t="s">
         <v>31</v>
@@ -12707,7 +12707,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -12730,7 +12730,7 @@
         <v>27</v>
       </c>
       <c r="E180">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F180" t="s">
         <v>34</v>
@@ -12753,7 +12753,7 @@
         <v>27</v>
       </c>
       <c r="E181">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F181" t="s">
         <v>28</v>
@@ -12776,7 +12776,7 @@
         <v>27</v>
       </c>
       <c r="E182">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F182" t="s">
         <v>31</v>
@@ -12799,7 +12799,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -12822,7 +12822,7 @@
         <v>27</v>
       </c>
       <c r="E184">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F184" t="s">
         <v>34</v>
@@ -12845,7 +12845,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -12868,7 +12868,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F186" t="s">
         <v>31</v>
@@ -12891,7 +12891,7 @@
         <v>27</v>
       </c>
       <c r="E187">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F187" t="s">
         <v>28</v>
@@ -12914,7 +12914,7 @@
         <v>27</v>
       </c>
       <c r="E188">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F188" t="s">
         <v>34</v>
@@ -12937,7 +12937,7 @@
         <v>27</v>
       </c>
       <c r="E189">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F189" t="s">
         <v>28</v>
@@ -12960,7 +12960,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F190" t="s">
         <v>31</v>
@@ -12983,7 +12983,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -13006,7 +13006,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F192" t="s">
         <v>34</v>
@@ -13029,7 +13029,7 @@
         <v>27</v>
       </c>
       <c r="E193">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -13052,7 +13052,7 @@
         <v>27</v>
       </c>
       <c r="E194">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F194" t="s">
         <v>31</v>
@@ -13075,7 +13075,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -13098,7 +13098,7 @@
         <v>27</v>
       </c>
       <c r="E196">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F196" t="s">
         <v>34</v>
@@ -13121,7 +13121,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -13144,7 +13144,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F198" t="s">
         <v>31</v>
@@ -13167,7 +13167,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -13190,7 +13190,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F200" t="s">
         <v>34</v>
@@ -13213,7 +13213,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -13236,7 +13236,7 @@
         <v>27</v>
       </c>
       <c r="E202">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -13259,7 +13259,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F203" t="s">
         <v>31</v>
@@ -13282,7 +13282,7 @@
         <v>27</v>
       </c>
       <c r="E204">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -13305,7 +13305,7 @@
         <v>27</v>
       </c>
       <c r="E205">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F205" t="s">
         <v>34</v>
@@ -13328,7 +13328,7 @@
         <v>27</v>
       </c>
       <c r="E206">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -13351,7 +13351,7 @@
         <v>27</v>
       </c>
       <c r="E207">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F207" t="s">
         <v>31</v>
@@ -13374,7 +13374,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -13397,7 +13397,7 @@
         <v>27</v>
       </c>
       <c r="E209">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F209" t="s">
         <v>34</v>
@@ -13420,7 +13420,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -13443,7 +13443,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F211" t="s">
         <v>31</v>
@@ -13466,7 +13466,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -13489,7 +13489,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F213" t="s">
         <v>34</v>
@@ -13512,7 +13512,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -13535,7 +13535,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F215" t="s">
         <v>31</v>
@@ -13558,7 +13558,7 @@
         <v>27</v>
       </c>
       <c r="E216">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F216" t="s">
         <v>28</v>
@@ -13581,7 +13581,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F217" t="s">
         <v>34</v>
@@ -13604,7 +13604,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -13627,7 +13627,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F219" t="s">
         <v>31</v>
@@ -13650,7 +13650,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -13673,7 +13673,7 @@
         <v>27</v>
       </c>
       <c r="E221">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F221" t="s">
         <v>34</v>
@@ -13696,7 +13696,7 @@
         <v>27</v>
       </c>
       <c r="E222">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F222" t="s">
         <v>28</v>
@@ -13719,7 +13719,7 @@
         <v>27</v>
       </c>
       <c r="E223">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F223" t="s">
         <v>31</v>
@@ -13765,7 +13765,7 @@
         <v>27</v>
       </c>
       <c r="E225">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F225" t="s">
         <v>34</v>
@@ -13788,7 +13788,7 @@
         <v>27</v>
       </c>
       <c r="E226">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F226" t="s">
         <v>28</v>
@@ -13811,7 +13811,7 @@
         <v>27</v>
       </c>
       <c r="E227">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F227" t="s">
         <v>28</v>
@@ -13834,7 +13834,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F228" t="s">
         <v>31</v>
@@ -13857,7 +13857,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -13880,7 +13880,7 @@
         <v>27</v>
       </c>
       <c r="E230">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F230" t="s">
         <v>34</v>
@@ -13903,7 +13903,7 @@
         <v>27</v>
       </c>
       <c r="E231">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F231" t="s">
         <v>28</v>
@@ -13926,7 +13926,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F232" t="s">
         <v>31</v>
@@ -13949,7 +13949,7 @@
         <v>27</v>
       </c>
       <c r="E233">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F233" t="s">
         <v>28</v>
@@ -13972,7 +13972,7 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F234" t="s">
         <v>34</v>
@@ -13995,7 +13995,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -14018,7 +14018,7 @@
         <v>27</v>
       </c>
       <c r="E236">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F236" t="s">
         <v>31</v>
@@ -14041,7 +14041,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -14064,7 +14064,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F238" t="s">
         <v>34</v>
@@ -14087,7 +14087,7 @@
         <v>27</v>
       </c>
       <c r="E239">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F239" t="s">
         <v>28</v>
@@ -14110,7 +14110,7 @@
         <v>27</v>
       </c>
       <c r="E240">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F240" t="s">
         <v>31</v>
@@ -14133,7 +14133,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -14156,7 +14156,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F242" t="s">
         <v>34</v>
@@ -14179,7 +14179,7 @@
         <v>27</v>
       </c>
       <c r="E243">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -14202,7 +14202,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F244" t="s">
         <v>31</v>
@@ -14225,7 +14225,7 @@
         <v>27</v>
       </c>
       <c r="E245">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F245" t="s">
         <v>28</v>
@@ -14248,7 +14248,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F246" t="s">
         <v>34</v>
@@ -14271,7 +14271,7 @@
         <v>27</v>
       </c>
       <c r="E247">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F247" t="s">
         <v>28</v>
@@ -14294,7 +14294,7 @@
         <v>27</v>
       </c>
       <c r="E248">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F248" t="s">
         <v>31</v>
@@ -14317,7 +14317,7 @@
         <v>27</v>
       </c>
       <c r="E249">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F249" t="s">
         <v>28</v>
@@ -14340,7 +14340,7 @@
         <v>27</v>
       </c>
       <c r="E250">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F250" t="s">
         <v>34</v>
@@ -14363,7 +14363,7 @@
         <v>27</v>
       </c>
       <c r="E251">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F251" t="s">
         <v>28</v>
@@ -14386,7 +14386,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -14409,7 +14409,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F253" t="s">
         <v>31</v>
@@ -14432,7 +14432,7 @@
         <v>27</v>
       </c>
       <c r="E254">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F254" t="s">
         <v>28</v>
@@ -14455,7 +14455,7 @@
         <v>27</v>
       </c>
       <c r="E255">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F255" t="s">
         <v>34</v>
@@ -14478,7 +14478,7 @@
         <v>27</v>
       </c>
       <c r="E256">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F256" t="s">
         <v>28</v>
@@ -14501,7 +14501,7 @@
         <v>27</v>
       </c>
       <c r="E257">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F257" t="s">
         <v>31</v>
@@ -14524,7 +14524,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -14547,7 +14547,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F259" t="s">
         <v>34</v>
@@ -14570,7 +14570,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -14593,7 +14593,7 @@
         <v>27</v>
       </c>
       <c r="E261">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F261" t="s">
         <v>31</v>
@@ -14616,7 +14616,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -14639,7 +14639,7 @@
         <v>27</v>
       </c>
       <c r="E263">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F263" t="s">
         <v>34</v>
@@ -14662,7 +14662,7 @@
         <v>27</v>
       </c>
       <c r="E264">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -14685,7 +14685,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F265" t="s">
         <v>31</v>
@@ -14708,7 +14708,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -14731,7 +14731,7 @@
         <v>27</v>
       </c>
       <c r="E267">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F267" t="s">
         <v>34</v>
@@ -14754,7 +14754,7 @@
         <v>27</v>
       </c>
       <c r="E268">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F268" t="s">
         <v>28</v>
@@ -14777,7 +14777,7 @@
         <v>27</v>
       </c>
       <c r="E269">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F269" t="s">
         <v>31</v>
@@ -14800,7 +14800,7 @@
         <v>27</v>
       </c>
       <c r="E270">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F270" t="s">
         <v>28</v>
@@ -14823,7 +14823,7 @@
         <v>27</v>
       </c>
       <c r="E271">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F271" t="s">
         <v>34</v>
@@ -14846,7 +14846,7 @@
         <v>27</v>
       </c>
       <c r="E272">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F272" t="s">
         <v>28</v>
@@ -14869,7 +14869,7 @@
         <v>27</v>
       </c>
       <c r="E273">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F273" t="s">
         <v>31</v>
@@ -14892,7 +14892,7 @@
         <v>27</v>
       </c>
       <c r="E274">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F274" t="s">
         <v>28</v>
@@ -14915,7 +14915,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F275" t="s">
         <v>34</v>
@@ -14938,7 +14938,7 @@
         <v>27</v>
       </c>
       <c r="E276">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F276" t="s">
         <v>28</v>
@@ -14961,7 +14961,7 @@
         <v>27</v>
       </c>
       <c r="E277">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F277" t="s">
         <v>28</v>
@@ -14984,7 +14984,7 @@
         <v>27</v>
       </c>
       <c r="E278">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F278" t="s">
         <v>31</v>
@@ -15007,7 +15007,7 @@
         <v>27</v>
       </c>
       <c r="E279">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -15030,7 +15030,7 @@
         <v>27</v>
       </c>
       <c r="E280">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F280" t="s">
         <v>34</v>
@@ -15053,7 +15053,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -15076,7 +15076,7 @@
         <v>27</v>
       </c>
       <c r="E282">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F282" t="s">
         <v>31</v>
@@ -15099,7 +15099,7 @@
         <v>27</v>
       </c>
       <c r="E283">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F283" t="s">
         <v>28</v>
@@ -15122,7 +15122,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F284" t="s">
         <v>34</v>
@@ -15145,7 +15145,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -15168,7 +15168,7 @@
         <v>27</v>
       </c>
       <c r="E286">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F286" t="s">
         <v>31</v>
@@ -15191,7 +15191,7 @@
         <v>27</v>
       </c>
       <c r="E287">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F287" t="s">
         <v>28</v>
@@ -15214,7 +15214,7 @@
         <v>27</v>
       </c>
       <c r="E288">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F288" t="s">
         <v>34</v>
@@ -15237,7 +15237,7 @@
         <v>27</v>
       </c>
       <c r="E289">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F289" t="s">
         <v>28</v>
@@ -15260,7 +15260,7 @@
         <v>27</v>
       </c>
       <c r="E290">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F290" t="s">
         <v>31</v>
@@ -15283,7 +15283,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -15306,7 +15306,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F292" t="s">
         <v>34</v>
@@ -15329,7 +15329,7 @@
         <v>27</v>
       </c>
       <c r="E293">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -15352,7 +15352,7 @@
         <v>27</v>
       </c>
       <c r="E294">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F294" t="s">
         <v>31</v>
@@ -15375,7 +15375,7 @@
         <v>27</v>
       </c>
       <c r="E295">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F295" t="s">
         <v>28</v>
@@ -15398,7 +15398,7 @@
         <v>27</v>
       </c>
       <c r="E296">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F296" t="s">
         <v>34</v>
@@ -15421,7 +15421,7 @@
         <v>27</v>
       </c>
       <c r="E297">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F297" t="s">
         <v>28</v>
@@ -15444,7 +15444,7 @@
         <v>27</v>
       </c>
       <c r="E298">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F298" t="s">
         <v>31</v>
@@ -15467,7 +15467,7 @@
         <v>27</v>
       </c>
       <c r="E299">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F299" t="s">
         <v>28</v>
@@ -15490,7 +15490,7 @@
         <v>27</v>
       </c>
       <c r="E300">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F300" t="s">
         <v>34</v>
@@ -15513,7 +15513,7 @@
         <v>27</v>
       </c>
       <c r="E301">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F301" t="s">
         <v>28</v>

--- a/all-test-reports/vulnerability/vulnerability_test_report.xlsx
+++ b/all-test-reports/vulnerability/vulnerability_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 11:40:42 am</t>
+    <t>28/7/2026, 11:43:44 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1694,7 +1694,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="10">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>28</v>
@@ -1717,7 +1717,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="10">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>31</v>
@@ -1740,7 +1740,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="10">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>28</v>
@@ -1763,7 +1763,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="10">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>34</v>
@@ -1786,7 +1786,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="10">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>28</v>
@@ -1809,7 +1809,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="10">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>31</v>
@@ -1832,7 +1832,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="10">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>28</v>
@@ -1855,7 +1855,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="10">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>34</v>
@@ -1878,7 +1878,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="10">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>28</v>
@@ -1901,7 +1901,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="10">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>31</v>
@@ -1924,7 +1924,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="10">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>28</v>
@@ -1947,7 +1947,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="10">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>34</v>
@@ -1970,7 +1970,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="10">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>28</v>
@@ -1993,7 +1993,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="10">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>31</v>
@@ -2016,7 +2016,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="10">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>28</v>
@@ -2039,7 +2039,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="10">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>34</v>
@@ -2062,7 +2062,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="10">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>28</v>
@@ -2085,7 +2085,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>31</v>
@@ -2108,7 +2108,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="10">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>28</v>
@@ -2131,7 +2131,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="10">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>34</v>
@@ -2154,7 +2154,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="10">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>28</v>
@@ -2177,7 +2177,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="10">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>31</v>
@@ -2200,7 +2200,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="10">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>28</v>
@@ -2223,7 +2223,7 @@
         <v>27</v>
       </c>
       <c r="E25" s="10">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>34</v>
@@ -2246,7 +2246,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="10">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>28</v>
@@ -2269,7 +2269,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="10">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>31</v>
@@ -2292,7 +2292,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>28</v>
@@ -2338,7 +2338,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="10">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>28</v>
@@ -2361,7 +2361,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="10">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>31</v>
@@ -2384,7 +2384,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="10">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>28</v>
@@ -2407,7 +2407,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="10">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>31</v>
@@ -2430,7 +2430,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="10">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>28</v>
@@ -2453,7 +2453,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="10">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>34</v>
@@ -2476,7 +2476,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="10">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>28</v>
@@ -2499,7 +2499,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="10">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>31</v>
@@ -2522,7 +2522,7 @@
         <v>27</v>
       </c>
       <c r="E38" s="10">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>28</v>
@@ -2545,7 +2545,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="10">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>34</v>
@@ -2568,7 +2568,7 @@
         <v>27</v>
       </c>
       <c r="E40" s="10">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>28</v>
@@ -2591,7 +2591,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="10">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>31</v>
@@ -2637,7 +2637,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="10">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>34</v>
@@ -2660,7 +2660,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="10">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>28</v>
@@ -2683,7 +2683,7 @@
         <v>27</v>
       </c>
       <c r="E45" s="10">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>31</v>
@@ -2706,7 +2706,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="10">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>28</v>
@@ -2729,7 +2729,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="10">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>34</v>
@@ -2752,7 +2752,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="10">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>28</v>
@@ -2775,7 +2775,7 @@
         <v>27</v>
       </c>
       <c r="E49" s="10">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>31</v>
@@ -2798,7 +2798,7 @@
         <v>27</v>
       </c>
       <c r="E50" s="10">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>28</v>
@@ -2821,7 +2821,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="10">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>34</v>
@@ -2844,7 +2844,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="10">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>28</v>
@@ -2867,7 +2867,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="10">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>31</v>
@@ -2890,7 +2890,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="10">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>28</v>
@@ -2913,7 +2913,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="10">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>34</v>
@@ -2936,7 +2936,7 @@
         <v>27</v>
       </c>
       <c r="E56" s="10">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>28</v>
@@ -2959,7 +2959,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="10">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>31</v>
@@ -2982,7 +2982,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="10">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>28</v>
@@ -3005,7 +3005,7 @@
         <v>27</v>
       </c>
       <c r="E59" s="10">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>34</v>
@@ -3028,7 +3028,7 @@
         <v>27</v>
       </c>
       <c r="E60" s="10">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>28</v>
@@ -3051,7 +3051,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="10">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>31</v>
@@ -3074,7 +3074,7 @@
         <v>27</v>
       </c>
       <c r="E62" s="10">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>28</v>
@@ -3097,7 +3097,7 @@
         <v>27</v>
       </c>
       <c r="E63" s="10">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>31</v>
@@ -3120,7 +3120,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="10">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>28</v>
@@ -3166,7 +3166,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="10">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>28</v>
@@ -3189,7 +3189,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="10">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>31</v>
@@ -3212,7 +3212,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>28</v>
@@ -3235,7 +3235,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="10">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>34</v>
@@ -3258,7 +3258,7 @@
         <v>27</v>
       </c>
       <c r="E70" s="10">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>28</v>
@@ -3281,7 +3281,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="10">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>31</v>
@@ -3304,7 +3304,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>28</v>
@@ -3327,7 +3327,7 @@
         <v>27</v>
       </c>
       <c r="E73" s="10">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>34</v>
@@ -3350,7 +3350,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="10">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>28</v>
@@ -3373,7 +3373,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="10">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>31</v>
@@ -3396,7 +3396,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="10">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>28</v>
@@ -3419,7 +3419,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="10">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>34</v>
@@ -3442,7 +3442,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="10">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>28</v>
@@ -3465,7 +3465,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="10">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>31</v>
@@ -3488,7 +3488,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="10">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>28</v>
@@ -3511,7 +3511,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="10">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>34</v>
@@ -3534,7 +3534,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="10">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>28</v>
@@ -3557,7 +3557,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="10">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>31</v>
@@ -3580,7 +3580,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="10">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>28</v>
@@ -3603,7 +3603,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="10">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>34</v>
@@ -3626,7 +3626,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="10">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>28</v>
@@ -3649,7 +3649,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="10">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>31</v>
@@ -3672,7 +3672,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="10">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>28</v>
@@ -3695,7 +3695,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>34</v>
@@ -3718,7 +3718,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="10">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>28</v>
@@ -3741,7 +3741,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="10">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>31</v>
@@ -3764,7 +3764,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="10">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>28</v>
@@ -3787,7 +3787,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="10">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>31</v>
@@ -3810,7 +3810,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="10">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>28</v>
@@ -3833,7 +3833,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="10">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>34</v>
@@ -3856,7 +3856,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="10">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F96" s="8" t="s">
         <v>28</v>
@@ -3879,7 +3879,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="10">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>31</v>
@@ -3902,7 +3902,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="10">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>28</v>
@@ -3925,7 +3925,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="10">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>34</v>
@@ -3948,7 +3948,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="10">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>28</v>
@@ -3994,7 +3994,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>28</v>
@@ -4017,7 +4017,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="10">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>34</v>
@@ -4040,7 +4040,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="10">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>28</v>
@@ -4063,7 +4063,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="10">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>31</v>
@@ -4086,7 +4086,7 @@
         <v>27</v>
       </c>
       <c r="E106" s="10">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>28</v>
@@ -4109,7 +4109,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="10">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>34</v>
@@ -4132,7 +4132,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>28</v>
@@ -4155,7 +4155,7 @@
         <v>27</v>
       </c>
       <c r="E109" s="10">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>31</v>
@@ -4178,7 +4178,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="10">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>28</v>
@@ -4201,7 +4201,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="10">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>34</v>
@@ -4224,7 +4224,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="10">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>28</v>
@@ -4247,7 +4247,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="10">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F113" s="8" t="s">
         <v>31</v>
@@ -4270,7 +4270,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="10">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>28</v>
@@ -4293,7 +4293,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="10">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>34</v>
@@ -4316,7 +4316,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="10">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>28</v>
@@ -4339,7 +4339,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="10">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F117" s="8" t="s">
         <v>31</v>
@@ -4385,7 +4385,7 @@
         <v>27</v>
       </c>
       <c r="E119" s="10">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F119" s="8" t="s">
         <v>34</v>
@@ -4408,7 +4408,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="10">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F120" s="8" t="s">
         <v>28</v>
@@ -4431,7 +4431,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="10">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F121" s="8" t="s">
         <v>31</v>
@@ -4454,7 +4454,7 @@
         <v>27</v>
       </c>
       <c r="E122" s="10">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F122" s="8" t="s">
         <v>28</v>
@@ -4477,7 +4477,7 @@
         <v>27</v>
       </c>
       <c r="E123" s="10">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>31</v>
@@ -4523,7 +4523,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>34</v>
@@ -4546,7 +4546,7 @@
         <v>27</v>
       </c>
       <c r="E126" s="10">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F126" s="8" t="s">
         <v>28</v>
@@ -4569,7 +4569,7 @@
         <v>27</v>
       </c>
       <c r="E127" s="10">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F127" s="8" t="s">
         <v>31</v>
@@ -4592,7 +4592,7 @@
         <v>27</v>
       </c>
       <c r="E128" s="10">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F128" s="8" t="s">
         <v>28</v>
@@ -4615,7 +4615,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="10">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F129" s="8" t="s">
         <v>34</v>
@@ -4638,7 +4638,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="10">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F130" s="8" t="s">
         <v>28</v>
@@ -4661,7 +4661,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="10">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F131" s="8" t="s">
         <v>31</v>
@@ -4684,7 +4684,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="10">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F132" s="8" t="s">
         <v>28</v>
@@ -4707,7 +4707,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="10">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F133" s="8" t="s">
         <v>34</v>
@@ -4730,7 +4730,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F134" s="8" t="s">
         <v>28</v>
@@ -4753,7 +4753,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="10">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F135" s="8" t="s">
         <v>31</v>
@@ -4776,7 +4776,7 @@
         <v>27</v>
       </c>
       <c r="E136" s="10">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F136" s="8" t="s">
         <v>28</v>
@@ -4799,7 +4799,7 @@
         <v>27</v>
       </c>
       <c r="E137" s="10">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F137" s="8" t="s">
         <v>34</v>
@@ -4822,7 +4822,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="10">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F138" s="8" t="s">
         <v>28</v>
@@ -4845,7 +4845,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="10">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F139" s="8" t="s">
         <v>31</v>
@@ -4868,7 +4868,7 @@
         <v>27</v>
       </c>
       <c r="E140" s="10">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F140" s="8" t="s">
         <v>28</v>
@@ -4914,7 +4914,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="10">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F142" s="8" t="s">
         <v>28</v>
@@ -4937,7 +4937,7 @@
         <v>27</v>
       </c>
       <c r="E143" s="10">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F143" s="8" t="s">
         <v>31</v>
@@ -4960,7 +4960,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="10">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F144" s="8" t="s">
         <v>28</v>
@@ -4983,7 +4983,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="10">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F145" s="8" t="s">
         <v>34</v>
@@ -5006,7 +5006,7 @@
         <v>27</v>
       </c>
       <c r="E146" s="10">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>28</v>
@@ -5029,7 +5029,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="10">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F147" s="8" t="s">
         <v>31</v>
@@ -5052,7 +5052,7 @@
         <v>27</v>
       </c>
       <c r="E148" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F148" s="8" t="s">
         <v>28</v>
@@ -5075,7 +5075,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="10">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F149" s="8" t="s">
         <v>34</v>
@@ -5098,7 +5098,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="10">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>28</v>
@@ -5121,7 +5121,7 @@
         <v>27</v>
       </c>
       <c r="E151" s="10">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>31</v>
@@ -5144,7 +5144,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="10">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>28</v>
@@ -5167,7 +5167,7 @@
         <v>27</v>
       </c>
       <c r="E153" s="10">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F153" s="8" t="s">
         <v>31</v>
@@ -5190,7 +5190,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="10">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>28</v>
@@ -5213,7 +5213,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="10">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F155" s="8" t="s">
         <v>34</v>
@@ -5236,7 +5236,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="10">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F156" s="8" t="s">
         <v>28</v>
@@ -5259,7 +5259,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="10">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F157" s="8" t="s">
         <v>31</v>
@@ -5282,7 +5282,7 @@
         <v>27</v>
       </c>
       <c r="E158" s="10">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F158" s="8" t="s">
         <v>28</v>
@@ -5305,7 +5305,7 @@
         <v>27</v>
       </c>
       <c r="E159" s="10">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F159" s="8" t="s">
         <v>34</v>
@@ -5328,7 +5328,7 @@
         <v>27</v>
       </c>
       <c r="E160" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F160" s="8" t="s">
         <v>28</v>
@@ -5351,7 +5351,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="10">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F161" s="8" t="s">
         <v>31</v>
@@ -5374,7 +5374,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="10">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F162" s="8" t="s">
         <v>28</v>
@@ -5397,7 +5397,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="10">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F163" s="8" t="s">
         <v>34</v>
@@ -5420,7 +5420,7 @@
         <v>27</v>
       </c>
       <c r="E164" s="10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F164" s="8" t="s">
         <v>28</v>
@@ -5443,7 +5443,7 @@
         <v>27</v>
       </c>
       <c r="E165" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F165" s="8" t="s">
         <v>31</v>
@@ -5466,7 +5466,7 @@
         <v>27</v>
       </c>
       <c r="E166" s="10">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F166" s="8" t="s">
         <v>28</v>
@@ -5489,7 +5489,7 @@
         <v>27</v>
       </c>
       <c r="E167" s="10">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F167" s="8" t="s">
         <v>34</v>
@@ -5512,7 +5512,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="10">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F168" s="8" t="s">
         <v>28</v>
@@ -5535,7 +5535,7 @@
         <v>27</v>
       </c>
       <c r="E169" s="10">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F169" s="8" t="s">
         <v>31</v>
@@ -5558,7 +5558,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="10">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F170" s="8" t="s">
         <v>28</v>
@@ -5581,7 +5581,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="10">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F171" s="8" t="s">
         <v>34</v>
@@ -5604,7 +5604,7 @@
         <v>27</v>
       </c>
       <c r="E172" s="10">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F172" s="8" t="s">
         <v>28</v>
@@ -5627,7 +5627,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="10">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F173" s="8" t="s">
         <v>31</v>
@@ -5650,7 +5650,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="10">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F174" s="8" t="s">
         <v>28</v>
@@ -5673,7 +5673,7 @@
         <v>27</v>
       </c>
       <c r="E175" s="10">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F175" s="8" t="s">
         <v>34</v>
@@ -5696,7 +5696,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="10">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F176" s="8" t="s">
         <v>28</v>
@@ -5719,7 +5719,7 @@
         <v>27</v>
       </c>
       <c r="E177" s="10">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F177" s="8" t="s">
         <v>28</v>
@@ -5742,7 +5742,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F178" s="8" t="s">
         <v>31</v>
@@ -5765,7 +5765,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="10">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F179" s="8" t="s">
         <v>28</v>
@@ -5788,7 +5788,7 @@
         <v>27</v>
       </c>
       <c r="E180" s="10">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F180" s="8" t="s">
         <v>34</v>
@@ -5811,7 +5811,7 @@
         <v>27</v>
       </c>
       <c r="E181" s="10">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F181" s="8" t="s">
         <v>28</v>
@@ -5834,7 +5834,7 @@
         <v>27</v>
       </c>
       <c r="E182" s="10">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F182" s="8" t="s">
         <v>31</v>
@@ -5857,7 +5857,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="10">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F183" s="8" t="s">
         <v>28</v>
@@ -5903,7 +5903,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="10">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F185" s="8" t="s">
         <v>28</v>
@@ -5926,7 +5926,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="10">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F186" s="8" t="s">
         <v>31</v>
@@ -5949,7 +5949,7 @@
         <v>27</v>
       </c>
       <c r="E187" s="10">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F187" s="8" t="s">
         <v>28</v>
@@ -5972,7 +5972,7 @@
         <v>27</v>
       </c>
       <c r="E188" s="10">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F188" s="8" t="s">
         <v>34</v>
@@ -5995,7 +5995,7 @@
         <v>27</v>
       </c>
       <c r="E189" s="10">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F189" s="8" t="s">
         <v>28</v>
@@ -6018,7 +6018,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="10">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F190" s="8" t="s">
         <v>31</v>
@@ -6041,7 +6041,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="10">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F191" s="8" t="s">
         <v>28</v>
@@ -6064,7 +6064,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="10">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F192" s="8" t="s">
         <v>34</v>
@@ -6087,7 +6087,7 @@
         <v>27</v>
       </c>
       <c r="E193" s="10">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F193" s="8" t="s">
         <v>28</v>
@@ -6133,7 +6133,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="10">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F195" s="8" t="s">
         <v>28</v>
@@ -6156,7 +6156,7 @@
         <v>27</v>
       </c>
       <c r="E196" s="10">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F196" s="8" t="s">
         <v>34</v>
@@ -6179,7 +6179,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="10">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F197" s="8" t="s">
         <v>28</v>
@@ -6202,7 +6202,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="10">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F198" s="8" t="s">
         <v>31</v>
@@ -6225,7 +6225,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F199" s="8" t="s">
         <v>28</v>
@@ -6248,7 +6248,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="10">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F200" s="8" t="s">
         <v>34</v>
@@ -6271,7 +6271,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="10">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F201" s="8" t="s">
         <v>28</v>
@@ -6317,7 +6317,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F203" s="8" t="s">
         <v>31</v>
@@ -6340,7 +6340,7 @@
         <v>27</v>
       </c>
       <c r="E204" s="10">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F204" s="8" t="s">
         <v>28</v>
@@ -6363,7 +6363,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="10">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F205" s="8" t="s">
         <v>34</v>
@@ -6386,7 +6386,7 @@
         <v>27</v>
       </c>
       <c r="E206" s="10">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F206" s="8" t="s">
         <v>28</v>
@@ -6409,7 +6409,7 @@
         <v>27</v>
       </c>
       <c r="E207" s="10">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F207" s="8" t="s">
         <v>31</v>
@@ -6432,7 +6432,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="10">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F208" s="8" t="s">
         <v>28</v>
@@ -6455,7 +6455,7 @@
         <v>27</v>
       </c>
       <c r="E209" s="10">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F209" s="8" t="s">
         <v>34</v>
@@ -6478,7 +6478,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="10">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F210" s="8" t="s">
         <v>28</v>
@@ -6501,7 +6501,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F211" s="8" t="s">
         <v>31</v>
@@ -6524,7 +6524,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="10">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F212" s="8" t="s">
         <v>28</v>
@@ -6547,7 +6547,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="10">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F213" s="8" t="s">
         <v>34</v>
@@ -6570,7 +6570,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="10">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F214" s="8" t="s">
         <v>28</v>
@@ -6593,7 +6593,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F215" s="8" t="s">
         <v>31</v>
@@ -6616,7 +6616,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="10">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F216" s="8" t="s">
         <v>28</v>
@@ -6639,7 +6639,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="10">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F217" s="8" t="s">
         <v>34</v>
@@ -6662,7 +6662,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="10">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F218" s="8" t="s">
         <v>28</v>
@@ -6685,7 +6685,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="10">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F219" s="8" t="s">
         <v>31</v>
@@ -6708,7 +6708,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="10">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F220" s="8" t="s">
         <v>28</v>
@@ -6731,7 +6731,7 @@
         <v>27</v>
       </c>
       <c r="E221" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F221" s="8" t="s">
         <v>34</v>
@@ -6754,7 +6754,7 @@
         <v>27</v>
       </c>
       <c r="E222" s="10">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F222" s="8" t="s">
         <v>28</v>
@@ -6800,7 +6800,7 @@
         <v>27</v>
       </c>
       <c r="E224" s="10">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F224" s="8" t="s">
         <v>28</v>
@@ -6846,7 +6846,7 @@
         <v>27</v>
       </c>
       <c r="E226" s="10">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F226" s="8" t="s">
         <v>28</v>
@@ -6892,7 +6892,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="10">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F228" s="8" t="s">
         <v>31</v>
@@ -6915,7 +6915,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="10">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F229" s="8" t="s">
         <v>28</v>
@@ -6938,7 +6938,7 @@
         <v>27</v>
       </c>
       <c r="E230" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F230" s="8" t="s">
         <v>34</v>
@@ -6961,7 +6961,7 @@
         <v>27</v>
       </c>
       <c r="E231" s="10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F231" s="8" t="s">
         <v>28</v>
@@ -6984,7 +6984,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="10">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F232" s="8" t="s">
         <v>31</v>
@@ -7007,7 +7007,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="10">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F233" s="8" t="s">
         <v>28</v>
@@ -7030,7 +7030,7 @@
         <v>27</v>
       </c>
       <c r="E234" s="10">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F234" s="8" t="s">
         <v>34</v>
@@ -7053,7 +7053,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="10">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F235" s="8" t="s">
         <v>28</v>
@@ -7076,7 +7076,7 @@
         <v>27</v>
       </c>
       <c r="E236" s="10">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F236" s="8" t="s">
         <v>31</v>
@@ -7099,7 +7099,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="10">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F237" s="8" t="s">
         <v>28</v>
@@ -7122,7 +7122,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="10">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F238" s="8" t="s">
         <v>34</v>
@@ -7145,7 +7145,7 @@
         <v>27</v>
       </c>
       <c r="E239" s="10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F239" s="8" t="s">
         <v>28</v>
@@ -7168,7 +7168,7 @@
         <v>27</v>
       </c>
       <c r="E240" s="10">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F240" s="8" t="s">
         <v>31</v>
@@ -7191,7 +7191,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="10">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F241" s="8" t="s">
         <v>28</v>
@@ -7214,7 +7214,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="10">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F242" s="8" t="s">
         <v>34</v>
@@ -7237,7 +7237,7 @@
         <v>27</v>
       </c>
       <c r="E243" s="10">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F243" s="8" t="s">
         <v>28</v>
@@ -7260,7 +7260,7 @@
         <v>27</v>
       </c>
       <c r="E244" s="10">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F244" s="8" t="s">
         <v>31</v>
@@ -7283,7 +7283,7 @@
         <v>27</v>
       </c>
       <c r="E245" s="10">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F245" s="8" t="s">
         <v>28</v>
@@ -7306,7 +7306,7 @@
         <v>27</v>
       </c>
       <c r="E246" s="10">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F246" s="8" t="s">
         <v>34</v>
@@ -7329,7 +7329,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F247" s="8" t="s">
         <v>28</v>
@@ -7352,7 +7352,7 @@
         <v>27</v>
       </c>
       <c r="E248" s="10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F248" s="8" t="s">
         <v>31</v>
@@ -7375,7 +7375,7 @@
         <v>27</v>
       </c>
       <c r="E249" s="10">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F249" s="8" t="s">
         <v>28</v>
@@ -7398,7 +7398,7 @@
         <v>27</v>
       </c>
       <c r="E250" s="10">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F250" s="8" t="s">
         <v>34</v>
@@ -7421,7 +7421,7 @@
         <v>27</v>
       </c>
       <c r="E251" s="10">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F251" s="8" t="s">
         <v>28</v>
@@ -7444,7 +7444,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="10">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F252" s="8" t="s">
         <v>28</v>
@@ -7467,7 +7467,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="10">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F253" s="8" t="s">
         <v>31</v>
@@ -7490,7 +7490,7 @@
         <v>27</v>
       </c>
       <c r="E254" s="10">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="F254" s="8" t="s">
         <v>28</v>
@@ -7513,7 +7513,7 @@
         <v>27</v>
       </c>
       <c r="E255" s="10">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F255" s="8" t="s">
         <v>34</v>
@@ -7536,7 +7536,7 @@
         <v>27</v>
       </c>
       <c r="E256" s="10">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F256" s="8" t="s">
         <v>28</v>
@@ -7559,7 +7559,7 @@
         <v>27</v>
       </c>
       <c r="E257" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F257" s="8" t="s">
         <v>31</v>
@@ -7582,7 +7582,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="10">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F258" s="8" t="s">
         <v>28</v>
@@ -7605,7 +7605,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="10">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F259" s="8" t="s">
         <v>34</v>
@@ -7628,7 +7628,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="10">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F260" s="8" t="s">
         <v>28</v>
@@ -7651,7 +7651,7 @@
         <v>27</v>
       </c>
       <c r="E261" s="10">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F261" s="8" t="s">
         <v>31</v>
@@ -7674,7 +7674,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="10">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F262" s="8" t="s">
         <v>28</v>
@@ -7697,7 +7697,7 @@
         <v>27</v>
       </c>
       <c r="E263" s="10">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F263" s="8" t="s">
         <v>34</v>
@@ -7720,7 +7720,7 @@
         <v>27</v>
       </c>
       <c r="E264" s="10">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F264" s="8" t="s">
         <v>28</v>
@@ -7743,7 +7743,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="10">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F265" s="8" t="s">
         <v>31</v>
@@ -7766,7 +7766,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="10">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F266" s="8" t="s">
         <v>28</v>
@@ -7789,7 +7789,7 @@
         <v>27</v>
       </c>
       <c r="E267" s="10">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F267" s="8" t="s">
         <v>34</v>
@@ -7812,7 +7812,7 @@
         <v>27</v>
       </c>
       <c r="E268" s="10">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F268" s="8" t="s">
         <v>28</v>
@@ -7835,7 +7835,7 @@
         <v>27</v>
       </c>
       <c r="E269" s="10">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F269" s="8" t="s">
         <v>31</v>
@@ -7881,7 +7881,7 @@
         <v>27</v>
       </c>
       <c r="E271" s="10">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F271" s="8" t="s">
         <v>34</v>
@@ -7904,7 +7904,7 @@
         <v>27</v>
       </c>
       <c r="E272" s="10">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F272" s="8" t="s">
         <v>28</v>
@@ -7927,7 +7927,7 @@
         <v>27</v>
       </c>
       <c r="E273" s="10">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F273" s="8" t="s">
         <v>31</v>
@@ -7950,7 +7950,7 @@
         <v>27</v>
       </c>
       <c r="E274" s="10">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F274" s="8" t="s">
         <v>28</v>
@@ -7973,7 +7973,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="10">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F275" s="8" t="s">
         <v>34</v>
@@ -7996,7 +7996,7 @@
         <v>27</v>
       </c>
       <c r="E276" s="10">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F276" s="8" t="s">
         <v>28</v>
@@ -8019,7 +8019,7 @@
         <v>27</v>
       </c>
       <c r="E277" s="10">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F277" s="8" t="s">
         <v>28</v>
@@ -8042,7 +8042,7 @@
         <v>27</v>
       </c>
       <c r="E278" s="10">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F278" s="8" t="s">
         <v>31</v>
@@ -8065,7 +8065,7 @@
         <v>27</v>
       </c>
       <c r="E279" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F279" s="8" t="s">
         <v>28</v>
@@ -8088,7 +8088,7 @@
         <v>27</v>
       </c>
       <c r="E280" s="10">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F280" s="8" t="s">
         <v>34</v>
@@ -8111,7 +8111,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="10">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F281" s="8" t="s">
         <v>28</v>
@@ -8134,7 +8134,7 @@
         <v>27</v>
       </c>
       <c r="E282" s="10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F282" s="8" t="s">
         <v>31</v>
@@ -8157,7 +8157,7 @@
         <v>27</v>
       </c>
       <c r="E283" s="10">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F283" s="8" t="s">
         <v>28</v>
@@ -8180,7 +8180,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="10">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F284" s="8" t="s">
         <v>34</v>
@@ -8203,7 +8203,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="10">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F285" s="8" t="s">
         <v>28</v>
@@ -8226,7 +8226,7 @@
         <v>27</v>
       </c>
       <c r="E286" s="10">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F286" s="8" t="s">
         <v>31</v>
@@ -8249,7 +8249,7 @@
         <v>27</v>
       </c>
       <c r="E287" s="10">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F287" s="8" t="s">
         <v>28</v>
@@ -8272,7 +8272,7 @@
         <v>27</v>
       </c>
       <c r="E288" s="10">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F288" s="8" t="s">
         <v>34</v>
@@ -8295,7 +8295,7 @@
         <v>27</v>
       </c>
       <c r="E289" s="10">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F289" s="8" t="s">
         <v>28</v>
@@ -8318,7 +8318,7 @@
         <v>27</v>
       </c>
       <c r="E290" s="10">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F290" s="8" t="s">
         <v>31</v>
@@ -8341,7 +8341,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="10">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F291" s="8" t="s">
         <v>28</v>
@@ -8364,7 +8364,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="10">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F292" s="8" t="s">
         <v>34</v>
@@ -8387,7 +8387,7 @@
         <v>27</v>
       </c>
       <c r="E293" s="10">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F293" s="8" t="s">
         <v>28</v>
@@ -8410,7 +8410,7 @@
         <v>27</v>
       </c>
       <c r="E294" s="10">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F294" s="8" t="s">
         <v>31</v>
@@ -8433,7 +8433,7 @@
         <v>27</v>
       </c>
       <c r="E295" s="10">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F295" s="8" t="s">
         <v>28</v>
@@ -8456,7 +8456,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="10">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F296" s="8" t="s">
         <v>34</v>
@@ -8479,7 +8479,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="10">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F297" s="8" t="s">
         <v>28</v>
@@ -8502,7 +8502,7 @@
         <v>27</v>
       </c>
       <c r="E298" s="10">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F298" s="8" t="s">
         <v>31</v>
@@ -8525,7 +8525,7 @@
         <v>27</v>
       </c>
       <c r="E299" s="10">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F299" s="8" t="s">
         <v>28</v>
@@ -8548,7 +8548,7 @@
         <v>27</v>
       </c>
       <c r="E300" s="10">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F300" s="8" t="s">
         <v>34</v>
@@ -8636,7 +8636,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -8659,7 +8659,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
         <v>31</v>
@@ -8682,7 +8682,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -8705,7 +8705,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
         <v>34</v>
@@ -8728,7 +8728,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -8751,7 +8751,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>31</v>
@@ -8774,7 +8774,7 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -8797,7 +8797,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
@@ -8820,7 +8820,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -8843,7 +8843,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s">
         <v>31</v>
@@ -8866,7 +8866,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -8889,7 +8889,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F13" t="s">
         <v>34</v>
@@ -8912,7 +8912,7 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -8935,7 +8935,7 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F15" t="s">
         <v>31</v>
@@ -8958,7 +8958,7 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -8981,7 +8981,7 @@
         <v>27</v>
       </c>
       <c r="E17">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F17" t="s">
         <v>34</v>
@@ -9004,7 +9004,7 @@
         <v>27</v>
       </c>
       <c r="E18">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -9027,7 +9027,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F19" t="s">
         <v>31</v>
@@ -9050,7 +9050,7 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -9073,7 +9073,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F21" t="s">
         <v>34</v>
@@ -9096,7 +9096,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -9119,7 +9119,7 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F23" t="s">
         <v>31</v>
@@ -9142,7 +9142,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -9165,7 +9165,7 @@
         <v>27</v>
       </c>
       <c r="E25">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F25" t="s">
         <v>34</v>
@@ -9188,7 +9188,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -9211,7 +9211,7 @@
         <v>27</v>
       </c>
       <c r="E27">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F27" t="s">
         <v>31</v>
@@ -9234,7 +9234,7 @@
         <v>27</v>
       </c>
       <c r="E28">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -9280,7 +9280,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -9303,7 +9303,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F31" t="s">
         <v>31</v>
@@ -9326,7 +9326,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -9349,7 +9349,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F33" t="s">
         <v>31</v>
@@ -9372,7 +9372,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -9395,7 +9395,7 @@
         <v>27</v>
       </c>
       <c r="E35">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
@@ -9418,7 +9418,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -9441,7 +9441,7 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F37" t="s">
         <v>31</v>
@@ -9464,7 +9464,7 @@
         <v>27</v>
       </c>
       <c r="E38">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -9487,7 +9487,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F39" t="s">
         <v>34</v>
@@ -9510,7 +9510,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -9533,7 +9533,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F41" t="s">
         <v>31</v>
@@ -9579,7 +9579,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F43" t="s">
         <v>34</v>
@@ -9602,7 +9602,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -9625,7 +9625,7 @@
         <v>27</v>
       </c>
       <c r="E45">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F45" t="s">
         <v>31</v>
@@ -9648,7 +9648,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -9671,7 +9671,7 @@
         <v>27</v>
       </c>
       <c r="E47">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F47" t="s">
         <v>34</v>
@@ -9694,7 +9694,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -9717,7 +9717,7 @@
         <v>27</v>
       </c>
       <c r="E49">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F49" t="s">
         <v>31</v>
@@ -9740,7 +9740,7 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F50" t="s">
         <v>28</v>
@@ -9763,7 +9763,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F51" t="s">
         <v>34</v>
@@ -9786,7 +9786,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -9809,7 +9809,7 @@
         <v>27</v>
       </c>
       <c r="E53">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F53" t="s">
         <v>31</v>
@@ -9832,7 +9832,7 @@
         <v>27</v>
       </c>
       <c r="E54">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -9855,7 +9855,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F55" t="s">
         <v>34</v>
@@ -9878,7 +9878,7 @@
         <v>27</v>
       </c>
       <c r="E56">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -9901,7 +9901,7 @@
         <v>27</v>
       </c>
       <c r="E57">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F57" t="s">
         <v>31</v>
@@ -9924,7 +9924,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -9947,7 +9947,7 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F59" t="s">
         <v>34</v>
@@ -9970,7 +9970,7 @@
         <v>27</v>
       </c>
       <c r="E60">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -9993,7 +9993,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F61" t="s">
         <v>31</v>
@@ -10016,7 +10016,7 @@
         <v>27</v>
       </c>
       <c r="E62">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F62" t="s">
         <v>28</v>
@@ -10039,7 +10039,7 @@
         <v>27</v>
       </c>
       <c r="E63">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F63" t="s">
         <v>31</v>
@@ -10062,7 +10062,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -10108,7 +10108,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -10131,7 +10131,7 @@
         <v>27</v>
       </c>
       <c r="E67">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F67" t="s">
         <v>31</v>
@@ -10154,7 +10154,7 @@
         <v>27</v>
       </c>
       <c r="E68">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
@@ -10177,7 +10177,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F69" t="s">
         <v>34</v>
@@ -10200,7 +10200,7 @@
         <v>27</v>
       </c>
       <c r="E70">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -10223,7 +10223,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F71" t="s">
         <v>31</v>
@@ -10246,7 +10246,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -10269,7 +10269,7 @@
         <v>27</v>
       </c>
       <c r="E73">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F73" t="s">
         <v>34</v>
@@ -10292,7 +10292,7 @@
         <v>27</v>
       </c>
       <c r="E74">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -10315,7 +10315,7 @@
         <v>27</v>
       </c>
       <c r="E75">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F75" t="s">
         <v>31</v>
@@ -10338,7 +10338,7 @@
         <v>27</v>
       </c>
       <c r="E76">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
@@ -10361,7 +10361,7 @@
         <v>27</v>
       </c>
       <c r="E77">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F77" t="s">
         <v>34</v>
@@ -10384,7 +10384,7 @@
         <v>27</v>
       </c>
       <c r="E78">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
@@ -10407,7 +10407,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F79" t="s">
         <v>31</v>
@@ -10430,7 +10430,7 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
@@ -10453,7 +10453,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F81" t="s">
         <v>34</v>
@@ -10476,7 +10476,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -10499,7 +10499,7 @@
         <v>27</v>
       </c>
       <c r="E83">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F83" t="s">
         <v>31</v>
@@ -10522,7 +10522,7 @@
         <v>27</v>
       </c>
       <c r="E84">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
@@ -10545,7 +10545,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F85" t="s">
         <v>34</v>
@@ -10568,7 +10568,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -10591,7 +10591,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F87" t="s">
         <v>31</v>
@@ -10614,7 +10614,7 @@
         <v>27</v>
       </c>
       <c r="E88">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -10637,7 +10637,7 @@
         <v>27</v>
       </c>
       <c r="E89">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F89" t="s">
         <v>34</v>
@@ -10660,7 +10660,7 @@
         <v>27</v>
       </c>
       <c r="E90">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F90" t="s">
         <v>28</v>
@@ -10683,7 +10683,7 @@
         <v>27</v>
       </c>
       <c r="E91">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F91" t="s">
         <v>31</v>
@@ -10706,7 +10706,7 @@
         <v>27</v>
       </c>
       <c r="E92">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
@@ -10729,7 +10729,7 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F93" t="s">
         <v>31</v>
@@ -10752,7 +10752,7 @@
         <v>27</v>
       </c>
       <c r="E94">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -10775,7 +10775,7 @@
         <v>27</v>
       </c>
       <c r="E95">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F95" t="s">
         <v>34</v>
@@ -10798,7 +10798,7 @@
         <v>27</v>
       </c>
       <c r="E96">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -10821,7 +10821,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F97" t="s">
         <v>31</v>
@@ -10844,7 +10844,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -10867,7 +10867,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F99" t="s">
         <v>34</v>
@@ -10890,7 +10890,7 @@
         <v>27</v>
       </c>
       <c r="E100">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
@@ -10936,7 +10936,7 @@
         <v>27</v>
       </c>
       <c r="E102">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
@@ -10959,7 +10959,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F103" t="s">
         <v>34</v>
@@ -10982,7 +10982,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -11005,7 +11005,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F105" t="s">
         <v>31</v>
@@ -11028,7 +11028,7 @@
         <v>27</v>
       </c>
       <c r="E106">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
@@ -11051,7 +11051,7 @@
         <v>27</v>
       </c>
       <c r="E107">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F107" t="s">
         <v>34</v>
@@ -11074,7 +11074,7 @@
         <v>27</v>
       </c>
       <c r="E108">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
@@ -11097,7 +11097,7 @@
         <v>27</v>
       </c>
       <c r="E109">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F109" t="s">
         <v>31</v>
@@ -11120,7 +11120,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -11143,7 +11143,7 @@
         <v>27</v>
       </c>
       <c r="E111">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F111" t="s">
         <v>34</v>
@@ -11166,7 +11166,7 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F112" t="s">
         <v>28</v>
@@ -11189,7 +11189,7 @@
         <v>27</v>
       </c>
       <c r="E113">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F113" t="s">
         <v>31</v>
@@ -11212,7 +11212,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -11235,7 +11235,7 @@
         <v>27</v>
       </c>
       <c r="E115">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F115" t="s">
         <v>34</v>
@@ -11258,7 +11258,7 @@
         <v>27</v>
       </c>
       <c r="E116">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F116" t="s">
         <v>28</v>
@@ -11281,7 +11281,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F117" t="s">
         <v>31</v>
@@ -11327,7 +11327,7 @@
         <v>27</v>
       </c>
       <c r="E119">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F119" t="s">
         <v>34</v>
@@ -11350,7 +11350,7 @@
         <v>27</v>
       </c>
       <c r="E120">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
@@ -11373,7 +11373,7 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F121" t="s">
         <v>31</v>
@@ -11396,7 +11396,7 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -11419,7 +11419,7 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F123" t="s">
         <v>31</v>
@@ -11465,7 +11465,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F125" t="s">
         <v>34</v>
@@ -11488,7 +11488,7 @@
         <v>27</v>
       </c>
       <c r="E126">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
@@ -11511,7 +11511,7 @@
         <v>27</v>
       </c>
       <c r="E127">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F127" t="s">
         <v>31</v>
@@ -11534,7 +11534,7 @@
         <v>27</v>
       </c>
       <c r="E128">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -11557,7 +11557,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F129" t="s">
         <v>34</v>
@@ -11580,7 +11580,7 @@
         <v>27</v>
       </c>
       <c r="E130">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
@@ -11603,7 +11603,7 @@
         <v>27</v>
       </c>
       <c r="E131">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F131" t="s">
         <v>31</v>
@@ -11626,7 +11626,7 @@
         <v>27</v>
       </c>
       <c r="E132">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F132" t="s">
         <v>28</v>
@@ -11649,7 +11649,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F133" t="s">
         <v>34</v>
@@ -11672,7 +11672,7 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -11695,7 +11695,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F135" t="s">
         <v>31</v>
@@ -11718,7 +11718,7 @@
         <v>27</v>
       </c>
       <c r="E136">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
@@ -11741,7 +11741,7 @@
         <v>27</v>
       </c>
       <c r="E137">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F137" t="s">
         <v>34</v>
@@ -11764,7 +11764,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -11787,7 +11787,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F139" t="s">
         <v>31</v>
@@ -11810,7 +11810,7 @@
         <v>27</v>
       </c>
       <c r="E140">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
@@ -11856,7 +11856,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -11879,7 +11879,7 @@
         <v>27</v>
       </c>
       <c r="E143">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F143" t="s">
         <v>31</v>
@@ -11902,7 +11902,7 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F144" t="s">
         <v>28</v>
@@ -11925,7 +11925,7 @@
         <v>27</v>
       </c>
       <c r="E145">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F145" t="s">
         <v>34</v>
@@ -11948,7 +11948,7 @@
         <v>27</v>
       </c>
       <c r="E146">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F146" t="s">
         <v>28</v>
@@ -11971,7 +11971,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F147" t="s">
         <v>31</v>
@@ -11994,7 +11994,7 @@
         <v>27</v>
       </c>
       <c r="E148">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
@@ -12017,7 +12017,7 @@
         <v>27</v>
       </c>
       <c r="E149">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F149" t="s">
         <v>34</v>
@@ -12040,7 +12040,7 @@
         <v>27</v>
       </c>
       <c r="E150">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
@@ -12063,7 +12063,7 @@
         <v>27</v>
       </c>
       <c r="E151">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F151" t="s">
         <v>31</v>
@@ -12086,7 +12086,7 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F152" t="s">
         <v>28</v>
@@ -12109,7 +12109,7 @@
         <v>27</v>
       </c>
       <c r="E153">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F153" t="s">
         <v>31</v>
@@ -12132,7 +12132,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -12155,7 +12155,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F155" t="s">
         <v>34</v>
@@ -12178,7 +12178,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -12201,7 +12201,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F157" t="s">
         <v>31</v>
@@ -12224,7 +12224,7 @@
         <v>27</v>
       </c>
       <c r="E158">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F158" t="s">
         <v>28</v>
@@ -12247,7 +12247,7 @@
         <v>27</v>
       </c>
       <c r="E159">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F159" t="s">
         <v>34</v>
@@ -12270,7 +12270,7 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F160" t="s">
         <v>28</v>
@@ -12293,7 +12293,7 @@
         <v>27</v>
       </c>
       <c r="E161">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F161" t="s">
         <v>31</v>
@@ -12316,7 +12316,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -12339,7 +12339,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F163" t="s">
         <v>34</v>
@@ -12362,7 +12362,7 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
@@ -12385,7 +12385,7 @@
         <v>27</v>
       </c>
       <c r="E165">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F165" t="s">
         <v>31</v>
@@ -12408,7 +12408,7 @@
         <v>27</v>
       </c>
       <c r="E166">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -12431,7 +12431,7 @@
         <v>27</v>
       </c>
       <c r="E167">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F167" t="s">
         <v>34</v>
@@ -12454,7 +12454,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -12477,7 +12477,7 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F169" t="s">
         <v>31</v>
@@ -12500,7 +12500,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -12523,7 +12523,7 @@
         <v>27</v>
       </c>
       <c r="E171">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F171" t="s">
         <v>34</v>
@@ -12546,7 +12546,7 @@
         <v>27</v>
       </c>
       <c r="E172">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
@@ -12569,7 +12569,7 @@
         <v>27</v>
       </c>
       <c r="E173">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F173" t="s">
         <v>31</v>
@@ -12592,7 +12592,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -12615,7 +12615,7 @@
         <v>27</v>
       </c>
       <c r="E175">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F175" t="s">
         <v>34</v>
@@ -12638,7 +12638,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -12661,7 +12661,7 @@
         <v>27</v>
       </c>
       <c r="E177">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
@@ -12684,7 +12684,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F178" t="s">
         <v>31</v>
@@ -12707,7 +12707,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -12730,7 +12730,7 @@
         <v>27</v>
       </c>
       <c r="E180">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F180" t="s">
         <v>34</v>
@@ -12753,7 +12753,7 @@
         <v>27</v>
       </c>
       <c r="E181">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F181" t="s">
         <v>28</v>
@@ -12776,7 +12776,7 @@
         <v>27</v>
       </c>
       <c r="E182">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F182" t="s">
         <v>31</v>
@@ -12799,7 +12799,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -12845,7 +12845,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -12868,7 +12868,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F186" t="s">
         <v>31</v>
@@ -12891,7 +12891,7 @@
         <v>27</v>
       </c>
       <c r="E187">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F187" t="s">
         <v>28</v>
@@ -12914,7 +12914,7 @@
         <v>27</v>
       </c>
       <c r="E188">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F188" t="s">
         <v>34</v>
@@ -12937,7 +12937,7 @@
         <v>27</v>
       </c>
       <c r="E189">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F189" t="s">
         <v>28</v>
@@ -12960,7 +12960,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F190" t="s">
         <v>31</v>
@@ -12983,7 +12983,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -13006,7 +13006,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F192" t="s">
         <v>34</v>
@@ -13029,7 +13029,7 @@
         <v>27</v>
       </c>
       <c r="E193">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -13075,7 +13075,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -13098,7 +13098,7 @@
         <v>27</v>
       </c>
       <c r="E196">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F196" t="s">
         <v>34</v>
@@ -13121,7 +13121,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -13144,7 +13144,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F198" t="s">
         <v>31</v>
@@ -13167,7 +13167,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -13190,7 +13190,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F200" t="s">
         <v>34</v>
@@ -13213,7 +13213,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -13259,7 +13259,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F203" t="s">
         <v>31</v>
@@ -13282,7 +13282,7 @@
         <v>27</v>
       </c>
       <c r="E204">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -13305,7 +13305,7 @@
         <v>27</v>
       </c>
       <c r="E205">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F205" t="s">
         <v>34</v>
@@ -13328,7 +13328,7 @@
         <v>27</v>
       </c>
       <c r="E206">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -13351,7 +13351,7 @@
         <v>27</v>
       </c>
       <c r="E207">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F207" t="s">
         <v>31</v>
@@ -13374,7 +13374,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -13397,7 +13397,7 @@
         <v>27</v>
       </c>
       <c r="E209">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F209" t="s">
         <v>34</v>
@@ -13420,7 +13420,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -13443,7 +13443,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F211" t="s">
         <v>31</v>
@@ -13466,7 +13466,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -13489,7 +13489,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F213" t="s">
         <v>34</v>
@@ -13512,7 +13512,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -13535,7 +13535,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F215" t="s">
         <v>31</v>
@@ -13558,7 +13558,7 @@
         <v>27</v>
       </c>
       <c r="E216">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F216" t="s">
         <v>28</v>
@@ -13581,7 +13581,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F217" t="s">
         <v>34</v>
@@ -13604,7 +13604,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -13627,7 +13627,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F219" t="s">
         <v>31</v>
@@ -13650,7 +13650,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -13673,7 +13673,7 @@
         <v>27</v>
       </c>
       <c r="E221">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F221" t="s">
         <v>34</v>
@@ -13696,7 +13696,7 @@
         <v>27</v>
       </c>
       <c r="E222">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F222" t="s">
         <v>28</v>
@@ -13742,7 +13742,7 @@
         <v>27</v>
       </c>
       <c r="E224">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F224" t="s">
         <v>28</v>
@@ -13788,7 +13788,7 @@
         <v>27</v>
       </c>
       <c r="E226">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F226" t="s">
         <v>28</v>
@@ -13834,7 +13834,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F228" t="s">
         <v>31</v>
@@ -13857,7 +13857,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -13880,7 +13880,7 @@
         <v>27</v>
       </c>
       <c r="E230">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F230" t="s">
         <v>34</v>
@@ -13903,7 +13903,7 @@
         <v>27</v>
       </c>
       <c r="E231">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F231" t="s">
         <v>28</v>
@@ -13926,7 +13926,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F232" t="s">
         <v>31</v>
@@ -13949,7 +13949,7 @@
         <v>27</v>
       </c>
       <c r="E233">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F233" t="s">
         <v>28</v>
@@ -13972,7 +13972,7 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F234" t="s">
         <v>34</v>
@@ -13995,7 +13995,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -14018,7 +14018,7 @@
         <v>27</v>
       </c>
       <c r="E236">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F236" t="s">
         <v>31</v>
@@ -14041,7 +14041,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -14064,7 +14064,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F238" t="s">
         <v>34</v>
@@ -14087,7 +14087,7 @@
         <v>27</v>
       </c>
       <c r="E239">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F239" t="s">
         <v>28</v>
@@ -14110,7 +14110,7 @@
         <v>27</v>
       </c>
       <c r="E240">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F240" t="s">
         <v>31</v>
@@ -14133,7 +14133,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -14156,7 +14156,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F242" t="s">
         <v>34</v>
@@ -14179,7 +14179,7 @@
         <v>27</v>
       </c>
       <c r="E243">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -14202,7 +14202,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F244" t="s">
         <v>31</v>
@@ -14225,7 +14225,7 @@
         <v>27</v>
       </c>
       <c r="E245">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F245" t="s">
         <v>28</v>
@@ -14248,7 +14248,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F246" t="s">
         <v>34</v>
@@ -14271,7 +14271,7 @@
         <v>27</v>
       </c>
       <c r="E247">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F247" t="s">
         <v>28</v>
@@ -14294,7 +14294,7 @@
         <v>27</v>
       </c>
       <c r="E248">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F248" t="s">
         <v>31</v>
@@ -14317,7 +14317,7 @@
         <v>27</v>
       </c>
       <c r="E249">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F249" t="s">
         <v>28</v>
@@ -14340,7 +14340,7 @@
         <v>27</v>
       </c>
       <c r="E250">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F250" t="s">
         <v>34</v>
@@ -14363,7 +14363,7 @@
         <v>27</v>
       </c>
       <c r="E251">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F251" t="s">
         <v>28</v>
@@ -14386,7 +14386,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -14409,7 +14409,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F253" t="s">
         <v>31</v>
@@ -14432,7 +14432,7 @@
         <v>27</v>
       </c>
       <c r="E254">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="F254" t="s">
         <v>28</v>
@@ -14455,7 +14455,7 @@
         <v>27</v>
       </c>
       <c r="E255">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F255" t="s">
         <v>34</v>
@@ -14478,7 +14478,7 @@
         <v>27</v>
       </c>
       <c r="E256">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F256" t="s">
         <v>28</v>
@@ -14501,7 +14501,7 @@
         <v>27</v>
       </c>
       <c r="E257">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F257" t="s">
         <v>31</v>
@@ -14524,7 +14524,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -14547,7 +14547,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F259" t="s">
         <v>34</v>
@@ -14570,7 +14570,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -14593,7 +14593,7 @@
         <v>27</v>
       </c>
       <c r="E261">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F261" t="s">
         <v>31</v>
@@ -14616,7 +14616,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -14639,7 +14639,7 @@
         <v>27</v>
       </c>
       <c r="E263">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F263" t="s">
         <v>34</v>
@@ -14662,7 +14662,7 @@
         <v>27</v>
       </c>
       <c r="E264">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -14685,7 +14685,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F265" t="s">
         <v>31</v>
@@ -14708,7 +14708,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -14731,7 +14731,7 @@
         <v>27</v>
       </c>
       <c r="E267">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F267" t="s">
         <v>34</v>
@@ -14754,7 +14754,7 @@
         <v>27</v>
       </c>
       <c r="E268">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F268" t="s">
         <v>28</v>
@@ -14777,7 +14777,7 @@
         <v>27</v>
       </c>
       <c r="E269">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F269" t="s">
         <v>31</v>
@@ -14823,7 +14823,7 @@
         <v>27</v>
       </c>
       <c r="E271">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F271" t="s">
         <v>34</v>
@@ -14846,7 +14846,7 @@
         <v>27</v>
       </c>
       <c r="E272">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F272" t="s">
         <v>28</v>
@@ -14869,7 +14869,7 @@
         <v>27</v>
       </c>
       <c r="E273">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F273" t="s">
         <v>31</v>
@@ -14892,7 +14892,7 @@
         <v>27</v>
       </c>
       <c r="E274">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F274" t="s">
         <v>28</v>
@@ -14915,7 +14915,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F275" t="s">
         <v>34</v>
@@ -14938,7 +14938,7 @@
         <v>27</v>
       </c>
       <c r="E276">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F276" t="s">
         <v>28</v>
@@ -14961,7 +14961,7 @@
         <v>27</v>
       </c>
       <c r="E277">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F277" t="s">
         <v>28</v>
@@ -14984,7 +14984,7 @@
         <v>27</v>
       </c>
       <c r="E278">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F278" t="s">
         <v>31</v>
@@ -15007,7 +15007,7 @@
         <v>27</v>
       </c>
       <c r="E279">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -15030,7 +15030,7 @@
         <v>27</v>
       </c>
       <c r="E280">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F280" t="s">
         <v>34</v>
@@ -15053,7 +15053,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -15076,7 +15076,7 @@
         <v>27</v>
       </c>
       <c r="E282">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F282" t="s">
         <v>31</v>
@@ -15099,7 +15099,7 @@
         <v>27</v>
       </c>
       <c r="E283">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F283" t="s">
         <v>28</v>
@@ -15122,7 +15122,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F284" t="s">
         <v>34</v>
@@ -15145,7 +15145,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -15168,7 +15168,7 @@
         <v>27</v>
       </c>
       <c r="E286">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F286" t="s">
         <v>31</v>
@@ -15191,7 +15191,7 @@
         <v>27</v>
       </c>
       <c r="E287">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F287" t="s">
         <v>28</v>
@@ -15214,7 +15214,7 @@
         <v>27</v>
       </c>
       <c r="E288">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F288" t="s">
         <v>34</v>
@@ -15237,7 +15237,7 @@
         <v>27</v>
       </c>
       <c r="E289">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F289" t="s">
         <v>28</v>
@@ -15260,7 +15260,7 @@
         <v>27</v>
       </c>
       <c r="E290">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F290" t="s">
         <v>31</v>
@@ -15283,7 +15283,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -15306,7 +15306,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F292" t="s">
         <v>34</v>
@@ -15329,7 +15329,7 @@
         <v>27</v>
       </c>
       <c r="E293">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -15352,7 +15352,7 @@
         <v>27</v>
       </c>
       <c r="E294">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F294" t="s">
         <v>31</v>
@@ -15375,7 +15375,7 @@
         <v>27</v>
       </c>
       <c r="E295">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F295" t="s">
         <v>28</v>
@@ -15398,7 +15398,7 @@
         <v>27</v>
       </c>
       <c r="E296">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F296" t="s">
         <v>34</v>
@@ -15421,7 +15421,7 @@
         <v>27</v>
       </c>
       <c r="E297">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F297" t="s">
         <v>28</v>
@@ -15444,7 +15444,7 @@
         <v>27</v>
       </c>
       <c r="E298">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F298" t="s">
         <v>31</v>
@@ -15467,7 +15467,7 @@
         <v>27</v>
       </c>
       <c r="E299">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F299" t="s">
         <v>28</v>
@@ -15490,7 +15490,7 @@
         <v>27</v>
       </c>
       <c r="E300">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F300" t="s">
         <v>34</v>

--- a/all-test-reports/vulnerability/vulnerability_test_report.xlsx
+++ b/all-test-reports/vulnerability/vulnerability_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 11:43:44 am</t>
+    <t>28/7/2026, 11:57:29 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1694,7 +1694,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="10">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>28</v>
@@ -1717,7 +1717,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="10">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>31</v>
@@ -1740,7 +1740,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="10">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>28</v>
@@ -1763,7 +1763,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="10">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>34</v>
@@ -1786,7 +1786,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="10">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>28</v>
@@ -1809,7 +1809,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="10">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>31</v>
@@ -1832,7 +1832,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="10">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>28</v>
@@ -1855,7 +1855,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="10">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>34</v>
@@ -1878,7 +1878,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="10">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>28</v>
@@ -1901,7 +1901,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="10">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>31</v>
@@ -1924,7 +1924,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="10">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>28</v>
@@ -1947,7 +1947,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="10">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>34</v>
@@ -1970,7 +1970,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>28</v>
@@ -1993,7 +1993,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>31</v>
@@ -2016,7 +2016,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="10">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>28</v>
@@ -2039,7 +2039,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>34</v>
@@ -2062,7 +2062,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="10">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>28</v>
@@ -2085,7 +2085,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>31</v>
@@ -2131,7 +2131,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="10">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>34</v>
@@ -2154,7 +2154,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="10">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>28</v>
@@ -2177,7 +2177,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>31</v>
@@ -2200,7 +2200,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="10">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>28</v>
@@ -2246,7 +2246,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="10">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>28</v>
@@ -2269,7 +2269,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="10">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>31</v>
@@ -2292,7 +2292,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="10">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>28</v>
@@ -2315,7 +2315,7 @@
         <v>27</v>
       </c>
       <c r="E29" s="10">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>34</v>
@@ -2338,7 +2338,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="10">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>28</v>
@@ -2361,7 +2361,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="10">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>31</v>
@@ -2384,7 +2384,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="10">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>28</v>
@@ -2407,7 +2407,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="10">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>31</v>
@@ -2430,7 +2430,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="10">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>28</v>
@@ -2453,7 +2453,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="10">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>34</v>
@@ -2476,7 +2476,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="10">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>28</v>
@@ -2499,7 +2499,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>31</v>
@@ -2522,7 +2522,7 @@
         <v>27</v>
       </c>
       <c r="E38" s="10">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>28</v>
@@ -2545,7 +2545,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="10">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>34</v>
@@ -2568,7 +2568,7 @@
         <v>27</v>
       </c>
       <c r="E40" s="10">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>28</v>
@@ -2591,7 +2591,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>31</v>
@@ -2614,7 +2614,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="10">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>28</v>
@@ -2637,7 +2637,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="10">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>34</v>
@@ -2660,7 +2660,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="10">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>28</v>
@@ -2683,7 +2683,7 @@
         <v>27</v>
       </c>
       <c r="E45" s="10">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>31</v>
@@ -2706,7 +2706,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="10">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>28</v>
@@ -2729,7 +2729,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="10">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>34</v>
@@ -2752,7 +2752,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="10">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>28</v>
@@ -2775,7 +2775,7 @@
         <v>27</v>
       </c>
       <c r="E49" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>31</v>
@@ -2798,7 +2798,7 @@
         <v>27</v>
       </c>
       <c r="E50" s="10">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>28</v>
@@ -2821,7 +2821,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>34</v>
@@ -2844,7 +2844,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="10">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>28</v>
@@ -2867,7 +2867,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="10">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>31</v>
@@ -2890,7 +2890,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="10">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>28</v>
@@ -2913,7 +2913,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="10">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>34</v>
@@ -2936,7 +2936,7 @@
         <v>27</v>
       </c>
       <c r="E56" s="10">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>28</v>
@@ -2959,7 +2959,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="10">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>31</v>
@@ -2982,7 +2982,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="10">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>28</v>
@@ -3005,7 +3005,7 @@
         <v>27</v>
       </c>
       <c r="E59" s="10">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>34</v>
@@ -3051,7 +3051,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="10">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>31</v>
@@ -3074,7 +3074,7 @@
         <v>27</v>
       </c>
       <c r="E62" s="10">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>28</v>
@@ -3097,7 +3097,7 @@
         <v>27</v>
       </c>
       <c r="E63" s="10">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>31</v>
@@ -3120,7 +3120,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="10">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>28</v>
@@ -3143,7 +3143,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="10">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>34</v>
@@ -3166,7 +3166,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="10">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>28</v>
@@ -3189,7 +3189,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="10">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>31</v>
@@ -3212,7 +3212,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="10">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>28</v>
@@ -3235,7 +3235,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="10">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>34</v>
@@ -3258,7 +3258,7 @@
         <v>27</v>
       </c>
       <c r="E70" s="10">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>28</v>
@@ -3281,7 +3281,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="10">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>31</v>
@@ -3304,7 +3304,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="10">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>28</v>
@@ -3350,7 +3350,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="10">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>28</v>
@@ -3373,7 +3373,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="10">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>31</v>
@@ -3396,7 +3396,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="10">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>28</v>
@@ -3419,7 +3419,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="10">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>34</v>
@@ -3442,7 +3442,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="10">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>28</v>
@@ -3465,7 +3465,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="10">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>31</v>
@@ -3488,7 +3488,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="10">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>28</v>
@@ -3511,7 +3511,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="10">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>34</v>
@@ -3534,7 +3534,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="10">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>28</v>
@@ -3557,7 +3557,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="10">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>31</v>
@@ -3580,7 +3580,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="10">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>28</v>
@@ -3603,7 +3603,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="10">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>34</v>
@@ -3626,7 +3626,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="10">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>28</v>
@@ -3649,7 +3649,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="10">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>31</v>
@@ -3672,7 +3672,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>28</v>
@@ -3695,7 +3695,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="10">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>34</v>
@@ -3718,7 +3718,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="10">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>28</v>
@@ -3741,7 +3741,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="10">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>31</v>
@@ -3764,7 +3764,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="10">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>28</v>
@@ -3787,7 +3787,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="10">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>31</v>
@@ -3810,7 +3810,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="10">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>28</v>
@@ -3833,7 +3833,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="10">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>34</v>
@@ -3879,7 +3879,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="10">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>31</v>
@@ -3902,7 +3902,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="10">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>28</v>
@@ -3925,7 +3925,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="10">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>34</v>
@@ -3948,7 +3948,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="10">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>28</v>
@@ -3971,7 +3971,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="10">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>31</v>
@@ -3994,7 +3994,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>28</v>
@@ -4017,7 +4017,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="10">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>34</v>
@@ -4040,7 +4040,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="10">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>28</v>
@@ -4063,7 +4063,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="10">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>31</v>
@@ -4086,7 +4086,7 @@
         <v>27</v>
       </c>
       <c r="E106" s="10">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>28</v>
@@ -4109,7 +4109,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="10">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>34</v>
@@ -4132,7 +4132,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="10">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>28</v>
@@ -4155,7 +4155,7 @@
         <v>27</v>
       </c>
       <c r="E109" s="10">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>31</v>
@@ -4178,7 +4178,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="10">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>28</v>
@@ -4201,7 +4201,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="10">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>34</v>
@@ -4224,7 +4224,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="10">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>28</v>
@@ -4247,7 +4247,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="10">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F113" s="8" t="s">
         <v>31</v>
@@ -4270,7 +4270,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="10">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>28</v>
@@ -4293,7 +4293,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="10">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>34</v>
@@ -4316,7 +4316,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="10">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>28</v>
@@ -4339,7 +4339,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="10">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F117" s="8" t="s">
         <v>31</v>
@@ -4362,7 +4362,7 @@
         <v>27</v>
       </c>
       <c r="E118" s="10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F118" s="8" t="s">
         <v>28</v>
@@ -4385,7 +4385,7 @@
         <v>27</v>
       </c>
       <c r="E119" s="10">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F119" s="8" t="s">
         <v>34</v>
@@ -4408,7 +4408,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="10">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F120" s="8" t="s">
         <v>28</v>
@@ -4431,7 +4431,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="10">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F121" s="8" t="s">
         <v>31</v>
@@ -4454,7 +4454,7 @@
         <v>27</v>
       </c>
       <c r="E122" s="10">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F122" s="8" t="s">
         <v>28</v>
@@ -4477,7 +4477,7 @@
         <v>27</v>
       </c>
       <c r="E123" s="10">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>31</v>
@@ -4523,7 +4523,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="10">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>34</v>
@@ -4546,7 +4546,7 @@
         <v>27</v>
       </c>
       <c r="E126" s="10">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F126" s="8" t="s">
         <v>28</v>
@@ -4569,7 +4569,7 @@
         <v>27</v>
       </c>
       <c r="E127" s="10">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F127" s="8" t="s">
         <v>31</v>
@@ -4592,7 +4592,7 @@
         <v>27</v>
       </c>
       <c r="E128" s="10">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F128" s="8" t="s">
         <v>28</v>
@@ -4615,7 +4615,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="10">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F129" s="8" t="s">
         <v>34</v>
@@ -4661,7 +4661,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="10">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F131" s="8" t="s">
         <v>31</v>
@@ -4684,7 +4684,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="10">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F132" s="8" t="s">
         <v>28</v>
@@ -4707,7 +4707,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="10">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F133" s="8" t="s">
         <v>34</v>
@@ -4730,7 +4730,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="10">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F134" s="8" t="s">
         <v>28</v>
@@ -4753,7 +4753,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F135" s="8" t="s">
         <v>31</v>
@@ -4776,7 +4776,7 @@
         <v>27</v>
       </c>
       <c r="E136" s="10">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F136" s="8" t="s">
         <v>28</v>
@@ -4799,7 +4799,7 @@
         <v>27</v>
       </c>
       <c r="E137" s="10">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F137" s="8" t="s">
         <v>34</v>
@@ -4822,7 +4822,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="10">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F138" s="8" t="s">
         <v>28</v>
@@ -4845,7 +4845,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="10">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F139" s="8" t="s">
         <v>31</v>
@@ -4868,7 +4868,7 @@
         <v>27</v>
       </c>
       <c r="E140" s="10">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F140" s="8" t="s">
         <v>28</v>
@@ -4891,7 +4891,7 @@
         <v>27</v>
       </c>
       <c r="E141" s="10">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F141" s="8" t="s">
         <v>34</v>
@@ -4914,7 +4914,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F142" s="8" t="s">
         <v>28</v>
@@ -4937,7 +4937,7 @@
         <v>27</v>
       </c>
       <c r="E143" s="10">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F143" s="8" t="s">
         <v>31</v>
@@ -4960,7 +4960,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="10">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F144" s="8" t="s">
         <v>28</v>
@@ -4983,7 +4983,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="10">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F145" s="8" t="s">
         <v>34</v>
@@ -5006,7 +5006,7 @@
         <v>27</v>
       </c>
       <c r="E146" s="10">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>28</v>
@@ -5029,7 +5029,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="10">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F147" s="8" t="s">
         <v>31</v>
@@ -5052,7 +5052,7 @@
         <v>27</v>
       </c>
       <c r="E148" s="10">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F148" s="8" t="s">
         <v>28</v>
@@ -5075,7 +5075,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="10">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F149" s="8" t="s">
         <v>34</v>
@@ -5098,7 +5098,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="10">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>28</v>
@@ -5144,7 +5144,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="10">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>28</v>
@@ -5190,7 +5190,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="10">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>28</v>
@@ -5213,7 +5213,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="10">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F155" s="8" t="s">
         <v>34</v>
@@ -5236,7 +5236,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="10">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F156" s="8" t="s">
         <v>28</v>
@@ -5259,7 +5259,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="10">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F157" s="8" t="s">
         <v>31</v>
@@ -5282,7 +5282,7 @@
         <v>27</v>
       </c>
       <c r="E158" s="10">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F158" s="8" t="s">
         <v>28</v>
@@ -5305,7 +5305,7 @@
         <v>27</v>
       </c>
       <c r="E159" s="10">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F159" s="8" t="s">
         <v>34</v>
@@ -5328,7 +5328,7 @@
         <v>27</v>
       </c>
       <c r="E160" s="10">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F160" s="8" t="s">
         <v>28</v>
@@ -5351,7 +5351,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F161" s="8" t="s">
         <v>31</v>
@@ -5374,7 +5374,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="10">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F162" s="8" t="s">
         <v>28</v>
@@ -5397,7 +5397,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F163" s="8" t="s">
         <v>34</v>
@@ -5420,7 +5420,7 @@
         <v>27</v>
       </c>
       <c r="E164" s="10">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F164" s="8" t="s">
         <v>28</v>
@@ -5443,7 +5443,7 @@
         <v>27</v>
       </c>
       <c r="E165" s="10">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F165" s="8" t="s">
         <v>31</v>
@@ -5466,7 +5466,7 @@
         <v>27</v>
       </c>
       <c r="E166" s="10">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F166" s="8" t="s">
         <v>28</v>
@@ -5489,7 +5489,7 @@
         <v>27</v>
       </c>
       <c r="E167" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F167" s="8" t="s">
         <v>34</v>
@@ -5512,7 +5512,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="10">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F168" s="8" t="s">
         <v>28</v>
@@ -5535,7 +5535,7 @@
         <v>27</v>
       </c>
       <c r="E169" s="10">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F169" s="8" t="s">
         <v>31</v>
@@ -5558,7 +5558,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="10">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F170" s="8" t="s">
         <v>28</v>
@@ -5581,7 +5581,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F171" s="8" t="s">
         <v>34</v>
@@ -5604,7 +5604,7 @@
         <v>27</v>
       </c>
       <c r="E172" s="10">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F172" s="8" t="s">
         <v>28</v>
@@ -5627,7 +5627,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="10">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F173" s="8" t="s">
         <v>31</v>
@@ -5650,7 +5650,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="10">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F174" s="8" t="s">
         <v>28</v>
@@ -5673,7 +5673,7 @@
         <v>27</v>
       </c>
       <c r="E175" s="10">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F175" s="8" t="s">
         <v>34</v>
@@ -5696,7 +5696,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="10">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F176" s="8" t="s">
         <v>28</v>
@@ -5719,7 +5719,7 @@
         <v>27</v>
       </c>
       <c r="E177" s="10">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F177" s="8" t="s">
         <v>28</v>
@@ -5742,7 +5742,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="10">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F178" s="8" t="s">
         <v>31</v>
@@ -5765,7 +5765,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="10">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F179" s="8" t="s">
         <v>28</v>
@@ -5788,7 +5788,7 @@
         <v>27</v>
       </c>
       <c r="E180" s="10">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F180" s="8" t="s">
         <v>34</v>
@@ -5811,7 +5811,7 @@
         <v>27</v>
       </c>
       <c r="E181" s="10">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F181" s="8" t="s">
         <v>28</v>
@@ -5834,7 +5834,7 @@
         <v>27</v>
       </c>
       <c r="E182" s="10">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F182" s="8" t="s">
         <v>31</v>
@@ -5857,7 +5857,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="10">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F183" s="8" t="s">
         <v>28</v>
@@ -5880,7 +5880,7 @@
         <v>27</v>
       </c>
       <c r="E184" s="10">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F184" s="8" t="s">
         <v>34</v>
@@ -5903,7 +5903,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="10">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F185" s="8" t="s">
         <v>28</v>
@@ -5926,7 +5926,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="10">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F186" s="8" t="s">
         <v>31</v>
@@ -5949,7 +5949,7 @@
         <v>27</v>
       </c>
       <c r="E187" s="10">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F187" s="8" t="s">
         <v>28</v>
@@ -5972,7 +5972,7 @@
         <v>27</v>
       </c>
       <c r="E188" s="10">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F188" s="8" t="s">
         <v>34</v>
@@ -5995,7 +5995,7 @@
         <v>27</v>
       </c>
       <c r="E189" s="10">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F189" s="8" t="s">
         <v>28</v>
@@ -6018,7 +6018,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="10">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F190" s="8" t="s">
         <v>31</v>
@@ -6041,7 +6041,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="10">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F191" s="8" t="s">
         <v>28</v>
@@ -6064,7 +6064,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="10">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F192" s="8" t="s">
         <v>34</v>
@@ -6087,7 +6087,7 @@
         <v>27</v>
       </c>
       <c r="E193" s="10">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F193" s="8" t="s">
         <v>28</v>
@@ -6110,7 +6110,7 @@
         <v>27</v>
       </c>
       <c r="E194" s="10">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F194" s="8" t="s">
         <v>31</v>
@@ -6133,7 +6133,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="10">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F195" s="8" t="s">
         <v>28</v>
@@ -6156,7 +6156,7 @@
         <v>27</v>
       </c>
       <c r="E196" s="10">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F196" s="8" t="s">
         <v>34</v>
@@ -6179,7 +6179,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="10">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F197" s="8" t="s">
         <v>28</v>
@@ -6202,7 +6202,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="10">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F198" s="8" t="s">
         <v>31</v>
@@ -6225,7 +6225,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="10">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F199" s="8" t="s">
         <v>28</v>
@@ -6248,7 +6248,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="10">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F200" s="8" t="s">
         <v>34</v>
@@ -6271,7 +6271,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="10">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F201" s="8" t="s">
         <v>28</v>
@@ -6294,7 +6294,7 @@
         <v>27</v>
       </c>
       <c r="E202" s="10">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F202" s="8" t="s">
         <v>28</v>
@@ -6317,7 +6317,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="10">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F203" s="8" t="s">
         <v>31</v>
@@ -6340,7 +6340,7 @@
         <v>27</v>
       </c>
       <c r="E204" s="10">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F204" s="8" t="s">
         <v>28</v>
@@ -6363,7 +6363,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="10">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F205" s="8" t="s">
         <v>34</v>
@@ -6386,7 +6386,7 @@
         <v>27</v>
       </c>
       <c r="E206" s="10">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F206" s="8" t="s">
         <v>28</v>
@@ -6409,7 +6409,7 @@
         <v>27</v>
       </c>
       <c r="E207" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F207" s="8" t="s">
         <v>31</v>
@@ -6432,7 +6432,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F208" s="8" t="s">
         <v>28</v>
@@ -6455,7 +6455,7 @@
         <v>27</v>
       </c>
       <c r="E209" s="10">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F209" s="8" t="s">
         <v>34</v>
@@ -6478,7 +6478,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="10">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F210" s="8" t="s">
         <v>28</v>
@@ -6501,7 +6501,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="10">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F211" s="8" t="s">
         <v>31</v>
@@ -6524,7 +6524,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="10">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F212" s="8" t="s">
         <v>28</v>
@@ -6547,7 +6547,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="10">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F213" s="8" t="s">
         <v>34</v>
@@ -6570,7 +6570,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="10">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F214" s="8" t="s">
         <v>28</v>
@@ -6593,7 +6593,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="10">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F215" s="8" t="s">
         <v>31</v>
@@ -6616,7 +6616,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="10">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F216" s="8" t="s">
         <v>28</v>
@@ -6639,7 +6639,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="10">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F217" s="8" t="s">
         <v>34</v>
@@ -6662,7 +6662,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="10">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F218" s="8" t="s">
         <v>28</v>
@@ -6685,7 +6685,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="10">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F219" s="8" t="s">
         <v>31</v>
@@ -6708,7 +6708,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F220" s="8" t="s">
         <v>28</v>
@@ -6731,7 +6731,7 @@
         <v>27</v>
       </c>
       <c r="E221" s="10">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F221" s="8" t="s">
         <v>34</v>
@@ -6754,7 +6754,7 @@
         <v>27</v>
       </c>
       <c r="E222" s="10">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F222" s="8" t="s">
         <v>28</v>
@@ -6777,7 +6777,7 @@
         <v>27</v>
       </c>
       <c r="E223" s="10">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F223" s="8" t="s">
         <v>31</v>
@@ -6800,7 +6800,7 @@
         <v>27</v>
       </c>
       <c r="E224" s="10">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F224" s="8" t="s">
         <v>28</v>
@@ -6823,7 +6823,7 @@
         <v>27</v>
       </c>
       <c r="E225" s="10">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F225" s="8" t="s">
         <v>34</v>
@@ -6846,7 +6846,7 @@
         <v>27</v>
       </c>
       <c r="E226" s="10">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F226" s="8" t="s">
         <v>28</v>
@@ -6869,7 +6869,7 @@
         <v>27</v>
       </c>
       <c r="E227" s="10">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F227" s="8" t="s">
         <v>28</v>
@@ -6892,7 +6892,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F228" s="8" t="s">
         <v>31</v>
@@ -6915,7 +6915,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="10">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F229" s="8" t="s">
         <v>28</v>
@@ -6938,7 +6938,7 @@
         <v>27</v>
       </c>
       <c r="E230" s="10">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F230" s="8" t="s">
         <v>34</v>
@@ -6961,7 +6961,7 @@
         <v>27</v>
       </c>
       <c r="E231" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F231" s="8" t="s">
         <v>28</v>
@@ -6984,7 +6984,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="10">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F232" s="8" t="s">
         <v>31</v>
@@ -7030,7 +7030,7 @@
         <v>27</v>
       </c>
       <c r="E234" s="10">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F234" s="8" t="s">
         <v>34</v>
@@ -7053,7 +7053,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="10">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F235" s="8" t="s">
         <v>28</v>
@@ -7076,7 +7076,7 @@
         <v>27</v>
       </c>
       <c r="E236" s="10">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F236" s="8" t="s">
         <v>31</v>
@@ -7099,7 +7099,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="10">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F237" s="8" t="s">
         <v>28</v>
@@ -7122,7 +7122,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="10">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F238" s="8" t="s">
         <v>34</v>
@@ -7145,7 +7145,7 @@
         <v>27</v>
       </c>
       <c r="E239" s="10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F239" s="8" t="s">
         <v>28</v>
@@ -7168,7 +7168,7 @@
         <v>27</v>
       </c>
       <c r="E240" s="10">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F240" s="8" t="s">
         <v>31</v>
@@ -7191,7 +7191,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="10">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F241" s="8" t="s">
         <v>28</v>
@@ -7214,7 +7214,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="10">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F242" s="8" t="s">
         <v>34</v>
@@ -7237,7 +7237,7 @@
         <v>27</v>
       </c>
       <c r="E243" s="10">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F243" s="8" t="s">
         <v>28</v>
@@ -7260,7 +7260,7 @@
         <v>27</v>
       </c>
       <c r="E244" s="10">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F244" s="8" t="s">
         <v>31</v>
@@ -7283,7 +7283,7 @@
         <v>27</v>
       </c>
       <c r="E245" s="10">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F245" s="8" t="s">
         <v>28</v>
@@ -7329,7 +7329,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F247" s="8" t="s">
         <v>28</v>
@@ -7352,7 +7352,7 @@
         <v>27</v>
       </c>
       <c r="E248" s="10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F248" s="8" t="s">
         <v>31</v>
@@ -7375,7 +7375,7 @@
         <v>27</v>
       </c>
       <c r="E249" s="10">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F249" s="8" t="s">
         <v>28</v>
@@ -7398,7 +7398,7 @@
         <v>27</v>
       </c>
       <c r="E250" s="10">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F250" s="8" t="s">
         <v>34</v>
@@ -7444,7 +7444,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="10">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F252" s="8" t="s">
         <v>28</v>
@@ -7467,7 +7467,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="10">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F253" s="8" t="s">
         <v>31</v>
@@ -7490,7 +7490,7 @@
         <v>27</v>
       </c>
       <c r="E254" s="10">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F254" s="8" t="s">
         <v>28</v>
@@ -7513,7 +7513,7 @@
         <v>27</v>
       </c>
       <c r="E255" s="10">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F255" s="8" t="s">
         <v>34</v>
@@ -7536,7 +7536,7 @@
         <v>27</v>
       </c>
       <c r="E256" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F256" s="8" t="s">
         <v>28</v>
@@ -7559,7 +7559,7 @@
         <v>27</v>
       </c>
       <c r="E257" s="10">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F257" s="8" t="s">
         <v>31</v>
@@ -7582,7 +7582,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="10">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F258" s="8" t="s">
         <v>28</v>
@@ -7605,7 +7605,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="10">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F259" s="8" t="s">
         <v>34</v>
@@ -7628,7 +7628,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="10">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F260" s="8" t="s">
         <v>28</v>
@@ -7651,7 +7651,7 @@
         <v>27</v>
       </c>
       <c r="E261" s="10">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F261" s="8" t="s">
         <v>31</v>
@@ -7674,7 +7674,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="10">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F262" s="8" t="s">
         <v>28</v>
@@ -7697,7 +7697,7 @@
         <v>27</v>
       </c>
       <c r="E263" s="10">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F263" s="8" t="s">
         <v>34</v>
@@ -7720,7 +7720,7 @@
         <v>27</v>
       </c>
       <c r="E264" s="10">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F264" s="8" t="s">
         <v>28</v>
@@ -7743,7 +7743,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="10">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F265" s="8" t="s">
         <v>31</v>
@@ -7766,7 +7766,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="10">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F266" s="8" t="s">
         <v>28</v>
@@ -7789,7 +7789,7 @@
         <v>27</v>
       </c>
       <c r="E267" s="10">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F267" s="8" t="s">
         <v>34</v>
@@ -7812,7 +7812,7 @@
         <v>27</v>
       </c>
       <c r="E268" s="10">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F268" s="8" t="s">
         <v>28</v>
@@ -7835,7 +7835,7 @@
         <v>27</v>
       </c>
       <c r="E269" s="10">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F269" s="8" t="s">
         <v>31</v>
@@ -7858,7 +7858,7 @@
         <v>27</v>
       </c>
       <c r="E270" s="10">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F270" s="8" t="s">
         <v>28</v>
@@ -7904,7 +7904,7 @@
         <v>27</v>
       </c>
       <c r="E272" s="10">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F272" s="8" t="s">
         <v>28</v>
@@ -7927,7 +7927,7 @@
         <v>27</v>
       </c>
       <c r="E273" s="10">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F273" s="8" t="s">
         <v>31</v>
@@ -7950,7 +7950,7 @@
         <v>27</v>
       </c>
       <c r="E274" s="10">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F274" s="8" t="s">
         <v>28</v>
@@ -7973,7 +7973,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="10">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F275" s="8" t="s">
         <v>34</v>
@@ -7996,7 +7996,7 @@
         <v>27</v>
       </c>
       <c r="E276" s="10">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F276" s="8" t="s">
         <v>28</v>
@@ -8019,7 +8019,7 @@
         <v>27</v>
       </c>
       <c r="E277" s="10">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F277" s="8" t="s">
         <v>28</v>
@@ -8042,7 +8042,7 @@
         <v>27</v>
       </c>
       <c r="E278" s="10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F278" s="8" t="s">
         <v>31</v>
@@ -8065,7 +8065,7 @@
         <v>27</v>
       </c>
       <c r="E279" s="10">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F279" s="8" t="s">
         <v>28</v>
@@ -8088,7 +8088,7 @@
         <v>27</v>
       </c>
       <c r="E280" s="10">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F280" s="8" t="s">
         <v>34</v>
@@ -8111,7 +8111,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="10">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F281" s="8" t="s">
         <v>28</v>
@@ -8134,7 +8134,7 @@
         <v>27</v>
       </c>
       <c r="E282" s="10">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F282" s="8" t="s">
         <v>31</v>
@@ -8157,7 +8157,7 @@
         <v>27</v>
       </c>
       <c r="E283" s="10">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F283" s="8" t="s">
         <v>28</v>
@@ -8180,7 +8180,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="10">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F284" s="8" t="s">
         <v>34</v>
@@ -8203,7 +8203,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="10">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F285" s="8" t="s">
         <v>28</v>
@@ -8226,7 +8226,7 @@
         <v>27</v>
       </c>
       <c r="E286" s="10">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F286" s="8" t="s">
         <v>31</v>
@@ -8249,7 +8249,7 @@
         <v>27</v>
       </c>
       <c r="E287" s="10">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F287" s="8" t="s">
         <v>28</v>
@@ -8272,7 +8272,7 @@
         <v>27</v>
       </c>
       <c r="E288" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F288" s="8" t="s">
         <v>34</v>
@@ -8295,7 +8295,7 @@
         <v>27</v>
       </c>
       <c r="E289" s="10">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F289" s="8" t="s">
         <v>28</v>
@@ -8318,7 +8318,7 @@
         <v>27</v>
       </c>
       <c r="E290" s="10">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F290" s="8" t="s">
         <v>31</v>
@@ -8341,7 +8341,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F291" s="8" t="s">
         <v>28</v>
@@ -8364,7 +8364,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="10">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F292" s="8" t="s">
         <v>34</v>
@@ -8387,7 +8387,7 @@
         <v>27</v>
       </c>
       <c r="E293" s="10">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F293" s="8" t="s">
         <v>28</v>
@@ -8410,7 +8410,7 @@
         <v>27</v>
       </c>
       <c r="E294" s="10">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F294" s="8" t="s">
         <v>31</v>
@@ -8433,7 +8433,7 @@
         <v>27</v>
       </c>
       <c r="E295" s="10">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F295" s="8" t="s">
         <v>28</v>
@@ -8456,7 +8456,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="10">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F296" s="8" t="s">
         <v>34</v>
@@ -8479,7 +8479,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F297" s="8" t="s">
         <v>28</v>
@@ -8502,7 +8502,7 @@
         <v>27</v>
       </c>
       <c r="E298" s="10">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F298" s="8" t="s">
         <v>31</v>
@@ -8525,7 +8525,7 @@
         <v>27</v>
       </c>
       <c r="E299" s="10">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F299" s="8" t="s">
         <v>28</v>
@@ -8548,7 +8548,7 @@
         <v>27</v>
       </c>
       <c r="E300" s="10">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F300" s="8" t="s">
         <v>34</v>
@@ -8571,7 +8571,7 @@
         <v>27</v>
       </c>
       <c r="E301" s="10">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F301" s="8" t="s">
         <v>28</v>
@@ -8636,7 +8636,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -8659,7 +8659,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F3" t="s">
         <v>31</v>
@@ -8682,7 +8682,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -8705,7 +8705,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
         <v>34</v>
@@ -8728,7 +8728,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -8751,7 +8751,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F7" t="s">
         <v>31</v>
@@ -8774,7 +8774,7 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -8797,7 +8797,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
@@ -8820,7 +8820,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -8843,7 +8843,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
         <v>31</v>
@@ -8866,7 +8866,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -8889,7 +8889,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s">
         <v>34</v>
@@ -8912,7 +8912,7 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -8935,7 +8935,7 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F15" t="s">
         <v>31</v>
@@ -8958,7 +8958,7 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -8981,7 +8981,7 @@
         <v>27</v>
       </c>
       <c r="E17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F17" t="s">
         <v>34</v>
@@ -9004,7 +9004,7 @@
         <v>27</v>
       </c>
       <c r="E18">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -9027,7 +9027,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F19" t="s">
         <v>31</v>
@@ -9073,7 +9073,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F21" t="s">
         <v>34</v>
@@ -9096,7 +9096,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -9119,7 +9119,7 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F23" t="s">
         <v>31</v>
@@ -9142,7 +9142,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -9188,7 +9188,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -9211,7 +9211,7 @@
         <v>27</v>
       </c>
       <c r="E27">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F27" t="s">
         <v>31</v>
@@ -9234,7 +9234,7 @@
         <v>27</v>
       </c>
       <c r="E28">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -9257,7 +9257,7 @@
         <v>27</v>
       </c>
       <c r="E29">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F29" t="s">
         <v>34</v>
@@ -9280,7 +9280,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -9303,7 +9303,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F31" t="s">
         <v>31</v>
@@ -9326,7 +9326,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -9349,7 +9349,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F33" t="s">
         <v>31</v>
@@ -9372,7 +9372,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -9395,7 +9395,7 @@
         <v>27</v>
       </c>
       <c r="E35">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
@@ -9418,7 +9418,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -9441,7 +9441,7 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F37" t="s">
         <v>31</v>
@@ -9464,7 +9464,7 @@
         <v>27</v>
       </c>
       <c r="E38">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -9487,7 +9487,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F39" t="s">
         <v>34</v>
@@ -9510,7 +9510,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -9533,7 +9533,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F41" t="s">
         <v>31</v>
@@ -9556,7 +9556,7 @@
         <v>27</v>
       </c>
       <c r="E42">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -9579,7 +9579,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F43" t="s">
         <v>34</v>
@@ -9602,7 +9602,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -9625,7 +9625,7 @@
         <v>27</v>
       </c>
       <c r="E45">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F45" t="s">
         <v>31</v>
@@ -9648,7 +9648,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -9671,7 +9671,7 @@
         <v>27</v>
       </c>
       <c r="E47">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F47" t="s">
         <v>34</v>
@@ -9694,7 +9694,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -9717,7 +9717,7 @@
         <v>27</v>
       </c>
       <c r="E49">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F49" t="s">
         <v>31</v>
@@ -9740,7 +9740,7 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F50" t="s">
         <v>28</v>
@@ -9763,7 +9763,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F51" t="s">
         <v>34</v>
@@ -9786,7 +9786,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -9809,7 +9809,7 @@
         <v>27</v>
       </c>
       <c r="E53">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F53" t="s">
         <v>31</v>
@@ -9832,7 +9832,7 @@
         <v>27</v>
       </c>
       <c r="E54">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -9855,7 +9855,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F55" t="s">
         <v>34</v>
@@ -9878,7 +9878,7 @@
         <v>27</v>
       </c>
       <c r="E56">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -9901,7 +9901,7 @@
         <v>27</v>
       </c>
       <c r="E57">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F57" t="s">
         <v>31</v>
@@ -9924,7 +9924,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -9947,7 +9947,7 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F59" t="s">
         <v>34</v>
@@ -9993,7 +9993,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F61" t="s">
         <v>31</v>
@@ -10016,7 +10016,7 @@
         <v>27</v>
       </c>
       <c r="E62">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F62" t="s">
         <v>28</v>
@@ -10039,7 +10039,7 @@
         <v>27</v>
       </c>
       <c r="E63">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F63" t="s">
         <v>31</v>
@@ -10062,7 +10062,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -10085,7 +10085,7 @@
         <v>27</v>
       </c>
       <c r="E65">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F65" t="s">
         <v>34</v>
@@ -10108,7 +10108,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -10131,7 +10131,7 @@
         <v>27</v>
       </c>
       <c r="E67">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F67" t="s">
         <v>31</v>
@@ -10154,7 +10154,7 @@
         <v>27</v>
       </c>
       <c r="E68">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
@@ -10177,7 +10177,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F69" t="s">
         <v>34</v>
@@ -10200,7 +10200,7 @@
         <v>27</v>
       </c>
       <c r="E70">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -10223,7 +10223,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F71" t="s">
         <v>31</v>
@@ -10246,7 +10246,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -10292,7 +10292,7 @@
         <v>27</v>
       </c>
       <c r="E74">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -10315,7 +10315,7 @@
         <v>27</v>
       </c>
       <c r="E75">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F75" t="s">
         <v>31</v>
@@ -10338,7 +10338,7 @@
         <v>27</v>
       </c>
       <c r="E76">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
@@ -10361,7 +10361,7 @@
         <v>27</v>
       </c>
       <c r="E77">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F77" t="s">
         <v>34</v>
@@ -10384,7 +10384,7 @@
         <v>27</v>
       </c>
       <c r="E78">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
@@ -10407,7 +10407,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F79" t="s">
         <v>31</v>
@@ -10430,7 +10430,7 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
@@ -10453,7 +10453,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F81" t="s">
         <v>34</v>
@@ -10476,7 +10476,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -10499,7 +10499,7 @@
         <v>27</v>
       </c>
       <c r="E83">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F83" t="s">
         <v>31</v>
@@ -10522,7 +10522,7 @@
         <v>27</v>
       </c>
       <c r="E84">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
@@ -10545,7 +10545,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F85" t="s">
         <v>34</v>
@@ -10568,7 +10568,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -10591,7 +10591,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F87" t="s">
         <v>31</v>
@@ -10614,7 +10614,7 @@
         <v>27</v>
       </c>
       <c r="E88">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -10637,7 +10637,7 @@
         <v>27</v>
       </c>
       <c r="E89">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F89" t="s">
         <v>34</v>
@@ -10660,7 +10660,7 @@
         <v>27</v>
       </c>
       <c r="E90">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F90" t="s">
         <v>28</v>
@@ -10683,7 +10683,7 @@
         <v>27</v>
       </c>
       <c r="E91">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F91" t="s">
         <v>31</v>
@@ -10706,7 +10706,7 @@
         <v>27</v>
       </c>
       <c r="E92">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
@@ -10729,7 +10729,7 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F93" t="s">
         <v>31</v>
@@ -10752,7 +10752,7 @@
         <v>27</v>
       </c>
       <c r="E94">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -10775,7 +10775,7 @@
         <v>27</v>
       </c>
       <c r="E95">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F95" t="s">
         <v>34</v>
@@ -10821,7 +10821,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F97" t="s">
         <v>31</v>
@@ -10844,7 +10844,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -10867,7 +10867,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F99" t="s">
         <v>34</v>
@@ -10890,7 +10890,7 @@
         <v>27</v>
       </c>
       <c r="E100">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
@@ -10913,7 +10913,7 @@
         <v>27</v>
       </c>
       <c r="E101">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F101" t="s">
         <v>31</v>
@@ -10936,7 +10936,7 @@
         <v>27</v>
       </c>
       <c r="E102">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
@@ -10959,7 +10959,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F103" t="s">
         <v>34</v>
@@ -10982,7 +10982,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -11005,7 +11005,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F105" t="s">
         <v>31</v>
@@ -11028,7 +11028,7 @@
         <v>27</v>
       </c>
       <c r="E106">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
@@ -11051,7 +11051,7 @@
         <v>27</v>
       </c>
       <c r="E107">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F107" t="s">
         <v>34</v>
@@ -11074,7 +11074,7 @@
         <v>27</v>
       </c>
       <c r="E108">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
@@ -11097,7 +11097,7 @@
         <v>27</v>
       </c>
       <c r="E109">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F109" t="s">
         <v>31</v>
@@ -11120,7 +11120,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -11143,7 +11143,7 @@
         <v>27</v>
       </c>
       <c r="E111">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F111" t="s">
         <v>34</v>
@@ -11166,7 +11166,7 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F112" t="s">
         <v>28</v>
@@ -11189,7 +11189,7 @@
         <v>27</v>
       </c>
       <c r="E113">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F113" t="s">
         <v>31</v>
@@ -11212,7 +11212,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -11235,7 +11235,7 @@
         <v>27</v>
       </c>
       <c r="E115">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F115" t="s">
         <v>34</v>
@@ -11258,7 +11258,7 @@
         <v>27</v>
       </c>
       <c r="E116">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F116" t="s">
         <v>28</v>
@@ -11281,7 +11281,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F117" t="s">
         <v>31</v>
@@ -11304,7 +11304,7 @@
         <v>27</v>
       </c>
       <c r="E118">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F118" t="s">
         <v>28</v>
@@ -11327,7 +11327,7 @@
         <v>27</v>
       </c>
       <c r="E119">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F119" t="s">
         <v>34</v>
@@ -11350,7 +11350,7 @@
         <v>27</v>
       </c>
       <c r="E120">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
@@ -11373,7 +11373,7 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F121" t="s">
         <v>31</v>
@@ -11396,7 +11396,7 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -11419,7 +11419,7 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F123" t="s">
         <v>31</v>
@@ -11465,7 +11465,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F125" t="s">
         <v>34</v>
@@ -11488,7 +11488,7 @@
         <v>27</v>
       </c>
       <c r="E126">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
@@ -11511,7 +11511,7 @@
         <v>27</v>
       </c>
       <c r="E127">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F127" t="s">
         <v>31</v>
@@ -11534,7 +11534,7 @@
         <v>27</v>
       </c>
       <c r="E128">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -11557,7 +11557,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F129" t="s">
         <v>34</v>
@@ -11603,7 +11603,7 @@
         <v>27</v>
       </c>
       <c r="E131">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F131" t="s">
         <v>31</v>
@@ -11626,7 +11626,7 @@
         <v>27</v>
       </c>
       <c r="E132">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F132" t="s">
         <v>28</v>
@@ -11649,7 +11649,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F133" t="s">
         <v>34</v>
@@ -11672,7 +11672,7 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -11695,7 +11695,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F135" t="s">
         <v>31</v>
@@ -11718,7 +11718,7 @@
         <v>27</v>
       </c>
       <c r="E136">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
@@ -11741,7 +11741,7 @@
         <v>27</v>
       </c>
       <c r="E137">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F137" t="s">
         <v>34</v>
@@ -11764,7 +11764,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -11787,7 +11787,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F139" t="s">
         <v>31</v>
@@ -11810,7 +11810,7 @@
         <v>27</v>
       </c>
       <c r="E140">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
@@ -11833,7 +11833,7 @@
         <v>27</v>
       </c>
       <c r="E141">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F141" t="s">
         <v>34</v>
@@ -11856,7 +11856,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -11879,7 +11879,7 @@
         <v>27</v>
       </c>
       <c r="E143">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F143" t="s">
         <v>31</v>
@@ -11902,7 +11902,7 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F144" t="s">
         <v>28</v>
@@ -11925,7 +11925,7 @@
         <v>27</v>
       </c>
       <c r="E145">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F145" t="s">
         <v>34</v>
@@ -11948,7 +11948,7 @@
         <v>27</v>
       </c>
       <c r="E146">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F146" t="s">
         <v>28</v>
@@ -11971,7 +11971,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F147" t="s">
         <v>31</v>
@@ -11994,7 +11994,7 @@
         <v>27</v>
       </c>
       <c r="E148">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
@@ -12017,7 +12017,7 @@
         <v>27</v>
       </c>
       <c r="E149">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F149" t="s">
         <v>34</v>
@@ -12040,7 +12040,7 @@
         <v>27</v>
       </c>
       <c r="E150">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
@@ -12086,7 +12086,7 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F152" t="s">
         <v>28</v>
@@ -12132,7 +12132,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -12155,7 +12155,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F155" t="s">
         <v>34</v>
@@ -12178,7 +12178,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -12201,7 +12201,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F157" t="s">
         <v>31</v>
@@ -12224,7 +12224,7 @@
         <v>27</v>
       </c>
       <c r="E158">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F158" t="s">
         <v>28</v>
@@ -12247,7 +12247,7 @@
         <v>27</v>
       </c>
       <c r="E159">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F159" t="s">
         <v>34</v>
@@ -12270,7 +12270,7 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F160" t="s">
         <v>28</v>
@@ -12293,7 +12293,7 @@
         <v>27</v>
       </c>
       <c r="E161">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F161" t="s">
         <v>31</v>
@@ -12316,7 +12316,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -12339,7 +12339,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F163" t="s">
         <v>34</v>
@@ -12362,7 +12362,7 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
@@ -12385,7 +12385,7 @@
         <v>27</v>
       </c>
       <c r="E165">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F165" t="s">
         <v>31</v>
@@ -12408,7 +12408,7 @@
         <v>27</v>
       </c>
       <c r="E166">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -12431,7 +12431,7 @@
         <v>27</v>
       </c>
       <c r="E167">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F167" t="s">
         <v>34</v>
@@ -12454,7 +12454,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -12477,7 +12477,7 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F169" t="s">
         <v>31</v>
@@ -12500,7 +12500,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -12523,7 +12523,7 @@
         <v>27</v>
       </c>
       <c r="E171">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F171" t="s">
         <v>34</v>
@@ -12546,7 +12546,7 @@
         <v>27</v>
       </c>
       <c r="E172">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
@@ -12569,7 +12569,7 @@
         <v>27</v>
       </c>
       <c r="E173">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F173" t="s">
         <v>31</v>
@@ -12592,7 +12592,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -12615,7 +12615,7 @@
         <v>27</v>
       </c>
       <c r="E175">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F175" t="s">
         <v>34</v>
@@ -12638,7 +12638,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -12661,7 +12661,7 @@
         <v>27</v>
       </c>
       <c r="E177">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
@@ -12684,7 +12684,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F178" t="s">
         <v>31</v>
@@ -12707,7 +12707,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -12730,7 +12730,7 @@
         <v>27</v>
       </c>
       <c r="E180">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F180" t="s">
         <v>34</v>
@@ -12753,7 +12753,7 @@
         <v>27</v>
       </c>
       <c r="E181">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F181" t="s">
         <v>28</v>
@@ -12776,7 +12776,7 @@
         <v>27</v>
       </c>
       <c r="E182">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F182" t="s">
         <v>31</v>
@@ -12799,7 +12799,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -12822,7 +12822,7 @@
         <v>27</v>
       </c>
       <c r="E184">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F184" t="s">
         <v>34</v>
@@ -12845,7 +12845,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -12868,7 +12868,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F186" t="s">
         <v>31</v>
@@ -12891,7 +12891,7 @@
         <v>27</v>
       </c>
       <c r="E187">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F187" t="s">
         <v>28</v>
@@ -12914,7 +12914,7 @@
         <v>27</v>
       </c>
       <c r="E188">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F188" t="s">
         <v>34</v>
@@ -12937,7 +12937,7 @@
         <v>27</v>
       </c>
       <c r="E189">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F189" t="s">
         <v>28</v>
@@ -12960,7 +12960,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F190" t="s">
         <v>31</v>
@@ -12983,7 +12983,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -13006,7 +13006,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F192" t="s">
         <v>34</v>
@@ -13029,7 +13029,7 @@
         <v>27</v>
       </c>
       <c r="E193">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -13052,7 +13052,7 @@
         <v>27</v>
       </c>
       <c r="E194">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F194" t="s">
         <v>31</v>
@@ -13075,7 +13075,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -13098,7 +13098,7 @@
         <v>27</v>
       </c>
       <c r="E196">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F196" t="s">
         <v>34</v>
@@ -13121,7 +13121,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -13144,7 +13144,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F198" t="s">
         <v>31</v>
@@ -13167,7 +13167,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -13190,7 +13190,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F200" t="s">
         <v>34</v>
@@ -13213,7 +13213,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -13236,7 +13236,7 @@
         <v>27</v>
       </c>
       <c r="E202">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -13259,7 +13259,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F203" t="s">
         <v>31</v>
@@ -13282,7 +13282,7 @@
         <v>27</v>
       </c>
       <c r="E204">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -13305,7 +13305,7 @@
         <v>27</v>
       </c>
       <c r="E205">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F205" t="s">
         <v>34</v>
@@ -13328,7 +13328,7 @@
         <v>27</v>
       </c>
       <c r="E206">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -13351,7 +13351,7 @@
         <v>27</v>
       </c>
       <c r="E207">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F207" t="s">
         <v>31</v>
@@ -13374,7 +13374,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -13397,7 +13397,7 @@
         <v>27</v>
       </c>
       <c r="E209">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F209" t="s">
         <v>34</v>
@@ -13420,7 +13420,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -13443,7 +13443,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F211" t="s">
         <v>31</v>
@@ -13466,7 +13466,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -13489,7 +13489,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F213" t="s">
         <v>34</v>
@@ -13512,7 +13512,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -13535,7 +13535,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F215" t="s">
         <v>31</v>
@@ -13558,7 +13558,7 @@
         <v>27</v>
       </c>
       <c r="E216">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F216" t="s">
         <v>28</v>
@@ -13581,7 +13581,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F217" t="s">
         <v>34</v>
@@ -13604,7 +13604,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -13627,7 +13627,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F219" t="s">
         <v>31</v>
@@ -13650,7 +13650,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -13673,7 +13673,7 @@
         <v>27</v>
       </c>
       <c r="E221">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F221" t="s">
         <v>34</v>
@@ -13696,7 +13696,7 @@
         <v>27</v>
       </c>
       <c r="E222">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F222" t="s">
         <v>28</v>
@@ -13719,7 +13719,7 @@
         <v>27</v>
       </c>
       <c r="E223">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F223" t="s">
         <v>31</v>
@@ -13742,7 +13742,7 @@
         <v>27</v>
       </c>
       <c r="E224">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F224" t="s">
         <v>28</v>
@@ -13765,7 +13765,7 @@
         <v>27</v>
       </c>
       <c r="E225">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F225" t="s">
         <v>34</v>
@@ -13788,7 +13788,7 @@
         <v>27</v>
       </c>
       <c r="E226">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F226" t="s">
         <v>28</v>
@@ -13811,7 +13811,7 @@
         <v>27</v>
       </c>
       <c r="E227">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F227" t="s">
         <v>28</v>
@@ -13834,7 +13834,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F228" t="s">
         <v>31</v>
@@ -13857,7 +13857,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -13880,7 +13880,7 @@
         <v>27</v>
       </c>
       <c r="E230">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F230" t="s">
         <v>34</v>
@@ -13903,7 +13903,7 @@
         <v>27</v>
       </c>
       <c r="E231">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F231" t="s">
         <v>28</v>
@@ -13926,7 +13926,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F232" t="s">
         <v>31</v>
@@ -13972,7 +13972,7 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F234" t="s">
         <v>34</v>
@@ -13995,7 +13995,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -14018,7 +14018,7 @@
         <v>27</v>
       </c>
       <c r="E236">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F236" t="s">
         <v>31</v>
@@ -14041,7 +14041,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -14064,7 +14064,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F238" t="s">
         <v>34</v>
@@ -14087,7 +14087,7 @@
         <v>27</v>
       </c>
       <c r="E239">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F239" t="s">
         <v>28</v>
@@ -14110,7 +14110,7 @@
         <v>27</v>
       </c>
       <c r="E240">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F240" t="s">
         <v>31</v>
@@ -14133,7 +14133,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -14156,7 +14156,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F242" t="s">
         <v>34</v>
@@ -14179,7 +14179,7 @@
         <v>27</v>
       </c>
       <c r="E243">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -14202,7 +14202,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F244" t="s">
         <v>31</v>
@@ -14225,7 +14225,7 @@
         <v>27</v>
       </c>
       <c r="E245">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F245" t="s">
         <v>28</v>
@@ -14271,7 +14271,7 @@
         <v>27</v>
       </c>
       <c r="E247">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F247" t="s">
         <v>28</v>
@@ -14294,7 +14294,7 @@
         <v>27</v>
       </c>
       <c r="E248">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F248" t="s">
         <v>31</v>
@@ -14317,7 +14317,7 @@
         <v>27</v>
       </c>
       <c r="E249">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F249" t="s">
         <v>28</v>
@@ -14340,7 +14340,7 @@
         <v>27</v>
       </c>
       <c r="E250">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F250" t="s">
         <v>34</v>
@@ -14386,7 +14386,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -14409,7 +14409,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F253" t="s">
         <v>31</v>
@@ -14432,7 +14432,7 @@
         <v>27</v>
       </c>
       <c r="E254">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F254" t="s">
         <v>28</v>
@@ -14455,7 +14455,7 @@
         <v>27</v>
       </c>
       <c r="E255">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F255" t="s">
         <v>34</v>
@@ -14478,7 +14478,7 @@
         <v>27</v>
       </c>
       <c r="E256">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F256" t="s">
         <v>28</v>
@@ -14501,7 +14501,7 @@
         <v>27</v>
       </c>
       <c r="E257">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F257" t="s">
         <v>31</v>
@@ -14524,7 +14524,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -14547,7 +14547,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F259" t="s">
         <v>34</v>
@@ -14570,7 +14570,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -14593,7 +14593,7 @@
         <v>27</v>
       </c>
       <c r="E261">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F261" t="s">
         <v>31</v>
@@ -14616,7 +14616,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -14639,7 +14639,7 @@
         <v>27</v>
       </c>
       <c r="E263">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F263" t="s">
         <v>34</v>
@@ -14662,7 +14662,7 @@
         <v>27</v>
       </c>
       <c r="E264">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -14685,7 +14685,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F265" t="s">
         <v>31</v>
@@ -14708,7 +14708,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -14731,7 +14731,7 @@
         <v>27</v>
       </c>
       <c r="E267">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F267" t="s">
         <v>34</v>
@@ -14754,7 +14754,7 @@
         <v>27</v>
       </c>
       <c r="E268">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F268" t="s">
         <v>28</v>
@@ -14777,7 +14777,7 @@
         <v>27</v>
       </c>
       <c r="E269">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F269" t="s">
         <v>31</v>
@@ -14800,7 +14800,7 @@
         <v>27</v>
       </c>
       <c r="E270">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F270" t="s">
         <v>28</v>
@@ -14846,7 +14846,7 @@
         <v>27</v>
       </c>
       <c r="E272">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F272" t="s">
         <v>28</v>
@@ -14869,7 +14869,7 @@
         <v>27</v>
       </c>
       <c r="E273">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F273" t="s">
         <v>31</v>
@@ -14892,7 +14892,7 @@
         <v>27</v>
       </c>
       <c r="E274">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F274" t="s">
         <v>28</v>
@@ -14915,7 +14915,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F275" t="s">
         <v>34</v>
@@ -14938,7 +14938,7 @@
         <v>27</v>
       </c>
       <c r="E276">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F276" t="s">
         <v>28</v>
@@ -14961,7 +14961,7 @@
         <v>27</v>
       </c>
       <c r="E277">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F277" t="s">
         <v>28</v>
@@ -14984,7 +14984,7 @@
         <v>27</v>
       </c>
       <c r="E278">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F278" t="s">
         <v>31</v>
@@ -15007,7 +15007,7 @@
         <v>27</v>
       </c>
       <c r="E279">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -15030,7 +15030,7 @@
         <v>27</v>
       </c>
       <c r="E280">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F280" t="s">
         <v>34</v>
@@ -15053,7 +15053,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -15076,7 +15076,7 @@
         <v>27</v>
       </c>
       <c r="E282">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F282" t="s">
         <v>31</v>
@@ -15099,7 +15099,7 @@
         <v>27</v>
       </c>
       <c r="E283">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F283" t="s">
         <v>28</v>
@@ -15122,7 +15122,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F284" t="s">
         <v>34</v>
@@ -15145,7 +15145,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -15168,7 +15168,7 @@
         <v>27</v>
       </c>
       <c r="E286">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F286" t="s">
         <v>31</v>
@@ -15191,7 +15191,7 @@
         <v>27</v>
       </c>
       <c r="E287">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F287" t="s">
         <v>28</v>
@@ -15214,7 +15214,7 @@
         <v>27</v>
       </c>
       <c r="E288">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F288" t="s">
         <v>34</v>
@@ -15237,7 +15237,7 @@
         <v>27</v>
       </c>
       <c r="E289">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F289" t="s">
         <v>28</v>
@@ -15260,7 +15260,7 @@
         <v>27</v>
       </c>
       <c r="E290">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F290" t="s">
         <v>31</v>
@@ -15283,7 +15283,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -15306,7 +15306,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F292" t="s">
         <v>34</v>
@@ -15329,7 +15329,7 @@
         <v>27</v>
       </c>
       <c r="E293">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -15352,7 +15352,7 @@
         <v>27</v>
       </c>
       <c r="E294">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F294" t="s">
         <v>31</v>
@@ -15375,7 +15375,7 @@
         <v>27</v>
       </c>
       <c r="E295">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F295" t="s">
         <v>28</v>
@@ -15398,7 +15398,7 @@
         <v>27</v>
       </c>
       <c r="E296">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F296" t="s">
         <v>34</v>
@@ -15421,7 +15421,7 @@
         <v>27</v>
       </c>
       <c r="E297">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F297" t="s">
         <v>28</v>
@@ -15444,7 +15444,7 @@
         <v>27</v>
       </c>
       <c r="E298">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F298" t="s">
         <v>31</v>
@@ -15467,7 +15467,7 @@
         <v>27</v>
       </c>
       <c r="E299">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F299" t="s">
         <v>28</v>
@@ -15490,7 +15490,7 @@
         <v>27</v>
       </c>
       <c r="E300">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F300" t="s">
         <v>34</v>
@@ -15513,7 +15513,7 @@
         <v>27</v>
       </c>
       <c r="E301">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F301" t="s">
         <v>28</v>
